--- a/Cottage_Villa_Service_Benchmark.xlsx
+++ b/Cottage_Villa_Service_Benchmark.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5817" uniqueCount="1804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6292" uniqueCount="2029">
   <si>
     <t xml:space="preserve">Row ID</t>
   </si>
@@ -5090,7 +5090,13 @@
     <t xml:space="preserve">Service Offering Recommendations — Good / Better / Best by Function</t>
   </si>
   <si>
-    <t xml:space="preserve">Three candidate offerings per function, derived from the Synthesis tab. "Good" = maintenance-free essentials (lightest viable package). "Better" = Base + Choice (market midpoint with a published add-on menu). "Best" = bundled villa experience (premium, CCRC-style inclusions). Indicative prices come from the sources cited; they are benchmarks, not a pricing recommendation.</t>
+    <t xml:space="preserve">Purpose: decide which services to offer cottage residents, function by function, at three levels. Section A lists each concrete service element and whether it is Included, À la carte (available at a posted price) or Not offered at each level. Section B summarizes each function's three offerings and the evidence behind them. Unit price point and price range will later determine which level fits which product; that mapping is deliberately deferred, and price references from the sources are kept in the last column of Section B for that later step.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Service element matrix — what to offer at each level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service element</t>
   </si>
   <si>
     <t xml:space="preserve">GOOD — Maintenance-Free Essentials</t>
@@ -5102,22 +5108,718 @@
     <t xml:space="preserve">BEST — Bundled Villa Experience</t>
   </si>
   <si>
+    <t xml:space="preserve">Who offers it in the data (evidence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled group shuttle for shopping, banking and errands within ~10 miles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall base; Provincial/Discovery (Wood); 5 of 6 Saxman communities; 55 Lopez communities list transportation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ride the main community's existing routes; no cottage-specific vehicle needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled medical-appointment transportation within ~10 miles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (set days only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (any weekday)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (any day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall base (10-mile radius); Wood 10-mile radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radius and days are the levers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trips beyond the radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not offered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (per mile or per trip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall ancillary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post the rate; do not bundle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unscheduled / personal on-demand rides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (hourly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included allowance (set trips per month), then à la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamilton Trace lists unscheduled transportation à la carte (Saxman); Witzgall private car service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowance is the Best differentiator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After-hours and airport runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte, booked through concierge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low volume; keep à la carte at every level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport for community outings and excursions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included with outing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garbry Ridge "routine outings" (Saxman); Witzgall excursions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket cost is separate (see Life Enrichment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access to main-community calendar, events, clubs and common areas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Same as community residents" at both Wood operators; Witzgall base; all 6 Saxman; 52 Lopez communities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero marginal cost; never withhold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fitness center, pool and wellness-center access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall base; Wesley Village, Cedarhurst (Saxman); Lopez campus-amenity lists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counted here and under Wellness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottage-neighborhood programming (block events, resident council, cottage liaison)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not observed in the data; fills the gap Saxman notes between detached living and campus life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheap way to make cottages feel like a neighborhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off-campus excursions and ticketed events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (at cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (annual outing credit), then at cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall ancillary ($ at cost); Garbry Ridge outings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit, not unlimited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialty classes and workshop materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (enrichment credit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal training / small-group instruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (discounted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third-party or campus trainer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority registration and concierge booking for limited-seat events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not observed; Best-tier differentiator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access to all community dining venues at posted prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good Samaritan Quincy, Hamilton Trace "restaurant dining available separately"; Wood Integrated (à la carte)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access is free; food is not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly breakfast social at clubhouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included daily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included daily (plus Sunday brunch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crown Point Christian weekly; Legacies, Villa St. Benedict, Wesley Woods daily; Opus East Memphis brunch (Lopez); Wesley Village weekday breakfast (Saxman); Witzgall base option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest-cost daily touchpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declining-balance dining credit usable at any venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (modest monthly credit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (larger monthly credit or meal plan below)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall $300 card; Lake Forest Place, Friendship Village Dublin, The Stratford, Twin Lakes/Twin Towers "flexible meal allowance" (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred over fixed meals because cottages have full kitchens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed meal plan (1 meal/day, or 10–30 meals/month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (optional plan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (1/day or 20–30/month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provincial/Discovery 2 meals, Integrated 1 meal (Wood); Robin Run 15/month (Saxman); Traditions 30/month, Silver Maples 10/month, Village at Germantown 20/month (Lopez); Witzgall 1/day base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best-tier core inclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full 3-meal plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte upgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall upgrade; Western Reserve Masonic, Silver Elm, Homestead Del City (Lopez, AL-adjacent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only for care-adjacent buyers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guest meals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (monthly guest allowance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall ancillary; Hamilton Trace (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa meal delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (per-delivery fee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall delivery fee; Holland Home Raybrook "daily meal delivery available" (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery is a genuine cottage-specific service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private dining / catering for resident events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (concierge-arranged)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not observed; hospitality norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Routine housekeeping subscription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (monthly subscription or hourly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included bi-weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highgrove ~optional (Saxman); Legacy Living $25/hr (Lopez); bi-weekly is the most common Lopez cadence and the Witzgall base; weekly at Five Star, Concordia OKC, Zarrow Pointe, Provincial/Discovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadence is the primary lever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade to weekly cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall upgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat-linen service (bed and bath)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five Star, Wittenberg, Laurel Lake, Concordia OKC (Lopez); Witzgall ancillary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pairs naturally with weekly housekeeping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual deep / spring clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included once per year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Stratford "weekly and annual spring cleaning" (Lopez); Witzgall deep cleaning; Cedarhurst deep cleaning à la carte (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carpet, window and specialty cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedarhurst carpet cleaning (Saxman); Witzgall deep cleaning rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move-in / move-out turnover clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (turnover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall move-in fee covers prep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laundry &amp; Linen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-unit washer/dryer (or hookups)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (residence feature)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Near-universal in Lopez inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature, not a service; listed so the tiers are complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal laundry service (wash, dry, fold)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (per load or monthly package)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (discounted package)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall ancillary; Trilogy campuses "laundry service available"; American House Rochester Hills, Bridgeway (Lopez); Hamilton Trace (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linen service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See Housekeeping row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fitness, pool and wellness programming on the campus calendar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall base; 5 of 6 Saxman; Lopez campus lists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly on-site wellness clinic (blood pressure, weight, medication review)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall base; Hamilton Trace and Garbry Ridge monthly/available clinic (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light-touch, nurse-led</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily check-in call or app check-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (opt-in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attic Angel "optional daily check-in service" (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also a safety feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home health, therapy and rehab access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referral only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinated on request (third-party rates)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinated by a wellness navigator (third-party rates)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedarhurst, Garbry Ridge, Wesley Village in-home assistance (Saxman); Trilogy, Kirby Pines rehab "available" (Lopez); Witzgall PT/OT copays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never bundled in any source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual wellness allowance or free health-center days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twin Lakes yearly allowance; Village at Germantown 10 free health-center days (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCRC-style differentiator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medication management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Care service; keep out of base at every level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7 monitored emergency call system (pendant or pull cords)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74 Lopez communities; Witzgall base; 5 of 6 Saxman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table stakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus-wide mobile pendant (works outside the home)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall "wireless" system; Traditions Reagan Park "emergency pendant" (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-hour on-site staff response to the cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main-community response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (dedicated response protocol)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (priority routing for cottage neighborhood)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall notes longer response times on spread footprints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design the route, not just the device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gated or controlled entry / 24-hour security patrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traditions North Willow gated; Twin Lakes, Trezevant, Kirby Pines, Holy Cross 24-hr security (Lopez); Our Lady of Angels security (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site-dependent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-home sensors / fall detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not observed in sources; emerging standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional technology layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock-and-leave home checks while traveling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not observed; natural for a "proactive lifestyle" buyer (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replacement pendant / fob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exterior maintenance, lawn care, landscaping, snow and ice removal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102 Lopez communities; Witzgall "core value proposition"; Saxman "most consistently observed"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never optional at any level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair and replacement of community-owned appliances and systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall base; Pacific Springs "repairs" (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work-order response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business hours plus emergency line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-hour emergency maintenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-hour with priority response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waunakee Valley, Touchmark "emergency maintenance" (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preventive interior maintenance (filters, detectors, seasonal checks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall "routine interior appliance and utility maintenance"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handyman for resident-requested work (hanging, assembly, small fixes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (set hours per month), then à la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedarhurst handyman à la carte (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonal extras (gutters, power-wash, window cleaning)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not itemized in sources; typical HOA-style service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interior refresh (paint, carpet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At turnover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled cycle during tenancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not itemized in sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best-tier differentiator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water, sewer, trash and recycling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabor Hills, Wilson Commons, Madonna Manor water/sewer/trash only; Our Lady of Angels water only (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor for every level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric and gas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident-paid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"All utilities" at Traditions, Legacies, Oaks at Bartlett (Lopez); Garbry Ridge (Saxman); Witzgall standard utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic cable and Wi-Fi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall base; Wesley Village cable (Saxman); many Lopez bundles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirkland Crossings, Twin Lakes, Wesley Glen phone included (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium cable / streaming package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touchmark "expanded basic cable" (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property taxes and building insurance (structure-dependent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not applicable (rental)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included where the structure creates them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequent at entry-fee CCRCs: Three Pillars, Hillcrest, Twin Lakes, Wesley Manor (Lopez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ownership-structure decision, not a service decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concierge &amp; Convenience Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front-desk assistance during business hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard at all communities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published à la carte menu with monthly-statement billing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (short list)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (full Base + Choice menu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (full menu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saxman Base + Choice recommendation; Cedarhurst, Hamilton Trace menus; Witzgall ancillary structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The menu itself is the "Better" product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottage services coordinator (single point of contact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (shared)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (dedicated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not observed; addresses Witzgall's spread-footprint operating risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7 concierge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five Star Residences, Robinwood (Lopez); Hamilton Trace concierge à la carte (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package receipt and delivery to the villa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (pickup at desk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (delivered)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor coordination (movers, tech help, contractors)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not observed in sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pet services (deposit/rent; walking, sitting, pet care)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall pet deposit/rent; Cedarhurst pet care (Saxman)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salon and spa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamilton Trace, Garbry Ridge (Saxman); many Lopez campuses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly convenience credit usable across the menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Moorings $490 "discretionary dollar account" (Lopez) is the closest analogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple way to make Best feel all-inclusive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service structure (how the levels are packaged)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base rent covers residence, maintenance, base utilities, emergency response, campus access; everything else à la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base plus a bundled mid-level service package (bi-weekly housekeeping, full utilities, dining credit, monthly clinic) with a transparent add-on menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bundled all-inclusive service package (weekly housekeeping and linen, daily meal, all utilities, concierge, wellness allowance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saxman "Base + Choice"; Witzgall included vs. ancillary split; Lopez spans all three</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price mapping deferred to a later step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte = available at a posted price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Offering summary by function — the three offerings, why, and price references for later</t>
+  </si>
+  <si>
     <t xml:space="preserve">Why these three (evidence)</t>
   </si>
   <si>
-    <t xml:space="preserve">Indicative pricing from sources</t>
+    <t xml:space="preserve">Price references from sources (secondary; for the later pricing step)</t>
   </si>
   <si>
     <t xml:space="preserve">Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Scheduled group shuttle on the community's existing routes (shopping, banking, worship) within a 10-mile radius; medical appointments on set days. No personal transportation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good, plus scheduled medical transportation within 10 miles on any weekday, and a published per-trip / per-mile rate for trips beyond 10 miles and for unscheduled rides.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better, plus a private on-demand car service allowance (e.g., a set number of personal trips per month) and after-hours / airport runs bookable through concierge.</t>
+    <t xml:space="preserve">Scheduled group shuttle on the community's existing routes (shopping, banking, worship) within ~10 miles; medical appointments on set days. No personal transportation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good, plus scheduled medical transportation within ~10 miles on any weekday, and a posted rate for trips beyond the radius and for unscheduled rides.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better, plus a personal on-demand trip allowance each month and after-hours / airport runs bookable through concierge.</t>
   </si>
   <si>
     <t xml:space="preserve">Scheduled transportation within ~10 miles is included at Provincial/Discovery (Wood), in the Witzgall model and at 5 of 6 Saxman communities; it is never itemized in the Lopez inventory. Personal/unscheduled transportation is à la carte everywhere it is mentioned (Hamilton Trace, Witzgall).</t>
@@ -5132,10 +5834,10 @@
     <t xml:space="preserve">Full access to the main community's calendar, fitness center, pool and common areas on the same basis as apartment residents. Outings and ticketed events pay-per-use.</t>
   </si>
   <si>
-    <t xml:space="preserve">Good, plus a cottage-specific social program (neighborhood events, resident-led clubs, a cottage liaison) and a small annual outing credit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better, plus concierge-booked excursions, specialty classes and personal training with a monthly enrichment credit, and priority registration for limited-seat events.</t>
+    <t xml:space="preserve">Good, plus cottage-neighborhood programming (block events, resident council, a cottage liaison).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better, plus concierge-booked excursions, specialty classes and personal training backed by an enrichment credit, and priority registration for limited-seat events.</t>
   </si>
   <si>
     <t xml:space="preserve">Every source treats campus programming as an inclusion ("same as community residents" at both Wood operators; included in Witzgall; present at all 6 Saxman communities). Only excursions, materials and personal training are ever priced.</t>
@@ -5144,16 +5846,16 @@
     <t xml:space="preserve">Excursion tickets at cost $20–$100+; workshop materials $10–$30/class; personal training $60–$90/hr (Witzgall).</t>
   </si>
   <si>
-    <t xml:space="preserve">No meal plan in the base rent. Restaurant dining open to cottage residents at posted prices; a weekly continental breakfast or coffee social at the clubhouse.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A monthly declining-balance dining credit (in the $300–$600 range) usable at any venue, with optional upgrade plans (10, 15 or 30 meals/month) priced separately and villa delivery at a per-meal fee.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One chef-prepared meal per day (or 20–30 meals/month) included, plus daily continental breakfast, guest-meal allowance and villa delivery included; upgrade path to a full 3-meal plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dining is the most variable function: 17 of 53 Lopez mentions are optional or credit-based; Saxman ranges from none to 15 meals/month; Wood shows 1 vs 2 meals; Witzgall's base is breakfast, 1 meal/day or a $300 card. Full kitchens make a heavy plan unnecessary for most buyers.</t>
+    <t xml:space="preserve">No meal plan. Dining venues open to cottage residents at posted prices; a weekly continental breakfast or coffee social at the clubhouse; guest meals à la carte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily continental breakfast plus a modest monthly declining-balance dining credit usable at any venue; optional meal plans (10, 15 or 30 meals/month) and villa delivery at posted prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily breakfast plus one chef-prepared meal per day (or 20–30 meals/month) included, with villa delivery and a guest-meal allowance included; 3-meal plan as an upgrade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dining is the most variable function: 17 of 53 Lopez mentions are optional or credit-based; Saxman ranges from none to 15 meals/month; Wood shows 1 vs 2 meals; Witzgall's base is breakfast, 1 meal/day or a declining-balance card. Full kitchens make a heavy plan unnecessary for most buyers.</t>
   </si>
   <si>
     <t xml:space="preserve">Declining-balance credits observed: $300/mo (Witzgall), $490 (Lake Forest Place), $540 (Friendship Village Dublin), $600 (The Stratford) (Lopez). 3-meal upgrade $600–$900/mo; guest meals $15–$25; delivery $5–$10/meal (Witzgall).</t>
@@ -5162,31 +5864,28 @@
     <t xml:space="preserve">Lopez; Witzgall; Wood; Saxman</t>
   </si>
   <si>
-    <t xml:space="preserve">Not included. Housekeeping sold as a stand-alone monthly subscription or hourly service at a published rate; annual deep clean offered as an add-on.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bi-weekly light housekeeping included; weekly upgrade, deep cleaning and carpet cleaning at published prices.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly housekeeping with flat-linen service included, plus an annual spring deep clean; deep cleaning and organizing on request.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bi-weekly is the most common included cadence in Lopez and is the Witzgall base; monthly or optional at the light end (Robin Run, Garbry Ridge, Highgrove ~$240/mo, Integrated Senior Living none); weekly plus linen at the premium end (Five Star, Concordia OKC, Zarrow Pointe, Provincial/Discovery).</t>
+    <t xml:space="preserve">Not bundled. Housekeeping sold as a monthly subscription or hourly at a posted rate; deep clean à la carte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bi-weekly light housekeeping included; weekly upgrade, linen, deep, carpet and window cleaning at posted prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly housekeeping with flat-linen service included, plus an annual spring deep clean; specialty cleaning on request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bi-weekly is the most common included cadence in Lopez and is the Witzgall base; monthly or optional at the light end (Robin Run, Garbry Ridge, Highgrove, Integrated Senior Living none); weekly plus linen at the premium end (Five Star, Concordia OKC, Zarrow Pointe, Provincial/Discovery).</t>
   </si>
   <si>
     <t xml:space="preserve">Stand-alone: ~$240/mo (Saxman, Highgrove) or $25/hr (Lopez, Legacy Living Florence). Weekly upgrade over bi-weekly: +$150–$300/mo; deep clean $40–$60/hr (Witzgall).</t>
   </si>
   <si>
-    <t xml:space="preserve">Laundry &amp; Linen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-unit washer/dryer (or hookups) provided; no laundry service.</t>
+    <t xml:space="preserve">In-unit washer/dryer (or hookups); no laundry service.</t>
   </si>
   <si>
     <t xml:space="preserve">In-unit washer/dryer plus optional personal laundry and linen service priced per load or as a monthly package.</t>
   </si>
   <si>
-    <t xml:space="preserve">In-unit washer/dryer plus weekly flat-linen service included; personal laundry package included or discounted.</t>
+    <t xml:space="preserve">In-unit washer/dryer plus weekly flat-linen service included; personal laundry package at a discounted rate.</t>
   </si>
   <si>
     <t xml:space="preserve">In-unit washer/dryer is near-universal in the Lopez inventory (a residence feature, not a service). Linen service rides with weekly housekeeping at the premium communities; laundry "available" at Trilogy campuses; Witzgall prices it as an add-on.</t>
@@ -5198,16 +5897,16 @@
     <t xml:space="preserve">Lopez; Witzgall; Saxman</t>
   </si>
   <si>
-    <t xml:space="preserve">Fitness center and pool access included; wellness programming on the community calendar. Clinical services referred to third parties.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good, plus a monthly on-site wellness clinic (blood pressure, weight, medication review) and an optional daily check-in call; home health and therapy providers coordinated on request at their rates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better, plus an annual wellness/health-services allowance, a set number of free health-center days per year, and a resident wellness navigator who coordinates home care, therapy and medication management.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cottage-specific wellness is thin in Lopez (mostly campus access, occasional clinic/rehab "available", Twin Lakes annual allowance, Village at Germantown 10 free health-center days). Witzgall includes a monthly check-up and prices care services; Saxman shows wellness clinics at 5 of 6; Wood reported N/A.</t>
+    <t xml:space="preserve">Fitness center and pool access; wellness programming on the community calendar; clinical services by referral.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good, plus a monthly on-site wellness clinic and an opt-in daily check-in; home health and therapy coordinated on request at provider rates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better, plus an annual wellness allowance or free health-center days and a wellness navigator who coordinates home care, therapy and medication management.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottage-specific wellness is thin in Lopez (mostly campus access; occasional clinic/rehab "available"; Twin Lakes annual allowance; Village at Germantown 10 free health-center days). Witzgall includes a monthly check-up and prices care services; Saxman shows wellness clinics at 5 of 6; Wood reported N/A.</t>
   </si>
   <si>
     <t xml:space="preserve">Medication management $300–$600/mo; PT/OT at copay; personal training $60–$90/hr (Witzgall).</t>
@@ -5216,103 +5915,79 @@
     <t xml:space="preserve">Lopez; Witzgall; Saxman; Wood</t>
   </si>
   <si>
-    <t xml:space="preserve">24/7 emergency call system (pendant or pull cords) monitored by the main community; standard exterior lighting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good, plus a wireless/mobile pendant that works across campus, 24-hour on-campus staff response and an optional daily check-in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better, plus gated or controlled entry, 24-hour security/EMT presence, in-home smart sensors or fall detection, and priority response routing for the cottage neighborhood.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emergency response is the second most common Lopez inclusion (74 communities), included in the Witzgall base and at 5 of 6 Saxman communities. 24-hour security and gated entry appear at the CCRC/premium end (Twin Lakes, Trezevant, Kirby Pines, Holy Cross Village). Witzgall flags slower response times on spread footprints.</t>
+    <t xml:space="preserve">24/7 monitored emergency call system (pendant or pull cords) answered by the main community.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good, plus a campus-wide mobile pendant, a dedicated 24-hour response protocol for the cottages, and an opt-in daily check-in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better, plus gated or controlled entry, 24-hour security presence, in-home sensors or fall detection, lock-and-leave home checks, and priority response routing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emergency response is the second most common Lopez inclusion (74 communities), included in the Witzgall base and at 5 of 6 Saxman communities. 24-hour security and gated entry appear at the CCRC/premium end. Witzgall flags slower response times on spread footprints.</t>
   </si>
   <si>
     <t xml:space="preserve">Replacement pendant/fob $100–$150 one-time (Witzgall); no recurring charge observed in any source.</t>
   </si>
   <si>
-    <t xml:space="preserve">All exterior maintenance, lawn care, landscaping, snow and ice removal, plus repair of community-owned appliances and systems. Work-order response during business hours.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good, plus 24-hour emergency maintenance, routine interior preventive maintenance (filters, smoke detectors, seasonal checks) and a published handyman rate for resident-requested work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better, plus included handyman hours each month, seasonal services (gutter, power-wash, window cleaning), and pre-scheduled interior refresh (paint/carpet) on a set cycle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unanimous: maintenance is the single most common Lopez inclusion (102 communities), the Witzgall "core value proposition," and Saxman's "most consistently observed" service. It should never be optional; the tiers differ only in responsiveness and scope.</t>
+    <t xml:space="preserve">All exterior maintenance, lawn, landscaping, snow and ice, plus repair of community-owned appliances and systems; business-hours work orders with an emergency line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good, plus 24-hour emergency maintenance, preventive interior maintenance (filters, detectors, seasonal checks) and a posted handyman rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better, plus included handyman hours each month, seasonal exterior services (gutters, power-wash, windows) and a scheduled interior refresh cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unanimous: maintenance is the single most common Lopez inclusion (102 communities), the Witzgall "core value proposition," and Saxman's "most consistently observed" service. Never optional; the levels differ only in responsiveness and scope.</t>
   </si>
   <si>
     <t xml:space="preserve">Handyman appears only as an à la carte item (Cedarhurst, Saxman); no benchmark price in the sources.</t>
   </si>
   <si>
-    <t xml:space="preserve">Water, sewer and trash included; resident pays electric, gas, cable, internet and phone directly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All standard utilities (electric, gas, water, sewer, trash) plus basic cable and Wi-Fi bundled into the monthly fee; phone optional.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better, plus premium cable/streaming package, phone, and (for entry-fee structures) property taxes and building insurance carried by the community.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilities are the most common Lopez line item (118 communities) and span exactly these three levels: water/sewer/trash only (Tabor Hills, Wilson Commons), all utilities plus cable/Wi-Fi (Traditions, Legacies, Oaks at Bartlett), and all utilities plus phone/cable/internet/taxes/insurance (Twin Lakes, Maple Knoll, Friendship Village Dublin). Witzgall bundles standard utilities and basic cable/Wi-Fi in rent; Saxman ranges from water-only to full bundles.</t>
+    <t xml:space="preserve">Water, sewer, trash and recycling included; resident pays electric, gas, cable, internet and phone directly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All standard utilities (electric, gas, water, sewer, trash) plus basic cable and Wi-Fi bundled; phone optional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better, plus phone and a premium cable/streaming package; property taxes and insurance carried by the community where the ownership structure creates them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilities are the most common Lopez line item (118 communities) and span exactly these three levels. Witzgall bundles standard utilities and basic cable/Wi-Fi; Saxman ranges from water-only to full bundles.</t>
   </si>
   <si>
     <t xml:space="preserve">Bundled inside the monthly fee in every source; no separate utility pricing reported.</t>
   </si>
   <si>
-    <t xml:space="preserve">Concierge &amp; Convenience Services (Additional / À La Carte)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front-desk assistance during business hours; a printed price list for the few services offered (housekeeping, guest meals).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A published Base + Choice menu: housekeeping upgrades, laundry, dining plans, unscheduled transportation, pet services, deep/carpet cleaning, handyman, guest meals, salon, home-health referrals, each with a posted price; billed on the monthly statement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better, plus 24/7 concierge (package receipt, reservations, vendor coordination, travel/lock-and-leave home checks), a monthly convenience credit, and a dedicated cottage services coordinator.</t>
+    <t xml:space="preserve">Business-hours front desk and a short posted price list (housekeeping, guest meals, pet fees).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A full published Base + Choice menu (housekeeping upgrades, laundry, dining plans, unscheduled transport, pet services, specialty cleaning, handyman, guest meals, salon, home-health referrals) billed on the monthly statement, with a shared cottage services coordinator and package pickup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better, plus 24/7 concierge, package delivery to the villa, vendor coordination, a dedicated cottage services coordinator and a monthly convenience credit.</t>
   </si>
   <si>
     <t xml:space="preserve">Saxman recommends Base + Choice explicitly and lists the fullest menus (Cedarhurst, Hamilton Trace). Witzgall structures the same items as an ancillary revenue stream. 24/7 concierge appears at Five Star and Robinwood in Lopez. Wood's operators reported nothing beyond meals, housekeeping and transport.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pet deposit $250–$500 plus $25–$50/mo; private care &amp; support $300–$600/mo (Witzgall). Other menu items: see Housekeeping, Culinary, Transportation rows.</t>
+    <t xml:space="preserve">Pet deposit $250–$500 plus $25–$50/mo; private care &amp; support $300–$600/mo (Witzgall). Other menu prices: see Housekeeping, Culinary, Transportation rows.</t>
   </si>
   <si>
     <t xml:space="preserve">Saxman; Witzgall; Lopez; Wood</t>
   </si>
   <si>
-    <t xml:space="preserve">Packaging &amp; Pricing Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single rental rate covering residence, maintenance, base utilities and emergency response; everything else à la carte. Positions against the lighter models (Highgrove, Bay Ridge, Swanhaven, Integrated Senior Living).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base rent plus a modest bundled service fee (bi-weekly housekeeping, full utilities, dining credit, monthly clinic) with a transparent add-on menu and a second-person fee. Positions against the Witzgall rental profile and mid-market Lopez communities.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All-inclusive monthly fee (weekly housekeeping and linen, daily meal, all utilities, concierge, wellness allowance), rental or entry-fee, positioned against Smith Crossing, Five Star, The Stratford, Twin Lakes and Lake Forest Place.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Witzgall: rental cottages earn a 15–30% premium over IL apartments and lease faster without an entrance fee; monthly rents $2,500–$6,500+. Lopez median reported monthly fee ≈ $2,800 with a $515–$6,900 spread. Saxman: a proactive lifestyle buyer values independence plus fewer responsibilities, so the base must feel light.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption for planning only: Good ≈ $2,500–$3,500/mo, Better ≈ $3,500–$5,000/mo, Best ≈ $5,000–$6,500+/mo, mapped onto the Witzgall $2,500–$6,500+ range. Move-in fee $1,000–$5,000; second person $500–$1,000/mo (Witzgall).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Witzgall; Lopez; Saxman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package view — what each tier includes at a glance</t>
+    <t xml:space="preserve">C. Package view — each level at a glance (services only; pricing to be layered on later)</t>
   </si>
   <si>
     <t xml:space="preserve">Element</t>
   </si>
   <si>
-    <t xml:space="preserve">Always included (all tiers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interior/exterior maintenance, lawn, snow, landscaping; water/sewer/trash; emergency call system; scheduled shuttle within ~10 miles; full campus programming and fitness access; in-unit washer/dryer; attached garage.</t>
+    <t xml:space="preserve">Always included (all levels)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interior/exterior maintenance, lawn, snow, landscaping; water/sewer/trash; 24/7 emergency call system; scheduled shuttle within ~10 miles; full campus programming and fitness access; in-unit washer/dryer; attached garage.</t>
   </si>
   <si>
     <t xml:space="preserve">Same</t>
@@ -5321,7 +5996,7 @@
     <t xml:space="preserve">À la carte only</t>
   </si>
   <si>
-    <t xml:space="preserve">Bi-weekly included; weekly upgrade priced</t>
+    <t xml:space="preserve">Bi-weekly included; weekly and linen priced</t>
   </si>
   <si>
     <t xml:space="preserve">Weekly with linen included; annual deep clean</t>
@@ -5330,13 +6005,13 @@
     <t xml:space="preserve">Dining</t>
   </si>
   <si>
-    <t xml:space="preserve">Pay as you go; weekly breakfast social</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly dining credit; upgrade plans priced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 meal/day (or 20–30/month) plus breakfast included</t>
+    <t xml:space="preserve">Venue access; weekly breakfast social; pay as you go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily breakfast plus dining credit; plans and delivery priced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily breakfast plus 1 meal/day (or 20–30/month), delivery and guest allowance included</t>
   </si>
   <si>
     <t xml:space="preserve">Water/sewer/trash</t>
@@ -5345,46 +6020,46 @@
     <t xml:space="preserve">All utilities plus basic cable and Wi-Fi</t>
   </si>
   <si>
-    <t xml:space="preserve">All utilities plus phone, premium cable; taxes/insurance where applicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheduled group only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus scheduled medical within 10 miles; posted rates beyond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus personal on-demand trip allowance and airport runs</t>
+    <t xml:space="preserve">All utilities plus phone and premium cable; taxes/insurance where applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled group; medical on set days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus medical any weekday; posted rates beyond radius and on demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus personal trip allowance and concierge-booked airport runs</t>
   </si>
   <si>
     <t xml:space="preserve">Wellness &amp; safety</t>
   </si>
   <si>
-    <t xml:space="preserve">Emergency pendant; fitness access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus monthly clinic; daily check-in option; campus-wide mobile pendant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus wellness allowance, health-center days, navigator; 24-hr security / gated</t>
+    <t xml:space="preserve">Fitness access; emergency pendant; referrals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus monthly clinic; opt-in check-in; mobile pendant; cottage response protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus wellness allowance, navigator, gated/24-hr security, sensors, home checks</t>
   </si>
   <si>
     <t xml:space="preserve">Convenience</t>
   </si>
   <si>
-    <t xml:space="preserve">Business-hours front desk; short price list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Published Base + Choice menu; second-person fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/7 concierge; monthly convenience credit; cottage services coordinator</t>
+    <t xml:space="preserve">Business-hours desk; short price list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full Base + Choice menu; shared coordinator; package pickup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7 concierge; dedicated coordinator; delivery; vendor coordination; convenience credit</t>
   </si>
   <si>
     <t xml:space="preserve">Target buyer (per Saxman / Witzgall)</t>
   </si>
   <si>
-    <t xml:space="preserve">Most independent, price-sensitive downsizer who wants to stop mowing</t>
+    <t xml:space="preserve">Most independent downsizer who wants to stop mowing and keep costs visible</t>
   </si>
   <si>
     <t xml:space="preserve">Mainstream active adult who wants choices without a care-driven decision</t>
@@ -5402,7 +6077,7 @@
     <t xml:space="preserve">Witzgall rental profile; Hamilton Trace; Cedarhurst of Frankfort; Woodland Terrace; Cedarbrook of Northville; Provincial/Discovery IL</t>
   </si>
   <si>
-    <t xml:space="preserve">Smith Crossing; Five Star Residences; The Stratford; Twin Lakes; Lake Forest Place; Concordia Life Plan (OKC); Zarrow Pointe</t>
+    <t xml:space="preserve">Smith Crossing (per Saxman); Five Star Residences; The Stratford; Twin Lakes; Lake Forest Place; Concordia Life Plan (OKC); Zarrow Pointe</t>
   </si>
   <si>
     <t xml:space="preserve">Sources, attribution and method notes</t>
@@ -5468,7 +6143,7 @@
     <t xml:space="preserve">• Synthesis counts use COUNTIFS formulas over the tier columns and recalculate if rows are edited. Lopez pricing statistics reference the contiguous Lopez block (rows 2–216).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Recommendations are analytical judgments built from the synthesis; the Good/Better/Best price bands in the Packaging row are a planning assumption mapped onto Witzgall's $2,500–$6,500+ range, not sourced pricing.</t>
+    <t xml:space="preserve">• Recommendations are analytical judgments built from the synthesis and are service-first: they decide what to offer at each level per function. Mapping levels to unit price points and price ranges is deferred to a later step; source price references are kept in Section B of the Good-Better-Best tab for that purpose.</t>
   </si>
   <si>
     <t xml:space="preserve">• Workbook built Sept 17, 2026 from the four sources above.</t>
@@ -5559,7 +6234,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5575,7 +6250,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
     <fill>
@@ -5598,20 +6273,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -5664,7 +6357,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5738,6 +6431,34 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5816,7 +6537,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFEDEDED"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -5826,9 +6547,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFE2EFDA"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFC6EFCE"/>
+      <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -27680,14 +28401,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27695,7 +28417,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
         <v>1676</v>
       </c>
@@ -27707,424 +28429,1989 @@
       <c r="G2" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="8" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>1572</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>1677</v>
-      </c>
-      <c r="C4" s="14" t="s">
+      <c r="B5" s="1" t="s">
         <v>1678</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>1679</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="D5" s="14" t="s">
         <v>1680</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="E5" s="15" t="s">
         <v>1681</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>1682</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="G5" s="1" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>1683</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="B6" s="4" t="s">
         <v>1684</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="C6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>1685</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>1686</v>
       </c>
-      <c r="F5" s="4" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>1687</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="C7" s="16" t="s">
         <v>1688</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="D7" s="16" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>1701</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>1708</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>1689</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>1690</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>1691</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>1692</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>1693</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>1688</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+      <c r="B12" s="4" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>1715</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>1722</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>1726</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>1729</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B19" s="4" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>1734</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>1735</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>1739</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>1740</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>1694</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>1695</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="D21" s="16" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>1745</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>1750</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>1758</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>1764</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>1765</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>1770</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>1773</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>1775</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>1778</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>1779</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>1788</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>1792</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>1796</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>1798</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>1800</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>1803</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>1696</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>1697</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>1698</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="G41" s="4" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>1827</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>1830</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>1833</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>1839</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>1842</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>1846</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>1847</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>1849</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>1854</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>1861</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>1865</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>1871</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>1879</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>1884</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>1888</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>1891</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>1893</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>1894</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>1765</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D68" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>1900</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>1907</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="19" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="8" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>1681</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>1915</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" s="23" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D78" s="25" t="s">
+        <v>1919</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>1921</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" s="23" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C79" s="24" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D79" s="25" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>1927</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" s="23" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C80" s="24" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D80" s="25" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>1931</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>1932</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>1700</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>1701</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>1702</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>1703</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>1704</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>1705</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>1706</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>1707</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>1709</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>1710</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="B81" s="23" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C81" s="24" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D81" s="25" t="s">
+        <v>1936</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="9" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B82" s="23" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D82" s="25" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>1943</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>1712</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>1713</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>1714</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>1715</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>1716</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="B83" s="23" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D83" s="25" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>1948</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>1949</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>1718</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>1719</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>1720</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>1721</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>1722</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="B84" s="23" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C84" s="24" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D84" s="25" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>1955</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>1723</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>1724</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>1725</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>1726</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>1727</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="B85" s="23" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C85" s="24" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D85" s="25" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>1959</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>1960</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>1728</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>1729</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>1730</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>1731</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>1732</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>1734</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>1735</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>1736</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>1737</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>1738</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>1740</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>1741</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>1742</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>1743</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>1744</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>1745</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>1748</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1677</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>1678</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="B86" s="23" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C86" s="24" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D86" s="25" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>1965</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B87" s="23" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C87" s="24" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D87" s="25" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>1970</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>1679</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>1749</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+      <c r="C90" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="9" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B91" s="23" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C91" s="24" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D91" s="25" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>1752</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>1753</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>1755</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>1756</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>1757</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
+      <c r="B92" s="23" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C92" s="24" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D92" s="25" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="9" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B93" s="23" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C93" s="24" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D93" s="25" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="9" t="s">
         <v>1100</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+      <c r="B94" s="23" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C94" s="24" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D94" s="25" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>1762</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>1766</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>1767</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>1768</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>1769</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>1770</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>1771</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>1773</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>1774</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>1775</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
-        <v>1777</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>1779</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>1780</v>
+      <c r="B95" s="23" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C95" s="24" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D95" s="25" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="9" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B96" s="23" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C96" s="24" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D96" s="25" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="9" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B97" s="23" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C97" s="24" t="s">
+        <v>1996</v>
+      </c>
+      <c r="D97" s="25" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="9" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B98" s="23" t="s">
+        <v>1999</v>
+      </c>
+      <c r="C98" s="24" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D98" s="25" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="9" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B99" s="23" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C99" s="24" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D99" s="25" t="s">
+        <v>2005</v>
       </c>
     </row>
   </sheetData>
@@ -28159,7 +30446,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1781</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28167,19 +30454,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1782</v>
+        <v>2007</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1783</v>
+        <v>2008</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1784</v>
+        <v>2009</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1785</v>
+        <v>2010</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1786</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28193,14 +30480,14 @@
         <v>37</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1787</v>
+        <v>2012</v>
       </c>
       <c r="E4" s="4" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Laura Lopez")</f>
         <v>215</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1788</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28214,14 +30501,14 @@
         <v>1423</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1789</v>
+        <v>2014</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Ken Witzgall")</f>
         <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1790</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28235,14 +30522,14 @@
         <v>1457</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1791</v>
+        <v>2016</v>
       </c>
       <c r="E6" s="4" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Scott Wood")</f>
         <v>2</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1792</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28256,24 +30543,24 @@
         <v>1457</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1793</v>
+        <v>2018</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Jennifer Saxman")</f>
         <v>11</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1794</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>1795</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1796</v>
+        <v>2021</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -28283,7 +30570,7 @@
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1797</v>
+        <v>2022</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -28293,7 +30580,7 @@
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1798</v>
+        <v>2023</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -28303,7 +30590,7 @@
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>1799</v>
+        <v>2024</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -28313,7 +30600,7 @@
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1800</v>
+        <v>2025</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -28323,7 +30610,7 @@
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>1801</v>
+        <v>2026</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -28333,7 +30620,7 @@
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1802</v>
+        <v>2027</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -28343,7 +30630,7 @@
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1803</v>
+        <v>2028</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>

--- a/Cottage_Villa_Service_Benchmark.xlsx
+++ b/Cottage_Villa_Service_Benchmark.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6292" uniqueCount="2029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6361" uniqueCount="2067">
   <si>
     <t xml:space="preserve">Row ID</t>
   </si>
@@ -5108,7 +5108,10 @@
     <t xml:space="preserve">BEST — Bundled Villa Experience</t>
   </si>
   <si>
-    <t xml:space="preserve">Who offers it in the data (evidence)</t>
+    <t xml:space="preserve">Market prevalence (Lopez inventory, n = 215)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who offers it in the data (evidence: Witzgall / Wood / Saxman / named Lopez communities)</t>
   </si>
   <si>
     <t xml:space="preserve">Design note</t>
@@ -5117,6 +5120,9 @@
     <t xml:space="preserve">Scheduled group shuttle for shopping, banking and errands within ~10 miles</t>
   </si>
   <si>
+    <t xml:space="preserve">55 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall base; Provincial/Discovery (Wood); 5 of 6 Saxman communities; 55 Lopez communities list transportation</t>
   </si>
   <si>
@@ -5135,6 +5141,9 @@
     <t xml:space="preserve">Included (any day)</t>
   </si>
   <si>
+    <t xml:space="preserve">0 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall base (10-mile radius); Wood 10-mile radius</t>
   </si>
   <si>
@@ -5150,6 +5159,9 @@
     <t xml:space="preserve">À la carte (per mile or per trip)</t>
   </si>
   <si>
+    <t xml:space="preserve">Not itemized in Lopez inventory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall ancillary</t>
   </si>
   <si>
@@ -5198,6 +5210,9 @@
     <t xml:space="preserve">Access to main-community calendar, events, clubs and common areas</t>
   </si>
   <si>
+    <t xml:space="preserve">42 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">"Same as community residents" at both Wood operators; Witzgall base; all 6 Saxman; 52 Lopez communities</t>
   </si>
   <si>
@@ -5207,6 +5222,9 @@
     <t xml:space="preserve">Fitness center, pool and wellness-center access</t>
   </si>
   <si>
+    <t xml:space="preserve">48 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall base; Wesley Village, Cedarhurst (Saxman); Lopez campus-amenity lists</t>
   </si>
   <si>
@@ -5243,6 +5261,9 @@
     <t xml:space="preserve">Included (enrichment credit)</t>
   </si>
   <si>
+    <t xml:space="preserve">12 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">—</t>
   </si>
   <si>
@@ -5252,6 +5273,9 @@
     <t xml:space="preserve">À la carte (discounted)</t>
   </si>
   <si>
+    <t xml:space="preserve">2 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Third-party or campus trainer</t>
   </si>
   <si>
@@ -5267,6 +5291,9 @@
     <t xml:space="preserve">Included (access)</t>
   </si>
   <si>
+    <t xml:space="preserve">26 of 215 list on-campus dining venues</t>
+  </si>
+  <si>
     <t xml:space="preserve">Good Samaritan Quincy, Hamilton Trace "restaurant dining available separately"; Wood Integrated (à la carte)</t>
   </si>
   <si>
@@ -5282,6 +5309,9 @@
     <t xml:space="preserve">Included daily (plus Sunday brunch)</t>
   </si>
   <si>
+    <t xml:space="preserve">6 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Crown Point Christian weekly; Legacies, Villa St. Benedict, Wesley Woods daily; Opus East Memphis brunch (Lopez); Wesley Village weekday breakfast (Saxman); Witzgall base option</t>
   </si>
   <si>
@@ -5297,6 +5327,9 @@
     <t xml:space="preserve">Included (larger monthly credit or meal plan below)</t>
   </si>
   <si>
+    <t xml:space="preserve">15 of 215 mention a dining credit, allowance or flexible plan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall $300 card; Lake Forest Place, Friendship Village Dublin, The Stratford, Twin Lakes/Twin Towers "flexible meal allowance" (Lopez)</t>
   </si>
   <si>
@@ -5312,6 +5345,9 @@
     <t xml:space="preserve">Included (1/day or 20–30/month)</t>
   </si>
   <si>
+    <t xml:space="preserve">28 of 215 mention included meals or a meal plan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Provincial/Discovery 2 meals, Integrated 1 meal (Wood); Robin Run 15/month (Saxman); Traditions 30/month, Silver Maples 10/month, Village at Germantown 20/month (Lopez); Witzgall 1/day base</t>
   </si>
   <si>
@@ -5345,6 +5381,9 @@
     <t xml:space="preserve">À la carte (per-delivery fee)</t>
   </si>
   <si>
+    <t xml:space="preserve">1 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall delivery fee; Holland Home Raybrook "daily meal delivery available" (Lopez)</t>
   </si>
   <si>
@@ -5372,6 +5411,9 @@
     <t xml:space="preserve">Included weekly</t>
   </si>
   <si>
+    <t xml:space="preserve">68 of 215 mention housekeeping (any cadence)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Highgrove ~optional (Saxman); Legacy Living $25/hr (Lopez); bi-weekly is the most common Lopez cadence and the Witzgall base; weekly at Five Star, Concordia OKC, Zarrow Pointe, Provincial/Discovery</t>
   </si>
   <si>
@@ -5381,12 +5423,18 @@
     <t xml:space="preserve">Upgrade to weekly cadence</t>
   </si>
   <si>
+    <t xml:space="preserve">44 of 215 mention weekly housekeeping or cleaning</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall upgrade</t>
   </si>
   <si>
     <t xml:space="preserve">Flat-linen service (bed and bath)</t>
   </si>
   <si>
+    <t xml:space="preserve">20 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Five Star, Wittenberg, Laurel Lake, Concordia OKC (Lopez); Witzgall ancillary</t>
   </si>
   <si>
@@ -5429,6 +5477,9 @@
     <t xml:space="preserve">Included (residence feature)</t>
   </si>
   <si>
+    <t xml:space="preserve">132 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Near-universal in Lopez inventory</t>
   </si>
   <si>
@@ -5444,6 +5495,9 @@
     <t xml:space="preserve">À la carte (discounted package)</t>
   </si>
   <si>
+    <t xml:space="preserve">7 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall ancillary; Trilogy campuses "laundry service available"; American House Rochester Hills, Bridgeway (Lopez); Hamilton Trace (Saxman)</t>
   </si>
   <si>
@@ -5456,12 +5510,18 @@
     <t xml:space="preserve">Fitness, pool and wellness programming on the campus calendar</t>
   </si>
   <si>
+    <t xml:space="preserve">49 of 215 mention fitness, pool or wellness access</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall base; 5 of 6 Saxman; Lopez campus lists</t>
   </si>
   <si>
     <t xml:space="preserve">Monthly on-site wellness clinic (blood pressure, weight, medication review)</t>
   </si>
   <si>
+    <t xml:space="preserve">5 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall base; Hamilton Trace and Garbry Ridge monthly/available clinic (Saxman)</t>
   </si>
   <si>
@@ -5492,6 +5552,9 @@
     <t xml:space="preserve">Coordinated by a wellness navigator (third-party rates)</t>
   </si>
   <si>
+    <t xml:space="preserve">20 of 215 mention therapy, rehab or home care (usually "available")</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cedarhurst, Garbry Ridge, Wesley Village in-home assistance (Saxman); Trilogy, Kirby Pines rehab "available" (Lopez); Witzgall PT/OT copays</t>
   </si>
   <si>
@@ -5501,6 +5564,9 @@
     <t xml:space="preserve">Annual wellness allowance or free health-center days</t>
   </si>
   <si>
+    <t xml:space="preserve">4 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Twin Lakes yearly allowance; Village at Germantown 10 free health-center days (Lopez)</t>
   </si>
   <si>
@@ -5519,6 +5585,9 @@
     <t xml:space="preserve">24/7 monitored emergency call system (pendant or pull cords)</t>
   </si>
   <si>
+    <t xml:space="preserve">68 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">74 Lopez communities; Witzgall base; 5 of 6 Saxman</t>
   </si>
   <si>
@@ -5528,6 +5597,9 @@
     <t xml:space="preserve">Campus-wide mobile pendant (works outside the home)</t>
   </si>
   <si>
+    <t xml:space="preserve">5 of 215 mention a wireless system or pendant specifically</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall "wireless" system; Traditions Reagan Park "emergency pendant" (Lopez)</t>
   </si>
   <si>
@@ -5543,6 +5615,9 @@
     <t xml:space="preserve">Included (priority routing for cottage neighborhood)</t>
   </si>
   <si>
+    <t xml:space="preserve">18 of 215 mention 24-hour security or EMT presence</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall notes longer response times on spread footprints</t>
   </si>
   <si>
@@ -5552,6 +5627,9 @@
     <t xml:space="preserve">Gated or controlled entry / 24-hour security patrol</t>
   </si>
   <si>
+    <t xml:space="preserve">20 of 215 mention gated entry or security</t>
+  </si>
+  <si>
     <t xml:space="preserve">Traditions North Willow gated; Twin Lakes, Trezevant, Kirby Pines, Holy Cross 24-hr security (Lopez); Our Lady of Angels security (Saxman)</t>
   </si>
   <si>
@@ -5579,6 +5657,9 @@
     <t xml:space="preserve">Exterior maintenance, lawn care, landscaping, snow and ice removal</t>
   </si>
   <si>
+    <t xml:space="preserve">103 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">102 Lopez communities; Witzgall "core value proposition"; Saxman "most consistently observed"</t>
   </si>
   <si>
@@ -5603,12 +5684,18 @@
     <t xml:space="preserve">24-hour with priority response</t>
   </si>
   <si>
+    <t xml:space="preserve">3 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Waunakee Valley, Touchmark "emergency maintenance" (Lopez)</t>
   </si>
   <si>
     <t xml:space="preserve">Preventive interior maintenance (filters, detectors, seasonal checks)</t>
   </si>
   <si>
+    <t xml:space="preserve">87 of 215 mention interior maintenance; preventive scope not specified</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall "routine interior appliance and utility maintenance"</t>
   </si>
   <si>
@@ -5645,6 +5732,9 @@
     <t xml:space="preserve">Water, sewer, trash and recycling</t>
   </si>
   <si>
+    <t xml:space="preserve">104 of 215 mention water, sewer, trash or utilities</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tabor Hills, Wilson Commons, Madonna Manor water/sewer/trash only; Our Lady of Angels water only (Saxman)</t>
   </si>
   <si>
@@ -5657,18 +5747,27 @@
     <t xml:space="preserve">Resident-paid</t>
   </si>
   <si>
+    <t xml:space="preserve">70 of 215 mention electric, gas or "all utilities"</t>
+  </si>
+  <si>
     <t xml:space="preserve">"All utilities" at Traditions, Legacies, Oaks at Bartlett (Lopez); Garbry Ridge (Saxman); Witzgall standard utilities</t>
   </si>
   <si>
     <t xml:space="preserve">Basic cable and Wi-Fi</t>
   </si>
   <si>
+    <t xml:space="preserve">77 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Witzgall base; Wesley Village cable (Saxman); many Lopez bundles</t>
   </si>
   <si>
     <t xml:space="preserve">Phone</t>
   </si>
   <si>
+    <t xml:space="preserve">29 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kirkland Crossings, Twin Lakes, Wesley Glen phone included (Lopez)</t>
   </si>
   <si>
@@ -5687,6 +5786,9 @@
     <t xml:space="preserve">Included where the structure creates them</t>
   </si>
   <si>
+    <t xml:space="preserve">26 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frequent at entry-fee CCRCs: Three Pillars, Hillcrest, Twin Lakes, Wesley Manor (Lopez)</t>
   </si>
   <si>
@@ -5714,6 +5816,9 @@
     <t xml:space="preserve">Included (full menu)</t>
   </si>
   <si>
+    <t xml:space="preserve">31 of 215 list at least one "available", "optional" or priced service</t>
+  </si>
+  <si>
     <t xml:space="preserve">Saxman Base + Choice recommendation; Cedarhurst, Hamilton Trace menus; Witzgall ancillary structure</t>
   </si>
   <si>
@@ -5735,6 +5840,9 @@
     <t xml:space="preserve">24/7 concierge</t>
   </si>
   <si>
+    <t xml:space="preserve">10 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Five Star Residences, Robinwood (Lopez); Hamilton Trace concierge à la carte (Saxman)</t>
   </si>
   <si>
@@ -5762,6 +5870,9 @@
     <t xml:space="preserve">Salon and spa</t>
   </si>
   <si>
+    <t xml:space="preserve">9 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hamilton Trace, Garbry Ridge (Saxman); many Lopez campuses</t>
   </si>
   <si>
@@ -5799,6 +5910,9 @@
   </si>
   <si>
     <t xml:space="preserve">À la carte = available at a posted price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prevalence counts are keyword matches over the Lopez amenity text in Consolidated Data (computed at build); "0 of 215" means the element appears only in Witzgall, Wood or Saxman, or in none of the sources.</t>
   </si>
   <si>
     <t xml:space="preserve">B. Offering summary by function — the three offerings, why, and price references for later</t>
@@ -28401,15 +28515,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28427,13 +28542,14 @@
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>1677</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>1572</v>
       </c>
@@ -28454,6 +28570,9 @@
       </c>
       <c r="G5" s="1" t="s">
         <v>1683</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>1684</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28461,7 +28580,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>52</v>
@@ -28473,10 +28592,13 @@
         <v>52</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1686</v>
+        <v>1687</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>1688</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28484,22 +28606,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>1695</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28507,22 +28632,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>1701</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28530,22 +28658,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D9" s="18" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>1699</v>
       </c>
-      <c r="E9" s="16" t="s">
-        <v>1700</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>1701</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>1702</v>
+        <v>1705</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>1706</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28553,22 +28684,25 @@
         <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1706</v>
+        <v>1700</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>1710</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28576,22 +28710,25 @@
         <v>13</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1709</v>
+        <v>1693</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1710</v>
+        <v>1713</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>1714</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28599,7 +28736,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>52</v>
@@ -28611,10 +28748,13 @@
         <v>52</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>1713</v>
+        <v>1717</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>1718</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28622,7 +28762,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>52</v>
@@ -28634,10 +28774,13 @@
         <v>52</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>1715</v>
+        <v>1720</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>1722</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28645,10 +28788,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1717</v>
+        <v>1723</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>52</v>
@@ -28657,10 +28800,13 @@
         <v>52</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>1718</v>
+        <v>1699</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>1719</v>
+        <v>1724</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>1725</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28668,22 +28814,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1720</v>
+        <v>1726</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>1721</v>
+        <v>1727</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>1721</v>
+        <v>1727</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>1722</v>
+        <v>1728</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>1723</v>
+        <v>1693</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>1724</v>
+        <v>1729</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>1730</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28691,22 +28840,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1725</v>
+        <v>1731</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>1726</v>
+        <v>1732</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1696</v>
+        <v>1733</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>1727</v>
+        <v>1700</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28714,22 +28866,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1728</v>
+        <v>1735</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>1729</v>
+        <v>1736</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>1696</v>
+        <v>1737</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>1730</v>
+        <v>1700</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>1738</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28737,22 +28892,25 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1731</v>
+        <v>1739</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1732</v>
+        <v>1699</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>1727</v>
+        <v>1740</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28760,22 +28918,25 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1733</v>
+        <v>1741</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>1734</v>
+        <v>1742</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>1734</v>
+        <v>1742</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>1734</v>
+        <v>1742</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1735</v>
+        <v>1743</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>1736</v>
+        <v>1744</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>1745</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28786,19 +28947,22 @@
         <v>353</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1737</v>
+        <v>1746</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>1738</v>
+        <v>1747</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>1739</v>
+        <v>1748</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1740</v>
+        <v>1749</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>1741</v>
+        <v>1750</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>1751</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28806,22 +28970,25 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1742</v>
+        <v>1752</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>1743</v>
+        <v>1753</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>1744</v>
+        <v>1754</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1745</v>
+        <v>1755</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>1746</v>
+        <v>1756</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>1757</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28829,22 +28996,25 @@
         <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1747</v>
+        <v>1758</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>1748</v>
+        <v>1759</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>1749</v>
+        <v>1760</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>1750</v>
+        <v>1761</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>1751</v>
+        <v>1762</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>1763</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28852,22 +29022,25 @@
         <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1752</v>
+        <v>1764</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>1753</v>
+        <v>1765</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>1753</v>
+        <v>1765</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1754</v>
+        <v>1749</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1755</v>
+        <v>1766</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>1767</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28875,22 +29048,25 @@
         <v>15</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1756</v>
+        <v>1768</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>1757</v>
+        <v>1769</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1758</v>
+        <v>1693</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1727</v>
+        <v>1770</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28898,22 +29074,25 @@
         <v>15</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1759</v>
+        <v>1771</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>1760</v>
+        <v>1772</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>1761</v>
+        <v>1773</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>1762</v>
+        <v>1774</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>1775</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28921,22 +29100,25 @@
         <v>15</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1763</v>
+        <v>1776</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>1764</v>
+        <v>1777</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>1765</v>
+        <v>1693</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>1727</v>
+        <v>1778</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28944,22 +29126,25 @@
         <v>124</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1766</v>
+        <v>1779</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>1767</v>
+        <v>1780</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>1768</v>
+        <v>1781</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>1769</v>
+        <v>1782</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>1770</v>
+        <v>1783</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>1771</v>
+        <v>1784</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>1785</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28967,22 +29152,25 @@
         <v>124</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1772</v>
+        <v>1786</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>1753</v>
+        <v>1765</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>1773</v>
+        <v>1787</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>1727</v>
+        <v>1788</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28990,22 +29178,25 @@
         <v>124</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1774</v>
+        <v>1789</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>1769</v>
+        <v>1782</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>1775</v>
+        <v>1790</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>1776</v>
+        <v>1791</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>1792</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29013,22 +29204,25 @@
         <v>124</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1777</v>
+        <v>1793</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>1778</v>
+        <v>1794</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>1779</v>
+        <v>1773</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>1727</v>
+        <v>1795</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29036,22 +29230,25 @@
         <v>124</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1780</v>
+        <v>1796</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>1781</v>
+        <v>1693</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>1727</v>
+        <v>1797</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29059,91 +29256,103 @@
         <v>124</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1782</v>
+        <v>1798</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>1783</v>
+        <v>1799</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>1783</v>
+        <v>1799</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>1783</v>
+        <v>1799</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>1784</v>
+        <v>1699</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>1785</v>
+        <v>1800</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>1801</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>1786</v>
+        <v>1802</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1787</v>
+        <v>1803</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>1788</v>
+        <v>1804</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>1788</v>
+        <v>1804</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>1788</v>
+        <v>1804</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>1789</v>
+        <v>1805</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>1790</v>
+        <v>1806</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>1807</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>1786</v>
+        <v>1802</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1791</v>
+        <v>1808</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>1792</v>
+        <v>1809</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>1793</v>
+        <v>1810</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>1794</v>
+        <v>1811</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>1727</v>
+        <v>1812</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>1786</v>
+        <v>1802</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1795</v>
+        <v>1813</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>1769</v>
+        <v>1782</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>1796</v>
+        <v>1790</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>1727</v>
+        <v>1814</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29151,7 +29360,7 @@
         <v>17</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1797</v>
+        <v>1815</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>52</v>
@@ -29163,10 +29372,13 @@
         <v>52</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>1798</v>
+        <v>1816</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>1727</v>
+        <v>1817</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29174,10 +29386,10 @@
         <v>17</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1799</v>
+        <v>1818</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D37" s="16" t="s">
         <v>52</v>
@@ -29186,10 +29398,13 @@
         <v>52</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>1800</v>
+        <v>1819</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>1801</v>
+        <v>1820</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>1821</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29197,22 +29412,25 @@
         <v>17</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1802</v>
+        <v>1822</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>1803</v>
+        <v>1823</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>1803</v>
+        <v>1823</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>1804</v>
+        <v>1773</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>1805</v>
+        <v>1824</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>1825</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29220,22 +29438,25 @@
         <v>17</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1806</v>
+        <v>1826</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>1807</v>
+        <v>1827</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1808</v>
+        <v>1828</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>1809</v>
+        <v>1829</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>1810</v>
+        <v>1830</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>1811</v>
+        <v>1831</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>1832</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29243,22 +29464,25 @@
         <v>17</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1812</v>
+        <v>1833</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>1813</v>
+        <v>1834</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>1814</v>
+        <v>1835</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>1836</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29266,22 +29490,25 @@
         <v>17</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1815</v>
+        <v>1837</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>1816</v>
+        <v>1700</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>1838</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29289,22 +29516,25 @@
         <v>17</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1817</v>
+        <v>1839</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>1696</v>
+        <v>1773</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>1727</v>
+        <v>1700</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29312,7 +29542,7 @@
         <v>18</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1818</v>
+        <v>1840</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>52</v>
@@ -29324,10 +29554,13 @@
         <v>52</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>1819</v>
+        <v>1841</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>1820</v>
+        <v>1842</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>1843</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29335,10 +29568,10 @@
         <v>18</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1821</v>
+        <v>1844</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D44" s="16" t="s">
         <v>52</v>
@@ -29347,10 +29580,13 @@
         <v>52</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>1822</v>
+        <v>1845</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>1727</v>
+        <v>1846</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29358,22 +29594,25 @@
         <v>18</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1823</v>
+        <v>1847</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>1824</v>
+        <v>1848</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>1825</v>
+        <v>1849</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>1826</v>
+        <v>1850</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>1827</v>
+        <v>1851</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>1828</v>
+        <v>1852</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>1853</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29381,22 +29620,25 @@
         <v>18</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1829</v>
+        <v>1854</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>1830</v>
+        <v>1855</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>1831</v>
+        <v>1856</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>1857</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29404,22 +29646,25 @@
         <v>18</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1832</v>
+        <v>1858</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>1833</v>
+        <v>1693</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>1834</v>
+        <v>1859</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>1860</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29427,22 +29672,25 @@
         <v>18</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1835</v>
+        <v>1861</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E48" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>1836</v>
+        <v>1693</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>1727</v>
+        <v>1862</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29450,22 +29698,25 @@
         <v>18</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1837</v>
+        <v>1863</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>1727</v>
+        <v>1700</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29473,7 +29724,7 @@
         <v>19</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1838</v>
+        <v>1864</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>52</v>
@@ -29485,10 +29736,13 @@
         <v>52</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>1839</v>
+        <v>1865</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>1840</v>
+        <v>1866</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>1867</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29496,7 +29750,7 @@
         <v>19</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1841</v>
+        <v>1868</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>52</v>
@@ -29508,10 +29762,13 @@
         <v>52</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>1842</v>
+        <v>1737</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>1727</v>
+        <v>1869</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29519,22 +29776,25 @@
         <v>19</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1843</v>
+        <v>1870</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>1844</v>
+        <v>1871</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>1845</v>
+        <v>1872</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>1846</v>
+        <v>1873</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>1847</v>
+        <v>1874</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>1727</v>
+        <v>1875</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29542,10 +29802,10 @@
         <v>19</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1848</v>
+        <v>1876</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D53" s="16" t="s">
         <v>52</v>
@@ -29554,10 +29814,13 @@
         <v>52</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>1849</v>
+        <v>1877</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1727</v>
+        <v>1878</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29565,22 +29828,25 @@
         <v>19</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1850</v>
+        <v>1879</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>1851</v>
+        <v>1880</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>1852</v>
+        <v>1693</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>1727</v>
+        <v>1881</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29588,22 +29854,25 @@
         <v>19</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1853</v>
+        <v>1882</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E55" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>1854</v>
+        <v>1693</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>1727</v>
+        <v>1883</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29611,22 +29880,25 @@
         <v>19</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>1855</v>
+        <v>1884</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>1856</v>
+        <v>1885</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>1856</v>
+        <v>1885</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>1857</v>
+        <v>1886</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>1858</v>
+        <v>1693</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>1859</v>
+        <v>1887</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>1888</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29634,7 +29906,7 @@
         <v>20</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1860</v>
+        <v>1889</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>52</v>
@@ -29646,10 +29918,13 @@
         <v>52</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>1861</v>
+        <v>1890</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>1862</v>
+        <v>1891</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>1892</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29657,10 +29932,10 @@
         <v>20</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>1863</v>
+        <v>1893</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>1864</v>
+        <v>1894</v>
       </c>
       <c r="D58" s="16" t="s">
         <v>52</v>
@@ -29669,10 +29944,13 @@
         <v>52</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>1865</v>
+        <v>1895</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>1727</v>
+        <v>1896</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29680,10 +29958,10 @@
         <v>20</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1866</v>
+        <v>1897</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>1864</v>
+        <v>1894</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>52</v>
@@ -29692,10 +29970,13 @@
         <v>52</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>1867</v>
+        <v>1898</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>1727</v>
+        <v>1899</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29703,22 +29984,25 @@
         <v>20</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1868</v>
+        <v>1900</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E60" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>1869</v>
+        <v>1901</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>1727</v>
+        <v>1902</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29726,22 +30010,25 @@
         <v>20</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1870</v>
+        <v>1903</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E61" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>1727</v>
+        <v>1904</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29749,30 +30036,33 @@
         <v>20</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1872</v>
+        <v>1905</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>1873</v>
+        <v>1906</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1873</v>
+        <v>1906</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>1874</v>
+        <v>1907</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>1875</v>
+        <v>1908</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>1876</v>
+        <v>1909</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>1910</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1878</v>
+        <v>1912</v>
       </c>
       <c r="C63" s="16" t="s">
         <v>52</v>
@@ -29784,236 +30074,271 @@
         <v>52</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>1879</v>
+        <v>1699</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>1727</v>
+        <v>1913</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1880</v>
+        <v>1914</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>1881</v>
+        <v>1915</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>1882</v>
+        <v>1916</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>1883</v>
+        <v>1917</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>1884</v>
+        <v>1918</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>1885</v>
+        <v>1919</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>1920</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1886</v>
+        <v>1921</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>1887</v>
+        <v>1922</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>1888</v>
+        <v>1923</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>1889</v>
+        <v>1773</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>1727</v>
+        <v>1924</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1890</v>
+        <v>1925</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="E66" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>1891</v>
+        <v>1926</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>1727</v>
+        <v>1927</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1892</v>
+        <v>1928</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>1893</v>
+        <v>1929</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>1894</v>
+        <v>1930</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>1765</v>
+        <v>1693</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>1727</v>
+        <v>1778</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1895</v>
+        <v>1931</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E68" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>1896</v>
+        <v>1699</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>1727</v>
+        <v>1932</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1897</v>
+        <v>1933</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>1898</v>
+        <v>1737</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>1727</v>
+        <v>1934</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1899</v>
+        <v>1935</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>1900</v>
+        <v>1936</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>1727</v>
+        <v>1937</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1901</v>
+        <v>1938</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="E71" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>1902</v>
+        <v>1773</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>1903</v>
+        <v>1939</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>1940</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
-        <v>1904</v>
+        <v>1941</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1905</v>
+        <v>1942</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>1906</v>
+        <v>1943</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1907</v>
+        <v>1944</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>1908</v>
+        <v>1945</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>1909</v>
+        <v>1699</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1946</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>1911</v>
+        <v>1948</v>
       </c>
       <c r="B74" s="20" t="s">
         <v>52</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>1912</v>
+        <v>1949</v>
       </c>
       <c r="D74" s="22" t="s">
-        <v>1694</v>
-      </c>
+        <v>1697</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>1913</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30030,13 +30355,13 @@
         <v>1681</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1914</v>
+        <v>1952</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>1915</v>
+        <v>1953</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1916</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30044,22 +30369,22 @@
         <v>13</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>1917</v>
+        <v>1955</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>1918</v>
+        <v>1956</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>1919</v>
+        <v>1957</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>1920</v>
+        <v>1958</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>1921</v>
+        <v>1959</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>1922</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30067,22 +30392,22 @@
         <v>14</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>1923</v>
+        <v>1961</v>
       </c>
       <c r="C79" s="24" t="s">
-        <v>1924</v>
+        <v>1962</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>1925</v>
+        <v>1963</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>1926</v>
+        <v>1964</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>1927</v>
+        <v>1965</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>1922</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30090,22 +30415,22 @@
         <v>15</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>1928</v>
+        <v>1966</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>1929</v>
+        <v>1967</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>1930</v>
+        <v>1968</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>1931</v>
+        <v>1969</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>1932</v>
+        <v>1970</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>1933</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30113,45 +30438,45 @@
         <v>124</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>1934</v>
+        <v>1972</v>
       </c>
       <c r="C81" s="24" t="s">
-        <v>1935</v>
+        <v>1973</v>
       </c>
       <c r="D81" s="25" t="s">
-        <v>1936</v>
+        <v>1974</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>1937</v>
+        <v>1975</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>1938</v>
+        <v>1976</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>1933</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="9" t="s">
-        <v>1786</v>
+        <v>1802</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>1939</v>
+        <v>1977</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>1940</v>
+        <v>1978</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>1941</v>
+        <v>1979</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>1942</v>
+        <v>1980</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>1943</v>
+        <v>1981</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>1944</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30159,22 +30484,22 @@
         <v>17</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>1945</v>
+        <v>1983</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>1946</v>
+        <v>1984</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>1947</v>
+        <v>1985</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>1948</v>
+        <v>1986</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>1949</v>
+        <v>1987</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>1950</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30182,22 +30507,22 @@
         <v>18</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>1951</v>
+        <v>1989</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>1952</v>
+        <v>1990</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>1953</v>
+        <v>1991</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>1954</v>
+        <v>1992</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>1955</v>
+        <v>1993</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>1944</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30205,22 +30530,22 @@
         <v>19</v>
       </c>
       <c r="B85" s="23" t="s">
-        <v>1956</v>
+        <v>1994</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>1957</v>
+        <v>1995</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>1958</v>
+        <v>1996</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>1959</v>
+        <v>1997</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>1960</v>
+        <v>1998</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>1944</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30228,55 +30553,55 @@
         <v>20</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>1961</v>
+        <v>1999</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>1962</v>
+        <v>2000</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>1963</v>
+        <v>2001</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>1964</v>
+        <v>2002</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>1965</v>
+        <v>2003</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>1944</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="9" t="s">
-        <v>1877</v>
+        <v>1911</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>1966</v>
+        <v>2004</v>
       </c>
       <c r="C87" s="24" t="s">
-        <v>1967</v>
+        <v>2005</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>1968</v>
+        <v>2006</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>1969</v>
+        <v>2007</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>1970</v>
+        <v>2008</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>1971</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="s">
-        <v>1972</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>1973</v>
+        <v>2011</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>1679</v>
@@ -30290,16 +30615,16 @@
     </row>
     <row r="91" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="9" t="s">
-        <v>1974</v>
+        <v>2012</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>1975</v>
+        <v>2013</v>
       </c>
       <c r="C91" s="24" t="s">
-        <v>1976</v>
+        <v>2014</v>
       </c>
       <c r="D91" s="25" t="s">
-        <v>1976</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30307,27 +30632,27 @@
         <v>124</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>1977</v>
+        <v>2015</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>1978</v>
+        <v>2016</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>1979</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="9" t="s">
-        <v>1980</v>
+        <v>2018</v>
       </c>
       <c r="B93" s="23" t="s">
-        <v>1981</v>
+        <v>2019</v>
       </c>
       <c r="C93" s="24" t="s">
-        <v>1982</v>
+        <v>2020</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>1983</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30335,13 +30660,13 @@
         <v>1100</v>
       </c>
       <c r="B94" s="23" t="s">
-        <v>1984</v>
+        <v>2022</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>1985</v>
+        <v>2023</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>1986</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30349,74 +30674,75 @@
         <v>13</v>
       </c>
       <c r="B95" s="23" t="s">
-        <v>1987</v>
+        <v>2025</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>1988</v>
+        <v>2026</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>1989</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="9" t="s">
-        <v>1990</v>
+        <v>2028</v>
       </c>
       <c r="B96" s="23" t="s">
-        <v>1991</v>
+        <v>2029</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>1992</v>
+        <v>2030</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>1993</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="9" t="s">
-        <v>1994</v>
+        <v>2032</v>
       </c>
       <c r="B97" s="23" t="s">
-        <v>1995</v>
+        <v>2033</v>
       </c>
       <c r="C97" s="24" t="s">
-        <v>1996</v>
+        <v>2034</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>1997</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="9" t="s">
-        <v>1998</v>
+        <v>2036</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>1999</v>
+        <v>2037</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>2000</v>
+        <v>2038</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>2001</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="9" t="s">
-        <v>2002</v>
+        <v>2040</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>2003</v>
+        <v>2041</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>2004</v>
+        <v>2042</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>2005</v>
+        <v>2043</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:G2"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="F74:H74"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30446,7 +30772,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2006</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30454,19 +30780,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2007</v>
+        <v>2045</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2008</v>
+        <v>2046</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2009</v>
+        <v>2047</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2010</v>
+        <v>2048</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>2011</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30480,14 +30806,14 @@
         <v>37</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>2012</v>
+        <v>2050</v>
       </c>
       <c r="E4" s="4" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Laura Lopez")</f>
         <v>215</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2013</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30501,14 +30827,14 @@
         <v>1423</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2014</v>
+        <v>2052</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Ken Witzgall")</f>
         <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2015</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30522,14 +30848,14 @@
         <v>1457</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>2016</v>
+        <v>2054</v>
       </c>
       <c r="E6" s="4" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Scott Wood")</f>
         <v>2</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2017</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30543,24 +30869,24 @@
         <v>1457</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>2018</v>
+        <v>2056</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Jennifer Saxman")</f>
         <v>11</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2019</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>2020</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2021</v>
+        <v>2059</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -30570,7 +30896,7 @@
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2022</v>
+        <v>2060</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -30580,7 +30906,7 @@
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2023</v>
+        <v>2061</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -30590,7 +30916,7 @@
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2024</v>
+        <v>2062</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -30600,7 +30926,7 @@
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2025</v>
+        <v>2063</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -30610,7 +30936,7 @@
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>2026</v>
+        <v>2064</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -30620,7 +30946,7 @@
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>2027</v>
+        <v>2065</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -30630,7 +30956,7 @@
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>2028</v>
+        <v>2066</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>

--- a/Cottage_Villa_Service_Benchmark.xlsx
+++ b/Cottage_Villa_Service_Benchmark.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Consolidated Data" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Synthesis" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Good-Better-Best" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Sources &amp; Method" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Transportation Detail" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sources &amp; Method" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Consolidated Data'!$A$1:$AI$231</definedName>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6361" uniqueCount="2067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6732" uniqueCount="2424">
   <si>
     <t xml:space="preserve">Row ID</t>
   </si>
@@ -4517,96 +4518,102 @@
     <t xml:space="preserve">Dining, deep cleaning, pet care, carpet cleaning, handyman, home health/therapy</t>
   </si>
   <si>
+    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. VERIFIED IN RESEARCH (Frankfort is in ILLINOIS): Cedarhurst states its Cottages "operate separately from the Assisted Living and Memory Care neighborhoods and do not include the same all-inclusive services and amenities"; cottage residents get ACCESS TO the AL/MC transportation rather than an included benefit. "Available" was the right word.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our Lady of Angels – Duplex Cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our Lady of Angels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplex Cottages (limited independent model)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limited independent model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meals not provided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security and emergency call system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water included; resident pays other utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. DATA-QUALITY FLAG (web research, Sept 2026): this community in Joliet, IL appears to have CLOSED in January 2023, and research indicates transportation was offered "on a cost basis". The "Not provided" label is therefore probably shorthand for "not included in the fee" rather than "did not exist". Verify before relying on this row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (limited)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamilton Trace – Cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CarDon &amp; Associates (per Lopez inventory)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fishers, IN (per Lopez inventory)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled transportation included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community programming available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant dining available separately</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly wellness clinic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emergency response included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water/sewer included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dining, salon, unscheduled transportation, guest meals, laundry and concierge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. Also appears in Lopez inventory (cross-check row).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robin Run Village – Garden Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garden Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community activities included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 meals/month included; additional meals available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly housekeeping included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance, lawn and snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most utilities included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional meals</t>
+  </si>
+  <si>
     <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Our Lady of Angels – Duplex Cottages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Our Lady of Angels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplex Cottages (limited independent model)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limited independent model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meals not provided</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security and emergency call system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water included; resident pays other utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included (limited)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamilton Trace – Cottages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CarDon &amp; Associates (per Lopez inventory)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fishers, IN (per Lopez inventory)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cottages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheduled transportation included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Community programming available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant dining available separately</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly wellness clinic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emergency response included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water/sewer included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dining, salon, unscheduled transportation, guest meals, laundry and concierge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. Also appears in Lopez inventory (cross-check row).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robin Run Village – Garden Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garden Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Community activities included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 meals/month included; additional meals available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly housekeeping included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance, lawn and snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Most utilities included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional meals</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wesley Village – Patio Homes</t>
   </si>
   <si>
@@ -4634,6 +4641,9 @@
     <t xml:space="preserve">Additional dining and in-home assistance</t>
   </si>
   <si>
+    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. LOCATION FLAG: the 77-patio-home product is in Wilmore, KENTUCKY. A separate Wesley Village in Pittston, PA has "Brooks Estates" cottages. Possible name collision; confirm which community this row refers to.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Garbry Ridge – Cottages</t>
   </si>
   <si>
@@ -4658,6 +4668,9 @@
     <t xml:space="preserve">Meals, therapy, wellness and salon</t>
   </si>
   <si>
+    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. VERIFIED IN RESEARCH: the cottage inclusion list carries only "routine outings to local and regional events", while the separate IL apartment list carries "scheduled transportation". The cottage tier is genuinely lesser, and this label captured it correctly.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Highgrove at Tates Creek – Detached Cottages</t>
   </si>
   <si>
@@ -4673,7 +4686,7 @@
     <t xml:space="preserve">Housekeeping offered as an optional add-on</t>
   </si>
   <si>
-    <t xml:space="preserve">Narrative example: "lighter service structure."</t>
+    <t xml:space="preserve">Narrative example: "lighter service structure." RESEARCH NOTE (Lexington, KY): Highgrove is the ONLY community in the transportation deep-dive found to publish days of operation - "Monday through Friday as well as transportation to Sunday church services". Its cottages are duplexes and quads rather than fully detached, which limits comparability.</t>
   </si>
   <si>
     <t xml:space="preserve">The Village at Bay Ridge</t>
@@ -4700,12 +4713,15 @@
     <t xml:space="preserve">Meals, housekeeping and laundry remain optional</t>
   </si>
   <si>
-    <t xml:space="preserve">Narrative example of a lighter model (transportation, activities or wellness may be available; meals, housekeeping and laundry can remain optional).</t>
+    <t xml:space="preserve">Narrative example of a lighter model (transportation, activities or wellness may be available; meals, housekeeping and laundry can remain optional). RESEARCH NOTE: located in Traverse City, MICHIGAN (Heritage Senior Communities). Its community bus is offered "to all residents at no additional cost" and runs scheduled trips PLUS "many other destinations based on regular resident requests", so here the request-driven channel is also free. This is the clearest counter-example to the scheduled-free / unscheduled-paid pattern.</t>
   </si>
   <si>
     <t xml:space="preserve">Swanhaven Manor</t>
   </si>
   <si>
+    <t xml:space="preserve">Narrative example of a lighter model (transportation, activities or wellness may be available; meals, housekeeping and laundry can remain optional). RESEARCH NOTE: located in Saginaw, MICHIGAN. Runs "regularly scheduled shopping trips in the complimentary Swanhaven Bus" to banks, groceries, shopping centres and restaurants. MEDICAL APPOINTMENTS ARE NOT NAMED, so transportation there is run as an activity programme rather than a medical-transport function.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Smith Crossing – Villas (heavier bundled model)</t>
   </si>
   <si>
@@ -5117,156 +5133,234 @@
     <t xml:space="preserve">Design note</t>
   </si>
   <si>
-    <t xml:space="preserve">Scheduled group shuttle for shopping, banking and errands within ~10 miles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55 of 215 Lopez communities mention it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Witzgall base; Provincial/Discovery (Wood); 5 of 6 Saxman communities; 55 Lopez communities list transportation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ride the main community's existing routes; no cottage-specific vehicle needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheduled medical-appointment transportation within ~10 miles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included (set days only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included (any weekday)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included (any day)</t>
+    <t xml:space="preserve">Transportation  [detail on the Transportation Detail tab]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled group shuttle to a published set of destinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The one near-universal inclusion. Witzgall base; Provincial/Discovery (Wood); 5 of 6 Saxman communities; 55 Lopez communities; every operating model found in the research includes at least this.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The floor at every tier. Run it on the main community's existing routes; no cottage-specific vehicle needed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group outings and excursions to events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included with outing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included with outing, plus an annual outing credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garbry Ridge cottages get ONLY "routine outings to local and regional events" (verified); Laurel Lake runs courtesy trips to "the symphony, theater and regional attractions"; Swanhaven runs them as an activity programme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest way to make a detached neighbourhood feel connected. Ticket cost stays separate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individually scheduled medical-appointment rides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not offered (referred to third-party ride services)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included, weekdays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included, any day, with a stated dialysis and recurring-therapy policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE line operators actually draw. Garbry Ridge gives cottages outings but reserves "scheduled transportation" for apartments; New Perspective states it "does not provide transportation to appointments" and only helps coordinate a rideshare. DIALYSIS AND RECURRING THERAPY WERE NEVER MENTIONED BY ANY COMMUNITY RESEARCHED, despite being the heaviest real demand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The key decision. Excluding it is defensible for residents who still drive, but it must be said plainly or they will assume otherwise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trips beyond the included area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not offered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A la carte at a posted per-mile or per-trip rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A la carte at a posted rate, with named destination hospitals inside the included area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No community published a mileage radius. The only real geographic rules found were a fee trigger ("There are charges for out of county rides"), a named-city limit ("Kalamazoo and Portage area") and a "standard route". Witzgall is the only source with prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consider defining a STANDARD ROUTE or a county rather than a radius. Both proved more workable in the market than a mileage line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unscheduled / personal on-demand rides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A la carte (per hour or per mile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included allowance of personal trips per month, then a la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not itemized in Lopez inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mainstream two-tier model: free on the schedule, paid off it. Maple Knoll charges "a nominal per-mile fee" for its chauffeur; Laurel Lake, South Franklin Circle, Westminster Place, Friendship Village Dublin and Discovery all publish the same split. BUT Village at Bay Ridge makes request-driven trips free too, so this is an operator pricing choice, not a sector rule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The clearest place to build a Better tier, and the only attribute where a rate basis was found in the market.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-campus circulator (home to clubhouse, dining, fitness)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almost nobody draws this distinction in writing. Maple Knoll is the exception, separating an on-campus "Shuttle on Demand" from its off-campus chauffeur service; Ohio Living runs campus loop buses separately from off-campus routes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specific to spread-out cottage sites, and more valuable there than a mileage radius. Answers "do I have to walk to the main building?"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level of assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curb-to-curb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Door-to-door</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escort into and through the appointment, by arrangement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A real, marketable distinction almost nobody makes. Ohio Living sells it as a branded product: an "escorted personal driver service" whose driver will "escort you throughout your trip and business", at flat fees. Robin Run advertises "door-to-door services".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cheap way to differentiate the Best tier without adding vehicles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After-hours and airport runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A la carte, booked through concierge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airport was named by only ONE community in the entire research (Maple Knoll, via its chauffeur service). Witzgall prices after-hours runs separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low volume. Keep it a la carte at every tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa / cottage eligibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same service as apartment residents; central pickup point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same service, with pickup at the villa door</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same service, with priority routing for the cottage neighbourhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT RELIABLE IN THE MARKET: of 9 detached-cottage communities, 3 give the same service, 2 explicitly give less, 4 do not say. Cedarhurst states its cottages "operate separately... and do not include the same all-inclusive services and amenities".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decide this deliberately and state it. It is the single most common ambiguity in the competitive set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published service terms (days, hours, lead time, capacity rule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published at move-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published, with 24-48 hour booking and a stated medical priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published, with guaranteed medical seats and third-party overflow at community cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A COMPETITIVE OPPORTUNITY. Across ~50 communities, ONE published days of operation, ONE published a booking requirement, and NONE published hours, a lead time in days, a capacity rule, or wheelchair accessibility.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publishing plain terms would differentiate on transparency alone, at no operating cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access to main-community calendar, events, clubs and common areas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Same as community residents" at both Wood operators; Witzgall base; all 6 Saxman; 52 Lopez communities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero marginal cost; never withhold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fitness center, pool and wellness-center access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 of 215 Lopez communities mention it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall base; Wesley Village, Cedarhurst (Saxman); Lopez campus-amenity lists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counted here and under Wellness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottage-neighborhood programming (block events, resident council, cottage liaison)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not observed in the data; fills the gap Saxman notes between detached living and campus life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheap way to make cottages feel like a neighborhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off-campus excursions and ticketed events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte (at cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (annual outing credit), then at cost</t>
   </si>
   <si>
     <t xml:space="preserve">0 of 215 Lopez communities mention it</t>
   </si>
   <si>
-    <t xml:space="preserve">Witzgall base (10-mile radius); Wood 10-mile radius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radius and days are the levers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trips beyond the radius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not offered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À la carte (per mile or per trip)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not itemized in Lopez inventory</t>
+    <t xml:space="preserve">Witzgall ancillary ($ at cost); Garbry Ridge outings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit, not unlimited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialty classes and workshop materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included (enrichment credit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 of 215 Lopez communities mention it</t>
   </si>
   <si>
     <t xml:space="preserve">Witzgall ancillary</t>
   </si>
   <si>
-    <t xml:space="preserve">Post the rate; do not bundle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unscheduled / personal on-demand rides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À la carte (hourly)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included allowance (set trips per month), then à la carte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamilton Trace lists unscheduled transportation à la carte (Saxman); Witzgall private car service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allowance is the Best differentiator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After-hours and airport runs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À la carte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À la carte, booked through concierge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low volume; keep à la carte at every level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport for community outings and excursions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included with outing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garbry Ridge "routine outings" (Saxman); Witzgall excursions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ticket cost is separate (see Life Enrichment)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access to main-community calendar, events, clubs and common areas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42 of 215 Lopez communities mention it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Same as community residents" at both Wood operators; Witzgall base; all 6 Saxman; 52 Lopez communities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zero marginal cost; never withhold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fitness center, pool and wellness-center access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48 of 215 Lopez communities mention it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Witzgall base; Wesley Village, Cedarhurst (Saxman); Lopez campus-amenity lists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Counted here and under Wellness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cottage-neighborhood programming (block events, resident council, cottage liaison)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not observed in the data; fills the gap Saxman notes between detached living and campus life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheap way to make cottages feel like a neighborhood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Off-campus excursions and ticketed events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À la carte (at cost)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included (annual outing credit), then at cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Witzgall ancillary ($ at cost); Garbry Ridge outings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit, not unlimited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specialty classes and workshop materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included (enrichment credit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 of 215 Lopez communities mention it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
     <t xml:space="preserve">Personal training / small-group instruction</t>
   </si>
   <si>
@@ -5927,39 +6021,42 @@
     <t xml:space="preserve">Sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Scheduled group shuttle on the community's existing routes (shopping, banking, worship) within ~10 miles; medical appointments on set days. No personal transportation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good, plus scheduled medical transportation within ~10 miles on any weekday, and a posted rate for trips beyond the radius and for unscheduled rides.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better, plus a personal on-demand trip allowance each month and after-hours / airport runs bookable through concierge.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheduled transportation within ~10 miles is included at Provincial/Discovery (Wood), in the Witzgall model and at 5 of 6 Saxman communities; it is never itemized in the Lopez inventory. Personal/unscheduled transportation is à la carte everywhere it is mentioned (Hamilton Trace, Witzgall).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beyond-radius medical: $2.50–$4.00/mile or $25–$50/trip; private car $30–$60/hr; airport $75–$150/trip (Witzgall).</t>
+    <t xml:space="preserve">Scheduled group shuttle on the community's existing routes (shopping, banking, groceries, worship) plus group outings. No individual appointment rides; residents are referred to third-party ride services, and the marketing says so plainly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good, plus individually scheduled medical-appointment rides on weekdays within a defined standard route or county, door-to-door, with a posted rate for trips beyond it and for unscheduled personal rides. Days, hours, booking lead time and the capacity rule are published.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better, plus a monthly allowance of personal on-demand trips, an on-campus circulator, escorted appointment service by arrangement, a stated dialysis and recurring-therapy policy, and concierge-booked airport runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep-dive research across ~50 communities (see the Transportation Detail tab) found five distinct service models hiding behind the single word. The mainstream is two-tier: scheduled trips free, off-schedule trips paid. Cottage residents do NOT reliably get the same service as apartment residents, and where it differs the cottage tier is lesser. Dialysis was never mentioned by any community researched; wheelchair accessibility was confirmed at none.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall is the only source with prices: beyond-radius medical $2.50-$4.00/mile or $25-$50/trip; private car $30-$60/hr; airport $75-$150/trip. In the market, only one community published even a rate BASIS (per mile) and it withheld the rate. No community in the detached-cottage set published any transportation price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall; Wood; Saxman; Lopez; ~50-community web research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full access to the main community's calendar, fitness center, pool and common areas on the same basis as apartment residents. Outings and ticketed events pay-per-use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good, plus cottage-neighborhood programming (block events, resident council, a cottage liaison).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better, plus concierge-booked excursions, specialty classes and personal training backed by an enrichment credit, and priority registration for limited-seat events.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every source treats campus programming as an inclusion ("same as community residents" at both Wood operators; included in Witzgall; present at all 6 Saxman communities). Only excursions, materials and personal training are ever priced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excursion tickets at cost $20–$100+; workshop materials $10–$30/class; personal training $60–$90/hr (Witzgall).</t>
   </si>
   <si>
     <t xml:space="preserve">Witzgall; Wood; Saxman; Lopez</t>
   </si>
   <si>
-    <t xml:space="preserve">Full access to the main community's calendar, fitness center, pool and common areas on the same basis as apartment residents. Outings and ticketed events pay-per-use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good, plus cottage-neighborhood programming (block events, resident council, a cottage liaison).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better, plus concierge-booked excursions, specialty classes and personal training backed by an enrichment credit, and priority registration for limited-seat events.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every source treats campus programming as an inclusion ("same as community residents" at both Wood operators; included in Witzgall; present at all 6 Saxman communities). Only excursions, materials and personal training are ever priced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excursion tickets at cost $20–$100+; workshop materials $10–$30/class; personal training $60–$90/hr (Witzgall).</t>
-  </si>
-  <si>
     <t xml:space="preserve">No meal plan. Dining venues open to cottage residents at posted prices; a weekly continental breakfast or coffee social at the clubhouse; guest meals à la carte.</t>
   </si>
   <si>
@@ -6137,13 +6234,13 @@
     <t xml:space="preserve">All utilities plus phone and premium cable; taxes/insurance where applicable</t>
   </si>
   <si>
-    <t xml:space="preserve">Scheduled group; medical on set days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus medical any weekday; posted rates beyond radius and on demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus personal trip allowance and concierge-booked airport runs</t>
+    <t xml:space="preserve">Scheduled group shuttle and outings only; appointments referred out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus weekday medical appointment rides, door-to-door, within a defined route or county; posted rates beyond; terms published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus personal trip allowance, on-campus circulator, escorted appointments and airport runs</t>
   </si>
   <si>
     <t xml:space="preserve">Wellness &amp; safety</t>
@@ -6194,6 +6291,978 @@
     <t xml:space="preserve">Smith Crossing (per Saxman); Five Star Residences; The Stratford; Twin Lakes; Lake Forest Place; Concordia Life Plan (OKC); Zarrow Pointe</t>
   </si>
   <si>
+    <t xml:space="preserve">Transportation — what the word actually means</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The villa study lists transportation at 55 communities. All 55 entries say only "Transportation" or "Transportation services". This tab breaks that single word into the decisions it hides, records what the four sources and public marketing actually say, and converts it into a sharper Good / Better / Best specification. It was built from targeted web research across roughly 50 communities. READ SECTION F BEFORE QUOTING ANYTHING: community websites were unreachable from this environment, so findings come from search-result summaries, and several plausible-sounding details failed exact-phrase verification.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. How much detail each source actually gives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it says about transportation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detail level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it does not tell us</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Lopez (215-community villa study)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 communities list transportation. 53 say exactly "Transportation"; 2 say "Transportation services". No entry gives any further detail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None beyond presence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost, radius, trip purposes, days, hours, booking rules, vehicle, capacity limits, villa eligibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ken Witzgall (rental model profile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included: scheduled group shuttles for shopping and banking; medical transport within a 10-mile radius. Extra: beyond 10 miles ($2.50–$4.00/mile or $25–$50/trip), private on-demand car ($30–$60/hour), after-hours airport runs ($75–$150/trip).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest of the four; the only source with prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days, hours, booking lead time, vehicle type, capacity rules, how the radius is measured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Wood (two operators)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provincial/Discovery: "the same as for community residents. 10-mile radius from the community." Integrated Senior Living (TX): "Not provided."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radius and eligibility only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost, purposes, scheduling, what happens beyond the radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jennifer Saxman (detached cottage benchmarking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six labels: Available / Not provided / Scheduled transportation included / Included / Included / Routine outings included. Separately lists "unscheduled transportation" on Hamilton Trace's à la carte menu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presence/absence, plus the most useful structural clue in any source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of the included service, radius, purposes, days, hours, booking rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public marketing and directories (this research)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almost universally "scheduled transportation" for appointments, shopping and outings, and nothing more. The operators themselves publish essentially no operational detail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low, and highly repetitive across operators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radius, hours, lead time, vehicle, fees. These live in resident handbooks and front-desk booklets that are rarely posted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The bare "Transportation" in the villa study is not a gap in that document. It mirrors what the operators themselves publish. Across roughly 50 communities researched, not one published a mileage radius, a day-and-hour schedule, a booking lead time, a vehicle specification, a wheelchair-accessibility statement, or a per-trip dollar amount on a public page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. The five service models actually found behind the one word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These are genuinely different products. Deciding which one to build is the real transportation decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the resident actually gets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communities found using it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fit for a detached cottage product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free scheduled group shuttle only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A bus or van on a fixed schedule to a fixed set of destinations. No individual rides. Often run by the activities team as a social programme rather than a transport function.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included; no paid tier offered or published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swanhaven Manor (the "complimentary Swanhaven Bus", trips to banks, groceries, shopping, restaurants; medical not named); American Senior Communities garden homes; Evergreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good fit as a floor. Cheap, social, and matches residents who still drive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free scheduled trips plus a paid personal or chauffeur tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The scheduled shuttle is free. Individual, off-schedule or longer trips are bought separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-tier and explicitly published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maple Knoll Village (free campus shuttle and weekly grocery run vs a chauffeur at "a nominal per-mile fee"); Laurel Lake (free "weekly/monthly courtesy trips" vs "for a fee... a Laurel Lake driver"); South Franklin Circle ("included at no charge" vs "a small fee"); Westminster Place (complimentary on "the standard route" vs fee-based beyond it); Friendship Village of Dublin ("complimentary... within the local area... additional destinations may be accommodated at cost"); Discovery ("at cost... outside the regular schedule")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MAINSTREAM MODEL and the natural Better tier. Four of eight Ohio communities published this split.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical-only, high service level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No general shuttle benefit. Instead a private car and driver, for doctor appointments only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included in the fee, but narrow in scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarrow Pointe villas: "Private Car and Driver for Doctor Appointments" appears as a discrete line item in the villa inclusions. The apartments get plain "transportation to and from Doctor Appointments".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A premium, differentiating option. Note it is the ONE case found where the villa product gets a BETTER service than the apartments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee-for-service for everything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rides are a billable service, charged to the resident statement. Sign-up required. Geography priced rather than bounded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chargeable throughout; rates published only in an in-house booklet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohio Living Breckenridge Village. Resident handbook: "There is a small fee for these services"; "There are charges for out of county rides"; "You must sign up to go on the scheduled routes"; and a branded escorted service, "Super Senior Transportation (SST)... An SST driver will escort you throughout your trip and business. There are flat fee charges." Directories wrongly describe this as covered by the monthly fee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viable for a Good tier if positioned honestly. Its virtue is transparency; its risk is that "transportation" then cannot be marketed as included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outings only, appointments explicitly excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group outings and events are covered. Medical and personal appointments are not provided at all; the community only helps coordinate a third-party ride.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outings included; appointments are the resident's own cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Perspective Senior Living (Woodland Terrace of Danville) operator FAQ: "New Perspective does not provide transportation to appointments; however, they do have a community van that is used to transport residents to events outside of the community... there may be commercial transportation options available for medical or other appointments, such as ride sharing programs, that they can assist in coordinating." Garbry Ridge cottages likewise get only "routine outings to local and regional events".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defensible and cheap, and honest about what cottage residents actually need. But it is the model most likely to disappoint a resident who assumed "transportation" meant rides to the doctor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. The ten attributes that define a transportation offering, and the decision on each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attribute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The question to answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the research found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BETTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed-schedule group shuttle, individually scheduled appointment rides, or on-demand personal rides?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two or three distinct services are normally bundled under one word. Maple Knoll is the clearest, separating an on-campus "Shuttle on Demand" from an off-campus "Chauffeur Service". Wyndemere is the only community found advertising "both scheduled and impromptu transportation".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled group shuttle only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group shuttle plus individually scheduled appointment rides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both, plus an on-demand personal tier and an on-campus circulator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trip purposes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which trips qualify? Medical, dialysis and therapy, groceries, shopping, banking, pharmacy, worship, group outings, personal errands, airport.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The one well-covered attribute. Medical appeared at 7 of 9 detached-cottage communities, shopping at 8 of 9. Banking appeared once, worship twice. DIALYSIS AND RECURRING THERAPY WERE NEVER MENTIONED by any community, despite being operationally the heaviest demand. Airport appeared only at Maple Knoll.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groceries, shopping, banking, group outings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds medical appointments, pharmacy, worship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds personal errands, airport, and a stated dialysis/therapy policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geographic radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How far is included, and what happens beyond?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT ONE of roughly 50 communities published a mileage radius. "Local", "nearby", "local and regional" are the universal unquantified terms. The only real geographic rules found were Ohio Living's fee trigger, "There are charges for out of county rides", Friendship Village Kalamazoo's named-city limit ("Kalamazoo and Portage area"), and Westminster Place's "standard route". The 10 to 15 mile figure is an industry norm quoted in third-party guidance, corroborated by Witzgall and Wood.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within ~10 miles; nothing beyond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~10 miles included; beyond at a posted per-mile or per-trip rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~15 miles included; beyond at a posted rate, with named destination hospitals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost to the resident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free, bundled, or charged? Per trip, per mile, per hour, or monthly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled local trips are usually included, but NOT always: Ohio Living charges and bills to the resident statement; Our Lady of Angels offered it "on a cost basis"; Cedarhurst excludes cottages from the all-inclusive rate. Only Maple Knoll published a rate BASIS (per mile) and even it withheld the rate. No community published an actual dollar figure. Witzgall is the only source in the study with prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled group trips included; nothing else offered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled included; unscheduled, private and out-of-radius at posted rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled included plus a monthly allowance of personal trips, then posted rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days and hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which days does each trip type run, and what hours?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almost never published. Highgrove at Tates Creek is the only community found stating days: "Monday through Friday as well as transportation to Sunday church services", implying no Saturday. Village at Bay Ridge runs groceries twice a week. Maple Knoll runs the grocery shuttle weekly. Friendship Village Kalamazoo says "weekly". Nobody published hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set days per purpose, weekdays only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set days per purpose, plus medical any weekday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended days including some weekend coverage; after-hours at a posted rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booking and lead time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How far ahead must a resident book, and through whom?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essentially never published. Ohio Living is the only source found stating a requirement: "You must sign up to go on the scheduled routes", with "Bus Route sheets... available at the front desk". Robin Run qualifies door-to-door trips as "(pre-arranged)". Because nobody publishes it, this must be designed rather than inherited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign-up sheet at the desk; several days notice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concierge booking, 24–48 hours notice, confirmation given</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concierge or app booking, short-notice accommodation where possible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity and priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What happens when demand exceeds the vehicle, and who gets priority?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not published anywhere. A targeted search for "when space permits" style qualifiers across the detached-cottage set returned nothing, and the one detailed capacity claim this research initially found failed exact-phrase verification (see Section F). Kirkland Crossings' operator handbook is the nearest real language: outings "may be cancelled for reasons including... severe or inclement weather and lack of interest."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space-permitting, medical prioritised, limits published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guaranteed medical seat; social trips space-permitting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guaranteed medical seat, with overflow covered by a third-party ride at community cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle and accessibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus, van, or car? Wheelchair accessible? How many?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rarely specified. Maple Knoll is the exception, quantifying "three full-time bus drivers" plus "a chauffeur for hire". Buses are named at Traditions at Beaumont, Primrose, Swanhaven and Laurel Lake. WHEELCHAIR ACCESSIBILITY WAS NOT CONFIRMED AT A SINGLE COMMUNITY, which is a notable gap given the resident profile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared van or bus, accessible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus for groups plus a car or van for appointments, accessible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds a sedan for personal and private trips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curb-to-curb, door-to-door, or escorted into the appointment?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A real and marketable distinction that almost nobody makes. Ohio Living sells it as a branded product: "Super Senior Transportation (SST) is an escorted personal driver service. An SST driver will escort you throughout your trip and business." Robin Run advertises "door-to-door services". Everyone else is silent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Door-to-door with driver assistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do detached-home residents get the same service as apartment residents?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MOST IMPORTANT FINDING. Not the same at several communities, and where it differs the cottage tier is LESSER. See Section E.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as apartment residents; central pickup point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as apartment residents; pickup at the villa door</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same, plus priority routing for the cottage neighbourhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. Community evidence — what each operator actually publishes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidence: VERIFIED = the exact phrase was re-queried and the source page returned it. LIKELY = search summary, substance probably right, wording not safe to quote. UNRELIABLE = directory boilerplate or text that failed verification; do not use. Every row needs one confirming page load before external publication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator / villa product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why it matters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedarhurst of Frankfort, IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedarhurst Senior Living; 32 cottages (opened 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Cedarhurst Cottages operate separately from the Assisted Living and Memory Care neighborhoods and do not include the same all-inclusive services and amenities." Cottage residents get "access to the activity programs, therapy services, and transportation options already available at" the AL/MC community. "Scheduled transportation" sits on the APARTMENT inclusion list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottages: not included in an all-inclusive rate. Apartments: included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPLICITLY LESSER. Cottages borrow the service rather than owning it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED (exact phrase re-queried; same disclaimer appears on Cedarhurst Topeka KS, Waterloo IL and Springfield IL, so it is corporate standard language for the Cottages line)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The strongest evidence in the research, and it explains why the benchmarking table could only say "Available" for this community. "Available" was the correct word.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garbry Ridge, Piqua, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCF Management; cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COTTAGE inclusions list carries only "routine outings to local and regional events" (alongside utilities, lawn care, landscaping, snow removal, 24-hour emergency call). The IL APARTMENT services list separately carries "scheduled transportation". An apartment-level extra-cost menu adds "special life enrichment events or outings" and "personal shopping services".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included items versus a separately priced menu. No prices published.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPLICITLY LESSER, and the mechanism is visible: cottages get GROUP OUTINGS, apartments get INDIVIDUAL SCHEDULED RIDES.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED (exact phrase re-queried)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows exactly how an operator scales the service down for detached homes, on the assumption those residents still drive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarrow Pointe, Tulsa, OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tulsa Jewish; The Villas (patio homes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Villas included-services list contains a discrete line item: "Private Car and Driver for Doctor Appointments", alongside Monthly Meal Allowance, Weekly Light Housekeeping, Weekly Flat Linen Service. The Apartments get the parallel item as plain "transportation to and from Doctor Appointments".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included, but narrow: doctor appointments only. Shopping, groceries, banking and errands are not listed as included for villas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BETTER THAN APARTMENTS. The only case found anywhere where the villa product gets an upgraded service tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY-HIGH (structured inclusions list plus a villa brochure PDF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proves a detached product can differentiate upward on transportation, not just downward.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohio Living Breckenridge Village, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohio Living; 73 Ranch Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident handbooks describe three services: campus loop buses; off-campus scheduled routes where "You must sign up to go on the scheduled routes" and "Bus Route sheets are available at the front desk"; and "Super Senior Transportation (SST)... an escorted personal driver service. An SST driver will escort you throughout your trip and business." Also "There are charges for out of county rides."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEE-FOR-SERVICE. "There is a small fee for these services"; rides "can be charged to the resident's statement"; SST carries "flat fee charges". Rates are in a front-desk booklet, not online.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNCONFIRMED. The three handbooks found are building-specific (apartments and brownstones). No ranch-home handbook was located.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY-HIGH on the handbook mechanics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MOST IMPORTANT CORRECTION to the assumption that transportation is an included amenity. Directories describe this community as covering transportation in the monthly fee. The handbook says otherwise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woodland Terrace of Danville, IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Perspective Senior Living; 50 cottage-style townhomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator FAQ: "New Perspective does not provide transportation to appointments; however, they do have a community van that is used to transport residents to events outside of the community. In addition, there may be commercial transportation options available for medical or other appointments, such as ride sharing programs, that they can assist in coordinating."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community outings included. Appointments not provided at all. "Some off-site transportation may incur extra fees."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not stated for the cottages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY-HIGH (returned near-identically across two independent queries)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only explicit SCOPE EXCLUSION found anywhere, and three directory sites flatly contradict it by claiming the community provides rides to doctor visits. Proof that directory transportation flags cannot be trusted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maple Knoll Village, Cincinnati, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maple Knoll Communities; 142 villas, 135 apartments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two named services: "Shuttle on Demand" for on-campus circulation plus "weekly to an area grocery store", and "Chauffeur Service" for "doctor appointments, the airport, and more". Staffing quantified as "three full-time bus drivers" plus "a chauffeur for hire". Also brokers Uber Health.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-tier and the only PER-MILE basis found: campus shuttle and weekly grocery run are "a free service"; the chauffeur carries "a nominal per-mile fee". The rate itself is unpublished.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong. Transportation sits on the independent living pages and the IL inventory is majority villa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY-HIGH (distinctive language, clearly community-authored)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The most sophisticated model found. The on-campus versus off-campus split is a real product distinction almost nobody else draws in writing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laurel Lake, Hudson, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Villas, 1,600–2,700+ sq ft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community FAQ: "Laurel Lake buses provide transportation for regularly scheduled weekly/monthly courtesy trips and special events like the symphony, theater and regional attractions. Additionally, for a fee, residents may also engage the services of a Laurel Lake driver."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-tier. Courtesy trips free on a fixed weekly/monthly schedule; personal driver "for a fee", amount unpublished.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely but not explicit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY-HIGH (first-party FAQ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only community treating CULTURAL EXCURSIONS as a distinct service line from errands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Franklin Circle, Chagrin Falls, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judson Smart Living; 27 cottage homes, 16 garden homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Scheduled transportation services to local trips and appointments are included at no charge; additional personal transportation is available for a small fee."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean published two-tier. Fee amount not published.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely, since pricing covers independent living as a whole, but not stated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY (first-party amenities and FAQ pages)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cleanest one-sentence statement of the mainstream two-tier model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Westminster Place, Evanston, IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presbyterian Homes; 104 cottages and townhouses, 40 acres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Complimentary shuttles run to nearby physician offices, Northwestern Memorial Hospital-Evanston, grocery stores, and community events; fee-based transport can be arranged for individual appointments beyond the standard route."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-tier, defined by a "standard route" rather than a radius.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not differentiated, despite 104 cottages on a 40-acre campus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY (recurred identically across two independent queries)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The "standard route" is the closest thing to a defined geographic structure found, and a practical alternative to a mileage radius.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Village at Bay Ridge, Traverse City, MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heritage Senior Communities; cottage-style homes with garages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The Village at Bay Ridge offers a convenient and fun Bay Ridge Community bus to all residents at no additional cost. The community bus takes regularly scheduled trips to various destinations, with many other destinations based on regular resident requests." Groceries twice a week; also doctor trips, the beach, the Farmer's Market.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything free, including the request-driven trips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAME — "to all residents" explicitly covers cottage and apartment residents alike.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE COUNTER-EXAMPLE. Here the unscheduled, request-driven channel is also free, which disproves any assumption that scheduled-free and unscheduled-paid is a universal convention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith Crossing, Orland Park, IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith Senior Living; free-standing villas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The monthly fee is all-inclusive, including all utilities, maintenance, housekeeping, dining plan, activities, amenities and scheduled transportation." Trips go to "local appointments, shopping, and community events".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included in an all-inclusive monthly fee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAME. Villas and apartments are both independent living under one fee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The clearest example of the bundled not-for-profit model, and the community the benchmarking table already flags as the heavily bundled end of the spectrum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highgrove at Tates Creek, Lexington, KY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 single-level cottages (duplexes and quads, not fully detached)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Highgrove residents ride in style! We offer scheduled transportation for shopping..." Separately: "scheduled transportation services Monday through Friday as well as transportation to Sunday church services."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Complimentary" claimed, but only in directory boilerplate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not found. Transportation does not appear on the cottage page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED for the opening phrase; LIKELY for the days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE ONLY COMMUNITY IN THE ENTIRE RESEARCH THAT PUBLISHES DAYS OF OPERATION. Monday to Friday plus Sunday worship implies no Saturday service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Senior Communities (5 properties)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zionsville, Brownsburg, Coventry, Rosegate, Beech Grove Meadows; Garden Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE SENTENCE USED VERBATIM ACROSS ALL FIVE: "Garden Home residents enjoy the company of their neighbors and opportunities to participate in a wide range of planned social activities, scheduled transportation to shopping, restaurants and appointments."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Free, scheduled transportation" and "complimentary" — marketing register, no fee schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES, named. The benefit is attached to "Garden Home residents" by name at all five.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED (exact-phrase probe returned the pages)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASC transportation is ONE corporate promise replicated five times, not five data points. Treating the five as five benchmarks double-counts. Note the trip list is narrow and omits medical-first framing entirely.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traditions Management (4 properties)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brookside, Reagan Park, Beaumont, Hunter Station; Garden Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A two-tier asymmetry in identical corporate copy: garden homes get the bare noun, "...utilities and full access to dining, amenities, social activities and events and transportation". AL and memory care get a defined service, "...scheduled transportation to medical appointments and outings". Hunter Station is the exception, naming transportation as a line item in the villa inclusion list. Beaumont is the only one extending it to independent living by name, with "a community bus... to scheduled weekly activities".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not published at any of the four.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIXED. Explicit at Hunter Station, named for IL at Beaumont, undefined at Brookside and Reagan Park.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traditions describes WHAT transportation does only for its higher-acuity tiers. For villa residents it lists the word and stops — the same flattening the villa study inherited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLC Management (2 properties)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Village at Hamilton Pointe; Village of Avon; garden homes and cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSPORTATION IS ABSENT FROM BOTH COMMUNITIES' OWN SITES. Services are "included in the monthly rent" but transportation is not among the enumerated inclusions. A third party describes only "setting up rides for doctor visits". At Avon, transportation appears on-site only as an ADMISSION CRITERION, describing what residents must do independently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not established.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT FOUND. Should be logged as unverified, not as included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY on the absence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordination is not provision. If a community only helps book a ride, "Transportation: included" in a benchmark overstates the benefit considerably.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country Club at Woodland Hills, Tulsa, OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery Senior Living; cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery brands the programme "Connections Transportation" and lists it on the cottage pages. "complimentary, scheduled Connections transportation"; "scheduled bus and sedan transportation (where available)". Brand level: "Individualized or same-day trips can be arranged at cost for those who need transportation outside the regular schedule."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-tier, drawn at SCHEDULED versus OFF-SCHEDULE rather than by distance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, apparently. Connections Transportation is listed on the cottage-living pages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directly relevant to the 10-mile radius claim in the source email. See the note below Section D.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friendship Village Kalamazoo, MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life Care Services; Garden Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"weekly transportation to medical and financial appointments in Kalamazoo and Portage area" and "weekly transportation to shopping, churches, etc."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included; no paid tier found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not differentiated: "Independent-living residents choose from apartments or garden homes and have access to... scheduled transportation."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only NAMED-CITY geographic limit found, and one of the few frequency statements ("weekly").</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swanhaven Manor, Saginaw, MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottages with attached garages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"regularly scheduled shopping trips in the complimentary Swanhaven Bus", with an Activity Coordinator planning trips to "banks, grocery stores, shopping centers, and favorite restaurants".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complimentary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY (the branded vehicle name suggests community-authored copy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ONLY community where MEDICAL APPOINTMENTS ARE NOT NAMED at all. Transportation here is run as an activity programme, not a medical-transport function.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our Lady of Angels, Joliet, IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplex cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transportation "available to residents on a cost basis" and "optional transportation for errands and appointments".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chargeable, not included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNRELIABLE (directory boilerplate) — and note the community CLOSED IN JANUARY 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two data-quality flags for the benchmarking table: the community is closed, and the "Not provided" label is probably shorthand for "not included in the fee" rather than "did not exist".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirkland Crossings, Pewaukee, WI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presbyterian Homes &amp; Services; 22 townhomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing says "complimentary transportation to shopping and outings". The operator's standard resident handbook says: "For some events, fees may be charged for cost of services such as transportation, tickets, or supplies" and outings "may be cancelled for reasons including, but not limited to, severe or inclement weather and lack of interest."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing says complimentary; the handbook reserves the right to charge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not differentiated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE GAP BETWEEN MARKETING AND HANDBOOK IS ITSELF THE FINDING, and it is the best available language on cancellation and capacity risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the 10-mile radius in the source email: dedicated and domain-restricted searches across Discovery Senior Living's brands found NO published mileage limit on any Discovery transportation page, and neither Oklahoma Discovery-family community states one. What Discovery standardises is the programme name and a scheduled-versus-off-schedule cost split. The 10-mile figure is most likely real as LOCAL PRACTICE at that community, and it is consistent with the 10 to 15 mile industry norm, but it should not be attributed to Discovery as a brand standard or extrapolated to other Discovery communities. This is an absence-of-evidence finding built on search indexing, since no Discovery page could be opened.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E. The question that matters most — do cottage residents get the same transportation?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answer: not reliably, and where it differs the cottage tier is LESSER. Of nine detached-cottage communities researched, three give cottage residents the same service, two explicitly give them less, and four do not say. The split tracks OPERATING MODEL, not geography or price point.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How transportation is treated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What cottage residents get</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implication for this product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not-for-profit CCRC / Life Plan Community with one all-inclusive fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transportation is bundled into a single monthly fee that covers every independent living housing type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE SAME as apartment residents. The detached home is a FLOOR PLAN CHOICE within one service tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith Crossing; Robin Run Village; Village at Bay Ridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the cottages sit inside one independent living fee, transportation can honestly be marketed as included, and it costs what it costs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For-profit operator adding cottages to an existing licensed building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cottages are a separate rental product that BORROWS campus services rather than owning them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LESS. Cottages get access to, or a social-outings subset of, the main community's service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedarhurst of Frankfort ("operate separately... do not include the same all-inclusive services and amenities"); Garbry Ridge (cottages get "routine outings"; apartments get "scheduled transportation")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the cottages are a distinct rental product, transportation becomes an à la carte or access-only benefit, and the marketing must say so.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa product positioned ABOVE the apartments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transportation is upgraded for the detached product rather than scaled down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORE. A private car and driver rather than a shared shuttle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarrow Pointe ("Private Car and Driver for Doctor Appointments" for villas; plain "transportation" for apartments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The differentiating option. Narrow scope, high perceived service level, and it suits residents who still drive but want help on medical days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• The operating model, not the site plan, determines whether cottage residents can be told transportation is included. Cedarhurst is the template for the unbundled approach; Smith Crossing is the template for the bundled one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Garbry Ridge shows the mechanism precisely: cottage residents are offered GROUP SOCIAL OUTINGS, a lifestyle amenity, while apartment residents get INDIVIDUAL SCHEDULED RIDES, a care-adjacent service. That is exactly what an operator designs when it assumes cottage buyers still have car keys.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Detached-home residents mostly still drive. Garages are a headline feature of nearly every villa product in the study, and public guidance notes that residents commonly keep a car and mix driving with the shuttle. A heavy individual-ride benefit may be poorly matched to actual demand at the Good tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• The counter-risk is the spread footprint. The rental-model report warns that decentralised cottages raise staff travel time for transport and emergency response, so a door-to-door promise on a large site costs materially more than the same promise in a vertical building.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Absence of a published distinction is not absence of a practical one. On campuses of 37 to 72 acres, walk-to-pickup distance may differ sharply between a villa and an apartment, and no operator addresses it in writing. Whether the shuttle comes to the villa door or the resident walks to the main building is a question only a sales counsellor can answer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F. Research reliability — read before quoting anything on this tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What happened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community websites were unreachable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A plausible, detailed finding turned out not to exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This session's own first search returned a richly detailed Hamilton Trace description covering "medical appointments, dialysis, and outpatient therapy... when space permits". An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator's own line: "Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior-living directories publish AI-generated pseudo-detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two researchers independently confirmed this. An exact-phrase probe on "scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores" returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do not admit any claim about dialysis, a "designated service radius", or "scheduled in advance" on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Place for Mom and Seniorly amenity flags are fixed checkboxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Complimentary Transportation" and "Transportation at Cost" are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directories contradicted operators twice, and the operator was right both times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The most concrete operational fact came from a resident review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A family member wrote of one community: "shuttle buses that take you for no charge to doctor's appointments and even have occasional community activities that they take people to." That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mine resident reviews for operational truth. They describe the service as used rather than as marketed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative findings are more reliable than positive ones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated "not found" results across roughly 50 communities are therefore the study's strongest conclusions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rely on the pattern that nothing is published. Treat individual quotes as provisional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G. How to close the gaps — the detail is obtainable, just not from marketing pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Chase RESIDENT HANDBOOKS, disclosure statements and residence agreements, not amenity pages. The only genuinely concrete, qualifier-bearing language in this entire research came from handbooks. One operator posts a handbook for every community, which would yield an operator-level transportation policy dataset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Specific unopened documents worth retrieving: the Smith Crossing independent living resident handbook; the Kirkland Crossings resident handbook plus its separate townhome and apartment brochures, whose comparison would answer the villa question definitively; a ranch-home handbook for Ohio Living Breckenridge; and the Laurel Lake villa project resident Q&amp;A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Ask Ohio Living Breckenridge for the "transportation booklet available at the front desk". It is named in the handbooks as the document holding the actual rates, and it is not online.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Mystery-shop for prices. Not one community in the detached-cottage set published a transportation price of any kind: no per-trip rate, no per-mile rate, no monthly charge. If à la carte pricing is needed, it must come from sales offices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Put the operational questions to sales counsellors by phone: radius, days, hours, booking lead time, fees, wheelchair accessibility, what happens when two residents want the vehicle at once, and above all whether the shuttle comes to the villa door or the resident walks to the main building. Based on this research, that last question is unanswerable from published material.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Re-run this research from an unrestricted network. Roughly 50 communities were covered here from search summaries alone; direct page access would convert most of the LIKELY rows in Section D into verified quotations.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources, attribution and method notes</t>
   </si>
   <si>
@@ -6258,6 +7327,9 @@
   </si>
   <si>
     <t xml:space="preserve">• Recommendations are analytical judgments built from the synthesis and are service-first: they decide what to offer at each level per function. Mapping levels to unit price points and price ranges is deferred to a later step; source price references are kept in Section B of the Good-Better-Best tab for that purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• A transportation deep-dive was added Sept 17, 2026, covering roughly 50 communities, because all 55 transportation entries in the villa study are the bare word "Transportation". Its method, evidence and reliability warnings are on the Transportation Detail tab. Community websites were unreachable from the build environment, so those findings rest on web-search summaries; several plausible-sounding details failed exact-phrase verification and were discarded.</t>
   </si>
   <si>
     <t xml:space="preserve">• Workbook built Sept 17, 2026 from the four sources above.</t>
@@ -6272,7 +7344,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6347,8 +7419,55 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF1F3864"/>
+      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6421,6 +7540,12 @@
         <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -6471,7 +7596,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6576,6 +7701,42 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6665,9 +7826,9 @@
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -26035,7 +27196,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="n">
         <v>220</v>
       </c>
@@ -26132,7 +27293,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
@@ -26197,7 +27358,7 @@
       </c>
       <c r="W222" s="2"/>
       <c r="X222" s="2" t="s">
-        <v>1485</v>
+        <v>1494</v>
       </c>
       <c r="Y222" s="2"/>
       <c r="Z222" s="2"/>
@@ -26205,7 +27366,7 @@
         <v>1469</v>
       </c>
       <c r="AB222" s="2" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="AC222" s="2" t="s">
         <v>1469</v>
@@ -26214,7 +27375,7 @@
         <v>52</v>
       </c>
       <c r="AE222" s="2" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="AF222" s="2" t="s">
         <v>52</v>
@@ -26226,7 +27387,7 @@
         <v>52</v>
       </c>
       <c r="AI222" s="2" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26243,16 +27404,16 @@
         <v>1457</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="I223" s="4" t="s">
         <v>53</v>
@@ -26266,35 +27427,35 @@
         <v>53</v>
       </c>
       <c r="N223" s="4" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="O223" s="4" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="P223" s="4" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q223" s="4" t="s">
         <v>1480</v>
       </c>
       <c r="R223" s="4" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="S223" s="4" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="T223" s="4" t="s">
         <v>592</v>
       </c>
       <c r="U223" s="4" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="V223" s="4" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="W223" s="4"/>
       <c r="X223" s="4" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="Y223" s="4"/>
       <c r="Z223" s="4"/>
@@ -26340,7 +27501,7 @@
         <v>1457</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>53</v>
@@ -26349,7 +27510,7 @@
         <v>53</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="I224" s="2" t="s">
         <v>53</v>
@@ -26366,13 +27527,13 @@
         <v>52</v>
       </c>
       <c r="O224" s="2" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="P224" s="2" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="Q224" s="2" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="R224" s="2" t="s">
         <v>1481</v>
@@ -26381,17 +27542,17 @@
         <v>1477</v>
       </c>
       <c r="T224" s="2" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="U224" s="2" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="V224" s="2" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="W224" s="2"/>
       <c r="X224" s="2" t="s">
-        <v>1485</v>
+        <v>1516</v>
       </c>
       <c r="Y224" s="2"/>
       <c r="Z224" s="2"/>
@@ -26423,7 +27584,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="n">
         <v>224</v>
       </c>
@@ -26437,7 +27598,7 @@
         <v>1457</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>53</v>
@@ -26446,7 +27607,7 @@
         <v>53</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="I225" s="4" t="s">
         <v>53</v>
@@ -26463,32 +27624,32 @@
         <v>52</v>
       </c>
       <c r="O225" s="4" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="P225" s="4" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="Q225" s="4" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="R225" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="S225" s="4" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="T225" s="4" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="U225" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="V225" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="W225" s="4"/>
       <c r="X225" s="4" t="s">
-        <v>1485</v>
+        <v>1526</v>
       </c>
       <c r="Y225" s="4"/>
       <c r="Z225" s="4"/>
@@ -26520,7 +27681,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
@@ -26534,7 +27695,7 @@
         <v>1457</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>53</v>
@@ -26543,7 +27704,7 @@
         <v>53</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="I226" s="2" t="s">
         <v>53</v>
@@ -26557,35 +27718,35 @@
         <v>53</v>
       </c>
       <c r="N226" s="2" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="O226" s="2" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="P226" s="2" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="Q226" s="2" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="R226" s="2" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="S226" s="2" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="T226" s="2" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="U226" s="2" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="V226" s="2" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
       <c r="W226" s="2"/>
       <c r="X226" s="2" t="s">
-        <v>1485</v>
+        <v>1535</v>
       </c>
       <c r="Y226" s="2"/>
       <c r="Z226" s="2"/>
@@ -26617,7 +27778,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="4" t="n">
         <v>226</v>
       </c>
@@ -26631,7 +27792,7 @@
         <v>1457</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="F227" s="4" t="s">
         <v>53</v>
@@ -26640,13 +27801,13 @@
         <v>53</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="I227" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="K227" s="5"/>
       <c r="L227" s="5"/>
@@ -26663,7 +27824,7 @@
         <v>53</v>
       </c>
       <c r="Q227" s="4" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="R227" s="4" t="s">
         <v>53</v>
@@ -26678,11 +27839,11 @@
         <v>53</v>
       </c>
       <c r="V227" s="4" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="W227" s="4"/>
       <c r="X227" s="4" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="Y227" s="4"/>
       <c r="Z227" s="4"/>
@@ -26714,7 +27875,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="n">
         <v>227</v>
       </c>
@@ -26728,7 +27889,7 @@
         <v>1457</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>53</v>
@@ -26737,7 +27898,7 @@
         <v>53</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="I228" s="2" t="s">
         <v>53</v>
@@ -26751,19 +27912,19 @@
         <v>53</v>
       </c>
       <c r="N228" s="2" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="O228" s="2" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="P228" s="2" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="Q228" s="2" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="R228" s="2" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="S228" s="2" t="s">
         <v>53</v>
@@ -26775,11 +27936,11 @@
         <v>53</v>
       </c>
       <c r="V228" s="2" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="W228" s="2"/>
       <c r="X228" s="2" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="Y228" s="2"/>
       <c r="Z228" s="2"/>
@@ -26811,7 +27972,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="n">
         <v>228</v>
       </c>
@@ -26825,7 +27986,7 @@
         <v>1457</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="F229" s="4" t="s">
         <v>53</v>
@@ -26834,7 +27995,7 @@
         <v>53</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="I229" s="4" t="s">
         <v>53</v>
@@ -26848,19 +28009,19 @@
         <v>53</v>
       </c>
       <c r="N229" s="4" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="O229" s="4" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="P229" s="4" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="Q229" s="4" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="R229" s="4" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="S229" s="4" t="s">
         <v>53</v>
@@ -26872,11 +28033,11 @@
         <v>53</v>
       </c>
       <c r="V229" s="4" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="W229" s="4"/>
       <c r="X229" s="4" t="s">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="Y229" s="4"/>
       <c r="Z229" s="4"/>
@@ -26922,16 +28083,16 @@
         <v>1457</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>1549</v>
+        <v>1554</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>1551</v>
+        <v>1556</v>
       </c>
       <c r="I230" s="2" t="s">
         <v>53</v>
@@ -26945,7 +28106,7 @@
         <v>53</v>
       </c>
       <c r="N230" s="2" t="s">
-        <v>1552</v>
+        <v>1557</v>
       </c>
       <c r="O230" s="2" t="s">
         <v>53</v>
@@ -26954,26 +28115,26 @@
         <v>53</v>
       </c>
       <c r="Q230" s="2" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="R230" s="2" t="s">
-        <v>1554</v>
+        <v>1559</v>
       </c>
       <c r="S230" s="2" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="T230" s="2" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="U230" s="2" t="s">
-        <v>1557</v>
+        <v>1562</v>
       </c>
       <c r="V230" s="2" t="s">
-        <v>1558</v>
+        <v>1563</v>
       </c>
       <c r="W230" s="2"/>
       <c r="X230" s="2" t="s">
-        <v>1559</v>
+        <v>1564</v>
       </c>
       <c r="Y230" s="2"/>
       <c r="Z230" s="2"/>
@@ -27019,16 +28180,16 @@
         <v>1457</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>1560</v>
+        <v>1565</v>
       </c>
       <c r="F231" s="4" t="s">
         <v>1428</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I231" s="4" t="s">
         <v>1428</v>
@@ -27042,35 +28203,35 @@
         <v>1428</v>
       </c>
       <c r="N231" s="4" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="O231" s="4" t="s">
-        <v>1564</v>
+        <v>1569</v>
       </c>
       <c r="P231" s="4" t="s">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="Q231" s="4" t="s">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="R231" s="4" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="S231" s="4" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="T231" s="4" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="U231" s="4" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="V231" s="4" t="s">
-        <v>1567</v>
+        <v>1572</v>
       </c>
       <c r="W231" s="4"/>
       <c r="X231" s="4" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Y231" s="4"/>
       <c r="Z231" s="4"/>
@@ -27137,34 +28298,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1569</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>1571</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1572</v>
+        <v>1577</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>172</v>
@@ -27176,13 +28337,13 @@
         <v>53</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27979,7 +29140,7 @@
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -27994,210 +29155,210 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>1579</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1580</v>
+        <v>1585</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1581</v>
+        <v>1586</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1582</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>1583</v>
+        <v>1588</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">COUNTIFS('Consolidated Data'!$B$2:$B$231,"Laura Lopez",'Consolidated Data'!$K$2:$K$231,"&gt;0")</f>
         <v>54</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>1584</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>1585</v>
+        <v>1590</v>
       </c>
       <c r="B29" s="5" t="n">
         <f aca="false">MIN('Consolidated Data'!$K$2:$K$216)</f>
         <v>515</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>1587</v>
+        <v>1592</v>
       </c>
       <c r="B30" s="5" t="n">
         <f aca="false">MEDIAN('Consolidated Data'!$K$2:$K$216)</f>
         <v>2799.5</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1588</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="B31" s="5" t="n">
         <f aca="false">MAX('Consolidated Data'!$L$2:$L$216)</f>
         <v>6900</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>1590</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="B32" s="4" t="n">
         <f aca="false">COUNTIFS('Consolidated Data'!$B$2:$B$231,"Laura Lopez",'Consolidated Data'!$M$2:$M$231,"Yes")</f>
         <v>63</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>1592</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="B33" s="4" t="n">
         <f aca="false">COUNTIFS('Consolidated Data'!$B$2:$B$231,"Laura Lopez",'Consolidated Data'!$M$2:$M$231,"CCRC (entry fee not stated)")</f>
         <v>35</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>1592</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1596</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>1597</v>
+        <v>1602</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1598</v>
+        <v>1603</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>1602</v>
+        <v>1607</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1603</v>
+        <v>1608</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>1604</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>1605</v>
+        <v>1610</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1606</v>
+        <v>1611</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1610</v>
+        <v>1615</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>1611</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>1572</v>
+        <v>1577</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1617</v>
+        <v>1622</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1620</v>
+        <v>1625</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1621</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28205,19 +29366,19 @@
         <v>13</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>1623</v>
+        <v>1628</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>1624</v>
+        <v>1629</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28225,19 +29386,19 @@
         <v>14</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1628</v>
+        <v>1633</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>1629</v>
+        <v>1634</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28245,19 +29406,19 @@
         <v>15</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1632</v>
+        <v>1637</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>1636</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28265,19 +29426,19 @@
         <v>16</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1637</v>
+        <v>1642</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>1638</v>
+        <v>1643</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>1639</v>
+        <v>1644</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>1640</v>
+        <v>1645</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28285,19 +29446,19 @@
         <v>17</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>1643</v>
+        <v>1648</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28305,19 +29466,19 @@
         <v>18</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>1648</v>
+        <v>1653</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>1649</v>
+        <v>1654</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>1650</v>
+        <v>1655</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>1651</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28325,19 +29486,19 @@
         <v>19</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1652</v>
+        <v>1657</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>1653</v>
+        <v>1658</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>1649</v>
+        <v>1654</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28345,19 +29506,19 @@
         <v>20</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1656</v>
+        <v>1661</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>1657</v>
+        <v>1662</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>1649</v>
+        <v>1654</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>1658</v>
+        <v>1663</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>1659</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28365,29 +29526,29 @@
         <v>21</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>1661</v>
+        <v>1666</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>1662</v>
+        <v>1667</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>1663</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>1664</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>1665</v>
+        <v>1670</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -28397,7 +29558,7 @@
     </row>
     <row r="58" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>1666</v>
+        <v>1671</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -28407,7 +29568,7 @@
     </row>
     <row r="59" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>1667</v>
+        <v>1672</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -28417,7 +29578,7 @@
     </row>
     <row r="60" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>1668</v>
+        <v>1673</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -28427,7 +29588,7 @@
     </row>
     <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>1669</v>
+        <v>1674</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -28437,7 +29598,7 @@
     </row>
     <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>1670</v>
+        <v>1675</v>
       </c>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -28447,7 +29608,7 @@
     </row>
     <row r="63" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>1671</v>
+        <v>1676</v>
       </c>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
@@ -28457,7 +29618,7 @@
     </row>
     <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>1672</v>
+        <v>1677</v>
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -28467,7 +29628,7 @@
     </row>
     <row r="65" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>1673</v>
+        <v>1678</v>
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
@@ -28477,7 +29638,7 @@
     </row>
     <row r="66" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>1674</v>
+        <v>1679</v>
       </c>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
@@ -28515,7 +29676,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -28529,12 +29690,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1675</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -28546,41 +29707,41 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1572</v>
+        <v>1577</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1678</v>
+        <v>1683</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1679</v>
+        <v>1684</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>1680</v>
+        <v>1685</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>1681</v>
+        <v>1686</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1682</v>
+        <v>1687</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1684</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>13</v>
+        <v>1690</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1685</v>
+        <v>1691</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>52</v>
@@ -28592,247 +29753,247 @@
         <v>52</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1686</v>
+        <v>1692</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1687</v>
+        <v>1693</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>1688</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>13</v>
+        <v>1690</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1689</v>
+        <v>1695</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>1690</v>
+        <v>1696</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="E7" s="16" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>1692</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>1693</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>13</v>
+        <v>1690</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>1698</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>1698</v>
+        <v>1701</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>1703</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1699</v>
+        <v>1692</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>13</v>
+        <v>1690</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>1703</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>1704</v>
+        <v>1707</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>1708</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>1709</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1699</v>
+        <v>1692</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1705</v>
+        <v>1710</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>1706</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>13</v>
+        <v>1690</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>1707</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>1709</v>
+      <c r="D10" s="4" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>1714</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1699</v>
+        <v>1715</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1700</v>
+        <v>1716</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>1710</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>13</v>
+        <v>1690</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1711</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>1712</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>1712</v>
+        <v>1718</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>1707</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>1712</v>
+        <v>52</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1713</v>
+        <v>1719</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>1714</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>14</v>
+        <v>1690</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1715</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>52</v>
+        <v>1721</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>1724</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>1716</v>
+        <v>1692</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>1717</v>
+        <v>1725</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>1718</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>14</v>
+        <v>1690</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1719</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>52</v>
+        <v>1727</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>1729</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>1720</v>
+        <v>1715</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>1721</v>
+        <v>1730</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>1722</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>14</v>
+        <v>1690</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1723</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>52</v>
+        <v>1732</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>1734</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>1735</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>1699</v>
+        <v>1692</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>1724</v>
+        <v>1736</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>1725</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>14</v>
+        <v>1690</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1726</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>1727</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>1727</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>1728</v>
+        <v>1738</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>1741</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>1729</v>
+        <v>1742</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>1730</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28840,25 +30001,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1731</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>1708</v>
+        <v>1744</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>1732</v>
+        <v>52</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1733</v>
+        <v>1745</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>1700</v>
+        <v>1746</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>1734</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28866,25 +30027,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1735</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>1736</v>
+        <v>1748</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>1737</v>
+        <v>1749</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>1738</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28892,129 +30053,129 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1739</v>
+        <v>1752</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>1697</v>
+        <v>1707</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1699</v>
+        <v>1715</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>1740</v>
+        <v>1753</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>1734</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1741</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>1742</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>1742</v>
+        <v>1755</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>1756</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>1742</v>
+        <v>1757</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1743</v>
+        <v>1758</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>1744</v>
+        <v>1759</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>1745</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>1746</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>1747</v>
+        <v>1761</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>1748</v>
+        <v>1763</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1749</v>
+        <v>1764</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>1750</v>
+        <v>1765</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>1751</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1752</v>
+        <v>1766</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>1753</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>1754</v>
+        <v>1707</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>1767</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1755</v>
+        <v>1768</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>1756</v>
+        <v>1765</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>1757</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1758</v>
+        <v>1770</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>1759</v>
+        <v>1707</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>1707</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>1760</v>
+        <v>52</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>1761</v>
+        <v>1715</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>1762</v>
+        <v>1771</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>1763</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29022,25 +30183,25 @@
         <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1764</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>1765</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>1765</v>
+        <v>1772</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>1773</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1749</v>
+        <v>1774</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1766</v>
+        <v>1775</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>1767</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29048,25 +30209,25 @@
         <v>15</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1768</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>1708</v>
+        <v>353</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>1778</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1693</v>
+        <v>1780</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1770</v>
+        <v>1781</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>1734</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29074,25 +30235,25 @@
         <v>15</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1771</v>
+        <v>1783</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>1772</v>
+        <v>1707</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>1784</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>52</v>
+        <v>1785</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>1773</v>
+        <v>1786</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>1774</v>
+        <v>1787</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>1775</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29100,129 +30261,129 @@
         <v>15</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1776</v>
+        <v>1789</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>1777</v>
+        <v>1790</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>1791</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>1693</v>
+        <v>1792</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>1778</v>
+        <v>1793</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>1734</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C27" s="18" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>1796</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>1780</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>1781</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>1782</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>1783</v>
-      </c>
       <c r="G27" s="4" t="s">
-        <v>1784</v>
+        <v>1797</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>1785</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1786</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>1697</v>
+        <v>1799</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>52</v>
+        <v>1800</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>1787</v>
+        <v>1758</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>1788</v>
+        <v>1801</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1789</v>
+        <v>1802</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>1708</v>
+        <v>1803</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>1782</v>
+        <v>52</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>1790</v>
+        <v>1804</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>1791</v>
+        <v>1805</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>1792</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1793</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>1708</v>
+        <v>1807</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>1707</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>1794</v>
+        <v>1762</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>1808</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>1773</v>
+        <v>1758</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>1795</v>
+        <v>1809</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29230,25 +30391,25 @@
         <v>124</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>1708</v>
+        <v>1810</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>1812</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>1813</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>1693</v>
+        <v>1814</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>1797</v>
+        <v>1815</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>1734</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29256,207 +30417,207 @@
         <v>124</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1798</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>1799</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>1799</v>
+        <v>1817</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>1796</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>1799</v>
+        <v>52</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>1699</v>
+        <v>1818</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>1800</v>
+        <v>1819</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>1801</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>1802</v>
+        <v>124</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1803</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>1804</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>1804</v>
+        <v>1820</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>1804</v>
+        <v>1813</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>1805</v>
+        <v>1821</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>1806</v>
+        <v>1822</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>1807</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>1802</v>
+        <v>124</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1808</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>1697</v>
+        <v>1824</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>1809</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>1810</v>
+        <v>1762</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>1825</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>1811</v>
+        <v>1804</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>1812</v>
+        <v>1826</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>1802</v>
+        <v>124</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1813</v>
+        <v>1827</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>1782</v>
+        <v>1762</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>1790</v>
+        <v>1758</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>1814</v>
+        <v>1828</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1815</v>
+        <v>1829</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>52</v>
+        <v>1830</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>52</v>
+        <v>1830</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>52</v>
+        <v>1830</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>1816</v>
+        <v>1715</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>1817</v>
+        <v>1831</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>1734</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>17</v>
+        <v>1833</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1818</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>1697</v>
+        <v>1834</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>1835</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>52</v>
+        <v>1835</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>52</v>
+        <v>1835</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>1819</v>
+        <v>1836</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>1820</v>
+        <v>1837</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>1821</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>17</v>
+        <v>1833</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1822</v>
+        <v>1839</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>1823</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>1823</v>
+        <v>1707</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>1841</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>1773</v>
+        <v>1842</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>1824</v>
+        <v>1843</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>1825</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>17</v>
+        <v>1833</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1826</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>1827</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>1828</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>1829</v>
+        <v>1844</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>1813</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>1830</v>
+        <v>1821</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>1831</v>
+        <v>1845</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>1832</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29464,25 +30625,25 @@
         <v>17</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1833</v>
-      </c>
-      <c r="C40" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>1697</v>
+        <v>1846</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>1834</v>
+        <v>1847</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>1835</v>
+        <v>1848</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>1836</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29490,25 +30651,25 @@
         <v>17</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1837</v>
+        <v>1849</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>1708</v>
+        <v>1707</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>1693</v>
+        <v>1850</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>1700</v>
+        <v>1851</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>1838</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29516,129 +30677,129 @@
         <v>17</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1839</v>
+        <v>1853</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>1708</v>
+        <v>1707</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>1854</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>1773</v>
+        <v>1804</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>1700</v>
+        <v>1855</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>1734</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1840</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>52</v>
+        <v>1857</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>1859</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>1860</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>1841</v>
+        <v>1861</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>1842</v>
+        <v>1862</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>1843</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1844</v>
+        <v>1864</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>52</v>
+        <v>1707</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>1707</v>
       </c>
       <c r="E44" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>1845</v>
+        <v>1865</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>1846</v>
+        <v>1866</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>1734</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1847</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>1848</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>1849</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>1850</v>
+        <v>1868</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>1851</v>
+        <v>1758</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>1852</v>
+        <v>1765</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>1853</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1854</v>
+        <v>1870</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D46" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>52</v>
+        <v>1707</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>1855</v>
+        <v>1804</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>1856</v>
+        <v>1765</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>1857</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29646,25 +30807,25 @@
         <v>18</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1858</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>1708</v>
+        <v>1871</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>1693</v>
+        <v>1872</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>1859</v>
+        <v>1873</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>1860</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29672,25 +30833,25 @@
         <v>18</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1861</v>
+        <v>1875</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>1708</v>
+        <v>1707</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E48" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>1693</v>
+        <v>1876</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>1862</v>
+        <v>1877</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29698,129 +30859,129 @@
         <v>18</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D49" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>1708</v>
+        <v>1878</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>1881</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>1699</v>
+        <v>1882</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>1700</v>
+        <v>1883</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>1734</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>52</v>
+        <v>1885</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>1707</v>
       </c>
       <c r="E50" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>1865</v>
+        <v>1886</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>1866</v>
+        <v>1887</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>1867</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>52</v>
+        <v>1889</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="E51" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>1737</v>
+        <v>1758</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>1869</v>
+        <v>1890</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>1734</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1870</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>1871</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>1872</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>1873</v>
+        <v>1892</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>1874</v>
+        <v>1758</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>1875</v>
+        <v>1893</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1876</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>52</v>
+        <v>1894</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>1877</v>
+        <v>1715</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1878</v>
+        <v>1765</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29828,25 +30989,25 @@
         <v>19</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1879</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>1708</v>
+        <v>1895</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>1880</v>
+        <v>52</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>1693</v>
+        <v>1896</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>1881</v>
+        <v>1897</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>1734</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29854,25 +31015,25 @@
         <v>19</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1882</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>1708</v>
+        <v>1899</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E55" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>1693</v>
+        <v>1768</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>1883</v>
+        <v>1900</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29880,36 +31041,36 @@
         <v>19</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>1884</v>
+        <v>1901</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>1885</v>
+        <v>1902</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>1885</v>
+        <v>1903</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>1886</v>
+        <v>1904</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>1693</v>
+        <v>1905</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>1887</v>
+        <v>1906</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>1888</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1889</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>52</v>
+        <v>1907</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>1707</v>
       </c>
       <c r="D57" s="16" t="s">
         <v>52</v>
@@ -29918,91 +31079,91 @@
         <v>52</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>1890</v>
+        <v>1908</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>1891</v>
+        <v>1909</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>1892</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>1893</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>52</v>
+        <v>1910</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>52</v>
+        <v>1911</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>1895</v>
+        <v>1758</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>1896</v>
+        <v>1912</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1897</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>52</v>
+        <v>1913</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="E59" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>1898</v>
+        <v>1758</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>1899</v>
+        <v>1914</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1900</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E60" s="16" t="s">
-        <v>52</v>
+        <v>1915</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>1917</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>1901</v>
+        <v>1758</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>1902</v>
+        <v>1918</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>1734</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30010,25 +31171,25 @@
         <v>20</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1903</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>1708</v>
+        <v>1920</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E61" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>1874</v>
+        <v>1921</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>1904</v>
+        <v>1922</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>1734</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30036,36 +31197,36 @@
         <v>20</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1905</v>
+        <v>1924</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>1906</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>1906</v>
+        <v>1925</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>1907</v>
+        <v>52</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>1908</v>
+        <v>1926</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>1909</v>
+        <v>1927</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>1910</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>1911</v>
+        <v>20</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1912</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>52</v>
+        <v>1928</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1925</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>52</v>
@@ -30074,675 +31235,779 @@
         <v>52</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>1699</v>
+        <v>1929</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>1913</v>
+        <v>1930</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>1911</v>
+        <v>20</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1914</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>1915</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>1916</v>
+        <v>1931</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>1917</v>
+        <v>52</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>1918</v>
+        <v>1932</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>1919</v>
+        <v>1933</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>1920</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>1911</v>
+        <v>20</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1921</v>
+        <v>1934</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>1922</v>
+        <v>1707</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>1762</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>1923</v>
+        <v>52</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>1773</v>
+        <v>1905</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>1924</v>
+        <v>1935</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>1911</v>
+        <v>20</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1925</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>1697</v>
+        <v>1936</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>1937</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>52</v>
+        <v>1938</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>1926</v>
+        <v>1939</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>1927</v>
+        <v>1940</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>1734</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>1911</v>
+        <v>1942</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1928</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>1697</v>
+        <v>1943</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>1929</v>
+        <v>52</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>1930</v>
+        <v>52</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>1693</v>
+        <v>1715</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>1778</v>
+        <v>1944</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>1911</v>
+        <v>1942</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1931</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>1708</v>
+        <v>1945</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>1947</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>52</v>
+        <v>1948</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>1699</v>
+        <v>1949</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>1932</v>
+        <v>1950</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>1734</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>1911</v>
+        <v>1942</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1933</v>
-      </c>
-      <c r="C69" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>1708</v>
+        <v>1952</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>1954</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>1737</v>
+        <v>1804</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>1934</v>
+        <v>1955</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
-        <v>1911</v>
+        <v>1942</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1935</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>1708</v>
+        <v>1956</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>1936</v>
+        <v>1957</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>1937</v>
+        <v>1958</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>1734</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="9" t="s">
-        <v>1911</v>
+        <v>1942</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1938</v>
+        <v>1959</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D71" s="17" t="s">
-        <v>1697</v>
+        <v>1707</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>1960</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>52</v>
+        <v>1961</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>1773</v>
+        <v>1758</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>1939</v>
+        <v>1809</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>1940</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>1715</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>1963</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="9" t="s">
         <v>1942</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>1943</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>1944</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>1945</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>1699</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>1946</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="19" t="s">
-        <v>1948</v>
-      </c>
-      <c r="B74" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C74" s="21" t="s">
-        <v>1949</v>
-      </c>
-      <c r="D74" s="22" t="s">
-        <v>1697</v>
-      </c>
-      <c r="F74" s="11" t="s">
-        <v>1950</v>
-      </c>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="8" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
-        <v>1572</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>1680</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>1681</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>1952</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>1953</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78" s="23" t="s">
-        <v>1955</v>
-      </c>
-      <c r="C78" s="24" t="s">
-        <v>1956</v>
-      </c>
-      <c r="D78" s="25" t="s">
-        <v>1957</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>1958</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>1959</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B79" s="23" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C79" s="24" t="s">
-        <v>1962</v>
-      </c>
-      <c r="D79" s="25" t="s">
-        <v>1963</v>
-      </c>
-      <c r="E79" s="4" t="s">
+      <c r="B73" s="4" t="s">
         <v>1964</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="C73" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>1768</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>1965</v>
       </c>
-      <c r="G79" s="4" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" s="23" t="s">
+      <c r="H73" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="9" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>1966</v>
       </c>
-      <c r="C80" s="24" t="s">
+      <c r="C74" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>1967</v>
       </c>
-      <c r="D80" s="25" t="s">
+      <c r="G74" s="4" t="s">
         <v>1968</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="H74" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="9" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>1969</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="C75" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>1970</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="H75" s="4" t="s">
         <v>1971</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B81" s="23" t="s">
+    <row r="76" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="C81" s="24" t="s">
+      <c r="B76" s="4" t="s">
         <v>1973</v>
       </c>
-      <c r="D81" s="25" t="s">
+      <c r="C76" s="4" t="s">
         <v>1974</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="D76" s="4" t="s">
         <v>1975</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="E76" s="4" t="s">
         <v>1976</v>
       </c>
-      <c r="G81" s="4" t="s">
-        <v>1971</v>
+      <c r="F76" s="4" t="s">
+        <v>1715</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>1977</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="19" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>1983</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>1984</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>1985</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="9" t="s">
-        <v>1802</v>
+        <v>13</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>1977</v>
+        <v>1986</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>1978</v>
+        <v>1987</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>1979</v>
+        <v>1988</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>1980</v>
+        <v>1989</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>1982</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>1984</v>
+        <v>1993</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>1985</v>
+        <v>1994</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>1986</v>
+        <v>1995</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>1987</v>
+        <v>1996</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>1988</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>1989</v>
+        <v>1998</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>1991</v>
+        <v>2000</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>1993</v>
+        <v>2002</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>1982</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="9" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="B85" s="23" t="s">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>1982</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>20</v>
+        <v>1833</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>1982</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="9" t="s">
-        <v>1911</v>
+        <v>17</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>2004</v>
+        <v>2015</v>
       </c>
       <c r="C87" s="24" t="s">
-        <v>2005</v>
+        <v>2016</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>2006</v>
+        <v>2017</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2007</v>
+        <v>2018</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2008</v>
+        <v>2019</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="8" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>2011</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>1680</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B88" s="23" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C88" s="24" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D88" s="25" t="s">
+        <v>2023</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>2024</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>2025</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" s="23" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C89" s="24" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D89" s="25" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>2029</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>2030</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B90" s="23" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C90" s="24" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D90" s="25" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>2035</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="9" t="s">
-        <v>2012</v>
+        <v>1942</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>2013</v>
+        <v>2036</v>
       </c>
       <c r="C91" s="24" t="s">
-        <v>2014</v>
+        <v>2037</v>
       </c>
       <c r="D91" s="25" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B92" s="23" t="s">
-        <v>2015</v>
-      </c>
-      <c r="C92" s="24" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D92" s="25" t="s">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="9" t="s">
-        <v>2018</v>
-      </c>
-      <c r="B93" s="23" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C93" s="24" t="s">
-        <v>2020</v>
-      </c>
-      <c r="D93" s="25" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="9" t="s">
-        <v>1100</v>
-      </c>
-      <c r="B94" s="23" t="s">
-        <v>2022</v>
-      </c>
-      <c r="C94" s="24" t="s">
-        <v>2023</v>
-      </c>
-      <c r="D94" s="25" t="s">
-        <v>2024</v>
+        <v>2038</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>2039</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>2040</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="8" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>1686</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="9" t="s">
-        <v>13</v>
+        <v>2044</v>
       </c>
       <c r="B95" s="23" t="s">
-        <v>2025</v>
+        <v>2045</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>2026</v>
+        <v>2046</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>2027</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="9" t="s">
-        <v>2028</v>
+        <v>124</v>
       </c>
       <c r="B96" s="23" t="s">
-        <v>2029</v>
+        <v>2047</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>2030</v>
+        <v>2048</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>2031</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="9" t="s">
-        <v>2032</v>
+        <v>2050</v>
       </c>
       <c r="B97" s="23" t="s">
-        <v>2033</v>
+        <v>2051</v>
       </c>
       <c r="C97" s="24" t="s">
-        <v>2034</v>
+        <v>2052</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>2035</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="9" t="s">
-        <v>2036</v>
+        <v>1100</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>2037</v>
+        <v>2054</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>2038</v>
+        <v>2055</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>2039</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="9" t="s">
-        <v>2040</v>
+        <v>13</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>2041</v>
+        <v>2057</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>2042</v>
+        <v>2058</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>2043</v>
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="9" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B100" s="23" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C100" s="24" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D100" s="25" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="9" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B101" s="23" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C101" s="24" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D101" s="25" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="9" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B102" s="23" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C102" s="24" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D102" s="25" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="9" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B103" s="23" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C103" s="24" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D103" s="25" t="s">
+        <v>2075</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="F74:H74"/>
+    <mergeCell ref="F78:H78"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30759,7 +32024,1356 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:H89"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>2099</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>2111</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>2129</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>2140</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>2141</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>2147</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>2151</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>2152</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>2153</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>2165</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>2170</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>2171</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>2177</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F30" s="24" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G30" s="25" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>2188</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>1722</v>
+      </c>
+      <c r="F32" s="24" t="s">
+        <v>2193</v>
+      </c>
+      <c r="G32" s="25" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>2196</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>2197</v>
+      </c>
+      <c r="G33" s="25" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="11" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>2204</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>2210</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>2211</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>2217</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>2218</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>2224</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>2225</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>2231</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>2239</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>2245</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>2246</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>2249</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>2253</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>2259</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>2260</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>2264</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>2265</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>2266</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>2267</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>2273</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>2286</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>2287</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>2293</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>2294</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>2300</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>2307</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>2319</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>2323</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>2325</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>2326</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>2331</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>2325</v>
+      </c>
+      <c r="F56" s="27" t="s">
+        <v>2332</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
+        <v>2334</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>2337</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>2338</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="11" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="28" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>2350</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>2356</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>2361</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="12" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+    </row>
+    <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="12" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+    </row>
+    <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="12" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+    </row>
+    <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="12" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+    </row>
+    <row r="71" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="12" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="8" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="29" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B75" s="30" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C75" s="30" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="29" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B76" s="30" t="s">
+        <v>2376</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="29" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C77" s="30" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="29" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B78" s="30" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C78" s="30" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="29" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B79" s="30" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="29" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B80" s="30" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C80" s="30" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="29" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B81" s="30" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C81" s="30" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="31" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="32" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B84" s="32"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="32"/>
+      <c r="F84" s="32"/>
+    </row>
+    <row r="85" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="32" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B85" s="32"/>
+      <c r="C85" s="32"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="32"/>
+      <c r="F85" s="32"/>
+    </row>
+    <row r="86" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="32" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B86" s="32"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="32"/>
+    </row>
+    <row r="87" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="32" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+    </row>
+    <row r="88" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="32" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+    </row>
+    <row r="89" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="32" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B89" s="32"/>
+      <c r="C89" s="32"/>
+      <c r="D89" s="32"/>
+      <c r="E89" s="32"/>
+      <c r="F89" s="32"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A89:F89"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -30771,201 +33385,211 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A1" s="33" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2045</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2046</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>2047</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>2048</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>2049</v>
+      <c r="B3" s="34" t="s">
+        <v>2401</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>2402</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>2403</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>2405</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>2050</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="D4" s="30" t="s">
+        <v>2406</v>
+      </c>
+      <c r="E4" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Laura Lopez")</f>
         <v>215</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>2051</v>
+      <c r="F4" s="30" t="s">
+        <v>2407</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="30" t="s">
         <v>1421</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="30" t="s">
         <v>1422</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="30" t="s">
         <v>1423</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>2052</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="D5" s="30" t="s">
+        <v>2408</v>
+      </c>
+      <c r="E5" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Ken Witzgall")</f>
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>2053</v>
+      <c r="F5" s="30" t="s">
+        <v>2409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="30" t="s">
         <v>1455</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="30" t="s">
         <v>1456</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="30" t="s">
         <v>1457</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>2054</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="D6" s="30" t="s">
+        <v>2410</v>
+      </c>
+      <c r="E6" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Scott Wood")</f>
         <v>2</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>2055</v>
+      <c r="F6" s="30" t="s">
+        <v>2411</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="30" t="s">
         <v>1471</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="30" t="s">
         <v>1472</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="30" t="s">
         <v>1457</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>2056</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="D7" s="30" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E7" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Jennifer Saxman")</f>
         <v>11</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>2057</v>
+      <c r="F7" s="30" t="s">
+        <v>2413</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>2058</v>
+      <c r="A9" s="31" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>2059</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="A10" s="32" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>2060</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="A11" s="32" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>2061</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="A12" s="32" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>2062</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+      <c r="A13" s="32" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>2063</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="A14" s="32" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>2064</v>
-      </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+      <c r="A15" s="32" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>2065</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="A16" s="32" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>2066</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="A17" s="32" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+    </row>
+    <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="32" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A12:F12"/>
@@ -30974,6 +33598,7 @@
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Cottage_Villa_Service_Benchmark.xlsx
+++ b/Cottage_Villa_Service_Benchmark.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6732" uniqueCount="2424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6739" uniqueCount="2431">
   <si>
     <t xml:space="preserve">Row ID</t>
   </si>
@@ -5193,7 +5193,7 @@
     <t xml:space="preserve">A la carte at a posted rate, with named destination hospitals inside the included area</t>
   </si>
   <si>
-    <t xml:space="preserve">No community published a mileage radius. The only real geographic rules found were a fee trigger ("There are charges for out of county rides"), a named-city limit ("Kalamazoo and Portage area") and a "standard route". Witzgall is the only source with prices.</t>
+    <t xml:space="preserve">Almost no community published a mileage radius. The one that did set it at 5 MILES for doctor appointments, half the figure in the source email. Other geographic rules found were a fee trigger ("There are charges for out of county rides"), a named-city limit ("Kalamazoo and Portage area") and a "standard route". Witzgall is the only source with prices.</t>
   </si>
   <si>
     <t xml:space="preserve">Consider defining a STANDARD ROUTE or a county rather than a radius. Both proved more workable in the market than a mileage line.</t>
@@ -5289,7 +5289,7 @@
     <t xml:space="preserve">Published, with guaranteed medical seats and third-party overflow at community cost</t>
   </si>
   <si>
-    <t xml:space="preserve">A COMPETITIVE OPPORTUNITY. Across ~50 communities, ONE published days of operation, ONE published a booking requirement, and NONE published hours, a lead time in days, a capacity rule, or wheelchair accessibility.</t>
+    <t xml:space="preserve">A COMPETITIVE OPPORTUNITY. Across ~50 communities, ONE published a radius (5 miles), ONE published a frequency schedule, ONE published days of the week, ONE published a booking requirement, and NONE published hours, a lead time in days, a capacity rule, or wheelchair accessibility.</t>
   </si>
   <si>
     <t xml:space="preserve">Publishing plain terms would differentiate on transparency alone, at no operating cost.</t>
@@ -6369,7 +6369,7 @@
     <t xml:space="preserve">Radius, hours, lead time, vehicle, fees. These live in resident handbooks and front-desk booklets that are rarely posted.</t>
   </si>
   <si>
-    <t xml:space="preserve">The bare "Transportation" in the villa study is not a gap in that document. It mirrors what the operators themselves publish. Across roughly 50 communities researched, not one published a mileage radius, a day-and-hour schedule, a booking lead time, a vehicle specification, a wheelchair-accessibility statement, or a per-trip dollar amount on a public page.</t>
+    <t xml:space="preserve">The bare "Transportation" in the villa study is not a gap in that document. It mirrors what the operators themselves publish. Across roughly 50 communities researched, exactly ONE published a mileage radius and ONE published an operating schedule (the same community, a sibling of an operator already in the study). None published a booking lead time in days, a vehicle specification, a wheelchair-accessibility statement, or a per-trip dollar amount.</t>
   </si>
   <si>
     <t xml:space="preserve">B. The five service models actually found behind the one word</t>
@@ -6534,7 +6534,7 @@
     <t xml:space="preserve">How far is included, and what happens beyond?</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT ONE of roughly 50 communities published a mileage radius. "Local", "nearby", "local and regional" are the universal unquantified terms. The only real geographic rules found were Ohio Living's fee trigger, "There are charges for out of county rides", Friendship Village Kalamazoo's named-city limit ("Kalamazoo and Portage area"), and Westminster Place's "standard route". The 10 to 15 mile figure is an industry norm quoted in third-party guidance, corroborated by Witzgall and Wood.</t>
+    <t xml:space="preserve">ALMOST NONE published a mileage radius. Exactly one did: a sibling property of an operator in this study publishes "complimentary transportation to and from doctor appointments within a 5 miles radius" — half the 10 miles reported by Witzgall and Wood. "Local", "nearby", "local and regional" are the universal unquantified terms. The only real geographic rules found were Ohio Living's fee trigger, "There are charges for out of county rides", Friendship Village Kalamazoo's named-city limit ("Kalamazoo and Portage area"), and Westminster Place's "standard route". The 10 to 15 mile figure is an industry norm quoted in third-party guidance, corroborated by Witzgall and Wood.</t>
   </si>
   <si>
     <t xml:space="preserve">Within ~10 miles; nothing beyond</t>
@@ -6570,7 +6570,7 @@
     <t xml:space="preserve">Which days does each trip type run, and what hours?</t>
   </si>
   <si>
-    <t xml:space="preserve">Almost never published. Highgrove at Tates Creek is the only community found stating days: "Monday through Friday as well as transportation to Sunday church services", implying no Saturday. Village at Bay Ridge runs groceries twice a week. Maple Knoll runs the grocery shuttle weekly. Friendship Village Kalamazoo says "weekly". Nobody published hours.</t>
+    <t xml:space="preserve">Almost never published. The fullest example found is a schedule structured BY TRIP PURPOSE: "a bus for medical appointments three days a week, a shuttle bus for shopping and other activities once a week, and group outings 2-3 times per month." Highgrove at Tates Creek is the only community found stating days of the week: "Monday through Friday as well as transportation to Sunday church services", implying no Saturday. Village at Bay Ridge runs groceries twice a week. Maple Knoll runs the grocery shuttle weekly. Friendship Village Kalamazoo says "weekly". Nobody published hours.</t>
   </si>
   <si>
     <t xml:space="preserve">Set days per purpose, weekdays only</t>
@@ -6679,6 +6679,27 @@
   </si>
   <si>
     <t xml:space="preserve">Why it matters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traditions at North Bend, Cincinnati, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traditions Management (sibling of four properties in this study)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE ONLY COMMUNITY FOUND TO PUBLISH BOTH A RADIUS AND A SCHEDULE. "complimentary transportation to and from doctor appointments within a 5 miles radius", plus "a weekly shopping trip in which transportation is provided and for all group outings". Frequency is structured by trip purpose: "a bus for medical appointments three days a week, a shuttle bus for shopping and other activities once a week, and group outings 2-3 times per month."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complimentary within the 5-mile radius. A sibling property, Reagan Park, adds a "pay-per-trip service for individually arranged destinations".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not stated. This community has independent living but the radius and schedule are described community-wide.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY (radius and frequency each recurred across two independently worded queries). One directory ALSO claims medical is free while shopping, worship and outings are fee-based, which inverts the market pattern AND contradicts the same page's own "weekly shopping trip in which transportation is provided" — treat that fee-inversion claim as UNRELIABLE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MOST OPERATIONALLY DETAILED FINDING IN THE RESEARCH. It shows the real published structure is FREQUENCY BY TRIP PURPOSE rather than one blanket promise, and that a radius as tight as 5 MILES is commercially viable — half the 10 miles reported by Witzgall and Wood.</t>
   </si>
   <si>
     <t xml:space="preserve">Cedarhurst of Frankfort, IL</t>
@@ -32024,7 +32045,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -32593,7 +32614,7 @@
       <c r="E38" s="4" t="s">
         <v>2210</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="18" t="s">
         <v>2211</v>
       </c>
       <c r="G38" s="4" t="s">
@@ -32639,7 +32660,7 @@
       <c r="E40" s="4" t="s">
         <v>2224</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="16" t="s">
         <v>2225</v>
       </c>
       <c r="G40" s="4" t="s">
@@ -32824,30 +32845,30 @@
         <v>2280</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>2274</v>
+        <v>2281</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2286</v>
-      </c>
-      <c r="F49" s="16" t="s">
         <v>2287</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>2281</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>2288</v>
@@ -32892,31 +32913,31 @@
       <c r="E51" s="4" t="s">
         <v>2300</v>
       </c>
-      <c r="F51" s="18" t="s">
-        <v>2274</v>
+      <c r="F51" s="16" t="s">
+        <v>2301</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>2307</v>
+        <v>2281</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>2308</v>
@@ -32939,53 +32960,53 @@
         <v>2313</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>2274</v>
+        <v>2314</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>2274</v>
+        <v>2281</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>2326</v>
+        <v>2281</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>2327</v>
@@ -33005,145 +33026,158 @@
         <v>2331</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2325</v>
-      </c>
-      <c r="F56" s="27" t="s">
         <v>2332</v>
       </c>
+      <c r="F56" s="18" t="s">
+        <v>2333</v>
+      </c>
       <c r="G56" s="4" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2338</v>
-      </c>
-      <c r="F57" s="18" t="s">
-        <v>2274</v>
+        <v>2332</v>
+      </c>
+      <c r="F57" s="27" t="s">
+        <v>2339</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2339</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="11" t="s">
         <v>2340</v>
       </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="s">
         <v>2341</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="28" t="s">
+      <c r="B58" s="4" t="s">
         <v>2342</v>
       </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="C58" s="4" t="s">
         <v>2343</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="D58" s="4" t="s">
         <v>2344</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="E58" s="4" t="s">
         <v>2345</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="F58" s="18" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>2346</v>
       </c>
-      <c r="E62" s="1" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="11" t="s">
         <v>2347</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="9" t="s">
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8" t="s">
         <v>2348</v>
       </c>
-      <c r="B63" s="4" t="s">
+    </row>
+    <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="28" t="s">
         <v>2349</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
         <v>2350</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="B63" s="1" t="s">
         <v>2351</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="C63" s="1" t="s">
         <v>2352</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>2353</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>2354</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="s">
-        <v>2363</v>
-      </c>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>2368</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>2369</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>2364</v>
+        <v>2370</v>
       </c>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -33153,7 +33187,7 @@
     </row>
     <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>2365</v>
+        <v>2371</v>
       </c>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -33163,7 +33197,7 @@
     </row>
     <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>2366</v>
+        <v>2372</v>
       </c>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
@@ -33173,7 +33207,7 @@
     </row>
     <row r="71" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>2367</v>
+        <v>2373</v>
       </c>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -33181,117 +33215,117 @@
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8" t="s">
-        <v>2368</v>
-      </c>
+    <row r="72" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="12" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>2369</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>2370</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>2371</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="29" t="s">
-        <v>2372</v>
-      </c>
-      <c r="B75" s="30" t="s">
-        <v>2373</v>
-      </c>
-      <c r="C75" s="30" t="s">
-        <v>2374</v>
+      <c r="A74" s="8" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>2378</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="29" t="s">
-        <v>2375</v>
+        <v>2379</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>2376</v>
+        <v>2380</v>
       </c>
       <c r="C76" s="30" t="s">
-        <v>2377</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="29" t="s">
-        <v>2378</v>
+        <v>2382</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>2379</v>
+        <v>2383</v>
       </c>
       <c r="C77" s="30" t="s">
-        <v>2380</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="29" t="s">
-        <v>2381</v>
+        <v>2385</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>2382</v>
+        <v>2386</v>
       </c>
       <c r="C78" s="30" t="s">
-        <v>2383</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="29" t="s">
-        <v>2384</v>
+        <v>2388</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>2385</v>
+        <v>2389</v>
       </c>
       <c r="C79" s="30" t="s">
-        <v>2386</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="29" t="s">
-        <v>2387</v>
+        <v>2391</v>
       </c>
       <c r="B80" s="30" t="s">
-        <v>2388</v>
+        <v>2392</v>
       </c>
       <c r="C80" s="30" t="s">
-        <v>2389</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="29" t="s">
-        <v>2390</v>
+        <v>2394</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>2391</v>
+        <v>2395</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>2392</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="31" t="s">
-        <v>2393</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="32" t="s">
-        <v>2394</v>
-      </c>
-      <c r="B84" s="32"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="32"/>
-      <c r="F84" s="32"/>
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="29" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B82" s="30" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="31" t="s">
+        <v>2400</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="32" t="s">
-        <v>2395</v>
+        <v>2401</v>
       </c>
       <c r="B85" s="32"/>
       <c r="C85" s="32"/>
@@ -33301,7 +33335,7 @@
     </row>
     <row r="86" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="32" t="s">
-        <v>2396</v>
+        <v>2402</v>
       </c>
       <c r="B86" s="32"/>
       <c r="C86" s="32"/>
@@ -33311,7 +33345,7 @@
     </row>
     <row r="87" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="32" t="s">
-        <v>2397</v>
+        <v>2403</v>
       </c>
       <c r="B87" s="32"/>
       <c r="C87" s="32"/>
@@ -33321,7 +33355,7 @@
     </row>
     <row r="88" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="32" t="s">
-        <v>2398</v>
+        <v>2404</v>
       </c>
       <c r="B88" s="32"/>
       <c r="C88" s="32"/>
@@ -33331,7 +33365,7 @@
     </row>
     <row r="89" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="32" t="s">
-        <v>2399</v>
+        <v>2405</v>
       </c>
       <c r="B89" s="32"/>
       <c r="C89" s="32"/>
@@ -33339,24 +33373,34 @@
       <c r="E89" s="32"/>
       <c r="F89" s="32"/>
     </row>
+    <row r="90" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="32" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B90" s="32"/>
+      <c r="C90" s="32"/>
+      <c r="D90" s="32"/>
+      <c r="E90" s="32"/>
+      <c r="F90" s="32"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A62:F62"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A86:F86"/>
     <mergeCell ref="A87:F87"/>
     <mergeCell ref="A88:F88"/>
     <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A90:F90"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -33386,7 +33430,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>2400</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33394,19 +33438,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>2401</v>
+        <v>2408</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>2402</v>
+        <v>2409</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>2403</v>
+        <v>2410</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>2404</v>
+        <v>2411</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>2405</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33420,14 +33464,14 @@
         <v>37</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>2406</v>
+        <v>2413</v>
       </c>
       <c r="E4" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Laura Lopez")</f>
         <v>215</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>2407</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33441,14 +33485,14 @@
         <v>1423</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>2408</v>
+        <v>2415</v>
       </c>
       <c r="E5" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Ken Witzgall")</f>
         <v>2</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>2409</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33462,14 +33506,14 @@
         <v>1457</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>2410</v>
+        <v>2417</v>
       </c>
       <c r="E6" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Scott Wood")</f>
         <v>2</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>2411</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33483,24 +33527,24 @@
         <v>1457</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>2412</v>
+        <v>2419</v>
       </c>
       <c r="E7" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Jennifer Saxman")</f>
         <v>11</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>2413</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>2414</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>2415</v>
+        <v>2422</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="32"/>
@@ -33510,7 +33554,7 @@
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>2416</v>
+        <v>2423</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="32"/>
@@ -33520,7 +33564,7 @@
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>2417</v>
+        <v>2424</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
@@ -33530,7 +33574,7 @@
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>2418</v>
+        <v>2425</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="32"/>
@@ -33540,7 +33584,7 @@
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>2419</v>
+        <v>2426</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="32"/>
@@ -33550,7 +33594,7 @@
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>2420</v>
+        <v>2427</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="32"/>
@@ -33560,7 +33604,7 @@
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>2421</v>
+        <v>2428</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="32"/>
@@ -33570,7 +33614,7 @@
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>2422</v>
+        <v>2429</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
@@ -33580,7 +33624,7 @@
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>2423</v>
+        <v>2430</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="32"/>

--- a/Cottage_Villa_Service_Benchmark.xlsx
+++ b/Cottage_Villa_Service_Benchmark.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6739" uniqueCount="2431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6746" uniqueCount="2433">
   <si>
     <t xml:space="preserve">Row ID</t>
   </si>
@@ -4518,7 +4518,7 @@
     <t xml:space="preserve">Dining, deep cleaning, pet care, carpet cleaning, handyman, home health/therapy</t>
   </si>
   <si>
-    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. VERIFIED IN RESEARCH (Frankfort is in ILLINOIS): Cedarhurst states its Cottages "operate separately from the Assisted Living and Memory Care neighborhoods and do not include the same all-inclusive services and amenities"; cottage residents get ACCESS TO the AL/MC transportation rather than an included benefit. "Available" was the right word.</t>
+    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. VERIFIED, BUT READ IN FULL (Frankfort is in ILLINOIS): Cedarhurst does state its Cottages "operate separately from the Assisted Living and Memory Care neighborhoods and do not include the same all-inclusive services and amenities" — but that disclaimer covers the all-inclusive package and the dining model, and the SAME pages state cottage residents "will have access to the activity programs, therapy services, and transportation options already available at" the main community. An earlier draft of this analysis treated Cedarhurst as the strongest evidence that cottages get less transportation; that reading was wrong and has been withdrawn.</t>
   </si>
   <si>
     <t xml:space="preserve">Our Lady of Angels – Duplex Cottages</t>
@@ -4668,7 +4668,7 @@
     <t xml:space="preserve">Meals, therapy, wellness and salon</t>
   </si>
   <si>
-    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. VERIFIED IN RESEARCH: the cottage inclusion list carries only "routine outings to local and regional events", while the separate IL apartment list carries "scheduled transportation". The cottage tier is genuinely lesser, and this label captured it correctly.</t>
+    <t xml:space="preserve">From Saxman benchmarking table of detached / separate homes. VERIFIED, WITH A CORRECTION: the cottage page's base inclusions contain NO transportation, while the IL apartment list names "scheduled transportation" — so this label captured a real difference. But "routine outings to local and regional events" appears on BOTH the cottage and apartment pages, so it is a shared campus amenity rather than a cottage substitute, and the community home page separately advertises free doctor-visit transportation with no tier qualifier.</t>
   </si>
   <si>
     <t xml:space="preserve">Highgrove at Tates Creek – Detached Cottages</t>
@@ -5157,7 +5157,7 @@
     <t xml:space="preserve">Included with outing, plus an annual outing credit</t>
   </si>
   <si>
-    <t xml:space="preserve">Garbry Ridge cottages get ONLY "routine outings to local and regional events" (verified); Laurel Lake runs courtesy trips to "the symphony, theater and regional attractions"; Swanhaven runs them as an activity programme</t>
+    <t xml:space="preserve">Verified at Garbry Ridge, whose cottage page lists "routine outings to local and regional events" — though note the same phrase also appears on its apartment page, so it is a shared amenity rather than a cottage substitute. Laurel Lake runs free courtesy trips to "the symphony, theater and regional attractions"; Swanhaven runs outings as an activity programme</t>
   </si>
   <si>
     <t xml:space="preserve">Cheapest way to make a detached neighbourhood feel connected. Ticket cost stays separate.</t>
@@ -5175,7 +5175,7 @@
     <t xml:space="preserve">Included, any day, with a stated dialysis and recurring-therapy policy</t>
   </si>
   <si>
-    <t xml:space="preserve">THE line operators actually draw. Garbry Ridge gives cottages outings but reserves "scheduled transportation" for apartments; New Perspective states it "does not provide transportation to appointments" and only helps coordinate a rideshare. DIALYSIS AND RECURRING THERAPY WERE NEVER MENTIONED BY ANY COMMUNITY RESEARCHED, despite being the heaviest real demand.</t>
+    <t xml:space="preserve">THE line operators actually draw, and it is drawn OPERATOR-WIDE rather than against cottages. New Perspective states it "does not provide transportation to appointments" and only helps coordinate a rideshare, for apartment residents as much as cottage residents. At Garbry Ridge the cottage inclusions list omits transportation while the apartment list names it, the one such case found. DIALYSIS AND RECURRING THERAPY WERE NEVER NAMED BY ANY COMMUNITY RESEARCHED, despite being the heaviest real demand.</t>
   </si>
   <si>
     <t xml:space="preserve">The key decision. Excluding it is defensible for residents who still drive, but it must be said plainly or they will assume otherwise.</t>
@@ -5193,7 +5193,7 @@
     <t xml:space="preserve">A la carte at a posted rate, with named destination hospitals inside the included area</t>
   </si>
   <si>
-    <t xml:space="preserve">Almost no community published a mileage radius. The one that did set it at 5 MILES for doctor appointments, half the figure in the source email. Other geographic rules found were a fee trigger ("There are charges for out of county rides"), a named-city limit ("Kalamazoo and Portage area") and a "standard route". Witzgall is the only source with prices.</t>
+    <t xml:space="preserve">NO COMMUNITY PUBLISHES A MILEAGE RADIUS. Two apparent exceptions were falsified on verification. Real boundaries are jurisdictional or vague: "There are charges for out of county rides" (verified), "local", a named-city limit, and one operator admitting to "a defined geographic area" without stating it. Witzgall is the only source in the project with prices.</t>
   </si>
   <si>
     <t xml:space="preserve">Consider defining a STANDARD ROUTE or a county rather than a radius. Both proved more workable in the market than a mileage line.</t>
@@ -5271,10 +5271,10 @@
     <t xml:space="preserve">Same service, with priority routing for the cottage neighbourhood</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT RELIABLE IN THE MARKET: of 9 detached-cottage communities, 3 give the same service, 2 explicitly give less, 4 do not say. Cedarhurst states its cottages "operate separately... and do not include the same all-inclusive services and amenities".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decide this deliberately and state it. It is the single most common ambiguity in the competitive set.</t>
+    <t xml:space="preserve">VERIFIED FINDING, REVERSED FROM AN EARLIER DRAFT: cottage residents generally get the SAME service as apartment residents, and occasionally BETTER (Zarrow Pointe villas get a private car and driver; apartments get a plain shuttle). Across seven communities there were ZERO verified cases of a lesser cottage tier. What varies is whether the operator states the terms at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parity is the market norm, so matching it is table stakes. The opportunity is to STATE the terms explicitly, which almost nobody does, or to differentiate upward as Zarrow Pointe does.</t>
   </si>
   <si>
     <t xml:space="preserve">Published service terms (days, hours, lead time, capacity rule)</t>
@@ -5289,7 +5289,7 @@
     <t xml:space="preserve">Published, with guaranteed medical seats and third-party overflow at community cost</t>
   </si>
   <si>
-    <t xml:space="preserve">A COMPETITIVE OPPORTUNITY. Across ~50 communities, ONE published a radius (5 miles), ONE published a frequency schedule, ONE published days of the week, ONE published a booking requirement, and NONE published hours, a lead time in days, a capacity rule, or wheelchair accessibility.</t>
+    <t xml:space="preserve">THE BIGGEST COMPETITIVE OPPORTUNITY IN THIS FUNCTION. After verification, across ~50 communities: ZERO published a mileage radius, ZERO published days of the week, ZERO published hours, ZERO published a booking lead time in hours, ZERO published a price for any paid tier, and ONE published a booking requirement ("You must sign up to go on the scheduled routes"). Wheelchair accessibility was claimed at exactly one community.</t>
   </si>
   <si>
     <t xml:space="preserve">Publishing plain terms would differentiate on transparency alone, at no operating cost.</t>
@@ -6030,10 +6030,10 @@
     <t xml:space="preserve">Better, plus a monthly allowance of personal on-demand trips, an on-campus circulator, escorted appointment service by arrangement, a stated dialysis and recurring-therapy policy, and concierge-booked airport runs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Deep-dive research across ~50 communities (see the Transportation Detail tab) found five distinct service models hiding behind the single word. The mainstream is two-tier: scheduled trips free, off-schedule trips paid. Cottage residents do NOT reliably get the same service as apartment residents, and where it differs the cottage tier is lesser. Dialysis was never mentioned by any community researched; wheelchair accessibility was confirmed at none.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Witzgall is the only source with prices: beyond-radius medical $2.50-$4.00/mile or $25-$50/trip; private car $30-$60/hr; airport $75-$150/trip. In the market, only one community published even a rate BASIS (per mile) and it withheld the rate. No community in the detached-cottage set published any transportation price.</t>
+    <t xml:space="preserve">Research across ~50 communities, then a verification pass, found five distinct service models behind the single word (see the Transportation Detail tab). The mainstream is two-tier: scheduled trips free, off-schedule trips paid, verified at four communities. Cottage residents generally get the SAME service as apartment residents and occasionally better; an earlier draft concluded the opposite and was withdrawn on verification. Dialysis was never named by any community; wheelchair accessibility was claimed at exactly one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witzgall is the only source in the project with prices: beyond-radius medical $2.50-$4.00/mile or $25-$50/trip; private car $30-$60/hr; airport $75-$150/trip. NOT ONE COMMUNITY IN THE MARKET RESEARCH PUBLISHED A DOLLAR RATE. Paid tiers are disclosed but priced only as "nominal", "a small fee", "for a fee", "at cost" or "flat fee", across at least three different mechanisms: per mile, flat fee, and an operator driver in an operator vehicle at an unstated rate.</t>
   </si>
   <si>
     <t xml:space="preserve">Witzgall; Wood; Saxman; Lopez; ~50-community web research</t>
@@ -6294,7 +6294,7 @@
     <t xml:space="preserve">Transportation — what the word actually means</t>
   </si>
   <si>
-    <t xml:space="preserve">The villa study lists transportation at 55 communities. All 55 entries say only "Transportation" or "Transportation services". This tab breaks that single word into the decisions it hides, records what the four sources and public marketing actually say, and converts it into a sharper Good / Better / Best specification. It was built from targeted web research across roughly 50 communities. READ SECTION F BEFORE QUOTING ANYTHING: community websites were unreachable from this environment, so findings come from search-result summaries, and several plausible-sounding details failed exact-phrase verification.</t>
+    <t xml:space="preserve">The villa study lists transportation at 55 communities. All 55 entries say only "Transportation" or "Transportation services". This tab breaks that word into the decisions it hides. It was built in two passes: a first research round across roughly 50 communities, then a VERIFICATION round that re-tested every important quote with exact-phrase and operator-domain-restricted probes. The verification round overturned several first-round findings, including the original headline. Where the two rounds disagree, the verified result is shown and the retraction is stated openly. Read Section F before quoting anything.</t>
   </si>
   <si>
     <t xml:space="preserve">A. How much detail each source actually gives</t>
@@ -6327,7 +6327,7 @@
     <t xml:space="preserve">Included: scheduled group shuttles for shopping and banking; medical transport within a 10-mile radius. Extra: beyond 10 miles ($2.50–$4.00/mile or $25–$50/trip), private on-demand car ($30–$60/hour), after-hours airport runs ($75–$150/trip).</t>
   </si>
   <si>
-    <t xml:space="preserve">Highest of the four; the only source with prices</t>
+    <t xml:space="preserve">Highest of the four, and the ONLY source anywhere in this project with actual prices</t>
   </si>
   <si>
     <t xml:space="preserve">Days, hours, booking lead time, vehicle type, capacity rules, how the radius is measured</t>
@@ -6360,19 +6360,19 @@
     <t xml:space="preserve">Public marketing and directories (this research)</t>
   </si>
   <si>
-    <t xml:space="preserve">Almost universally "scheduled transportation" for appointments, shopping and outings, and nothing more. The operators themselves publish essentially no operational detail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low, and highly repetitive across operators</t>
+    <t xml:space="preserve">Almost universally "scheduled transportation" and nothing more. Operators publish essentially no operational detail, and the directories that appear to supply it largely fabricate it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low, repetitive, and in places actively misleading</t>
   </si>
   <si>
     <t xml:space="preserve">Radius, hours, lead time, vehicle, fees. These live in resident handbooks and front-desk booklets that are rarely posted.</t>
   </si>
   <si>
-    <t xml:space="preserve">The bare "Transportation" in the villa study is not a gap in that document. It mirrors what the operators themselves publish. Across roughly 50 communities researched, exactly ONE published a mileage radius and ONE published an operating schedule (the same community, a sibling of an operator already in the study). None published a booking lead time in days, a vehicle specification, a wheelchair-accessibility statement, or a per-trip dollar amount.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B. The five service models actually found behind the one word</t>
+    <t xml:space="preserve">The bare "Transportation" in the villa study is not a gap in that document. It mirrors what the operators themselves publish. After a verification pass, the count of communities publishing a mileage radius is ZERO, publishing days of the week is ZERO, publishing a booking lead time in hours is ZERO, publishing a vehicle specification is effectively zero, and publishing a price for any paid tier is ZERO. Two apparent exceptions found in the first round were both traced to fabricated directory text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. The service models actually found behind the one word</t>
   </si>
   <si>
     <t xml:space="preserve">These are genuinely different products. Deciding which one to build is the real transportation decision.</t>
@@ -6390,7 +6390,7 @@
     <t xml:space="preserve">Cost structure</t>
   </si>
   <si>
-    <t xml:space="preserve">Communities found using it</t>
+    <t xml:space="preserve">Communities verified as using it</t>
   </si>
   <si>
     <t xml:space="preserve">Fit for a detached cottage product</t>
@@ -6405,25 +6405,25 @@
     <t xml:space="preserve">Included; no paid tier offered or published</t>
   </si>
   <si>
-    <t xml:space="preserve">Swanhaven Manor (the "complimentary Swanhaven Bus", trips to banks, groceries, shopping, restaurants; medical not named); American Senior Communities garden homes; Evergreen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good fit as a floor. Cheap, social, and matches residents who still drive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free scheduled trips plus a paid personal or chauffeur tier</t>
+    <t xml:space="preserve">Swanhaven Manor (the "complimentary Swanhaven Bus", trips to banks, groceries, shopping, restaurants; medical never named); American Senior Communities garden homes (one corporate sentence used verbatim at five properties)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good fit as a floor. Cheap, social, and matched to residents who still drive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free scheduled trips plus a paid personal tier</t>
   </si>
   <si>
     <t xml:space="preserve">The scheduled shuttle is free. Individual, off-schedule or longer trips are bought separately.</t>
   </si>
   <si>
-    <t xml:space="preserve">Two-tier and explicitly published</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maple Knoll Village (free campus shuttle and weekly grocery run vs a chauffeur at "a nominal per-mile fee"); Laurel Lake (free "weekly/monthly courtesy trips" vs "for a fee... a Laurel Lake driver"); South Franklin Circle ("included at no charge" vs "a small fee"); Westminster Place (complimentary on "the standard route" vs fee-based beyond it); Friendship Village of Dublin ("complimentary... within the local area... additional destinations may be accommodated at cost"); Discovery ("at cost... outside the regular schedule")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE MAINSTREAM MODEL and the natural Better tier. Four of eight Ohio communities published this split.</t>
+    <t xml:space="preserve">Two-tier, and disclosed as existing — but never priced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED AT FOUR communities: Maple Knoll ("a nominal per-mile fee" for a chauffeur who will take residents "anywhere they want to go"); Laurel Lake ("for a fee, residents may also engage the services of a Laurel Lake driver... using one of their fleet vehicles for personal trips"); South Franklin Circle ("offered with no charge... additional personal transportation is available for a small fee"); Ohio Living Breckenridge (charges out of county, flat-fee escorted service).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MAINSTREAM MODEL and the natural Better tier. Note it uses at least three different pricing mechanisms: per mile, flat fee, and operator-driver-and-vehicle at an unstated rate.</t>
   </si>
   <si>
     <t xml:space="preserve">Medical-only, high service level</t>
@@ -6435,13 +6435,13 @@
     <t xml:space="preserve">Included in the fee, but narrow in scope</t>
   </si>
   <si>
-    <t xml:space="preserve">Zarrow Pointe villas: "Private Car and Driver for Doctor Appointments" appears as a discrete line item in the villa inclusions. The apartments get plain "transportation to and from Doctor Appointments".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A premium, differentiating option. Note it is the ONE case found where the villa product gets a BETTER service than the apartments.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fee-for-service for everything</t>
+    <t xml:space="preserve">Zarrow Pointe villas: "Private Car and Driver for Doctor Appointments" appears as a discrete line item in the villa inclusions, in a list whose ordering was stable across four independent queries. The apartments get plain "Transportation to and from Doctor Appointments".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A premium, differentiating option, and the ONE verified case anywhere of a villa product getting a BETTER service than the apartments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee-for-service throughout</t>
   </si>
   <si>
     <t xml:space="preserve">Rides are a billable service, charged to the resident statement. Sign-up required. Geography priced rather than bounded.</t>
@@ -6450,25 +6450,25 @@
     <t xml:space="preserve">Chargeable throughout; rates published only in an in-house booklet</t>
   </si>
   <si>
-    <t xml:space="preserve">Ohio Living Breckenridge Village. Resident handbook: "There is a small fee for these services"; "There are charges for out of county rides"; "You must sign up to go on the scheduled routes"; and a branded escorted service, "Super Senior Transportation (SST)... An SST driver will escort you throughout your trip and business. There are flat fee charges." Directories wrongly describe this as covered by the monthly fee.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viable for a Good tier if positioned honestly. Its virtue is transparency; its risk is that "transportation" then cannot be marketed as included.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outings only, appointments explicitly excluded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group outings and events are covered. Medical and personal appointments are not provided at all; the community only helps coordinate a third-party ride.</t>
+    <t xml:space="preserve">Ohio Living Breckenridge Village. Handbook, all verified: "There is a small fee for these services"; "There are charges for out of county rides"; "You must sign up to go on the scheduled routes"; and a branded escorted service, "Super Senior Transportation (SST) is an escorted personal driver service with flat fee charges", for residents "who need assistance throughout the appointment". Directories wrongly describe this community as covering transportation in the monthly fee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viable for a Good tier if positioned honestly. Its virtue is transparency; its cost is that transportation then cannot be marketed as included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outings included, appointments excluded OPERATOR-WIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group outings and events are covered. Medical and personal appointments are not provided to anyone; the community only helps coordinate a third-party ride.</t>
   </si>
   <si>
     <t xml:space="preserve">Outings included; appointments are the resident's own cost</t>
   </si>
   <si>
-    <t xml:space="preserve">New Perspective Senior Living (Woodland Terrace of Danville) operator FAQ: "New Perspective does not provide transportation to appointments; however, they do have a community van that is used to transport residents to events outside of the community... there may be commercial transportation options available for medical or other appointments, such as ride sharing programs, that they can assist in coordinating." Garbry Ridge cottages likewise get only "routine outings to local and regional events".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defensible and cheap, and honest about what cottage residents actually need. But it is the model most likely to disappoint a resident who assumed "transportation" meant rides to the doctor.</t>
+    <t xml:space="preserve">New Perspective Senior Living, verified operator FAQ: "New Perspective does not provide transportation to appointments; however, they do have a community van that is used to transport residents to events outside of the community... there may be commercial transportation options available for medical or other appointments, such as ride sharing programs, that they can assist in coordinating."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defensible and cheap. CRUCIAL CORRECTION: this exclusion applies to apartments too. At its Danville community the cottage inclusion list separately names "accessible bus transportation", so cottage residents are not singled out.</t>
   </si>
   <si>
     <t xml:space="preserve">C. The ten attributes that define a transportation offering, and the decision on each</t>
@@ -6480,7 +6480,7 @@
     <t xml:space="preserve">The question to answer</t>
   </si>
   <si>
-    <t xml:space="preserve">What the research found</t>
+    <t xml:space="preserve">What the research found (after verification)</t>
   </si>
   <si>
     <t xml:space="preserve">GOOD</t>
@@ -6498,7 +6498,7 @@
     <t xml:space="preserve">Fixed-schedule group shuttle, individually scheduled appointment rides, or on-demand personal rides?</t>
   </si>
   <si>
-    <t xml:space="preserve">Two or three distinct services are normally bundled under one word. Maple Knoll is the clearest, separating an on-campus "Shuttle on Demand" from an off-campus "Chauffeur Service". Wyndemere is the only community found advertising "both scheduled and impromptu transportation".</t>
+    <t xml:space="preserve">Two or three distinct services are normally bundled under one word. Maple Knoll is the clearest, separating an on-campus "Shuttle on Demand" from an off-campus "Chauffeur Service". Ohio Living likewise runs campus loop buses separately from off-campus routes.</t>
   </si>
   <si>
     <t xml:space="preserve">Scheduled group shuttle only</t>
@@ -6516,7 +6516,7 @@
     <t xml:space="preserve">Which trips qualify? Medical, dialysis and therapy, groceries, shopping, banking, pharmacy, worship, group outings, personal errands, airport.</t>
   </si>
   <si>
-    <t xml:space="preserve">The one well-covered attribute. Medical appeared at 7 of 9 detached-cottage communities, shopping at 8 of 9. Banking appeared once, worship twice. DIALYSIS AND RECURRING THERAPY WERE NEVER MENTIONED by any community, despite being operationally the heaviest demand. Airport appeared only at Maple Knoll.</t>
+    <t xml:space="preserve">The one well-covered attribute. Medical and shopping are near-universal. Banking and worship appear occasionally. DIALYSIS AND RECURRING THERAPY WERE NEVER NAMED BY ANY COMMUNITY, despite being operationally the heaviest demand. Airport appeared twice in the whole study.</t>
   </si>
   <si>
     <t xml:space="preserve">Groceries, shopping, banking, group outings</t>
@@ -6534,16 +6534,16 @@
     <t xml:space="preserve">How far is included, and what happens beyond?</t>
   </si>
   <si>
-    <t xml:space="preserve">ALMOST NONE published a mileage radius. Exactly one did: a sibling property of an operator in this study publishes "complimentary transportation to and from doctor appointments within a 5 miles radius" — half the 10 miles reported by Witzgall and Wood. "Local", "nearby", "local and regional" are the universal unquantified terms. The only real geographic rules found were Ohio Living's fee trigger, "There are charges for out of county rides", Friendship Village Kalamazoo's named-city limit ("Kalamazoo and Portage area"), and Westminster Place's "standard route". The 10 to 15 mile figure is an industry norm quoted in third-party guidance, corroborated by Witzgall and Wood.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Within ~10 miles; nothing beyond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~10 miles included; beyond at a posted per-mile or per-trip rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~15 miles included; beyond at a posted rate, with named destination hospitals</t>
+    <t xml:space="preserve">NO COMMUNITY PUBLISHES A MILEAGE RADIUS. Both apparent exceptions found in round one were falsified in round two: a "5 mile radius" claim was absent from the operator's own domain, and a hospital named as a shuttle destination turned out not to exist. Real boundaries are JURISDICTIONAL or VAGUE: "There are charges for out of county rides" (verified), "local", and one operator's own admission of "a defined geographic area" without publishing it. The 10-to-15-mile figure is an industry norm from third-party guidance, corroborated only by Witzgall and Wood.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within a named county or a defined standard route; nothing beyond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That area included; beyond at a posted per-mile or per-trip rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A wider defined area, with named destination hospitals inside it</t>
   </si>
   <si>
     <t xml:space="preserve">Cost to the resident</t>
@@ -6552,13 +6552,13 @@
     <t xml:space="preserve">Free, bundled, or charged? Per trip, per mile, per hour, or monthly?</t>
   </si>
   <si>
-    <t xml:space="preserve">Scheduled local trips are usually included, but NOT always: Ohio Living charges and bills to the resident statement; Our Lady of Angels offered it "on a cost basis"; Cedarhurst excludes cottages from the all-inclusive rate. Only Maple Knoll published a rate BASIS (per mile) and even it withheld the rate. No community published an actual dollar figure. Witzgall is the only source in the study with prices.</t>
+    <t xml:space="preserve">Scheduled local trips are usually included, but NOT always: Ohio Living charges and bills to the resident statement. Where a paid tier exists it is consistently disclosed and consistently unpriced. NOT ONE COMMUNITY IN THE STUDY PUBLISHED A DOLLAR RATE. The universal vocabulary is "nominal", "small fee", "for a fee", "at cost", "flat fee". Witzgall remains the only source in the project with actual prices.</t>
   </si>
   <si>
     <t xml:space="preserve">Scheduled group trips included; nothing else offered</t>
   </si>
   <si>
-    <t xml:space="preserve">Scheduled included; unscheduled, private and out-of-radius at posted rates</t>
+    <t xml:space="preserve">Scheduled included; unscheduled, private and out-of-area at posted rates</t>
   </si>
   <si>
     <t xml:space="preserve">Scheduled included plus a monthly allowance of personal trips, then posted rates</t>
@@ -6570,13 +6570,13 @@
     <t xml:space="preserve">Which days does each trip type run, and what hours?</t>
   </si>
   <si>
-    <t xml:space="preserve">Almost never published. The fullest example found is a schedule structured BY TRIP PURPOSE: "a bus for medical appointments three days a week, a shuttle bus for shopping and other activities once a week, and group outings 2-3 times per month." Highgrove at Tates Creek is the only community found stating days of the week: "Monday through Friday as well as transportation to Sunday church services", implying no Saturday. Village at Bay Ridge runs groceries twice a week. Maple Knoll runs the grocery shuttle weekly. Friendship Village Kalamazoo says "weekly". Nobody published hours.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set days per purpose, weekdays only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set days per purpose, plus medical any weekday</t>
+    <t xml:space="preserve">NO COMMUNITY PUBLISHES DAYS OF THE WEEK OR HOURS. The one community reported in round one as publishing days was falsified in round two; that claim is withdrawn. The only frequency statements that survive are coarse: a weekly grocery run (Maple Knoll), "regularly scheduled weekly/monthly courtesy trips" (Laurel Lake) and "weekly" (Friendship Village Kalamazoo). Ohio Living keeps its route sheets on paper at the front desk, which is why no schedule is findable online.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set days per purpose, weekdays only, published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set days per purpose plus medical any weekday, published</t>
   </si>
   <si>
     <t xml:space="preserve">Extended days including some weekend coverage; after-hours at a posted rate</t>
@@ -6588,10 +6588,10 @@
     <t xml:space="preserve">How far ahead must a resident book, and through whom?</t>
   </si>
   <si>
-    <t xml:space="preserve">Essentially never published. Ohio Living is the only source found stating a requirement: "You must sign up to go on the scheduled routes", with "Bus Route sheets... available at the front desk". Robin Run qualifies door-to-door trips as "(pre-arranged)". Because nobody publishes it, this must be designed rather than inherited.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign-up sheet at the desk; several days notice</t>
+    <t xml:space="preserve">Essentially never published. Ohio Living is the only community with any booking language, and both halves are verified: "You must sign up to go on the scheduled routes", with route sheets at the front desk, and "Advance notice is very helpful to accommodate your transportation needs" — which is explicitly SOFT, with no fixed hour requirement anywhere. Because nobody publishes a rule, this must be designed rather than inherited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign-up sheet at the desk; a stated notice period</t>
   </si>
   <si>
     <t xml:space="preserve">Concierge booking, 24–48 hours notice, confirmation given</t>
@@ -6606,7 +6606,7 @@
     <t xml:space="preserve">What happens when demand exceeds the vehicle, and who gets priority?</t>
   </si>
   <si>
-    <t xml:space="preserve">Not published anywhere. A targeted search for "when space permits" style qualifiers across the detached-cottage set returned nothing, and the one detailed capacity claim this research initially found failed exact-phrase verification (see Section F). Kirkland Crossings' operator handbook is the nearest real language: outings "may be cancelled for reasons including... severe or inclement weather and lack of interest."</t>
+    <t xml:space="preserve">Not published anywhere. Targeted searching for "when space permits" style qualifiers across the detached-cottage set returned nothing, and the one detailed capacity claim round one found was falsified (see Section F). The nearest real language is an operator handbook warning that outings "may be cancelled for reasons including... severe or inclement weather and lack of interest".</t>
   </si>
   <si>
     <t xml:space="preserve">Space-permitting, medical prioritised, limits published</t>
@@ -6624,7 +6624,7 @@
     <t xml:space="preserve">Bus, van, or car? Wheelchair accessible? How many?</t>
   </si>
   <si>
-    <t xml:space="preserve">Rarely specified. Maple Knoll is the exception, quantifying "three full-time bus drivers" plus "a chauffeur for hire". Buses are named at Traditions at Beaumont, Primrose, Swanhaven and Laurel Lake. WHEELCHAIR ACCESSIBILITY WAS NOT CONFIRMED AT A SINGLE COMMUNITY, which is a notable gap given the resident profile.</t>
+    <t xml:space="preserve">Rarely specified, and a staffing count claimed in round one was falsified in round two. Buses are named at several communities; Laurel Lake's paid tier notably uses "one of their fleet vehicles", an operator-owned car with an operator-employed driver rather than a rideshare handoff. WHEELCHAIR ACCESSIBILITY WAS CLAIMED AT EXACTLY ONE COMMUNITY in the whole study, in a cottage inclusion list naming "accessible bus transportation". Everywhere else it is unstated, which is a striking gap given the resident profile.</t>
   </si>
   <si>
     <t xml:space="preserve">Shared van or bus, accessible</t>
@@ -6639,7 +6639,7 @@
     <t xml:space="preserve">Curb-to-curb, door-to-door, or escorted into the appointment?</t>
   </si>
   <si>
-    <t xml:space="preserve">A real and marketable distinction that almost nobody makes. Ohio Living sells it as a branded product: "Super Senior Transportation (SST) is an escorted personal driver service. An SST driver will escort you throughout your trip and business." Robin Run advertises "door-to-door services". Everyone else is silent.</t>
+    <t xml:space="preserve">A real, marketable distinction that almost nobody makes. Ohio Living sells it as a branded, flat-fee product: an "escorted personal driver service" for residents "who need assistance throughout the appointment". Robin Run advertises "door-to-door services". Everyone else is silent.</t>
   </si>
   <si>
     <t xml:space="preserve">Door-to-door with driver assistance</t>
@@ -6648,22 +6648,22 @@
     <t xml:space="preserve">Do detached-home residents get the same service as apartment residents?</t>
   </si>
   <si>
-    <t xml:space="preserve">THE MOST IMPORTANT FINDING. Not the same at several communities, and where it differs the cottage tier is LESSER. See Section E.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same as apartment residents; central pickup point</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same as apartment residents; pickup at the villa door</t>
+    <t xml:space="preserve">THE HEADLINE FINDING, AND IT REVERSED ON VERIFICATION. Cottage residents generally get the SAME service, occasionally better. See Section E.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as apartment residents, stated explicitly; central pickup point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same, with pickup at the villa door</t>
   </si>
   <si>
     <t xml:space="preserve">Same, plus priority routing for the cottage neighbourhood</t>
   </si>
   <si>
-    <t xml:space="preserve">D. Community evidence — what each operator actually publishes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidence: VERIFIED = the exact phrase was re-queried and the source page returned it. LIKELY = search summary, substance probably right, wording not safe to quote. UNRELIABLE = directory boilerplate or text that failed verification; do not use. Every row needs one confirming page load before external publication.</t>
+    <t xml:space="preserve">D. Community evidence, after verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED = an exact-phrase or operator-domain-restricted probe returned the operator's own page and reproduced the wording. LIKELY = reproduced consistently but not bindable by probe, often because the page is a PDF or a CMS page that is not phrase-indexed. FALSIFIED = the wording does not exist on the operator's site and appears only on directories. Even VERIFIED rows should get one confirming page load before external publication.</t>
   </si>
   <si>
     <t xml:space="preserve">Community</t>
@@ -6672,400 +6672,370 @@
     <t xml:space="preserve">Operator / villa product</t>
   </si>
   <si>
-    <t xml:space="preserve">What is published</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidence</t>
+    <t xml:space="preserve">What the operator actually publishes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
   </si>
   <si>
     <t xml:space="preserve">Why it matters</t>
   </si>
   <si>
-    <t xml:space="preserve">Traditions at North Bend, Cincinnati, OH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traditions Management (sibling of four properties in this study)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE ONLY COMMUNITY FOUND TO PUBLISH BOTH A RADIUS AND A SCHEDULE. "complimentary transportation to and from doctor appointments within a 5 miles radius", plus "a weekly shopping trip in which transportation is provided and for all group outings". Frequency is structured by trip purpose: "a bus for medical appointments three days a week, a shuttle bus for shopping and other activities once a week, and group outings 2-3 times per month."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complimentary within the 5-mile radius. A sibling property, Reagan Park, adds a "pay-per-trip service for individually arranged destinations".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not stated. This community has independent living but the radius and schedule are described community-wide.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY (radius and frequency each recurred across two independently worded queries). One directory ALSO claims medical is free while shopping, worship and outings are fee-based, which inverts the market pattern AND contradicts the same page's own "weekly shopping trip in which transportation is provided" — treat that fee-inversion claim as UNRELIABLE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE MOST OPERATIONALLY DETAILED FINDING IN THE RESEARCH. It shows the real published structure is FREQUENCY BY TRIP PURPOSE rather than one blanket promise, and that a radius as tight as 5 MILES is commercially viable — half the 10 miles reported by Witzgall and Wood.</t>
+    <t xml:space="preserve">Ohio Living Breckenridge Village, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohio Living; 73 Ranch Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident handbooks, all verified: campus loop buses plus off-campus scheduled routes; "You must sign up to go on the scheduled routes", with bus route sheets at the front desk; "Advance notice is very helpful to accommodate your transportation needs" (explicitly soft, no fixed hours); and "Super Senior Transportation (SST) is an escorted personal driver service with flat fee charges", for residents "who need assistance throughout the appointment". Geographic rule: "There are charges for out of county rides."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEE-FOR-SERVICE. "There is a small fee for these services"; rides billed to the resident statement; SST at flat fees. Rates live in a transportation booklet that "is available at the front desk", deliberately not online.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT PUBLISHED. Only four handbooks exist, all for apartment buildings. The 73 ranch homes have no handbook, so their terms are neither stated as the same nor as different. DO NOT ASSERT PARITY.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED (operator-domain probes recovered handbook text)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MOST IMPORTANT CORRECTION to the assumption that transportation is an included amenity, and the richest operational detail in the study. Directories describe this community as covering transportation in the monthly fee. The handbook says otherwise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maple Knoll Village, Cincinnati, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maple Knoll Communities; 142 villas, 135 apartments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two named services: "Shuttle on Demand", which is an ON-CAMPUS circulator, plus a weekly run to an area grocery store; and a "Chauffeur Service" covering "doctor appointments, the airport, and more", which will take residents "anywhere they want to go". Residents can also get assistance setting up transportation through Uber Health.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-tier, and the only PER-MILE basis found anywhere: the campus shuttle and weekly grocery run are "a free service"; the chauffeur carries "a nominal per-mile fee". The rate itself is unpublished.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong. Transportation sits on the independent living pages and the IL inventory is majority villa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED, with two round-one claims withdrawn: a "three full-time bus drivers" staffing count returned zero results and is removed, and Uber Health is a referral rather than brokering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The most sophisticated model found. The on-campus versus off-campus split is a real product distinction almost nobody else draws in writing, and it is the most relevant one for a spread-out cottage site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laurel Lake, Hudson, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Villas, 1,600–2,700+ sq ft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community FAQ: buses run "regularly scheduled weekly/monthly courtesy trips" and special events "like the symphony, theater and regional attractions". Additionally, "for a fee, residents may also engage the services of a Laurel Lake driver, using one of their fleet vehicles for personal trips."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-tier. Courtesy trips free on a fixed weekly/monthly schedule; the paid tier is an operator-employed driver in an operator-owned vehicle, which is a different instrument from a rideshare referral. Fee amount unpublished.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely but not explicit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED (the paid-tier sentence was the single strongest phrase match in the whole verification round)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only community treating CULTURAL EXCURSIONS as a distinct free service line, so its free tier is broader than a grocery-run model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Franklin Circle, Chagrin Falls, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judson Smart Living; 27 cottage homes, 16 garden homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exact operator wording: "Scheduled transportation services to scheduled, local trips/appointments are offered with no charge; additional personal transportation is available for a small fee."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean published two-tier. Fee amount not published. The qualifier "local" is doing real work and is undefined.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely, since pricing covers independent living as a whole, but not stated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED via operator-domain probe. Round one had the wording slightly wrong ("included at no charge"); the sentence above is the real one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cleanest one-sentence statement of the mainstream two-tier model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarrow Pointe, Tulsa, OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tulsa Jewish; The Villas (patio homes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Villas included-services list, with ordering stable across four independent queries: "Monthly Meal Allowance, Weekly Light Housekeeping, Weekly Flat Linen Service, Weekly Lawn Maintenance, Expanded Basic Cable, PRIVATE CAR AND DRIVER FOR DOCTOR APPOINTMENTS, Scheduled Activities and Cultural Events, Health and Wellness Programs, Personal Fitness Assessments." The Apartments list the parallel item as plain "Transportation to and from Doctor Appointments".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included, but narrow: doctor appointments only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BETTER THAN THE APARTMENTS. The only verified case anywhere of a villa product receiving an upgraded transportation tier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED (operator-domain probe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proves a detached product can differentiate UPWARD on transportation. A private car for medical days suits residents who still drive but want help when it matters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Village at Bay Ridge, Traverse City, MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heritage Senior Communities; cottage-style homes with garages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The Village at Bay Ridge offers a convenient and fun Bay Ridge Community bus to all residents at no additional cost. The community bus takes regularly scheduled trips to various destinations and many other destinations based on regular resident requests." Destinations include the beach, the Farmer's Market and downtown shops.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything free, including the request-driven trips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAME. "all residents" is unqualified and the community contains both cottage-style homes and apartments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED — the cleanest evidence in the whole study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE COUNTER-EXAMPLE to any assumption that unscheduled trips must be chargeable. Here the request-driven channel is free, which makes the paid tier an operator pricing choice rather than a sector rule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woodland Terrace of Danville, IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Perspective Senior Living; 50 cottage-style townhomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator FAQ: "New Perspective does not provide transportation to appointments; however, they do have a community van that is used to transport residents to events outside of the community. Additionally, there may be commercial transportation options available for medical or other appointments, such as ride sharing programs, that they can assist in coordinating." Separately, the Danville cottage inclusion list names "accessible bus transportation".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community outings included. Appointments not provided to anyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAME, once corrected. The appointment exclusion is OPERATOR-WIDE and applies to apartment residents equally; the cottage list separately names bus transportation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED, but REFRAMED. Round one treated this as a cottage limitation. It is not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only explicit SCOPE EXCLUSION found anywhere, and three directory sites flatly contradict it. Also the ONLY community in the entire study to claim an accessible vehicle.</t>
   </si>
   <si>
     <t xml:space="preserve">Cedarhurst of Frankfort, IL</t>
   </si>
   <si>
-    <t xml:space="preserve">Cedarhurst Senior Living; 32 cottages (opened 2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Cedarhurst Cottages operate separately from the Assisted Living and Memory Care neighborhoods and do not include the same all-inclusive services and amenities." Cottage residents get "access to the activity programs, therapy services, and transportation options already available at" the AL/MC community. "Scheduled transportation" sits on the APARTMENT inclusion list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cottages: not included in an all-inclusive rate. Apartments: included.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXPLICITLY LESSER. Cottages borrow the service rather than owning it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERIFIED (exact phrase re-queried; same disclaimer appears on Cedarhurst Topeka KS, Waterloo IL and Springfield IL, so it is corporate standard language for the Cottages line)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The strongest evidence in the research, and it explains why the benchmarking table could only say "Available" for this community. "Available" was the correct word.</t>
+    <t xml:space="preserve">Cedarhurst Senior Living; 32 independent living cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTH HALVES OF THE PARAGRAPH MATTER. First: "Cedarhurst Cottages operate separately from the Assisted Living and Memory Care neighborhoods and do not include the same all-inclusive services and amenities." But it continues, and a parallel sentence appears on cottage announcement pages in four locations with correct locality substitution: "Cottage residents will have access to the activity programs, therapy services, and TRANSPORTATION OPTIONS already available at Cedarhurst of [Frankfort]'s Assisted Living and Memory Care community."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Cedarhurst page prices transportation for cottages. The only priced extras named corporately are higher levels of care, salon services, pet accommodations and a one-time community fee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEUTRAL, arguably PARITY. The disclaimer is about the all-inclusive package and the dining model, NOT about transportation, which the same pages affirmatively grant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED for the disclaimer; LIKELY for the transportation-access sentence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUND ONE READ THIS COMMUNITY AGAINST ITS OWN TEXT and made it the strongest evidence for a lesser cottage tier. It is not that. This correction is the main reason the headline reversed.</t>
   </si>
   <si>
     <t xml:space="preserve">Garbry Ridge, Piqua, OH</t>
   </si>
   <si>
-    <t xml:space="preserve">HCF Management; cottages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTTAGE inclusions list carries only "routine outings to local and regional events" (alongside utilities, lawn care, landscaping, snow removal, 24-hour emergency call). The IL APARTMENT services list separately carries "scheduled transportation". An apartment-level extra-cost menu adds "special life enrichment events or outings" and "personal shopping services".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included items versus a separately priced menu. No prices published.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXPLICITLY LESSER, and the mechanism is visible: cottages get GROUP OUTINGS, apartments get INDIVIDUAL SCHEDULED RIDES.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERIFIED (exact phrase re-queried)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shows exactly how an operator scales the service down for detached homes, on the assumption those residents still drive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarrow Pointe, Tulsa, OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tulsa Jewish; The Villas (patio homes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Villas included-services list contains a discrete line item: "Private Car and Driver for Doctor Appointments", alongside Monthly Meal Allowance, Weekly Light Housekeeping, Weekly Flat Linen Service. The Apartments get the parallel item as plain "transportation to and from Doctor Appointments".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included, but narrow: doctor appointments only. Shopping, groceries, banking and errands are not listed as included for villas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BETTER THAN APARTMENTS. The only case found anywhere where the villa product gets an upgraded service tier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY-HIGH (structured inclusions list plus a villa brochure PDF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proves a detached product can differentiate upward on transportation, not just downward.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ohio Living Breckenridge Village, OH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ohio Living; 73 Ranch Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident handbooks describe three services: campus loop buses; off-campus scheduled routes where "You must sign up to go on the scheduled routes" and "Bus Route sheets are available at the front desk"; and "Super Senior Transportation (SST)... an escorted personal driver service. An SST driver will escort you throughout your trip and business." Also "There are charges for out of county rides."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEE-FOR-SERVICE. "There is a small fee for these services"; rides "can be charged to the resident's statement"; SST carries "flat fee charges". Rates are in a front-desk booklet, not online.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNCONFIRMED. The three handbooks found are building-specific (apartments and brownstones). No ranch-home handbook was located.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY-HIGH on the handbook mechanics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE MOST IMPORTANT CORRECTION to the assumption that transportation is an included amenity. Directories describe this community as covering transportation in the monthly fee. The handbook says otherwise.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Woodland Terrace of Danville, IN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Perspective Senior Living; 50 cottage-style townhomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operator FAQ: "New Perspective does not provide transportation to appointments; however, they do have a community van that is used to transport residents to events outside of the community. In addition, there may be commercial transportation options available for medical or other appointments, such as ride sharing programs, that they can assist in coordinating."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Community outings included. Appointments not provided at all. "Some off-site transportation may incur extra fees."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not stated for the cottages.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY-HIGH (returned near-identically across two independent queries)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The only explicit SCOPE EXCLUSION found anywhere, and three directory sites flatly contradict it by claiming the community provides rides to doctor visits. Proof that directory transportation flags cannot be trusted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maple Knoll Village, Cincinnati, OH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maple Knoll Communities; 142 villas, 135 apartments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two named services: "Shuttle on Demand" for on-campus circulation plus "weekly to an area grocery store", and "Chauffeur Service" for "doctor appointments, the airport, and more". Staffing quantified as "three full-time bus drivers" plus "a chauffeur for hire". Also brokers Uber Health.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two-tier and the only PER-MILE basis found: campus shuttle and weekly grocery run are "a free service"; the chauffeur carries "a nominal per-mile fee". The rate itself is unpublished.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong. Transportation sits on the independent living pages and the IL inventory is majority villa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY-HIGH (distinctive language, clearly community-authored)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The most sophisticated model found. The on-campus versus off-campus split is a real product distinction almost nobody else draws in writing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laurel Lake, Hudson, OH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Villas, 1,600–2,700+ sq ft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Community FAQ: "Laurel Lake buses provide transportation for regularly scheduled weekly/monthly courtesy trips and special events like the symphony, theater and regional attractions. Additionally, for a fee, residents may also engage the services of a Laurel Lake driver."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two-tier. Courtesy trips free on a fixed weekly/monthly schedule; personal driver "for a fee", amount unpublished.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likely but not explicit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY-HIGH (first-party FAQ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The only community treating CULTURAL EXCURSIONS as a distinct service line from errands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Franklin Circle, Chagrin Falls, OH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Judson Smart Living; 27 cottage homes, 16 garden homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Scheduled transportation services to local trips and appointments are included at no charge; additional personal transportation is available for a small fee."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean published two-tier. Fee amount not published.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likely, since pricing covers independent living as a whole, but not stated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY (first-party amenities and FAQ pages)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The cleanest one-sentence statement of the mainstream two-tier model.</t>
+    <t xml:space="preserve">HCF Management; 1,200 sq ft cottages, 2 bed / 2 bath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cottage page carries TWO lists. Base inclusions with the cottage: utilities, "Lawn care, landscaping and snow removal", "24 hour emergency call system" — WITH NO TRANSPORTATION OF ANY KIND. A second list of services available includes "routine outings to local and regional events". The independent living APARTMENT list separately contains "scheduled transportation". But the community HOME PAGE states, without any tier qualifier, that it "provides free transportation for doctor visits".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included items versus a separately available list. No prices published.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE ONE REMAINING CASE where a cottage list omits what an apartment list names. Narrower than round one claimed, and partly undercut by the home page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED for the cottage list and the home-page sentence; LIKELY for the apartment list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round one framed this as cottages getting outings INSTEAD OF transportation. That is wrong: "routine outings" appears on BOTH the cottage and apartment pages, so it is a shared campus amenity. The honest formulation is that the cottage inclusions omit transportation while the apartment inclusions name it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamilton Trace, Fishers, IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CarDon &amp; Associates; The Reserve cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Unscheduled transportation" is genuine CarDon site language, appearing in a services list alongside "guest meals, personal laundry service, personal concierge service, beauty salon/barber services". It is CarDon corporate boilerplate used at roughly eight communities. Also: "Both apartment and cottage residences at The Reserve include the use of all amenities."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE EXTRA-COST LABEL IS NOT VERIFIED. No CarDon page states that unscheduled transportation is chargeable; one rendering puts scheduled and unscheduled transportation in the SAME list; no price appears anywhere, including in CarDon's independent living FAQ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAME. Cottages differ by structure and payment plan only. No cottage-specific transportation carve-out exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIXED: the menu item is VERIFIED; the extra-cost inference is NOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The benchmarking table's "unscheduled transportation is à la carte" is half right. The item is real; its price status is an unverified inference that needs a phone call. The whole scheduled-free / unscheduled-paid thesis leans on this more than the evidence supports.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith Crossing, Orland Park, IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith Senior Living; free-standing Villas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The monthly fee is all-inclusive, including all utilities, maintenance, housekeeping, dining plan, activities, amenities and scheduled transportation." Product confirmed: "You can select an elegant, free-standing Villa or a spacious one- or two-bedroom condo-style senior-living apartment."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included in an all-inclusive monthly fee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAME. The all-inclusive statement is scoped to Independent Living as a whole, covering villas and apartments alike.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY (reproduced across four queries; the long string is not phrase-indexed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The clearest bundled model. Its resident handbook has a Transportation section at page 33 that search could not surface, making it the single highest-value document to retrieve.</t>
   </si>
   <si>
     <t xml:space="preserve">Westminster Place, Evanston, IL</t>
   </si>
   <si>
-    <t xml:space="preserve">Presbyterian Homes; 104 cottages and townhouses, 40 acres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Complimentary shuttles run to nearby physician offices, Northwestern Memorial Hospital-Evanston, grocery stores, and community events; fee-based transport can be arranged for individual appointments beyond the standard route."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two-tier, defined by a "standard route" rather than a radius.</t>
+    <t xml:space="preserve">Presbyterian Homes; 104 cottages and townhouses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual operator wording: "scheduled transportation to shops, appointments, and other necessary places", named inside the comprehensive monthly fee. NO paid tier appears anywhere on the operator's site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included in the monthly fee. No two-tier structure documented by the operator.</t>
   </si>
   <si>
     <t xml:space="preserve">Not differentiated, despite 104 cottages on a 40-acre campus.</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKELY (recurred identically across two independent queries)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The "standard route" is the closest thing to a defined geographic structure found, and a practical alternative to a mileage radius.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Village at Bay Ridge, Traverse City, MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heritage Senior Communities; cottage-style homes with garages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"The Village at Bay Ridge offers a convenient and fun Bay Ridge Community bus to all residents at no additional cost. The community bus takes regularly scheduled trips to various destinations, with many other destinations based on regular resident requests." Groceries twice a week; also doctor trips, the beach, the Farmer's Market.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everything free, including the request-driven trips.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAME — "to all residents" explicitly covers cottage and apartment residents alike.</t>
+    <t xml:space="preserve">ROUND-ONE QUOTE FALSIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The round-one quote about fee-based transport "beyond the standard route" to "Northwestern Memorial Hospital-Evanston" was directory text. NO SUCH HOSPITAL EXISTS — the Evanston hospital is Endeavor Health Evanston Hospital, while Northwestern Memorial is a separate downtown Chicago institution. A plausible name fused from two real ones is a textbook fabrication signature. This community no longer supports the two-tier finding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friendship Village of Dublin, OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life Care Services; River Point Villas and detached villas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual operator wording: "Using their fleet of licensed and insured vehicles, the transportation team takes residents to and from appointments, to the grocery store, on FVD field trips and to other activities organized by the Community Life department." Separately the site acknowledges "transportation to off-site medical appointments within a defined geographic area", without publishing the area.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bundled into the single LifeCare monthly fee. No paid off-schedule tier documented by the operator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not differentiated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUND-ONE QUOTES FALSIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both round-one quotes came from all-directory result sets and read as the generic "Complimentary Transportation / Transportation at Cost" checkbox pair rendered into prose. This community no longer supports the two-tier finding either. Note the operator DOES admit a geographic boundary exists while declining to state it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Senior Communities (5 properties)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zionsville, Brownsburg, Coventry, Rosegate, Beech Grove; Garden Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE SENTENCE USED VERBATIM ACROSS ALL FIVE: "Garden Home residents enjoy the company of their neighbors and opportunities to participate in a wide range of planned social activities, scheduled transportation to shopping, restaurants and appointments."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Free, scheduled transportation" and "complimentary" — marketing register, no fee schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES, named. The benefit attaches to "Garden Home residents" by name at all five.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED (exact-phrase probe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASC transportation is ONE corporate promise replicated five times, not five benchmarks. Treating the five as five data points double-counts. The trip list is also notably narrow and omits medical-first framing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traditions Management (4 properties)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brookside, Reagan Park, Beaumont, Hunter Station; Garden Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A two-tier asymmetry in templated corporate copy: garden homes get the bare noun, "...and transportation", while assisted living and memory care get a defined service, "scheduled transportation to medical appointments and outings". Hunter Station names transportation as a line item in the villa inclusion list; Beaumont extends it to independent living by name and mentions "a community bus... to scheduled weekly activities".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not published at any of the four.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIXED. Explicit at Hunter Station, named for IL at Beaumont, undefined at Brookside and Reagan Park.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY (the templating itself was confirmed by probe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traditions describes WHAT transportation does only for its higher-acuity tiers. For villa residents it lists the word and stops, which is the same flattening the villa study inherited. A separate probe of a sibling property produced an apparent 5-mile radius and weekly schedule that the operator's own domain did NOT confirm; that claim has been withdrawn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLC Management (2 properties)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Village at Hamilton Pointe; Village of Avon; garden homes and cottages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSPORTATION IS ABSENT FROM BOTH COMMUNITIES' OWN SITES. Services are "included in the monthly rent" but transportation is not among the enumerated inclusions. A third party describes only "setting up rides for doctor visits". At Avon, transportation appears on-site only as an ADMISSION CRITERION, describing what residents must be able to do independently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not established.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT FOUND. Should be logged as unverified, not as included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY on the absence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordination is not provision. If a community only helps book a ride, recording "Transportation: included" in a benchmark materially overstates the benefit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swanhaven Manor, Saginaw, MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottages with attached garages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"regularly scheduled shopping trips in the complimentary Swanhaven Bus", with an Activity Coordinator planning trips to "banks, grocery stores, shopping centers, and favorite restaurants".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complimentary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not found.</t>
   </si>
   <si>
     <t xml:space="preserve">LIKELY</t>
   </si>
   <si>
-    <t xml:space="preserve">THE COUNTER-EXAMPLE. Here the unscheduled, request-driven channel is also free, which disproves any assumption that scheduled-free and unscheduled-paid is a universal convention.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith Crossing, Orland Park, IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith Senior Living; free-standing villas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"The monthly fee is all-inclusive, including all utilities, maintenance, housekeeping, dining plan, activities, amenities and scheduled transportation." Trips go to "local appointments, shopping, and community events".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included in an all-inclusive monthly fee.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAME. Villas and apartments are both independent living under one fee.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The clearest example of the bundled not-for-profit model, and the community the benchmarking table already flags as the heavily bundled end of the spectrum.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highgrove at Tates Creek, Lexington, KY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 single-level cottages (duplexes and quads, not fully detached)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Highgrove residents ride in style! We offer scheduled transportation for shopping..." Separately: "scheduled transportation services Monday through Friday as well as transportation to Sunday church services."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Complimentary" claimed, but only in directory boilerplate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not found. Transportation does not appear on the cottage page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERIFIED for the opening phrase; LIKELY for the days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE ONLY COMMUNITY IN THE ENTIRE RESEARCH THAT PUBLISHES DAYS OF OPERATION. Monday to Friday plus Sunday worship implies no Saturday service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Senior Communities (5 properties)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zionsville, Brownsburg, Coventry, Rosegate, Beech Grove Meadows; Garden Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE SENTENCE USED VERBATIM ACROSS ALL FIVE: "Garden Home residents enjoy the company of their neighbors and opportunities to participate in a wide range of planned social activities, scheduled transportation to shopping, restaurants and appointments."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Free, scheduled transportation" and "complimentary" — marketing register, no fee schedule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES, named. The benefit is attached to "Garden Home residents" by name at all five.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERIFIED (exact-phrase probe returned the pages)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASC transportation is ONE corporate promise replicated five times, not five data points. Treating the five as five benchmarks double-counts. Note the trip list is narrow and omits medical-first framing entirely.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traditions Management (4 properties)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brookside, Reagan Park, Beaumont, Hunter Station; Garden Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A two-tier asymmetry in identical corporate copy: garden homes get the bare noun, "...utilities and full access to dining, amenities, social activities and events and transportation". AL and memory care get a defined service, "...scheduled transportation to medical appointments and outings". Hunter Station is the exception, naming transportation as a line item in the villa inclusion list. Beaumont is the only one extending it to independent living by name, with "a community bus... to scheduled weekly activities".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not published at any of the four.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIXED. Explicit at Hunter Station, named for IL at Beaumont, undefined at Brookside and Reagan Park.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traditions describes WHAT transportation does only for its higher-acuity tiers. For villa residents it lists the word and stops — the same flattening the villa study inherited.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLC Management (2 properties)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Village at Hamilton Pointe; Village of Avon; garden homes and cottages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRANSPORTATION IS ABSENT FROM BOTH COMMUNITIES' OWN SITES. Services are "included in the monthly rent" but transportation is not among the enumerated inclusions. A third party describes only "setting up rides for doctor visits". At Avon, transportation appears on-site only as an ADMISSION CRITERION, describing what residents must do independently.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not established.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT FOUND. Should be logged as unverified, not as included.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY on the absence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordination is not provision. If a community only helps book a ride, "Transportation: included" in a benchmark overstates the benefit considerably.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country Club at Woodland Hills, Tulsa, OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discovery Senior Living; cottages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discovery brands the programme "Connections Transportation" and lists it on the cottage pages. "complimentary, scheduled Connections transportation"; "scheduled bus and sedan transportation (where available)". Brand level: "Individualized or same-day trips can be arranged at cost for those who need transportation outside the regular schedule."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two-tier, drawn at SCHEDULED versus OFF-SCHEDULE rather than by distance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, apparently. Connections Transportation is listed on the cottage-living pages.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directly relevant to the 10-mile radius claim in the source email. See the note below Section D.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friendship Village Kalamazoo, MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life Care Services; Garden Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"weekly transportation to medical and financial appointments in Kalamazoo and Portage area" and "weekly transportation to shopping, churches, etc."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included; no paid tier found.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not differentiated: "Independent-living residents choose from apartments or garden homes and have access to... scheduled transportation."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The only NAMED-CITY geographic limit found, and one of the few frequency statements ("weekly").</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swanhaven Manor, Saginaw, MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cottages with attached garages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"regularly scheduled shopping trips in the complimentary Swanhaven Bus", with an Activity Coordinator planning trips to "banks, grocery stores, shopping centers, and favorite restaurants".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complimentary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not found.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY (the branded vehicle name suggests community-authored copy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The ONLY community where MEDICAL APPOINTMENTS ARE NOT NAMED at all. Transportation here is run as an activity programme, not a medical-transport function.</t>
+    <t xml:space="preserve">The ONLY community where MEDICAL APPOINTMENTS ARE NEVER NAMED. Transportation here is run as an activity programme, not a medical-transport function.</t>
   </si>
   <si>
     <t xml:space="preserve">Our Lady of Angels, Joliet, IL</t>
@@ -7080,7 +7050,7 @@
     <t xml:space="preserve">Chargeable, not included.</t>
   </si>
   <si>
-    <t xml:space="preserve">UNRELIABLE (directory boilerplate) — and note the community CLOSED IN JANUARY 2023</t>
+    <t xml:space="preserve">UNRELIABLE (directory boilerplate), and the community CLOSED IN JANUARY 2023</t>
   </si>
   <si>
     <t xml:space="preserve">Two data-quality flags for the benchmarking table: the community is closed, and the "Not provided" label is probably shorthand for "not included in the fee" rather than "did not exist".</t>
@@ -7098,94 +7068,130 @@
     <t xml:space="preserve">Marketing says complimentary; the handbook reserves the right to charge.</t>
   </si>
   <si>
-    <t xml:space="preserve">Not differentiated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE GAP BETWEEN MARKETING AND HANDBOOK IS ITSELF THE FINDING, and it is the best available language on cancellation and capacity risk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On the 10-mile radius in the source email: dedicated and domain-restricted searches across Discovery Senior Living's brands found NO published mileage limit on any Discovery transportation page, and neither Oklahoma Discovery-family community states one. What Discovery standardises is the programme name and a scheduled-versus-off-schedule cost split. The 10-mile figure is most likely real as LOCAL PRACTICE at that community, and it is consistent with the 10 to 15 mile industry norm, but it should not be attributed to Discovery as a brand standard or extrapolated to other Discovery communities. This is an absence-of-evidence finding built on search indexing, since no Discovery page could be opened.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E. The question that matters most — do cottage residents get the same transportation?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Answer: not reliably, and where it differs the cottage tier is LESSER. Of nine detached-cottage communities researched, three give cottage residents the same service, two explicitly give them less, and four do not say. The split tracks OPERATING MODEL, not geography or price point.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How transportation is treated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What cottage residents get</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implication for this product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not-for-profit CCRC / Life Plan Community with one all-inclusive fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transportation is bundled into a single monthly fee that covers every independent living housing type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE SAME as apartment residents. The detached home is a FLOOR PLAN CHOICE within one service tier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith Crossing; Robin Run Village; Village at Bay Ridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the cottages sit inside one independent living fee, transportation can honestly be marketed as included, and it costs what it costs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For-profit operator adding cottages to an existing licensed building</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The cottages are a separate rental product that BORROWS campus services rather than owning them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LESS. Cottages get access to, or a social-outings subset of, the main community's service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cedarhurst of Frankfort ("operate separately... do not include the same all-inclusive services and amenities"); Garbry Ridge (cottages get "routine outings"; apartments get "scheduled transportation")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the cottages are a distinct rental product, transportation becomes an à la carte or access-only benefit, and the marketing must say so.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa product positioned ABOVE the apartments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transportation is upgraded for the detached product rather than scaled down.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORE. A private car and driver rather than a shared shuttle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarrow Pointe ("Private Car and Driver for Doctor Appointments" for villas; plain "transportation" for apartments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The differentiating option. Narrow scope, high perceived service level, and it suits residents who still drive but want help on medical days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• The operating model, not the site plan, determines whether cottage residents can be told transportation is included. Cedarhurst is the template for the unbundled approach; Smith Crossing is the template for the bundled one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Garbry Ridge shows the mechanism precisely: cottage residents are offered GROUP SOCIAL OUTINGS, a lifestyle amenity, while apartment residents get INDIVIDUAL SCHEDULED RIDES, a care-adjacent service. That is exactly what an operator designs when it assumes cottage buyers still have car keys.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Detached-home residents mostly still drive. Garages are a headline feature of nearly every villa product in the study, and public guidance notes that residents commonly keep a car and mix driving with the shuttle. A heavy individual-ride benefit may be poorly matched to actual demand at the Good tier.</t>
+    <t xml:space="preserve">THE GAP BETWEEN MARKETING AND HANDBOOK IS ITSELF THE FINDING, and this is the best available language anywhere on cancellation and capacity risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the 10-mile radius in the source email: dedicated and domain-restricted searches across Discovery Senior Living's brands found NO published mileage limit on any Discovery transportation page. What Discovery standardises is a programme name, "Connections Transportation", and a scheduled-versus-off-schedule cost split, not a distance. The 10-mile figure is most likely real as local practice at that one community and consistent with the industry norm, but it should not be attributed to Discovery as a brand standard or extrapolated. A separate 5-mile radius found at a Traditions sibling property was also absent from that operator's own domain and has been withdrawn. The honest position is that mileage radii are used in operating practice and told to shoppers verbally, but are not published.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E. Do cottage residents get the same transportation? — this conclusion REVERSED on verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUND ONE CONCLUDED: cottage residents do not reliably get the same transportation, and where it differs the cottage tier is lesser. THAT IS WITHDRAWN. On verification, across seven detached-cottage communities there were ZERO verified cases of a cottage product receiving a lesser transportation tier, ONE verified case of it receiving a BETTER tier, and four cases of parity. The corrected finding: detached-cottage and villa residents generally receive the SAME transportation as apartment residents at the same community, and occasionally better. What is genuinely unreliable is DISCLOSURE, not the benefit. The real service limits that exist are set at operator level and apply to apartments equally.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verdict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarrow Pointe, Tulsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILLA TIER IS BETTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa inclusions name "Private Car and Driver for Doctor Appointments"; apartments get plain "Transportation to and from Doctor Appointments".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Village at Bay Ridge, Traverse City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARITY, and generous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community bus "to all residents at no additional cost", covering both scheduled trips and destinations "based on regular resident requests".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The appointment exclusion is operator-wide and applies to apartments too. The Danville cottage inclusion list separately names "accessible bus transportation".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED, reframed from round one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedarhurst of Frankfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEUTRAL, arguably PARITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The "operate separately" disclaimer covers the all-inclusive package and dining. The same pages state cottage residents "will have access to the activity programs, therapy services, and transportation options already available at" the main community.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disclaimer VERIFIED; access sentence LIKELY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith Crossing, Orland Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One all-inclusive independent living fee naming scheduled transportation, spanning free-standing villas and apartments alike.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamilton Trace, Fishers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Both apartment and cottage residences at The Reserve include the use of all amenities." No cottage-specific carve-out exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garbry Ridge, Piqua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE ONE POSSIBLE EXCEPTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cottage inclusions list omits transportation entirely while the apartment list names "scheduled transportation". But "routine outings" appears on BOTH pages, and the home page advertises free doctor-visit transportation with no tier qualifier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottage list VERIFIED; the "lesser tier" reading is weakened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohio Living Breckenridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNKNOWN — do not assume either way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four handbooks exist, all for apartment buildings. The 73 ranch homes have none, so their terms are simply not published.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absence VERIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touchmark, Silver Elm, Highgrove, TLC properties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT ESTABLISHED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing distinguishes the detached product from the apartment product in either direction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT FOUND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• What actually varies is DISCLOSURE. Operators very rarely state transportation terms separately for cottages, so a benchmarking table has to record "not stated" far more often than "different". Round one mistook that silence for a lesser benefit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Where a real limit exists it is SCOPE-BASED AND COMMUNITY-WIDE, not a cottage carve-out. One operator excludes appointment transport for everybody. Another carves cottages out of its all-inclusive package while explicitly keeping transportation in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• The one direction that IS evidenced is upward. A villa product can differentiate by offering a private car and driver for medical days, which suits a resident who still drives but wants help when it matters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Detached-home residents mostly still drive. Garages are a headline feature of nearly every villa product in the study, and public guidance notes residents commonly keep a car and mix driving with the shuttle. That argues for a light individual-ride benefit at the Good tier, not a heavy one.</t>
   </si>
   <si>
     <t xml:space="preserve">• The counter-risk is the spread footprint. The rental-model report warns that decentralised cottages raise staff travel time for transport and emergency response, so a door-to-door promise on a large site costs materially more than the same promise in a vertical building.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Absence of a published distinction is not absence of a practical one. On campuses of 37 to 72 acres, walk-to-pickup distance may differ sharply between a villa and an apartment, and no operator addresses it in writing. Whether the shuttle comes to the villa door or the resident walks to the main building is a question only a sales counsellor can answer.</t>
+    <t xml:space="preserve">• The unanswered practical question, which no operator addresses in writing: does the shuttle come to the villa door, or does the resident walk to the main building? On campuses of 37 to 72 acres that difference is the whole service. Only a sales counsellor can answer it.</t>
   </si>
   <si>
     <t xml:space="preserve">F. Research reliability — read before quoting anything on this tab</t>
@@ -7200,46 +7206,46 @@
     <t xml:space="preserve">What to do</t>
   </si>
   <si>
-    <t xml:space="preserve">Community websites were unreachable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.</t>
+    <t xml:space="preserve">Community websites could not be opened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This environment's network policy blocks direct page access to every external site, including through a headless browser, so all findings come from web-search result summaries written by a summarising model rather than from reading pages.</t>
   </si>
   <si>
     <t xml:space="preserve">Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.</t>
   </si>
   <si>
-    <t xml:space="preserve">A plausible, detailed finding turned out not to exist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This session's own first search returned a richly detailed Hamilton Trace description covering "medical appointments, dialysis, and outpatient therapy... when space permits". An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator's own line: "Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior-living directories publish AI-generated pseudo-detail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two researchers independently confirmed this. An exact-phrase probe on "scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores" returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do not admit any claim about dialysis, a "designated service radius", or "scheduled in advance" on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Place for Mom and Seniorly amenity flags are fixed checkboxes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Complimentary Transportation" and "Transportation at Cost" are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directories contradicted operators twice, and the operator was right both times</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.</t>
+    <t xml:space="preserve">THE DISCRIMINATOR: operator-domain-restricted search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A bare exact-phrase probe produces FALSE NEGATIVES on PDF text and on some content-managed FAQ pages, so a failed bare probe alone proves nothing. Restricting the search to the operator's own domain is what separates real text from fabrication, and it is how handbook PDFs and FAQ pages were cracked open at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use both. A phrase that fails the bare probe AND fails domain restriction, while appearing on directories, is fabricated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round one contained four fabricated findings, all of them plausible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A detailed capacity description at one community returned zero matches. A "5 mile radius" and a weekly schedule at another were absent from the operator's domain. A named destination hospital turned out NOT TO EXIST, its name fused from two real Chicago-area institutions. A staffing count of "three full-time bus drivers" returned nothing. All four were the kind of specific operational detail a benchmarking study most wants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distrust specificity that appears only in search summaries. The more useful the detail sounds, the harder it needs to be probed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The fabrications are systematically BIASED toward the paid tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both demoted two-tier quotes were on the chargeable side. Directories emit fixed "Complimentary Transportation" and "Transportation at Cost" checkboxes, which summarisers then render into confident prose about free and paid tiers that the operator never wrote.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presume any two-tier claim sourced from a directory is boilerplate until re-probed on the operator's own domain. The reliable directory signal is the boring checkbox, never the prose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directories contradicted operators three times, and the operator was right every time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three directories claim one community provides rides to doctor visits; its operator FAQ says it does not provide transportation to appointments at all. A directory says another community covers transportation in the monthly fee; its resident handbook says there is a fee and rides are billed to the statement.</t>
   </si>
   <si>
     <t xml:space="preserve">Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.</t>
@@ -7254,34 +7260,34 @@
     <t xml:space="preserve">Mine resident reviews for operational truth. They describe the service as used rather than as marketed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Negative findings are more reliable than positive ones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated "not found" results across roughly 50 communities are therefore the study's strongest conclusions.</t>
+    <t xml:space="preserve">Negative findings are the strongest results here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated "not published" results across roughly 50 communities are the study's most reliable conclusions, and verification made them stronger by removing the apparent exceptions.</t>
   </si>
   <si>
     <t xml:space="preserve">Rely on the pattern that nothing is published. Treat individual quotes as provisional.</t>
   </si>
   <si>
-    <t xml:space="preserve">G. How to close the gaps — the detail is obtainable, just not from marketing pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Chase RESIDENT HANDBOOKS, disclosure statements and residence agreements, not amenity pages. The only genuinely concrete, qualifier-bearing language in this entire research came from handbooks. One operator posts a handbook for every community, which would yield an operator-level transportation policy dataset.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Specific unopened documents worth retrieving: the Smith Crossing independent living resident handbook; the Kirkland Crossings resident handbook plus its separate townhome and apartment brochures, whose comparison would answer the villa question definitively; a ranch-home handbook for Ohio Living Breckenridge; and the Laurel Lake villa project resident Q&amp;A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Ask Ohio Living Breckenridge for the "transportation booklet available at the front desk". It is named in the handbooks as the document holding the actual rates, and it is not online.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Mystery-shop for prices. Not one community in the detached-cottage set published a transportation price of any kind: no per-trip rate, no per-mile rate, no monthly charge. If à la carte pricing is needed, it must come from sales offices.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Put the operational questions to sales counsellors by phone: radius, days, hours, booking lead time, fees, wheelchair accessibility, what happens when two residents want the vehicle at once, and above all whether the shuttle comes to the villa door or the resident walks to the main building. Based on this research, that last question is unanswerable from published material.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Re-run this research from an unrestricted network. Roughly 50 communities were covered here from search summaries alone; direct page access would convert most of the LIKELY rows in Section D into verified quotations.</t>
+    <t xml:space="preserve">G. How to close the gaps — the detail exists, just not on marketing pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Chase RESIDENT HANDBOOKS, disclosure statements and residence agreements, not amenity pages. Every genuinely concrete finding in this study came from a handbook or an operator FAQ. One operator posts a handbook for every community, which would yield an operator-level policy dataset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Specific documents identified but not readable here: the Smith Crossing independent living resident handbook, whose Transportation section sits at page 33; a Westminster Place "Guide to Costs and Benefits" PDF, the likeliest place an actual paid-tier rate would appear; Zarrow Pointe's villa and apartment brochures, whose comparison would settle the villa-versus-apartment question; and Ohio Living Breckenridge's weekly newsletter PDFs, which carry actual trip listings with departure times.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Ask Ohio Living Breckenridge for the transportation booklet "available at the front desk", named in its handbooks as the document holding the rates, and for a ranch-home equivalent. Its transportation department extension and sign-up line are published.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Mystery-shop for prices. Not one community in the entire study published a transportation price of any kind. The paid tier is consistently disclosed as existing and its price consistently withheld, so rates must come from sales offices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Settle the Hamilton Trace question by phone. "Unscheduled transportation" is verified as a real menu item, but whether it carries a charge is an unverified inference, and the scheduled-free / unscheduled-paid thesis leans on it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Put the operational questions to sales counsellors: radius, days, hours, booking lead time, fees, wheelchair accessibility, what happens when two residents want the vehicle at once, and whether the shuttle comes to the villa door. Based on this research, none of these is answerable from published material.</t>
   </si>
   <si>
     <t xml:space="preserve">Sources, attribution and method notes</t>
@@ -7452,14 +7458,14 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <name val="[('Community websites could not be opened', &quot;This environment's network policy blocks direct page access to every external site, including through a headless browser, so all findings come from web-search result summaries written by a summarising model rather than from reading pages.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('THE DISCRIMINATOR: operator-domain-restricted search', &quot;A bare exact-phrase probe produces FALSE NEGATIVES on PDF text and on some content-managed FAQ pages, so a failed bare probe alone proves nothing. Restricting the search to the operator's own domain is what separates real text from fabrication, and it is how handbook PDFs and FAQ pages were cracked open at all.&quot;, 'Use both. A phrase that fails the bare probe AND fails domain restriction, while appearing on directories, is fabricated.'), ('Round one contained four fabricated findings, all of them plausible', 'A detailed capacity description at one community returned zero matches. A &quot;5 mile radius&quot; and a weekly schedule at another were absent from the operator\'s domain. A named destination hospital turned out NOT TO EXIST, its name fused from two real Chicago-area institutions. A staffing count of &quot;three full-time bus drivers&quot; returned nothing. All four were the kind of specific operational detail a benchmarking study most wants.', 'Distrust specificity that appears only in search summaries. The more useful the detail sounds, the harder it needs to be probed.'), ('The fabrications are systematically BIASED toward the paid tier', 'Both demoted two-tier quotes were on the chargeable side. Directories emit fixed &quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; checkboxes, which summarisers then render into confident prose about free and paid tiers that the operator never wrote.', &quot;Presume any two-tier claim sourced from a directory is boilerplate until re-probed on the operator's own domain. The reliable directory signal is the boring checkbox, never the prose.&quot;), ('Directories contradicted operators three times, and the operator was right every time', 'Three directories claim one community provides rides to doctor visits; its operator FAQ says it does not provide transportation to appointments at all. A directory says another community covers transportation in the monthly fee; its resident handbook says there is a fee and rides are billed to the statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are the strongest results here', 'A summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not published&quot; results across roughly 50 communities are the study\'s most reliable conclusions, and verification made them stronger by removing the apparent exceptions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <name val="[('Community websites could not be opened', &quot;This environment's network policy blocks direct page access to every external site, including through a headless browser, so all findings come from web-search result summaries written by a summarising model rather than from reading pages.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('THE DISCRIMINATOR: operator-domain-restricted search', &quot;A bare exact-phrase probe produces FALSE NEGATIVES on PDF text and on some content-managed FAQ pages, so a failed bare probe alone proves nothing. Restricting the search to the operator's own domain is what separates real text from fabrication, and it is how handbook PDFs and FAQ pages were cracked open at all.&quot;, 'Use both. A phrase that fails the bare probe AND fails domain restriction, while appearing on directories, is fabricated.'), ('Round one contained four fabricated findings, all of them plausible', 'A detailed capacity description at one community returned zero matches. A &quot;5 mile radius&quot; and a weekly schedule at another were absent from the operator\'s domain. A named destination hospital turned out NOT TO EXIST, its name fused from two real Chicago-area institutions. A staffing count of &quot;three full-time bus drivers&quot; returned nothing. All four were the kind of specific operational detail a benchmarking study most wants.', 'Distrust specificity that appears only in search summaries. The more useful the detail sounds, the harder it needs to be probed.'), ('The fabrications are systematically BIASED toward the paid tier', 'Both demoted two-tier quotes were on the chargeable side. Directories emit fixed &quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; checkboxes, which summarisers then render into confident prose about free and paid tiers that the operator never wrote.', &quot;Presume any two-tier claim sourced from a directory is boilerplate until re-probed on the operator's own domain. The reliable directory signal is the boring checkbox, never the prose.&quot;), ('Directories contradicted operators three times, and the operator was right every time', 'Three directories claim one community provides rides to doctor visits; its operator FAQ says it does not provide transportation to appointments at all. A directory says another community covers transportation in the monthly fee; its resident handbook says there is a fee and rides are billed to the statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are the strongest results here', 'A summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not published&quot; results across roughly 50 communities are the study\'s most reliable conclusions, and verification made them stronger by removing the apparent exceptions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -7467,7 +7473,7 @@
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FF1F3864"/>
-      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <name val="[('Community websites could not be opened', &quot;This environment's network policy blocks direct page access to every external site, including through a headless browser, so all findings come from web-search result summaries written by a summarising model rather than from reading pages.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('THE DISCRIMINATOR: operator-domain-restricted search', &quot;A bare exact-phrase probe produces FALSE NEGATIVES on PDF text and on some content-managed FAQ pages, so a failed bare probe alone proves nothing. Restricting the search to the operator's own domain is what separates real text from fabrication, and it is how handbook PDFs and FAQ pages were cracked open at all.&quot;, 'Use both. A phrase that fails the bare probe AND fails domain restriction, while appearing on directories, is fabricated.'), ('Round one contained four fabricated findings, all of them plausible', 'A detailed capacity description at one community returned zero matches. A &quot;5 mile radius&quot; and a weekly schedule at another were absent from the operator\'s domain. A named destination hospital turned out NOT TO EXIST, its name fused from two real Chicago-area institutions. A staffing count of &quot;three full-time bus drivers&quot; returned nothing. All four were the kind of specific operational detail a benchmarking study most wants.', 'Distrust specificity that appears only in search summaries. The more useful the detail sounds, the harder it needs to be probed.'), ('The fabrications are systematically BIASED toward the paid tier', 'Both demoted two-tier quotes were on the chargeable side. Directories emit fixed &quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; checkboxes, which summarisers then render into confident prose about free and paid tiers that the operator never wrote.', &quot;Presume any two-tier claim sourced from a directory is boilerplate until re-probed on the operator's own domain. The reliable directory signal is the boring checkbox, never the prose.&quot;), ('Directories contradicted operators three times, and the operator was right every time', 'Three directories claim one community provides rides to doctor visits; its operator FAQ says it does not provide transportation to appointments at all. A directory says another community covers transportation in the monthly fee; its resident handbook says there is a fee and rides are billed to the statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are the strongest results here', 'A summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not published&quot; results across roughly 50 communities are the study\'s most reliable conclusions, and verification made them stronger by removing the apparent exceptions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -7475,7 +7481,7 @@
       <b val="true"/>
       <sz val="14"/>
       <color rgb="FF1F3864"/>
-      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <name val="[('Community websites could not be opened', &quot;This environment's network policy blocks direct page access to every external site, including through a headless browser, so all findings come from web-search result summaries written by a summarising model rather than from reading pages.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('THE DISCRIMINATOR: operator-domain-restricted search', &quot;A bare exact-phrase probe produces FALSE NEGATIVES on PDF text and on some content-managed FAQ pages, so a failed bare probe alone proves nothing. Restricting the search to the operator's own domain is what separates real text from fabrication, and it is how handbook PDFs and FAQ pages were cracked open at all.&quot;, 'Use both. A phrase that fails the bare probe AND fails domain restriction, while appearing on directories, is fabricated.'), ('Round one contained four fabricated findings, all of them plausible', 'A detailed capacity description at one community returned zero matches. A &quot;5 mile radius&quot; and a weekly schedule at another were absent from the operator\'s domain. A named destination hospital turned out NOT TO EXIST, its name fused from two real Chicago-area institutions. A staffing count of &quot;three full-time bus drivers&quot; returned nothing. All four were the kind of specific operational detail a benchmarking study most wants.', 'Distrust specificity that appears only in search summaries. The more useful the detail sounds, the harder it needs to be probed.'), ('The fabrications are systematically BIASED toward the paid tier', 'Both demoted two-tier quotes were on the chargeable side. Directories emit fixed &quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; checkboxes, which summarisers then render into confident prose about free and paid tiers that the operator never wrote.', &quot;Presume any two-tier claim sourced from a directory is boilerplate until re-probed on the operator's own domain. The reliable directory signal is the boring checkbox, never the prose.&quot;), ('Directories contradicted operators three times, and the operator was right every time', 'Three directories claim one community provides rides to doctor visits; its operator FAQ says it does not provide transportation to appointments at all. A directory says another community covers transportation in the monthly fee; its resident handbook says there is a fee and rides are billed to the statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are the strongest results here', 'A summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not published&quot; results across roughly 50 communities are the study\'s most reliable conclusions, and verification made them stronger by removing the apparent exceptions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -7483,7 +7489,7 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="[('Community websites were unreachable', &quot;This environment's network policy blocked direct page access to every community and directory site. All findings come from web-search result summaries, which are written by a summarising model reading the page rather than by reading the page directly.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('A plausible, detailed finding turned out not to exist', 'This session\'s own first search returned a richly detailed Hamilton Trace description covering &quot;medical appointments, dialysis, and outpatient therapy... when space permits&quot;. An exact-phrase probe later returned ZERO matching pages. It has been removed from this analysis. What survives verification for that community is the operator\'s own line: &quot;Included with a selected apartment or cottage is all interior, exterior and grounds maintenance, plus housekeeping and scheduled transportation.&quot;', 'Distrust specificity that appears only in search summaries. Verify by re-querying the exact phrase in quotation marks.'), ('Senior-living directories publish AI-generated pseudo-detail', 'Two researchers independently confirmed this. An exact-phrase probe on &quot;scheduled shuttles to physician offices, dialysis or therapy sessions, grocery stores&quot; returned zero senior-living communities, yet near-identical constructions were attributed to three different properties of one operator. The same skeleton appears with swapped nouns and no primary source.', 'Do not admit any claim about dialysis, a &quot;designated service radius&quot;, or &quot;scheduled in advance&quot; on directory authority alone. The details a benchmark most wants are the least trustworthy text on those sites.'), ('A Place for Mom and Seniorly amenity flags are fixed checkboxes', '&quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; are standing listing categories applied across an entire inventory, not community-specific statements. They produced false signal at two communities in this research.', 'Ignore those flags entirely for this attribute. The reliable directory signal is the boring structured checkbox, never the prose.'), ('Directories contradicted operators twice, and the operator was right both times', 'Three directories claim Woodland Terrace provides rides to doctor visits; the operator FAQ says it does not provide transportation to appointments. A directory says Ohio Living Breckenridge covers transportation in the monthly fee; the resident handbook says there is a fee and rides are billed to the resident statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are more reliable than positive ones', 'As one researcher put it, a summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not found&quot; results across roughly 50 communities are therefore the study\'s strongest conclusions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
+      <name val="[('Community websites could not be opened', &quot;This environment's network policy blocks direct page access to every external site, including through a headless browser, so all findings come from web-search result summaries written by a summarising model rather than from reading pages.&quot;, 'Treat every quotation as a lead. Open one confirming page before any of this goes into an external deliverable.'), ('THE DISCRIMINATOR: operator-domain-restricted search', &quot;A bare exact-phrase probe produces FALSE NEGATIVES on PDF text and on some content-managed FAQ pages, so a failed bare probe alone proves nothing. Restricting the search to the operator's own domain is what separates real text from fabrication, and it is how handbook PDFs and FAQ pages were cracked open at all.&quot;, 'Use both. A phrase that fails the bare probe AND fails domain restriction, while appearing on directories, is fabricated.'), ('Round one contained four fabricated findings, all of them plausible', 'A detailed capacity description at one community returned zero matches. A &quot;5 mile radius&quot; and a weekly schedule at another were absent from the operator\'s domain. A named destination hospital turned out NOT TO EXIST, its name fused from two real Chicago-area institutions. A staffing count of &quot;three full-time bus drivers&quot; returned nothing. All four were the kind of specific operational detail a benchmarking study most wants.', 'Distrust specificity that appears only in search summaries. The more useful the detail sounds, the harder it needs to be probed.'), ('The fabrications are systematically BIASED toward the paid tier', 'Both demoted two-tier quotes were on the chargeable side. Directories emit fixed &quot;Complimentary Transportation&quot; and &quot;Transportation at Cost&quot; checkboxes, which summarisers then render into confident prose about free and paid tiers that the operator never wrote.', &quot;Presume any two-tier claim sourced from a directory is boilerplate until re-probed on the operator's own domain. The reliable directory signal is the boring checkbox, never the prose.&quot;), ('Directories contradicted operators three times, and the operator was right every time', 'Three directories claim one community provides rides to doctor visits; its operator FAQ says it does not provide transportation to appointments at all. A directory says another community covers transportation in the monthly fee; its resident handbook says there is a fee and rides are billed to the statement.', 'Trust handbooks and FAQs over directories and over marketing pages. Where they conflict, the handbook governs.'), ('The most concrete operational fact came from a resident review', 'A family member wrote of one community: &quot;shuttle buses that take you for no charge to doctor\'s appointments and even have occasional community activities that they take people to.&quot; That single sentence supplies vehicle type, cost, primary purpose and a frequency qualifier, none of which the operator publishes.', 'Mine resident reviews for operational truth. They describe the service as used rather than as marketed.'), ('Negative findings are the strongest results here', 'A summariser can fail to surface text that exists, but is unlikely to invent a page-level absence across many differently worded queries. The repeated &quot;not published&quot; results across roughly 50 communities are the study\'s most reliable conclusions, and verification made them stronger by removing the apparent exceptions.', 'Rely on the pattern that nothing is published. Treat individual quotes as provisional.')]"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -27217,7 +27223,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="n">
         <v>220</v>
       </c>
@@ -27702,7 +27708,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
@@ -32045,14 +32051,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
   </cols>
@@ -32163,7 +32169,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
         <v>2102</v>
       </c>
@@ -32201,7 +32207,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="n">
         <v>1</v>
       </c>
@@ -32221,7 +32227,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="n">
         <v>2</v>
       </c>
@@ -32241,7 +32247,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="n">
         <v>3</v>
       </c>
@@ -32261,7 +32267,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>4</v>
       </c>
@@ -32281,7 +32287,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="n">
         <v>5</v>
       </c>
@@ -32329,7 +32335,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="n">
         <v>1</v>
       </c>
@@ -32352,7 +32358,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="n">
         <v>2</v>
       </c>
@@ -32375,7 +32381,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="n">
         <v>3</v>
       </c>
@@ -32398,7 +32404,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="n">
         <v>4</v>
       </c>
@@ -32421,7 +32427,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="n">
         <v>5</v>
       </c>
@@ -32444,7 +32450,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
         <v>6</v>
       </c>
@@ -32467,7 +32473,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
         <v>7</v>
       </c>
@@ -32490,7 +32496,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
         <v>8</v>
       </c>
@@ -32513,7 +32519,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
         <v>9</v>
       </c>
@@ -32536,7 +32542,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
         <v>10</v>
       </c>
@@ -32564,7 +32570,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
         <v>2200</v>
       </c>
@@ -32598,7 +32604,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
         <v>2206</v>
       </c>
@@ -32614,14 +32620,14 @@
       <c r="E38" s="4" t="s">
         <v>2210</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="16" t="s">
         <v>2211</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>2212</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
         <v>2213</v>
       </c>
@@ -32644,7 +32650,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
         <v>2220</v>
       </c>
@@ -32667,7 +32673,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
         <v>2227</v>
       </c>
@@ -32683,14 +32689,14 @@
       <c r="E41" s="4" t="s">
         <v>2231</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="16" t="s">
         <v>2232</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>2233</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
         <v>2234</v>
       </c>
@@ -32706,14 +32712,14 @@
       <c r="E42" s="4" t="s">
         <v>2238</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="16" t="s">
         <v>2239</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>2240</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
         <v>2241</v>
       </c>
@@ -32729,14 +32735,14 @@
       <c r="E43" s="4" t="s">
         <v>2245</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="16" t="s">
         <v>2246</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>2247</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
         <v>2248</v>
       </c>
@@ -32752,14 +32758,14 @@
       <c r="E44" s="4" t="s">
         <v>2252</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="16" t="s">
         <v>2253</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>2254</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
         <v>2255</v>
       </c>
@@ -32775,14 +32781,14 @@
       <c r="E45" s="4" t="s">
         <v>2259</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="16" t="s">
         <v>2260</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>2261</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
         <v>2262</v>
       </c>
@@ -32798,14 +32804,14 @@
       <c r="E46" s="4" t="s">
         <v>2266</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="16" t="s">
         <v>2267</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>2268</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
         <v>2269</v>
       </c>
@@ -32821,14 +32827,14 @@
       <c r="E47" s="4" t="s">
         <v>2273</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="27" t="s">
         <v>2274</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>2275</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
         <v>2276</v>
       </c>
@@ -32851,7 +32857,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
         <v>2283</v>
       </c>
@@ -32867,357 +32873,343 @@
       <c r="E49" s="4" t="s">
         <v>2287</v>
       </c>
-      <c r="F49" s="18" t="s">
-        <v>2281</v>
+      <c r="F49" s="27" t="s">
+        <v>2288</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2288</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2293</v>
-      </c>
-      <c r="F50" s="16" t="s">
         <v>2294</v>
       </c>
+      <c r="F50" s="27" t="s">
+        <v>2295</v>
+      </c>
       <c r="G50" s="4" t="s">
-        <v>2295</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2302</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>2281</v>
+        <v>2309</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2308</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2315</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>2281</v>
+        <v>2323</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2321</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>2322</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="F55" s="27" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>2334</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>2294</v>
+      </c>
+      <c r="F56" s="18" t="s">
         <v>2323</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>2324</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>2325</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>2326</v>
-      </c>
-      <c r="F55" s="18" t="s">
-        <v>2281</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>2327</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9" t="s">
-        <v>2328</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>2329</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>2330</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>2331</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>2332</v>
-      </c>
-      <c r="F56" s="18" t="s">
-        <v>2333</v>
-      </c>
       <c r="G56" s="4" t="s">
-        <v>2334</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9" t="s">
         <v>2335</v>
       </c>
-      <c r="B57" s="4" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="11" t="s">
         <v>2336</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="s">
         <v>2337</v>
       </c>
-      <c r="D57" s="4" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="28" t="s">
         <v>2338</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>2332</v>
-      </c>
-      <c r="F57" s="27" t="s">
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>2339</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="C61" s="1" t="s">
         <v>2340</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="9" t="s">
+      <c r="D61" s="1" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="s">
         <v>2341</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B62" s="4" t="s">
         <v>2342</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C62" s="4" t="s">
         <v>2343</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D62" s="16" t="s">
         <v>2344</v>
       </c>
-      <c r="E58" s="4" t="s">
+    </row>
+    <row r="63" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="s">
         <v>2345</v>
       </c>
-      <c r="F58" s="18" t="s">
-        <v>2281</v>
-      </c>
-      <c r="G58" s="4" t="s">
+      <c r="B63" s="4" t="s">
         <v>2346</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="11" t="s">
+      <c r="C63" s="4" t="s">
         <v>2347</v>
       </c>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
+      <c r="D63" s="16" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>2348</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="28" t="s">
+      <c r="C64" s="4" t="s">
         <v>2349</v>
       </c>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="D64" s="16" t="s">
         <v>2350</v>
       </c>
-      <c r="B63" s="1" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="s">
         <v>2351</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="B65" s="4" t="s">
         <v>2352</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="C65" s="4" t="s">
         <v>2353</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="D65" s="16" t="s">
         <v>2354</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="9" t="s">
+    <row r="66" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="s">
         <v>2355</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B66" s="4" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>2356</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="D66" s="18" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="9" t="s">
         <v>2357</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="B67" s="4" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>2358</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="D67" s="18" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="s">
         <v>2359</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="9" t="s">
+      <c r="B68" s="4" t="s">
         <v>2360</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="C68" s="4" t="s">
         <v>2361</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="D68" s="16" t="s">
         <v>2362</v>
       </c>
-      <c r="D65" s="4" t="s">
+    </row>
+    <row r="69" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="9" t="s">
         <v>2363</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="B69" s="4" t="s">
         <v>2364</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="9" t="s">
+      <c r="C69" s="4" t="s">
         <v>2365</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="D69" s="16" t="s">
         <v>2366</v>
       </c>
-      <c r="C66" s="4" t="s">
+    </row>
+    <row r="70" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="s">
         <v>2367</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="B70" s="4" t="s">
         <v>2368</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="C70" s="4" t="s">
         <v>2369</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="s">
+      <c r="D70" s="17" t="s">
         <v>2370</v>
       </c>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-    </row>
-    <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12" t="s">
-        <v>2371</v>
-      </c>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-    </row>
-    <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="s">
-        <v>2372</v>
-      </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-    </row>
-    <row r="71" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12" t="s">
-        <v>2373</v>
-      </c>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
     </row>
     <row r="72" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
@@ -33225,157 +33217,157 @@
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="8" t="s">
+    <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="12" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
+    </row>
+    <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="12" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+    </row>
+    <row r="75" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="12" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+    </row>
+    <row r="76" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="12" t="s">
         <v>2375</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+    </row>
+    <row r="77" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="12" t="s">
         <v>2376</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8" t="s">
         <v>2377</v>
       </c>
-      <c r="C75" s="1" t="s">
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
         <v>2378</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="29" t="s">
+      <c r="B80" s="1" t="s">
         <v>2379</v>
       </c>
-      <c r="B76" s="30" t="s">
+      <c r="C80" s="1" t="s">
         <v>2380</v>
-      </c>
-      <c r="C76" s="30" t="s">
-        <v>2381</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="29" t="s">
-        <v>2382</v>
-      </c>
-      <c r="B77" s="30" t="s">
-        <v>2383</v>
-      </c>
-      <c r="C77" s="30" t="s">
-        <v>2384</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="29" t="s">
-        <v>2385</v>
-      </c>
-      <c r="B78" s="30" t="s">
-        <v>2386</v>
-      </c>
-      <c r="C78" s="30" t="s">
-        <v>2387</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="29" t="s">
-        <v>2388</v>
-      </c>
-      <c r="B79" s="30" t="s">
-        <v>2389</v>
-      </c>
-      <c r="C79" s="30" t="s">
-        <v>2390</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="29" t="s">
-        <v>2391</v>
-      </c>
-      <c r="B80" s="30" t="s">
-        <v>2392</v>
-      </c>
-      <c r="C80" s="30" t="s">
-        <v>2393</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="29" t="s">
-        <v>2394</v>
+        <v>2381</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>2395</v>
+        <v>2382</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>2396</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="29" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B82" s="30" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="29" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B83" s="30" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C83" s="30" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="29" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B84" s="30" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C84" s="30" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="29" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B85" s="30" t="s">
+        <v>2394</v>
+      </c>
+      <c r="C85" s="30" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="29" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B86" s="30" t="s">
         <v>2397</v>
       </c>
-      <c r="B82" s="30" t="s">
+      <c r="C86" s="30" t="s">
         <v>2398</v>
       </c>
-      <c r="C82" s="30" t="s">
+    </row>
+    <row r="87" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="29" t="s">
         <v>2399</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="31" t="s">
+      <c r="B87" s="30" t="s">
         <v>2400</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="32" t="s">
+      <c r="C87" s="30" t="s">
         <v>2401</v>
       </c>
-      <c r="B85" s="32"/>
-      <c r="C85" s="32"/>
-      <c r="D85" s="32"/>
-      <c r="E85" s="32"/>
-      <c r="F85" s="32"/>
-    </row>
-    <row r="86" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="32" t="s">
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="31" t="s">
         <v>2402</v>
       </c>
-      <c r="B86" s="32"/>
-      <c r="C86" s="32"/>
-      <c r="D86" s="32"/>
-      <c r="E86" s="32"/>
-      <c r="F86" s="32"/>
-    </row>
-    <row r="87" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="32" t="s">
+    </row>
+    <row r="90" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="32" t="s">
         <v>2403</v>
-      </c>
-      <c r="B87" s="32"/>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-    </row>
-    <row r="88" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="32" t="s">
-        <v>2404</v>
-      </c>
-      <c r="B88" s="32"/>
-      <c r="C88" s="32"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-    </row>
-    <row r="89" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="32" t="s">
-        <v>2405</v>
-      </c>
-      <c r="B89" s="32"/>
-      <c r="C89" s="32"/>
-      <c r="D89" s="32"/>
-      <c r="E89" s="32"/>
-      <c r="F89" s="32"/>
-    </row>
-    <row r="90" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="32" t="s">
-        <v>2406</v>
       </c>
       <c r="B90" s="32"/>
       <c r="C90" s="32"/>
@@ -33383,24 +33375,75 @@
       <c r="E90" s="32"/>
       <c r="F90" s="32"/>
     </row>
+    <row r="91" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="32" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B91" s="32"/>
+      <c r="C91" s="32"/>
+      <c r="D91" s="32"/>
+      <c r="E91" s="32"/>
+      <c r="F91" s="32"/>
+    </row>
+    <row r="92" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="32" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B92" s="32"/>
+      <c r="C92" s="32"/>
+      <c r="D92" s="32"/>
+      <c r="E92" s="32"/>
+      <c r="F92" s="32"/>
+    </row>
+    <row r="93" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="32" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B93" s="32"/>
+      <c r="C93" s="32"/>
+      <c r="D93" s="32"/>
+      <c r="E93" s="32"/>
+      <c r="F93" s="32"/>
+    </row>
+    <row r="94" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="32" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B94" s="32"/>
+      <c r="C94" s="32"/>
+      <c r="D94" s="32"/>
+      <c r="E94" s="32"/>
+      <c r="F94" s="32"/>
+    </row>
+    <row r="95" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="32" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B95" s="32"/>
+      <c r="C95" s="32"/>
+      <c r="D95" s="32"/>
+      <c r="E95" s="32"/>
+      <c r="F95" s="32"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A77:F77"/>
     <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A95:F95"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -33430,7 +33473,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33438,19 +33481,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33464,14 +33507,14 @@
         <v>37</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="E4" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Laura Lopez")</f>
         <v>215</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33485,14 +33528,14 @@
         <v>1423</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="E5" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Ken Witzgall")</f>
         <v>2</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33506,14 +33549,14 @@
         <v>1457</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="E6" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Scott Wood")</f>
         <v>2</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33527,24 +33570,24 @@
         <v>1457</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="E7" s="30" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Jennifer Saxman")</f>
         <v>11</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="32"/>
@@ -33554,7 +33597,7 @@
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="32"/>
@@ -33564,7 +33607,7 @@
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
@@ -33574,7 +33617,7 @@
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="32"/>
@@ -33584,7 +33627,7 @@
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="32"/>
@@ -33594,7 +33637,7 @@
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="32"/>
@@ -33604,7 +33647,7 @@
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="32"/>
@@ -33614,7 +33657,7 @@
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
@@ -33624,7 +33667,7 @@
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="32"/>

--- a/Cottage_Villa_Service_Benchmark.xlsx
+++ b/Cottage_Villa_Service_Benchmark.xlsx
@@ -14,12 +14,14 @@
     <sheet name="Synthesis" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Good-Better-Best" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Service Elements" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Transportation Detail" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Sources &amp; Method" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Service Docs Linear" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Transportation Detail" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sources &amp; Method" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Consolidated Data'!$A$1:$AI$231</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Good-Better-Best'!$A$4:$F$34</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Service Docs Linear'!$A$4:$F$37</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Service Elements'!$A$4:$H$75</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -78,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6900" uniqueCount="2618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7090" uniqueCount="2707">
   <si>
     <t xml:space="preserve">Cottage &amp; Villa Service Benchmark — Start Here</t>
   </si>
@@ -6870,6 +6872,478 @@
   </si>
   <si>
     <t xml:space="preserve">Prevalence counts are keyword matches over the villa study amenity text. "0 of 215" means the element appears only in the Witzgall, Wood or Saxman material, or in none of the sources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Docs Linear — every service element, reorganised by level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The same data as the Service Elements tab, run linear. Each function sits in column A. Column B holds GOOD, BETTER and BEST as three rows beneath it. Read one row and you have the complete service specification for that function at that level: what is included in the fee, what is sold at a posted price, what is not offered, and any element whose value is a specification rather than a simple status. Every one of the 72 elements appears in exactly one column on every row, so nothing is dropped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCLUDED in the fee at this level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À LA CARTE at this level (available at a posted price)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT OFFERED at this level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPECIFIED AS — elements whose value is a spec rather than a status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Scheduled group shuttle to a published set of destinations
+• Group outings and excursions to events (with outing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5)
+• Individually scheduled medical-appointment rides (referred to third-party ride services)
+• Trips beyond the included area
+• Unscheduled / personal on-demand rides
+• On-campus circulator (home to clubhouse, dining, fitness)
+• After-hours and airport runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Level of assistance → Curb-to-curb
+• Villa / cottage eligibility → Same service as apartment residents; central pickup point
+• Published service terms (days, hours, lead time, capacity rule) → Published at move-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Scheduled group shuttle to a published set of destinations
+• Group outings and excursions to events (with outing)
+• Individually scheduled medical-appointment rides (weekdays)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Trips beyond the included area (at a posted per-mile or per-trip rate)
+• Unscheduled / personal on-demand rides (per hour or per mile)
+• After-hours and airport runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• On-campus circulator (home to clubhouse, dining, fitness)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Level of assistance → Door-to-door
+• Villa / cottage eligibility → Same service, with pickup at the villa door
+• Published service terms (days, hours, lead time, capacity rule) → Published, with 24-48 hour booking and a stated medical priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5)
+• Scheduled group shuttle to a published set of destinations
+• Group outings and excursions to events (with outing, plus an annual outing credit)
+• Individually scheduled medical-appointment rides (any day, with a stated dialysis and recurring-therapy policy)
+• Unscheduled / personal on-demand rides (allowance of personal trips per month, then a la carte)
+• On-campus circulator (home to clubhouse, dining, fitness)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Trips beyond the included area (at a posted rate, with named destination hospitals inside the included area)
+• After-hours and airport runs (booked through concierge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Level of assistance → Escort into and through the appointment, by arrangement
+• Villa / cottage eligibility → Same service, with priority routing for the cottage neighbourhood
+• Published service terms (days, hours, lead time, capacity rule) → Published, with guaranteed medical seats and third-party overflow at community cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Access to main-community calendar, events, clubs and common areas
+• Fitness center, pool and wellness-center access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Off-campus excursions and ticketed events (at cost)
+• Specialty classes and workshop materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Cottage-neighborhood programming (block events, resident council, cottage liaison)
+• Personal training / small-group instruction
+• Priority registration and concierge booking for limited-seat events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Access to main-community calendar, events, clubs and common areas
+• Fitness center, pool and wellness-center access
+• Cottage-neighborhood programming (block events, resident council, cottage liaison)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Off-campus excursions and ticketed events (at cost)
+• Specialty classes and workshop materials
+• Personal training / small-group instruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Priority registration and concierge booking for limited-seat events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6)
+• Access to main-community calendar, events, clubs and common areas
+• Fitness center, pool and wellness-center access
+• Cottage-neighborhood programming (block events, resident council, cottage liaison)
+• Off-campus excursions and ticketed events (annual outing credit), then at cost)
+• Specialty classes and workshop materials (enrichment credit)
+• Priority registration and concierge booking for limited-seat events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Personal training / small-group instruction (discounted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Access to all community dining venues at posted prices (access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Guest meals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5)
+• Declining-balance dining credit usable at any venue
+• Fixed meal plan (1 meal/day, or 10–30 meals/month)
+• Full 3-meal plan
+• Villa meal delivery
+• Private dining / catering for resident events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Continental breakfast → Weekly breakfast social at clubhouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Access to all community dining venues at posted prices (access)
+• Continental breakfast (daily)
+• Declining-balance dining credit usable at any venue (modest monthly credit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5)
+• Fixed meal plan (1 meal/day, or 10–30 meals/month) (optional plan)
+• Full 3-meal plan (upgrade)
+• Guest meals
+• Villa meal delivery (per-delivery fee)
+• Private dining / catering for resident events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6)
+• Access to all community dining venues at posted prices (access)
+• Continental breakfast (daily (plus Sunday brunch)
+• Declining-balance dining credit usable at any venue (larger monthly credit or meal plan below)
+• Fixed meal plan (1 meal/day, or 10–30 meals/month) (1/day or 20–30/month)
+• Guest meals (monthly guest allowance)
+• Villa meal delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Full 3-meal plan (upgrade)
+• Private dining / catering for resident events (concierge-arranged)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Move-in / move-out turnover clean (turnover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Routine housekeeping subscription (monthly subscription or hourly)
+• Annual deep / spring clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Upgrade to weekly cadence
+• Flat-linen service (bed and bath)
+• Carpet, window and specialty cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Routine housekeeping subscription (bi-weekly)
+• Move-in / move-out turnover clean (turnover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4)
+• Upgrade to weekly cadence (upgrade)
+• Flat-linen service (bed and bath)
+• Annual deep / spring clean
+• Carpet, window and specialty cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5)
+• Routine housekeeping subscription (weekly)
+• Upgrade to weekly cadence
+• Flat-linen service (bed and bath) (weekly)
+• Annual deep / spring clean (once per year)
+• Move-in / move-out turnover clean (turnover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Carpet, window and specialty cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• In-unit washer/dryer (or hookups) (residence feature)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Personal laundry service (wash, dry, fold)
+• Linen service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Personal laundry service (wash, dry, fold) (per load or monthly package)
+• Linen service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• In-unit washer/dryer (or hookups) (residence feature)
+• Linen service (weekly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Personal laundry service (wash, dry, fold) (discounted package)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Fitness, pool and wellness programming on the campus calendar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5)
+• Monthly on-site wellness clinic (blood pressure, weight, medication review)
+• Daily check-in call or app check-in
+• Annual wellness allowance or free health-center days
+• Medication management
+• Personal training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Home health, therapy and rehab access → Referral only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Fitness, pool and wellness programming on the campus calendar
+• Monthly on-site wellness clinic (blood pressure, weight, medication review)
+• Daily check-in call or app check-in (opt-in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Medication management
+• Personal training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Annual wellness allowance or free health-center days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Home health, therapy and rehab access → Coordinated on request (third-party rates)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4)
+• Fitness, pool and wellness programming on the campus calendar
+• Monthly on-site wellness clinic (blood pressure, weight, medication review)
+• Daily check-in call or app check-in (opt-in)
+• Annual wellness allowance or free health-center days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Home health, therapy and rehab access → Coordinated by a wellness navigator (third-party rates)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• 24/7 monitored emergency call system (pendant or pull cords)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Replacement pendant / fob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4)
+• Campus-wide mobile pendant (works outside the home)
+• Gated or controlled entry / 24-hour security patrol
+• In-home sensors / fall detection
+• Lock-and-leave home checks while traveling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• 24-hour on-site staff response to the cottages → Main-community response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• 24/7 monitored emergency call system (pendant or pull cords)
+• Campus-wide mobile pendant (works outside the home)
+• 24-hour on-site staff response to the cottages (dedicated response protocol)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• In-home sensors / fall detection
+• Lock-and-leave home checks while traveling
+• Replacement pendant / fob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Gated or controlled entry / 24-hour security patrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6)
+• 24/7 monitored emergency call system (pendant or pull cords)
+• Campus-wide mobile pendant (works outside the home)
+• 24-hour on-site staff response to the cottages (priority routing for cottage neighborhood)
+• Gated or controlled entry / 24-hour security patrol
+• In-home sensors / fall detection
+• Lock-and-leave home checks while traveling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Exterior maintenance, lawn care, landscaping, snow and ice removal
+• Repair and replacement of community-owned appliances and systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Handyman for resident-requested work (hanging, assembly, small fixes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Preventive interior maintenance (filters, detectors, seasonal checks)
+• Seasonal extras (gutters, power-wash, window cleaning)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Work-order response → Business hours plus emergency line
+• Interior refresh (paint, carpet) → At turnover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Exterior maintenance, lawn care, landscaping, snow and ice removal
+• Repair and replacement of community-owned appliances and systems
+• Preventive interior maintenance (filters, detectors, seasonal checks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Handyman for resident-requested work (hanging, assembly, small fixes)
+• Seasonal extras (gutters, power-wash, window cleaning)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Work-order response → 24-hour emergency maintenance
+• Interior refresh (paint, carpet) → At turnover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5)
+• Exterior maintenance, lawn care, landscaping, snow and ice removal
+• Repair and replacement of community-owned appliances and systems
+• Preventive interior maintenance (filters, detectors, seasonal checks)
+• Handyman for resident-requested work (hanging, assembly, small fixes) (set hours per month), then à la carte)
+• Seasonal extras (gutters, power-wash, window cleaning)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Work-order response → 24-hour with priority response
+• Interior refresh (paint, carpet) → Scheduled cycle during tenancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Water, sewer, trash and recycling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Phone
+• Premium cable / streaming package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Electric and gas → Resident-paid
+• Basic cable and Wi-Fi → Resident-paid
+• Property taxes and building insurance (structure-dependent) → Not applicable (rental)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Water, sewer, trash and recycling
+• Electric and gas
+• Basic cable and Wi-Fi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Property taxes and building insurance (structure-dependent) → Not applicable (rental)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6)
+• Water, sewer, trash and recycling
+• Electric and gas
+• Basic cable and Wi-Fi
+• Phone
+• Premium cable / streaming package
+• Property taxes and building insurance (structure-dependent) (where the structure creates them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Front-desk assistance during business hours
+• Published à la carte menu with monthly-statement billing (short list)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• Pet services (deposit/rent; walking, sitting, pet care)
+• Salon and spa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5)
+• Cottage services coordinator (single point of contact)
+• 24/7 concierge
+• Package receipt and delivery to the villa
+• Vendor coordination (movers, tech help, contractors)
+• Monthly convenience credit usable across the menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4)
+• Front-desk assistance during business hours
+• Published à la carte menu with monthly-statement billing (full Base + Choice menu)
+• Cottage services coordinator (single point of contact) (shared)
+• Package receipt and delivery to the villa (pickup at desk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)
+• Vendor coordination (movers, tech help, contractors)
+• Pet services (deposit/rent; walking, sitting, pet care)
+• Salon and spa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)
+• 24/7 concierge
+• Monthly convenience credit usable across the menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7)
+• Front-desk assistance during business hours
+• Published à la carte menu with monthly-statement billing (full menu)
+• Cottage services coordinator (single point of contact) (dedicated)
+• 24/7 concierge
+• Package receipt and delivery to the villa (delivered)
+• Vendor coordination (movers, tech help, contractors)
+• Monthly convenience credit usable across the menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Overall structure → Base rent covers residence, maintenance, base utilities, emergency response, campus access; everything else à la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Overall structure → Base plus a bundled mid-level service package (bi-weekly housekeeping, full utilities, dining credit, monthly clinic) with a transparent add-on menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)
+• Overall structure → Bundled all-inclusive service package (weekly housekeeping and linen, daily meal, all utilities, concierge, wellness allowance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte — posted price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specified as (a spec, not a status)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audit: 71 distinct service elements across 11 functions, each classified at all three levels (213 placements). Source of truth is the Service Elements tab; this tab is generated from it, so the two cannot drift apart. The "Specified as" column holds elements whose value at a level is a specification rather than an include/exclude call — for example a level of assistance of "Curb-to-curb", or a work-order response of "Business hours plus emergency line".</t>
   </si>
   <si>
     <t xml:space="preserve">Transportation — what the word actually means</t>
@@ -8075,7 +8549,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8208,6 +8682,18 @@
         <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF8F00"/>
+        <bgColor rgb="FFC55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FF666699"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
@@ -8273,7 +8759,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="120">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8678,6 +9164,54 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8715,7 +9249,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="24">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -8891,6 +9425,22 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBF8F00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF808080"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -8938,7 +9488,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFDEFE8"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFBF8F00"/>
       <rgbColor rgb="FFC55A11"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FFF2F5F9"/>
@@ -8964,6 +9514,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -34143,6 +34697,727 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C4" s="89" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D4" s="101" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E4" s="102" t="s">
+        <v>2268</v>
+      </c>
+      <c r="F4" s="90" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="81" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B5" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="104" t="s">
+        <v>2270</v>
+      </c>
+      <c r="D5" s="105" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E5" s="106" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F5" s="107" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="81"/>
+      <c r="B6" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="109" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D6" s="110" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E6" s="111" t="s">
+        <v>2275</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="81"/>
+      <c r="B7" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="109" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D7" s="110" t="s">
+        <v>2278</v>
+      </c>
+      <c r="E7" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="87" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="104" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D8" s="105" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E8" s="106" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F8" s="107" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="87"/>
+      <c r="B9" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="109" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D9" s="110" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E9" s="111" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="87"/>
+      <c r="B10" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="109" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D10" s="110" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E10" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="104" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D11" s="105" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E11" s="106" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F11" s="107" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="81"/>
+      <c r="B12" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="109" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D12" s="110" t="s">
+        <v>2293</v>
+      </c>
+      <c r="E12" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="81"/>
+      <c r="B13" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="109" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D13" s="110" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E13" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="87" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="104" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D14" s="105" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E14" s="106" t="s">
+        <v>2298</v>
+      </c>
+      <c r="F14" s="107" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="87"/>
+      <c r="B15" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="109" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D15" s="110" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E15" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="87"/>
+      <c r="B16" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="109" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D16" s="110" t="s">
+        <v>2302</v>
+      </c>
+      <c r="E16" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="104" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D17" s="105" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E17" s="106" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F17" s="107" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="81"/>
+      <c r="B18" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="109" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D18" s="110" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E18" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="81"/>
+      <c r="B19" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="109" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D19" s="110" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E19" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="B20" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="104" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D20" s="105" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E20" s="106" t="s">
+        <v>2309</v>
+      </c>
+      <c r="F20" s="107" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="87"/>
+      <c r="B21" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="109" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D21" s="110" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E21" s="111" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="87"/>
+      <c r="B22" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="109" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D22" s="110" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E22" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="81" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="104" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D23" s="105" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E23" s="106" t="s">
+        <v>2319</v>
+      </c>
+      <c r="F23" s="107" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="81"/>
+      <c r="B24" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="109" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D24" s="110" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E24" s="111" t="s">
+        <v>2323</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="81"/>
+      <c r="B25" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="109" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D25" s="110" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E25" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="87" t="s">
+        <v>183</v>
+      </c>
+      <c r="B26" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="104" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D26" s="105" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E26" s="106" t="s">
+        <v>2327</v>
+      </c>
+      <c r="F26" s="107" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="87"/>
+      <c r="B27" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="109" t="s">
+        <v>2329</v>
+      </c>
+      <c r="D27" s="110" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E27" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="87"/>
+      <c r="B28" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="109" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D28" s="110" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E28" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="104" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D29" s="105" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E29" s="106" t="s">
+        <v>2335</v>
+      </c>
+      <c r="F29" s="107" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="81"/>
+      <c r="B30" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="109" t="s">
+        <v>2337</v>
+      </c>
+      <c r="D30" s="110" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E30" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="81"/>
+      <c r="B31" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="109" t="s">
+        <v>2339</v>
+      </c>
+      <c r="D31" s="110" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E31" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="87" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="104" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D32" s="105" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E32" s="106" t="s">
+        <v>2342</v>
+      </c>
+      <c r="F32" s="107" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="87"/>
+      <c r="B33" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="109" t="s">
+        <v>2343</v>
+      </c>
+      <c r="D33" s="110" t="s">
+        <v>2344</v>
+      </c>
+      <c r="E33" s="111" t="s">
+        <v>2345</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="111" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="87"/>
+      <c r="B34" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="109" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D34" s="110" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E34" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="81" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B35" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="104" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D35" s="105" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E35" s="106" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F35" s="107" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="81"/>
+      <c r="B36" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="109" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D36" s="110" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E36" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="81"/>
+      <c r="B37" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="109" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D37" s="110" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E37" s="111" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="100" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B39" s="109" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C39" s="110" t="s">
+        <v>2350</v>
+      </c>
+      <c r="D39" s="111" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="79" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B41" s="79"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="79"/>
+      <c r="F41" s="79"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F37"/>
+  <mergeCells count="13">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A41:F41"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H95"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -34157,12 +35432,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="70" t="s">
-        <v>2264</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="79" t="s">
-        <v>2265</v>
+        <v>2354</v>
       </c>
       <c r="B2" s="79"/>
       <c r="C2" s="79"/>
@@ -34174,7 +35449,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>2266</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34182,240 +35457,240 @@
         <v>1740</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2267</v>
+        <v>2356</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2268</v>
+        <v>2357</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2269</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="101" t="s">
-        <v>2270</v>
+      <c r="A6" s="113" t="s">
+        <v>2359</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>2271</v>
+        <v>2360</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>2272</v>
+        <v>2361</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>2273</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="101" t="s">
-        <v>2274</v>
+      <c r="A7" s="113" t="s">
+        <v>2363</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2275</v>
+        <v>2364</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>2276</v>
+        <v>2365</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2277</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="101" t="s">
-        <v>2278</v>
+      <c r="A8" s="113" t="s">
+        <v>2367</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>2279</v>
+        <v>2368</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>2280</v>
+        <v>2369</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>2281</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="101" t="s">
-        <v>2282</v>
+      <c r="A9" s="113" t="s">
+        <v>2371</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>2283</v>
+        <v>2372</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>2284</v>
+        <v>2373</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>2285</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="101" t="s">
-        <v>2286</v>
+      <c r="A10" s="113" t="s">
+        <v>2375</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>2287</v>
+        <v>2376</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>2288</v>
+        <v>2377</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>2289</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="102" t="s">
-        <v>2290</v>
-      </c>
-      <c r="B11" s="102"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
+      <c r="A11" s="114" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B11" s="114"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>2291</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="71" t="s">
-        <v>2292</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>2293</v>
+        <v>2382</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2294</v>
+        <v>2383</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2295</v>
+        <v>2384</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2296</v>
+        <v>2385</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>2297</v>
+        <v>2386</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>2298</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="101" t="s">
-        <v>2299</v>
+      <c r="B16" s="113" t="s">
+        <v>2388</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>2300</v>
+        <v>2389</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>2301</v>
+        <v>2390</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>2302</v>
+        <v>2391</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>2303</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="101" t="s">
-        <v>2304</v>
+      <c r="B17" s="113" t="s">
+        <v>2393</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>2305</v>
+        <v>2394</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>2306</v>
+        <v>2395</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>2307</v>
+        <v>2396</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>2308</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="101" t="s">
-        <v>2309</v>
+      <c r="B18" s="113" t="s">
+        <v>2398</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>2310</v>
+        <v>2399</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>2311</v>
+        <v>2400</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>2312</v>
+        <v>2401</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>2313</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="101" t="s">
-        <v>2314</v>
+      <c r="B19" s="113" t="s">
+        <v>2403</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>2315</v>
+        <v>2404</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>2316</v>
+        <v>2405</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>2317</v>
+        <v>2406</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>2318</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="101" t="s">
-        <v>2319</v>
+      <c r="B20" s="113" t="s">
+        <v>2408</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>2320</v>
+        <v>2409</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>2321</v>
+        <v>2410</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>2322</v>
+        <v>2411</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>2323</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>2324</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>2293</v>
+        <v>2382</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2325</v>
+        <v>2414</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>2326</v>
+        <v>2415</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2327</v>
+        <v>2416</v>
       </c>
       <c r="E23" s="89" t="s">
         <v>1966</v>
@@ -34431,204 +35706,204 @@
       <c r="A24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="101" t="s">
-        <v>2328</v>
+      <c r="B24" s="113" t="s">
+        <v>2417</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>2329</v>
+        <v>2418</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>2330</v>
+        <v>2419</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>2331</v>
+        <v>2420</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>2332</v>
+        <v>2421</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>2333</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="101" t="s">
-        <v>2334</v>
+      <c r="B25" s="113" t="s">
+        <v>2423</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>2335</v>
+        <v>2424</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>2336</v>
+        <v>2425</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>2337</v>
+        <v>2426</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>2338</v>
+        <v>2427</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>2339</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="101" t="s">
-        <v>2340</v>
+      <c r="B26" s="113" t="s">
+        <v>2429</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>2341</v>
+        <v>2430</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>2342</v>
+        <v>2431</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>2343</v>
+        <v>2432</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>2344</v>
+        <v>2433</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>2345</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B27" s="101" t="s">
-        <v>2346</v>
+      <c r="B27" s="113" t="s">
+        <v>2435</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>2347</v>
+        <v>2436</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>2348</v>
+        <v>2437</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>2349</v>
+        <v>2438</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>2350</v>
+        <v>2439</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>2351</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="101" t="s">
-        <v>2352</v>
+      <c r="B28" s="113" t="s">
+        <v>2441</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>2353</v>
+        <v>2442</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>2354</v>
+        <v>2443</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>2355</v>
+        <v>2444</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>2356</v>
+        <v>2445</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>2357</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B29" s="101" t="s">
-        <v>2358</v>
+      <c r="B29" s="113" t="s">
+        <v>2447</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>2359</v>
+        <v>2448</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>2360</v>
+        <v>2449</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>2361</v>
+        <v>2450</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>2362</v>
+        <v>2451</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>2363</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B30" s="101" t="s">
-        <v>2364</v>
+      <c r="B30" s="113" t="s">
+        <v>2453</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>2365</v>
+        <v>2454</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>2366</v>
+        <v>2455</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>2367</v>
+        <v>2456</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>2368</v>
+        <v>2457</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>2369</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B31" s="101" t="s">
-        <v>2370</v>
+      <c r="B31" s="113" t="s">
+        <v>2459</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>2371</v>
+        <v>2460</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>2372</v>
+        <v>2461</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>2373</v>
+        <v>2462</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>2374</v>
+        <v>2463</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>2375</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B32" s="101" t="s">
+      <c r="B32" s="113" t="s">
         <v>2003</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>2376</v>
+        <v>2465</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>2377</v>
+        <v>2466</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>2004</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>2378</v>
+        <v>2467</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>2006</v>
@@ -34638,33 +35913,33 @@
       <c r="A33" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B33" s="101" t="s">
+      <c r="B33" s="113" t="s">
         <v>2014</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>2379</v>
+        <v>2468</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>2380</v>
+        <v>2469</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>2381</v>
+        <v>2470</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>2382</v>
+        <v>2471</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>2383</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>2384</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="79" t="s">
-        <v>2385</v>
+        <v>2474</v>
       </c>
       <c r="B36" s="79"/>
       <c r="C36" s="79"/>
@@ -34675,467 +35950,467 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>2386</v>
+        <v>2475</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>2387</v>
+        <v>2476</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>2388</v>
+        <v>2477</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2296</v>
+        <v>2385</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>2014</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>2389</v>
+        <v>2478</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>2390</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="34" t="s">
-        <v>2391</v>
+        <v>2480</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>2392</v>
+        <v>2481</v>
       </c>
       <c r="C38" s="72" t="s">
-        <v>2393</v>
+        <v>2482</v>
       </c>
       <c r="D38" s="72" t="s">
-        <v>2394</v>
+        <v>2483</v>
       </c>
       <c r="E38" s="72" t="s">
-        <v>2395</v>
-      </c>
-      <c r="F38" s="103" t="s">
-        <v>2396</v>
+        <v>2484</v>
+      </c>
+      <c r="F38" s="115" t="s">
+        <v>2485</v>
       </c>
       <c r="G38" s="72" t="s">
-        <v>2397</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="75" t="s">
-        <v>2398</v>
+        <v>2487</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>2399</v>
+        <v>2488</v>
       </c>
       <c r="C39" s="76" t="s">
-        <v>2400</v>
+        <v>2489</v>
       </c>
       <c r="D39" s="76" t="s">
-        <v>2401</v>
+        <v>2490</v>
       </c>
       <c r="E39" s="76" t="s">
-        <v>2402</v>
-      </c>
-      <c r="F39" s="103" t="s">
-        <v>2403</v>
+        <v>2491</v>
+      </c>
+      <c r="F39" s="115" t="s">
+        <v>2492</v>
       </c>
       <c r="G39" s="76" t="s">
-        <v>2404</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="34" t="s">
-        <v>2405</v>
+        <v>2494</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>2406</v>
+        <v>2495</v>
       </c>
       <c r="C40" s="72" t="s">
-        <v>2407</v>
+        <v>2496</v>
       </c>
       <c r="D40" s="72" t="s">
-        <v>2408</v>
+        <v>2497</v>
       </c>
       <c r="E40" s="72" t="s">
-        <v>2409</v>
-      </c>
-      <c r="F40" s="103" t="s">
-        <v>2410</v>
+        <v>2498</v>
+      </c>
+      <c r="F40" s="115" t="s">
+        <v>2499</v>
       </c>
       <c r="G40" s="72" t="s">
-        <v>2411</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="75" t="s">
-        <v>2412</v>
+        <v>2501</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>2413</v>
+        <v>2502</v>
       </c>
       <c r="C41" s="76" t="s">
-        <v>2414</v>
+        <v>2503</v>
       </c>
       <c r="D41" s="76" t="s">
-        <v>2415</v>
+        <v>2504</v>
       </c>
       <c r="E41" s="76" t="s">
-        <v>2416</v>
-      </c>
-      <c r="F41" s="103" t="s">
-        <v>2417</v>
+        <v>2505</v>
+      </c>
+      <c r="F41" s="115" t="s">
+        <v>2506</v>
       </c>
       <c r="G41" s="76" t="s">
-        <v>2418</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="34" t="s">
-        <v>2419</v>
+        <v>2508</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>2420</v>
+        <v>2509</v>
       </c>
       <c r="C42" s="72" t="s">
-        <v>2421</v>
+        <v>2510</v>
       </c>
       <c r="D42" s="72" t="s">
-        <v>2422</v>
+        <v>2511</v>
       </c>
       <c r="E42" s="72" t="s">
-        <v>2423</v>
-      </c>
-      <c r="F42" s="103" t="s">
-        <v>2424</v>
+        <v>2512</v>
+      </c>
+      <c r="F42" s="115" t="s">
+        <v>2513</v>
       </c>
       <c r="G42" s="72" t="s">
-        <v>2425</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="75" t="s">
-        <v>2426</v>
+        <v>2515</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>2427</v>
+        <v>2516</v>
       </c>
       <c r="C43" s="76" t="s">
-        <v>2428</v>
+        <v>2517</v>
       </c>
       <c r="D43" s="76" t="s">
-        <v>2429</v>
+        <v>2518</v>
       </c>
       <c r="E43" s="76" t="s">
-        <v>2430</v>
-      </c>
-      <c r="F43" s="103" t="s">
-        <v>2431</v>
+        <v>2519</v>
+      </c>
+      <c r="F43" s="115" t="s">
+        <v>2520</v>
       </c>
       <c r="G43" s="76" t="s">
-        <v>2432</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="34" t="s">
-        <v>2433</v>
+        <v>2522</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>2434</v>
+        <v>2523</v>
       </c>
       <c r="C44" s="72" t="s">
-        <v>2435</v>
+        <v>2524</v>
       </c>
       <c r="D44" s="72" t="s">
-        <v>2436</v>
+        <v>2525</v>
       </c>
       <c r="E44" s="72" t="s">
-        <v>2437</v>
-      </c>
-      <c r="F44" s="103" t="s">
-        <v>2438</v>
+        <v>2526</v>
+      </c>
+      <c r="F44" s="115" t="s">
+        <v>2527</v>
       </c>
       <c r="G44" s="72" t="s">
-        <v>2439</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="75" t="s">
-        <v>2440</v>
+        <v>2529</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>2441</v>
+        <v>2530</v>
       </c>
       <c r="C45" s="76" t="s">
-        <v>2442</v>
+        <v>2531</v>
       </c>
       <c r="D45" s="76" t="s">
-        <v>2443</v>
+        <v>2532</v>
       </c>
       <c r="E45" s="76" t="s">
-        <v>2444</v>
-      </c>
-      <c r="F45" s="103" t="s">
-        <v>2445</v>
+        <v>2533</v>
+      </c>
+      <c r="F45" s="115" t="s">
+        <v>2534</v>
       </c>
       <c r="G45" s="76" t="s">
-        <v>2446</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="34" t="s">
-        <v>2447</v>
+        <v>2536</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>2448</v>
+        <v>2537</v>
       </c>
       <c r="C46" s="72" t="s">
-        <v>2449</v>
+        <v>2538</v>
       </c>
       <c r="D46" s="72" t="s">
-        <v>2450</v>
+        <v>2539</v>
       </c>
       <c r="E46" s="72" t="s">
-        <v>2451</v>
-      </c>
-      <c r="F46" s="103" t="s">
-        <v>2452</v>
+        <v>2540</v>
+      </c>
+      <c r="F46" s="115" t="s">
+        <v>2541</v>
       </c>
       <c r="G46" s="72" t="s">
-        <v>2453</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="75" t="s">
-        <v>2454</v>
+        <v>2543</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>2455</v>
+        <v>2544</v>
       </c>
       <c r="C47" s="76" t="s">
-        <v>2456</v>
+        <v>2545</v>
       </c>
       <c r="D47" s="76" t="s">
-        <v>2457</v>
+        <v>2546</v>
       </c>
       <c r="E47" s="76" t="s">
-        <v>2458</v>
-      </c>
-      <c r="F47" s="104" t="s">
-        <v>2459</v>
+        <v>2547</v>
+      </c>
+      <c r="F47" s="116" t="s">
+        <v>2548</v>
       </c>
       <c r="G47" s="76" t="s">
-        <v>2460</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="34" t="s">
-        <v>2461</v>
+        <v>2550</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>2462</v>
+        <v>2551</v>
       </c>
       <c r="C48" s="72" t="s">
-        <v>2463</v>
+        <v>2552</v>
       </c>
       <c r="D48" s="72" t="s">
-        <v>2464</v>
+        <v>2553</v>
       </c>
       <c r="E48" s="72" t="s">
-        <v>2465</v>
-      </c>
-      <c r="F48" s="105" t="s">
-        <v>2466</v>
+        <v>2554</v>
+      </c>
+      <c r="F48" s="117" t="s">
+        <v>2555</v>
       </c>
       <c r="G48" s="72" t="s">
-        <v>2467</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="75" t="s">
-        <v>2468</v>
+        <v>2557</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>2469</v>
+        <v>2558</v>
       </c>
       <c r="C49" s="76" t="s">
-        <v>2470</v>
+        <v>2559</v>
       </c>
       <c r="D49" s="76" t="s">
-        <v>2471</v>
+        <v>2560</v>
       </c>
       <c r="E49" s="76" t="s">
-        <v>2472</v>
-      </c>
-      <c r="F49" s="104" t="s">
-        <v>2473</v>
+        <v>2561</v>
+      </c>
+      <c r="F49" s="116" t="s">
+        <v>2562</v>
       </c>
       <c r="G49" s="76" t="s">
-        <v>2474</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="34" t="s">
-        <v>2475</v>
+        <v>2564</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>2476</v>
+        <v>2565</v>
       </c>
       <c r="C50" s="72" t="s">
-        <v>2477</v>
+        <v>2566</v>
       </c>
       <c r="D50" s="72" t="s">
-        <v>2478</v>
+        <v>2567</v>
       </c>
       <c r="E50" s="72" t="s">
-        <v>2479</v>
-      </c>
-      <c r="F50" s="104" t="s">
-        <v>2480</v>
+        <v>2568</v>
+      </c>
+      <c r="F50" s="116" t="s">
+        <v>2569</v>
       </c>
       <c r="G50" s="72" t="s">
-        <v>2481</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="75" t="s">
-        <v>2482</v>
+        <v>2571</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>2483</v>
+        <v>2572</v>
       </c>
       <c r="C51" s="76" t="s">
-        <v>2484</v>
+        <v>2573</v>
       </c>
       <c r="D51" s="76" t="s">
-        <v>2485</v>
+        <v>2574</v>
       </c>
       <c r="E51" s="76" t="s">
-        <v>2486</v>
-      </c>
-      <c r="F51" s="103" t="s">
-        <v>2487</v>
+        <v>2575</v>
+      </c>
+      <c r="F51" s="115" t="s">
+        <v>2576</v>
       </c>
       <c r="G51" s="76" t="s">
-        <v>2488</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="34" t="s">
-        <v>2489</v>
+        <v>2578</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>2490</v>
+        <v>2579</v>
       </c>
       <c r="C52" s="72" t="s">
-        <v>2491</v>
+        <v>2580</v>
       </c>
       <c r="D52" s="72" t="s">
-        <v>2492</v>
+        <v>2581</v>
       </c>
       <c r="E52" s="72" t="s">
-        <v>2493</v>
-      </c>
-      <c r="F52" s="105" t="s">
-        <v>2494</v>
+        <v>2582</v>
+      </c>
+      <c r="F52" s="117" t="s">
+        <v>2583</v>
       </c>
       <c r="G52" s="72" t="s">
-        <v>2495</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="75" t="s">
-        <v>2496</v>
+        <v>2585</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>2497</v>
+        <v>2586</v>
       </c>
       <c r="C53" s="76" t="s">
-        <v>2498</v>
+        <v>2587</v>
       </c>
       <c r="D53" s="76" t="s">
-        <v>2499</v>
+        <v>2588</v>
       </c>
       <c r="E53" s="76" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F53" s="105" t="s">
-        <v>2501</v>
+        <v>2589</v>
+      </c>
+      <c r="F53" s="117" t="s">
+        <v>2590</v>
       </c>
       <c r="G53" s="76" t="s">
-        <v>2502</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="34" t="s">
-        <v>2503</v>
+        <v>2592</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>2504</v>
+        <v>2593</v>
       </c>
       <c r="C54" s="72" t="s">
-        <v>2505</v>
+        <v>2594</v>
       </c>
       <c r="D54" s="72" t="s">
-        <v>2506</v>
+        <v>2595</v>
       </c>
       <c r="E54" s="72" t="s">
-        <v>2507</v>
-      </c>
-      <c r="F54" s="105" t="s">
-        <v>2508</v>
+        <v>2596</v>
+      </c>
+      <c r="F54" s="117" t="s">
+        <v>2597</v>
       </c>
       <c r="G54" s="72" t="s">
-        <v>2509</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="75" t="s">
-        <v>2510</v>
+        <v>2599</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>2511</v>
+        <v>2600</v>
       </c>
       <c r="C55" s="76" t="s">
-        <v>2512</v>
+        <v>2601</v>
       </c>
       <c r="D55" s="76" t="s">
-        <v>2513</v>
+        <v>2602</v>
       </c>
       <c r="E55" s="76" t="s">
-        <v>2507</v>
-      </c>
-      <c r="F55" s="104" t="s">
-        <v>2514</v>
+        <v>2596</v>
+      </c>
+      <c r="F55" s="116" t="s">
+        <v>2603</v>
       </c>
       <c r="G55" s="76" t="s">
-        <v>2515</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="34" t="s">
-        <v>2516</v>
+        <v>2605</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>2517</v>
+        <v>2606</v>
       </c>
       <c r="C56" s="72" t="s">
-        <v>2518</v>
+        <v>2607</v>
       </c>
       <c r="D56" s="72" t="s">
-        <v>2519</v>
+        <v>2608</v>
       </c>
       <c r="E56" s="72" t="s">
-        <v>2479</v>
-      </c>
-      <c r="F56" s="105" t="s">
-        <v>2508</v>
+        <v>2568</v>
+      </c>
+      <c r="F56" s="117" t="s">
+        <v>2597</v>
       </c>
       <c r="G56" s="72" t="s">
-        <v>2520</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="79" t="s">
-        <v>2521</v>
+        <v>2610</v>
       </c>
       <c r="B57" s="79"/>
       <c r="C57" s="79"/>
@@ -35146,162 +36421,162 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>2522</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="106" t="s">
-        <v>2523</v>
-      </c>
-      <c r="B60" s="106"/>
-      <c r="C60" s="106"/>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
+      <c r="A60" s="118" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B60" s="118"/>
+      <c r="C60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>2386</v>
+        <v>2475</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>2524</v>
+        <v>2613</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>2525</v>
+        <v>2614</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>2389</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="101" t="s">
-        <v>2526</v>
+      <c r="A62" s="113" t="s">
+        <v>2615</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>2527</v>
+        <v>2616</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>2528</v>
+        <v>2617</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>2529</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="101" t="s">
-        <v>2530</v>
+      <c r="A63" s="113" t="s">
+        <v>2619</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>2531</v>
+        <v>2620</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>2532</v>
+        <v>2621</v>
       </c>
       <c r="D63" s="36" t="s">
-        <v>2529</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="101" t="s">
+      <c r="A64" s="113" t="s">
         <v>727</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>2533</v>
+        <v>2622</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>2534</v>
+        <v>2623</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>2535</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="101" t="s">
-        <v>2536</v>
+      <c r="A65" s="113" t="s">
+        <v>2625</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>2537</v>
+        <v>2626</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>2538</v>
+        <v>2627</v>
       </c>
       <c r="D65" s="36" t="s">
-        <v>2539</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="101" t="s">
-        <v>2540</v>
+      <c r="A66" s="113" t="s">
+        <v>2629</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>2533</v>
+        <v>2622</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>2541</v>
+        <v>2630</v>
       </c>
       <c r="D66" s="43" t="s">
-        <v>2508</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="101" t="s">
-        <v>2542</v>
+      <c r="A67" s="113" t="s">
+        <v>2631</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>2533</v>
+        <v>2622</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>2543</v>
+        <v>2632</v>
       </c>
       <c r="D67" s="43" t="s">
-        <v>2508</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="101" t="s">
-        <v>2544</v>
+      <c r="A68" s="113" t="s">
+        <v>2633</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>2545</v>
+        <v>2634</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>2546</v>
+        <v>2635</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>2547</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="101" t="s">
-        <v>2548</v>
+      <c r="A69" s="113" t="s">
+        <v>2637</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>2549</v>
+        <v>2638</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>2550</v>
+        <v>2639</v>
       </c>
       <c r="D69" s="36" t="s">
-        <v>2551</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="101" t="s">
-        <v>2552</v>
+      <c r="A70" s="113" t="s">
+        <v>2641</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>2553</v>
+        <v>2642</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>2554</v>
-      </c>
-      <c r="D70" s="107" t="s">
-        <v>2555</v>
+        <v>2643</v>
+      </c>
+      <c r="D70" s="119" t="s">
+        <v>2644</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>2556</v>
+        <v>2645</v>
       </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -35311,7 +36586,7 @@
     </row>
     <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>2557</v>
+        <v>2646</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -35321,7 +36596,7 @@
     </row>
     <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>2558</v>
+        <v>2647</v>
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -35331,7 +36606,7 @@
     </row>
     <row r="75" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>2559</v>
+        <v>2648</v>
       </c>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -35341,7 +36616,7 @@
     </row>
     <row r="76" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>2560</v>
+        <v>2649</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -35351,7 +36626,7 @@
     </row>
     <row r="77" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>2561</v>
+        <v>2650</v>
       </c>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -35361,105 +36636,105 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>2562</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>2563</v>
+        <v>2652</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>2564</v>
+        <v>2653</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>2565</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="101" t="s">
-        <v>2566</v>
+      <c r="A81" s="113" t="s">
+        <v>2655</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>2567</v>
+        <v>2656</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>2568</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="101" t="s">
-        <v>2569</v>
+      <c r="A82" s="113" t="s">
+        <v>2658</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>2570</v>
+        <v>2659</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>2571</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="101" t="s">
-        <v>2572</v>
+      <c r="A83" s="113" t="s">
+        <v>2661</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>2573</v>
+        <v>2662</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>2574</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="101" t="s">
-        <v>2575</v>
+      <c r="A84" s="113" t="s">
+        <v>2664</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>2576</v>
+        <v>2665</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>2577</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="101" t="s">
-        <v>2578</v>
+      <c r="A85" s="113" t="s">
+        <v>2667</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>2579</v>
+        <v>2668</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>2580</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="101" t="s">
-        <v>2581</v>
+      <c r="A86" s="113" t="s">
+        <v>2670</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>2582</v>
+        <v>2671</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>2583</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="101" t="s">
-        <v>2584</v>
+      <c r="A87" s="113" t="s">
+        <v>2673</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>2585</v>
+        <v>2674</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>2586</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>2587</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>2588</v>
+        <v>2677</v>
       </c>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -35469,7 +36744,7 @@
     </row>
     <row r="91" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>2589</v>
+        <v>2678</v>
       </c>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -35479,7 +36754,7 @@
     </row>
     <row r="92" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="14" t="s">
-        <v>2590</v>
+        <v>2679</v>
       </c>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -35489,7 +36764,7 @@
     </row>
     <row r="93" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>2591</v>
+        <v>2680</v>
       </c>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -35499,7 +36774,7 @@
     </row>
     <row r="94" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>2592</v>
+        <v>2681</v>
       </c>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -35509,7 +36784,7 @@
     </row>
     <row r="95" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="14" t="s">
-        <v>2593</v>
+        <v>2682</v>
       </c>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -35547,7 +36822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -35565,7 +36840,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="70" t="s">
-        <v>2594</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35573,19 +36848,19 @@
         <v>166</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2595</v>
+        <v>2684</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2596</v>
+        <v>2685</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2597</v>
+        <v>2686</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>2598</v>
+        <v>2687</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>2599</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35599,14 +36874,14 @@
         <v>201</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>2600</v>
+        <v>2689</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Laura Lopez")</f>
         <v>215</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>2601</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35620,14 +36895,14 @@
         <v>1586</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>2602</v>
+        <v>2691</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Ken Witzgall")</f>
         <v>2</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>2603</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35641,14 +36916,14 @@
         <v>1620</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>2604</v>
+        <v>2693</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Scott Wood")</f>
         <v>2</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>2605</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35662,24 +36937,24 @@
         <v>1620</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2606</v>
+        <v>2695</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Jennifer Saxman")</f>
         <v>11</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>2607</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>2608</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>2609</v>
+        <v>2698</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -35689,7 +36964,7 @@
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>2610</v>
+        <v>2699</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -35699,7 +36974,7 @@
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>2611</v>
+        <v>2700</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -35709,7 +36984,7 @@
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>2612</v>
+        <v>2701</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -35719,7 +36994,7 @@
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>2613</v>
+        <v>2702</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -35729,7 +37004,7 @@
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>2614</v>
+        <v>2703</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -35739,7 +37014,7 @@
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>2615</v>
+        <v>2704</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -35749,7 +37024,7 @@
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>2616</v>
+        <v>2705</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -35759,7 +37034,7 @@
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>2617</v>
+        <v>2706</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>

--- a/Cottage_Villa_Service_Benchmark.xlsx
+++ b/Cottage_Villa_Service_Benchmark.xlsx
@@ -13,16 +13,18 @@
     <sheet name="Consolidated Data" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Synthesis" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Good-Better-Best" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Service Elements" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Service Docs Linear" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Transportation Detail" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Sources &amp; Method" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Service Grid (MIM)" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Service Elements" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Service Docs Linear" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Transportation Detail" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Sources &amp; Method" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Consolidated Data'!$A$1:$AI$231</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Good-Better-Best'!$A$4:$F$34</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Service Docs Linear'!$A$4:$F$37</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Service Elements'!$A$4:$H$75</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Service Docs Linear'!$A$4:$F$37</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Service Elements'!$A$4:$H$75</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Service Grid (MIM)'!$A$5:$G$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -80,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7090" uniqueCount="2707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7243" uniqueCount="2795">
   <si>
     <t xml:space="preserve">Cottage &amp; Villa Service Benchmark — Start Here</t>
   </si>
@@ -5971,6 +5973,288 @@
     <t xml:space="preserve">Smith Crossing (per Saxman); Five Star Residences; The Stratford; Twin Lakes; Lake Forest Place; Concordia Life Plan (OKC); Zarrow Pointe</t>
   </si>
   <si>
+    <t xml:space="preserve">Service Grid — five functions, with MIM on every option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The working decision grid. Five functions, each with its service levels, and a MIM column that must read Yes on every option. MIM = for every new resident, the team meets them. It reads Yes on all sixteen rows including both Not Offered states, because the team still meets a new resident to explain what is and is not available at that community. The Confirmed by column carries the speaker and the timestamp from the 17 September call, so any row can be traced back to what was actually said. Rows that nobody has agreed to yet are flagged in the Status column — do not present those as decided.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source of the call evidence: "Connect - cottage services" meeting transcript, 17 September 2026, 16m 48s. Kevin Penn (Culinary), Justin Hollabaugh (Settings: housekeeping and maintenance), Curtis Avison. Transcription started late; Justin's position was re-confirmed on the record at 14:16–15:30.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service offering at this level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed by (speaker and timestamp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled group shuttle on existing routes (shopping, banking, groceries, worship) plus group outings. No individual appointment rides; residents referred to third-party ride services and told so plainly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included in the base fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not discussed on the call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report only — not discussed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BETTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds individually scheduled medical-appointment rides on weekdays, door-to-door, within a defined standard route or county. Posted rate beyond the area and for unscheduled personal rides. Days, hours, booking lead time and capacity rule published.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included, plus a published price list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds a monthly allowance of personal on-demand trips, an on-campus circulator, escorted appointment service, a stated dialysis and recurring-therapy policy, and concierge-booked airport runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All-inclusive fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life Enrichment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full access to the main community calendar, fitness centre, pool and common areas on the same basis as apartment residents. Outings and ticketed events pay-per-use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds cottage-neighbourhood programming: block events, a resident council and a cottage liaison. Excursions and specialty classes priced per use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included, plus priced classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not discussed on the call. NOTE: Curtis raised a weekly happy hour from life enrichment at 14:27, contingent on "they're going to get an extra 8 hours a week".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report only — one related remark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds concierge-booked excursions, specialty classes and personal training funded by a monthly enrichment credit, with priority registration for limited-seat events.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Culinary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT OFFERED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No meal offering at communities where the dining room cannot seat cottage residents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not offered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin 16:01 "you might have to add another category for culinary, which is worst, which means I can't do it." Kevin 11:42 "In a community type where they don't have a large enough dining room, honestly, I don't want to offer anything." Kevin 2:46 gives the case: "if you had a standalone MC and you had villas around it. You have no ability to feed them in the main building."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed on call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dining venues open to cottage residents at posted prices, eaten in the main building. Weekly coffee social or continental breakfast at the clubhouse. Guest meals à la carte. Resident pickup permitted. No delivery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchased — not in the fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin 0:03 "a general rule for me would be you can purchase meals as a meal package or meals a la carte, but you have to come to the main building to eat them." Kevin 12:08 on pickup: "Pick up is better."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds a purchased meal package or à la carte meals, eaten in the main building, plus resident pickup. Available only where the dining room has capacity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin 11:21 "I want to offer a la carte meals or meal packages that a resident can... buy where they come into the main building and eat a meal where that is possible, in community types where that is possible."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A limited included meal allowance, staggered to protect the dining room, rising to an included daily meal only where genuine surplus dining capacity exists and the unit is priced at full IL rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included — capacity-gated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin 4:12 is the ceiling he offered: "I wouldn't give it away... I guess you could include one meal a week or something like that... not every day of the week, and then hope for them to stagger that enough." Curtis 3:50 described the top case: "the best where it's like Plymouth and it's included like an IL apartment at full rate."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partly agreed — Kevin resisted daily inclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings: Housekeeping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No housekeeping offering at communities that cannot staff it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin 15:17 "we'd have to go community by community, because I can't universally say that." Curtis 15:30 gave the case: "an Arbor Grove with four apartments or whatever... if we can, we'll help, but otherwise we're not going to do it."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la carte only, at a published rate on a unit we define. Move-in and move-out turnover clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin 7:47 "moving forward, we would change it to... hey, it's a la carte. Do you want the package, right?" Justin 14:26 "we a la carte includes the packages." Justin 8:55 on who sets the unit: "Yes, yeah, we would define it right."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A defined package available for purchase, plus à la carte add-ons and scheduling. The package contents are not yet defined.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchased. OPEN: the report and the market put bi-weekly INSIDE the fee; Justin framed it as purchased.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin 9:13 "if we were to put a package in place, it would say, we're going to do these 10 things as part of the package." Justin 14:58 conditions: "they have the right equipment, the right people... we determine what that's actually going to be and it's not a loss in revenue."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN — decision needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly housekeeping with flat-linen service included, plus an annual deep clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included in the fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT agreed by Justin. He never agreed to put housekeeping in the fee. Live counter-example: Flourish runs this today and Justin 7:13 said "Yeah, we are right now, but it's got to change", because a proper clean takes "two to three, maybe 4 hours" (6:27).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT CONFIRMED — contradicted by Flourish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings: Maintenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All exterior maintenance, lawn, landscaping, snow and ice, plus repair of community-owned appliances and systems. Business-hours work orders with an emergency line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance was NOT discussed as a separate service line on the recorded portion of the call.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT CONFIRMED with owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds 24-hour emergency maintenance and preventive interior work (filters, detectors, seasonal checks). Resident-requested handyman jobs at a posted rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included, plus a posted handyman rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adds included handyman hours each month, seasonal exterior services (gutters, power-washing, windows) and a scheduled interior refresh cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIM audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live formula. If any option is ever set to something other than Yes, this reads FAIL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status key:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open / partly agreed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not confirmed with the owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report only, not discussed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four decisions still open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Housekeeping at Better and Best: in the fee, or purchased?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The report and the market put bi-weekly housekeeping inside the fee — of the communities that mention housekeeping, 87% include it. Justin framed it as purchased at 14:26. This is the single biggest open item and it decides two rows above.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Is Not Offered a level, or a separate feasibility flag?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It currently sits as a level for Culinary and Housekeeping. It is arguably a capability answer rather than a service level, in which case it should be a per-community flag applied across all five functions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Do we pursue a limited included meal at Culinary Best?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin offered one meal a week, staggered, at 4:12, and resisted daily inclusion. The alternative is to keep Best as dine-in only where surplus capacity genuinely exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Pricing unit for housekeeping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin floated 25 cents per square foot at 8:36, prefaced "we might say". Curtis pushed a structured hour at 8:50. The market supports an hourly rate and a monthly package; nothing in the 215-community study prices housekeeping by square foot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbers that came up on the call but are NOT commitments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who said it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 cents per square foot, minus the garage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin, 8:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypothetical. Prefaced "we might say". Not a rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 to 50 dollars for one hour a week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curtis, 15:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curtis's own illustration. Justin agreed to the good/better/best structure, not to the price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At least 30% product degradation in transit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin, 4:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">His stated figure, and the basis of his refusal to deliver.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two to three, maybe four hours to clean a Flourish cottage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin, 6:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">His stated figure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One FTE a day / an extra 8 hours a week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curtis, 1:13 and 14:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curtis's illustration of the staffing ask, not an agreed amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope note: this grid covers only the five functions requested. The full ten-function recommendation remains on the Good-Better-Best tab. Culinary and Settings rows reflect the 17 September call; Transportation, Life Enrichment and Maintenance reflect the market research only and have not been put to the owning leader.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Service Element Detail — every element, and whether it is Included, À la carte or Not offered at each level</t>
   </si>
   <si>
@@ -5980,15 +6264,6 @@
     <t xml:space="preserve">Service element</t>
   </si>
   <si>
-    <t xml:space="preserve">GOOD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BETTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEST</t>
-  </si>
-  <si>
     <t xml:space="preserve">Market prevalence (villa study, n = 215)</t>
   </si>
   <si>
@@ -6049,9 +6324,6 @@
     <t xml:space="preserve">Trips beyond the included area</t>
   </si>
   <si>
-    <t xml:space="preserve">Not offered</t>
-  </si>
-  <si>
     <t xml:space="preserve">A la carte at a posted per-mile or per-trip rate</t>
   </si>
   <si>
@@ -6860,9 +7132,6 @@
   </si>
   <si>
     <t xml:space="preserve">Legend:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Included in the fee</t>
   </si>
   <si>
     <t xml:space="preserve">À la carte — available at a posted price</t>
@@ -7719,9 +7988,6 @@
   </si>
   <si>
     <t xml:space="preserve">What the operator actually publishes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
   </si>
   <si>
     <t xml:space="preserve">Why it matters</t>
@@ -8418,7 +8684,7 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8542,6 +8808,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -8549,7 +8823,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8559,7 +8833,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333333"/>
+        <bgColor rgb="FF333399"/>
       </patternFill>
     </fill>
     <fill>
@@ -8678,6 +8952,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FF666699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0CECE"/>
+        <bgColor rgb="FFBFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
         <bgColor rgb="FFEDEDED"/>
       </patternFill>
@@ -8686,12 +8972,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBF8F00"/>
         <bgColor rgb="FFC55A11"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF808080"/>
-        <bgColor rgb="FF666699"/>
       </patternFill>
     </fill>
   </fills>
@@ -8759,7 +9039,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="132">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9128,6 +9408,74 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9140,7 +9488,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9160,15 +9508,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9184,7 +9524,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="24" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9204,7 +9544,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9216,20 +9556,8 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -9249,7 +9577,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="26">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -9420,6 +9748,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF808080"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD0CECE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF375623"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFE7E6E6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -9429,14 +9781,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFBF8F00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF808080"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -9460,14 +9804,14 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FFEDEDED"/>
+      <rgbColor rgb="FFD9EAD3"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFF4F6F8"/>
+      <rgbColor rgb="FFF2F5F9"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFD0CECE"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFDF6E3"/>
@@ -9480,18 +9824,18 @@
       <rgbColor rgb="FFEEF6EA"/>
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFFEB9C"/>
-      <rgbColor rgb="FFD9EAD3"/>
+      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFF4F6F8"/>
       <rgbColor rgb="FFFDEFE8"/>
       <rgbColor rgb="FFBF8F00"/>
       <rgbColor rgb="FFC55A11"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FFF2F5F9"/>
+      <rgbColor rgb="FFEDEDED"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -9499,7 +9843,7 @@
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF375623"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -9518,6 +9862,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -9919,6 +10267,248 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="70" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2772</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2773</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2774</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2777</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Laura Lopez")</f>
+        <v>215</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>2779</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Ken Witzgall")</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>2781</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Scott Wood")</f>
+        <v>2</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>2783</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Jennifer Saxman")</f>
+        <v>11</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+    </row>
+    <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>2792</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>2793</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -32865,6 +33455,674 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="79" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+    </row>
+    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E5" s="89" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E6" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F6" s="72" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G6" s="94" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="92"/>
+      <c r="B7" s="90" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E7" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F7" s="72" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G7" s="94" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="92"/>
+      <c r="B8" s="91" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C8" s="95" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D8" s="95" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E8" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G8" s="94" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="96" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E9" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" s="76" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G9" s="94" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="96"/>
+      <c r="B10" s="90" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E10" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G10" s="94" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="96"/>
+      <c r="B11" s="91" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C11" s="95" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D11" s="95" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E11" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" s="76" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G11" s="94" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="92" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B12" s="97" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C12" s="98" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D12" s="98" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E12" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F12" s="72" t="s">
+        <v>1992</v>
+      </c>
+      <c r="G12" s="99" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="92"/>
+      <c r="B13" s="89" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E13" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>1996</v>
+      </c>
+      <c r="G13" s="99" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="92"/>
+      <c r="B14" s="90" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E14" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="72" t="s">
+        <v>1998</v>
+      </c>
+      <c r="G14" s="99" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="92"/>
+      <c r="B15" s="91" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C15" s="95" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D15" s="95" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F15" s="72" t="s">
+        <v>2001</v>
+      </c>
+      <c r="G15" s="100" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="96" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B16" s="97" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C16" s="98" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D16" s="98" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E16" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F16" s="76" t="s">
+        <v>2005</v>
+      </c>
+      <c r="G16" s="99" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="96"/>
+      <c r="B17" s="89" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E17" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F17" s="76" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G17" s="99" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="96"/>
+      <c r="B18" s="90" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>2009</v>
+      </c>
+      <c r="E18" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" s="76" t="s">
+        <v>2010</v>
+      </c>
+      <c r="G18" s="100" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="96"/>
+      <c r="B19" s="91" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C19" s="95" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D19" s="95" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E19" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F19" s="76" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G19" s="101" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="92" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B20" s="89" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E20" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F20" s="72" t="s">
+        <v>2018</v>
+      </c>
+      <c r="G20" s="101" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="92"/>
+      <c r="B21" s="90" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>2021</v>
+      </c>
+      <c r="E21" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F21" s="72" t="s">
+        <v>2018</v>
+      </c>
+      <c r="G21" s="101" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="92"/>
+      <c r="B22" s="91" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C22" s="95" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D22" s="95" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E22" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22" s="72" t="s">
+        <v>2018</v>
+      </c>
+      <c r="G22" s="101" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="102" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="93" t="str">
+        <f aca="false">COUNTIF(E6:E22,"Yes")&amp;" of "&amp;COUNTA(E6:E22)&amp;" options carry MIM = Yes"</f>
+        <v>17 of 17 options carry MIM = Yes</v>
+      </c>
+      <c r="C24" s="93"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="103" t="str">
+        <f aca="false">IF(COUNTIF(E6:E22,"Yes")=COUNTA(E6:E22),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="F24" s="79" t="s">
+        <v>2024</v>
+      </c>
+      <c r="G24" s="79"/>
+    </row>
+    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="104" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E26" s="38" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="105" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B29" s="106" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C29" s="106"/>
+      <c r="D29" s="106"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="106"/>
+    </row>
+    <row r="30" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="105" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B30" s="106" t="s">
+        <v>2033</v>
+      </c>
+      <c r="C30" s="106"/>
+      <c r="D30" s="106"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="106"/>
+    </row>
+    <row r="31" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="105" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B31" s="106" t="s">
+        <v>2035</v>
+      </c>
+      <c r="C31" s="106"/>
+      <c r="D31" s="106"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="106"/>
+    </row>
+    <row r="32" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="105" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B32" s="106" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C32" s="106"/>
+      <c r="D32" s="106"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="106"/>
+      <c r="G32" s="106"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="107" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B36" s="72" t="s">
+        <v>2042</v>
+      </c>
+      <c r="C36" s="72" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="108" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B37" s="76" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C37" s="76" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="107" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B38" s="72" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C38" s="72" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="72"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="108" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B39" s="76" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C39" s="76" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="107" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B40" s="72" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C40" s="72" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+    </row>
+    <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="79" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B42" s="79"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="79"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="79"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:G22"/>
+  <mergeCells count="20">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="A42:G42"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H77"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -32879,12 +34137,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="70" t="s">
-        <v>1963</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="79" t="s">
-        <v>1964</v>
+        <v>2058</v>
       </c>
       <c r="B2" s="79"/>
       <c r="C2" s="79"/>
@@ -32899,299 +34157,299 @@
         <v>64</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1965</v>
+        <v>2059</v>
       </c>
       <c r="C4" s="89" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>1967</v>
+        <v>1975</v>
       </c>
       <c r="E4" s="91" t="s">
-        <v>1968</v>
+        <v>1978</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1969</v>
+        <v>2060</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1970</v>
+        <v>2061</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1971</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="92" t="s">
-        <v>1972</v>
-      </c>
-      <c r="B5" s="93" t="s">
-        <v>1973</v>
-      </c>
-      <c r="C5" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="D5" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="E5" s="94" t="s">
+      <c r="A5" s="109" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B5" s="110" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C5" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" s="111" t="s">
         <v>216</v>
       </c>
       <c r="F5" s="84" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
       <c r="G5" s="84" t="s">
-        <v>1975</v>
+        <v>2066</v>
       </c>
       <c r="H5" s="84" t="s">
-        <v>1976</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="92"/>
+      <c r="A6" s="109"/>
       <c r="B6" s="31" t="s">
-        <v>1977</v>
+        <v>2068</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1978</v>
+        <v>2069</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1978</v>
+        <v>2069</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1979</v>
+        <v>2070</v>
       </c>
       <c r="F6" s="72" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
       <c r="G6" s="72" t="s">
-        <v>1980</v>
+        <v>2071</v>
       </c>
       <c r="H6" s="72" t="s">
-        <v>1981</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="92"/>
+      <c r="A7" s="109"/>
       <c r="B7" s="31" t="s">
-        <v>1982</v>
-      </c>
-      <c r="C7" s="95" t="s">
-        <v>1983</v>
+        <v>2073</v>
+      </c>
+      <c r="C7" s="112" t="s">
+        <v>2074</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1984</v>
+        <v>2075</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>1985</v>
+        <v>2076</v>
       </c>
       <c r="F7" s="72" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
       <c r="G7" s="72" t="s">
-        <v>1986</v>
+        <v>2077</v>
       </c>
       <c r="H7" s="72" t="s">
-        <v>1987</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="92"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="31" t="s">
-        <v>1988</v>
-      </c>
-      <c r="C8" s="95" t="s">
-        <v>1989</v>
+        <v>2079</v>
+      </c>
+      <c r="C8" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>1990</v>
+        <v>2080</v>
       </c>
       <c r="E8" s="43" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>2065</v>
+      </c>
+      <c r="G8" s="72" t="s">
+        <v>2082</v>
+      </c>
+      <c r="H8" s="72" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="109"/>
+      <c r="B9" s="31" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C9" s="112" t="s">
         <v>1991</v>
       </c>
-      <c r="F8" s="72" t="s">
-        <v>1974</v>
-      </c>
-      <c r="G8" s="72" t="s">
-        <v>1992</v>
-      </c>
-      <c r="H8" s="72" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="92"/>
-      <c r="B9" s="31" t="s">
-        <v>1994</v>
-      </c>
-      <c r="C9" s="95" t="s">
-        <v>1989</v>
-      </c>
       <c r="D9" s="43" t="s">
-        <v>1995</v>
+        <v>2085</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>1996</v>
+        <v>2086</v>
       </c>
       <c r="F9" s="72" t="s">
-        <v>1997</v>
+        <v>2087</v>
       </c>
       <c r="G9" s="72" t="s">
-        <v>1998</v>
+        <v>2088</v>
       </c>
       <c r="H9" s="72" t="s">
-        <v>1999</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="92"/>
+      <c r="A10" s="109"/>
       <c r="B10" s="31" t="s">
-        <v>2000</v>
-      </c>
-      <c r="C10" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D10" s="95" t="s">
-        <v>1989</v>
+        <v>2090</v>
+      </c>
+      <c r="C10" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D10" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="E10" s="36" t="s">
         <v>216</v>
       </c>
       <c r="F10" s="72" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
       <c r="G10" s="72" t="s">
-        <v>2001</v>
+        <v>2091</v>
       </c>
       <c r="H10" s="72" t="s">
-        <v>2002</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="92"/>
+      <c r="A11" s="109"/>
       <c r="B11" s="31" t="s">
-        <v>2003</v>
+        <v>2093</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>2004</v>
+        <v>2094</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>2005</v>
+        <v>2095</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>2006</v>
+        <v>2096</v>
       </c>
       <c r="F11" s="72" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
       <c r="G11" s="72" t="s">
-        <v>2007</v>
+        <v>2097</v>
       </c>
       <c r="H11" s="72" t="s">
-        <v>2008</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="92"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="31" t="s">
-        <v>2009</v>
-      </c>
-      <c r="C12" s="95" t="s">
-        <v>1989</v>
+        <v>2099</v>
+      </c>
+      <c r="C12" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>2010</v>
+        <v>2100</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>2011</v>
+        <v>2101</v>
       </c>
       <c r="F12" s="72" t="s">
-        <v>1997</v>
+        <v>2087</v>
       </c>
       <c r="G12" s="72" t="s">
-        <v>2012</v>
+        <v>2102</v>
       </c>
       <c r="H12" s="72" t="s">
-        <v>2013</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="92"/>
+      <c r="A13" s="109"/>
       <c r="B13" s="31" t="s">
-        <v>2014</v>
+        <v>2104</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>2015</v>
+        <v>2105</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>2016</v>
+        <v>2106</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>2017</v>
+        <v>2107</v>
       </c>
       <c r="F13" s="72" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
       <c r="G13" s="72" t="s">
-        <v>2018</v>
+        <v>2108</v>
       </c>
       <c r="H13" s="72" t="s">
-        <v>2019</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="92"/>
+      <c r="A14" s="109"/>
       <c r="B14" s="31" t="s">
-        <v>2020</v>
+        <v>2110</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>2021</v>
+        <v>2111</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>2022</v>
+        <v>2112</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>2023</v>
+        <v>2113</v>
       </c>
       <c r="F14" s="72" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
       <c r="G14" s="72" t="s">
-        <v>2024</v>
+        <v>2114</v>
       </c>
       <c r="H14" s="72" t="s">
-        <v>2025</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="113" t="s">
         <v>178</v>
       </c>
-      <c r="B15" s="97" t="s">
-        <v>2026</v>
-      </c>
-      <c r="C15" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="D15" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="E15" s="94" t="s">
+      <c r="B15" s="114" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C15" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="E15" s="111" t="s">
         <v>216</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>2027</v>
+        <v>2117</v>
       </c>
       <c r="G15" s="88" t="s">
-        <v>2028</v>
+        <v>2118</v>
       </c>
       <c r="H15" s="88" t="s">
-        <v>2029</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="96"/>
+      <c r="A16" s="113"/>
       <c r="B16" s="33" t="s">
-        <v>2030</v>
+        <v>2120</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>216</v>
@@ -33203,22 +34461,22 @@
         <v>216</v>
       </c>
       <c r="F16" s="76" t="s">
-        <v>2031</v>
+        <v>2121</v>
       </c>
       <c r="G16" s="76" t="s">
-        <v>2032</v>
+        <v>2122</v>
       </c>
       <c r="H16" s="76" t="s">
-        <v>2033</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="96"/>
+      <c r="A17" s="113"/>
       <c r="B17" s="33" t="s">
-        <v>2034</v>
-      </c>
-      <c r="C17" s="95" t="s">
-        <v>1989</v>
+        <v>2124</v>
+      </c>
+      <c r="C17" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>216</v>
@@ -33227,1440 +34485,1440 @@
         <v>216</v>
       </c>
       <c r="F17" s="76" t="s">
-        <v>1997</v>
+        <v>2087</v>
       </c>
       <c r="G17" s="76" t="s">
-        <v>2035</v>
+        <v>2125</v>
       </c>
       <c r="H17" s="76" t="s">
-        <v>2036</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="96"/>
+      <c r="A18" s="113"/>
       <c r="B18" s="33" t="s">
-        <v>2037</v>
+        <v>2127</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>2038</v>
+        <v>2128</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>2038</v>
+        <v>2128</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>2039</v>
+        <v>2129</v>
       </c>
       <c r="F18" s="76" t="s">
-        <v>2040</v>
+        <v>2130</v>
       </c>
       <c r="G18" s="76" t="s">
-        <v>2041</v>
+        <v>2131</v>
       </c>
       <c r="H18" s="76" t="s">
-        <v>2042</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="96"/>
+      <c r="A19" s="113"/>
       <c r="B19" s="33" t="s">
-        <v>2043</v>
+        <v>2133</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>2045</v>
+        <v>2135</v>
       </c>
       <c r="F19" s="76" t="s">
-        <v>2046</v>
+        <v>2136</v>
       </c>
       <c r="G19" s="76" t="s">
-        <v>2047</v>
+        <v>2137</v>
       </c>
       <c r="H19" s="76" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="96"/>
+      <c r="A20" s="113"/>
       <c r="B20" s="33" t="s">
-        <v>2048</v>
-      </c>
-      <c r="C20" s="95" t="s">
-        <v>1989</v>
+        <v>2138</v>
+      </c>
+      <c r="C20" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>2049</v>
+        <v>2139</v>
       </c>
       <c r="F20" s="76" t="s">
-        <v>2050</v>
+        <v>2140</v>
       </c>
       <c r="G20" s="76" t="s">
-        <v>2047</v>
+        <v>2137</v>
       </c>
       <c r="H20" s="76" t="s">
-        <v>2051</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="96"/>
+      <c r="A21" s="113"/>
       <c r="B21" s="33" t="s">
-        <v>2052</v>
-      </c>
-      <c r="C21" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D21" s="95" t="s">
-        <v>1989</v>
+        <v>2142</v>
+      </c>
+      <c r="C21" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D21" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="E21" s="36" t="s">
         <v>216</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>1997</v>
+        <v>2087</v>
       </c>
       <c r="G21" s="76" t="s">
-        <v>2053</v>
+        <v>2143</v>
       </c>
       <c r="H21" s="76" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="92" t="s">
+      <c r="A22" s="109" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="93" t="s">
-        <v>2054</v>
-      </c>
-      <c r="C22" s="94" t="s">
-        <v>2055</v>
-      </c>
-      <c r="D22" s="94" t="s">
-        <v>2055</v>
-      </c>
-      <c r="E22" s="94" t="s">
-        <v>2055</v>
+      <c r="B22" s="110" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C22" s="111" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D22" s="111" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E22" s="111" t="s">
+        <v>2145</v>
       </c>
       <c r="F22" s="84" t="s">
-        <v>2056</v>
+        <v>2146</v>
       </c>
       <c r="G22" s="84" t="s">
-        <v>2057</v>
+        <v>2147</v>
       </c>
       <c r="H22" s="84" t="s">
-        <v>2058</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="92"/>
+      <c r="A23" s="109"/>
       <c r="B23" s="31" t="s">
         <v>516</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>2059</v>
+        <v>2149</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>2060</v>
+        <v>2150</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>2061</v>
+        <v>2151</v>
       </c>
       <c r="F23" s="72" t="s">
-        <v>2062</v>
+        <v>2152</v>
       </c>
       <c r="G23" s="72" t="s">
-        <v>2063</v>
+        <v>2153</v>
       </c>
       <c r="H23" s="72" t="s">
-        <v>2064</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="92"/>
+      <c r="A24" s="109"/>
       <c r="B24" s="31" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C24" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>2156</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>2157</v>
+      </c>
+      <c r="F24" s="72" t="s">
+        <v>2158</v>
+      </c>
+      <c r="G24" s="72" t="s">
+        <v>2159</v>
+      </c>
+      <c r="H24" s="72" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="109"/>
+      <c r="B25" s="31" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C25" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F25" s="72" t="s">
+        <v>2164</v>
+      </c>
+      <c r="G25" s="72" t="s">
+        <v>2165</v>
+      </c>
+      <c r="H25" s="72" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="109"/>
+      <c r="B26" s="31" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C26" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>2152</v>
+      </c>
+      <c r="G26" s="72" t="s">
+        <v>2169</v>
+      </c>
+      <c r="H26" s="72" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="109"/>
+      <c r="B27" s="31" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>2172</v>
+      </c>
+      <c r="F27" s="72" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G27" s="72" t="s">
+        <v>2173</v>
+      </c>
+      <c r="H27" s="72" t="s">
         <v>2065</v>
       </c>
-      <c r="C24" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>2066</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>2067</v>
-      </c>
-      <c r="F24" s="72" t="s">
-        <v>2068</v>
-      </c>
-      <c r="G24" s="72" t="s">
-        <v>2069</v>
-      </c>
-      <c r="H24" s="72" t="s">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="92"/>
-      <c r="B25" s="31" t="s">
-        <v>2071</v>
-      </c>
-      <c r="C25" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>2072</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>2073</v>
-      </c>
-      <c r="F25" s="72" t="s">
-        <v>2074</v>
-      </c>
-      <c r="G25" s="72" t="s">
-        <v>2075</v>
-      </c>
-      <c r="H25" s="72" t="s">
-        <v>2076</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="92"/>
-      <c r="B26" s="31" t="s">
-        <v>2077</v>
-      </c>
-      <c r="C26" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>2078</v>
-      </c>
-      <c r="E26" s="43" t="s">
-        <v>2078</v>
-      </c>
-      <c r="F26" s="72" t="s">
-        <v>2062</v>
-      </c>
-      <c r="G26" s="72" t="s">
-        <v>2079</v>
-      </c>
-      <c r="H26" s="72" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="92"/>
-      <c r="B27" s="31" t="s">
-        <v>2081</v>
-      </c>
-      <c r="C27" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>2082</v>
-      </c>
-      <c r="F27" s="72" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G27" s="72" t="s">
-        <v>2083</v>
-      </c>
-      <c r="H27" s="72" t="s">
-        <v>1974</v>
-      </c>
     </row>
     <row r="28" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="92"/>
+      <c r="A28" s="109"/>
       <c r="B28" s="31" t="s">
-        <v>2084</v>
-      </c>
-      <c r="C28" s="95" t="s">
-        <v>1989</v>
+        <v>2174</v>
+      </c>
+      <c r="C28" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>2085</v>
+        <v>2175</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>216</v>
       </c>
       <c r="F28" s="72" t="s">
-        <v>2086</v>
+        <v>2176</v>
       </c>
       <c r="G28" s="72" t="s">
+        <v>2177</v>
+      </c>
+      <c r="H28" s="72" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="109"/>
+      <c r="B29" s="31" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C29" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>2180</v>
+      </c>
+      <c r="F29" s="72" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G29" s="72" t="s">
+        <v>2181</v>
+      </c>
+      <c r="H29" s="72" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="113" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="114" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C30" s="115" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D30" s="111" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E30" s="111" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F30" s="88" t="s">
+        <v>2186</v>
+      </c>
+      <c r="G30" s="88" t="s">
+        <v>2187</v>
+      </c>
+      <c r="H30" s="88" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="113"/>
+      <c r="B31" s="33" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C31" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F31" s="76" t="s">
+        <v>2190</v>
+      </c>
+      <c r="G31" s="76" t="s">
+        <v>2191</v>
+      </c>
+      <c r="H31" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="113"/>
+      <c r="B32" s="33" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C32" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D32" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F32" s="76" t="s">
+        <v>2193</v>
+      </c>
+      <c r="G32" s="76" t="s">
+        <v>2194</v>
+      </c>
+      <c r="H32" s="76" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="113"/>
+      <c r="B33" s="33" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>2197</v>
+      </c>
+      <c r="F33" s="76" t="s">
+        <v>2176</v>
+      </c>
+      <c r="G33" s="76" t="s">
+        <v>2198</v>
+      </c>
+      <c r="H33" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="113"/>
+      <c r="B34" s="33" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C34" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F34" s="76" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G34" s="76" t="s">
+        <v>2200</v>
+      </c>
+      <c r="H34" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="113"/>
+      <c r="B35" s="33" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>2202</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F35" s="76" t="s">
         <v>2087</v>
       </c>
-      <c r="H28" s="72" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="92"/>
-      <c r="B29" s="31" t="s">
-        <v>2089</v>
-      </c>
-      <c r="C29" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E29" s="43" t="s">
-        <v>2090</v>
-      </c>
-      <c r="F29" s="72" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G29" s="72" t="s">
-        <v>2091</v>
-      </c>
-      <c r="H29" s="72" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="96" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" s="97" t="s">
-        <v>2092</v>
-      </c>
-      <c r="C30" s="98" t="s">
-        <v>2093</v>
-      </c>
-      <c r="D30" s="94" t="s">
-        <v>2094</v>
-      </c>
-      <c r="E30" s="94" t="s">
-        <v>2095</v>
-      </c>
-      <c r="F30" s="88" t="s">
-        <v>2096</v>
-      </c>
-      <c r="G30" s="88" t="s">
-        <v>2097</v>
-      </c>
-      <c r="H30" s="88" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="96"/>
-      <c r="B31" s="33" t="s">
-        <v>2099</v>
-      </c>
-      <c r="C31" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D31" s="43" t="s">
-        <v>2078</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F31" s="76" t="s">
-        <v>2100</v>
-      </c>
-      <c r="G31" s="76" t="s">
-        <v>2101</v>
-      </c>
-      <c r="H31" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="96"/>
-      <c r="B32" s="33" t="s">
-        <v>2102</v>
-      </c>
-      <c r="C32" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D32" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>2095</v>
-      </c>
-      <c r="F32" s="76" t="s">
-        <v>2103</v>
-      </c>
-      <c r="G32" s="76" t="s">
-        <v>2104</v>
-      </c>
-      <c r="H32" s="76" t="s">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="96"/>
-      <c r="B33" s="33" t="s">
-        <v>2106</v>
-      </c>
-      <c r="C33" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D33" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>2107</v>
-      </c>
-      <c r="F33" s="76" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G33" s="76" t="s">
-        <v>2108</v>
-      </c>
-      <c r="H33" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="96"/>
-      <c r="B34" s="33" t="s">
-        <v>2109</v>
-      </c>
-      <c r="C34" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D34" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="F34" s="76" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G34" s="76" t="s">
-        <v>2110</v>
-      </c>
-      <c r="H34" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="96"/>
-      <c r="B35" s="33" t="s">
-        <v>2111</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>2112</v>
-      </c>
-      <c r="D35" s="36" t="s">
-        <v>2112</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>2112</v>
-      </c>
-      <c r="F35" s="76" t="s">
-        <v>1997</v>
-      </c>
       <c r="G35" s="76" t="s">
-        <v>2113</v>
+        <v>2203</v>
       </c>
       <c r="H35" s="76" t="s">
-        <v>2114</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="92" t="s">
+      <c r="A36" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="B36" s="93" t="s">
-        <v>2115</v>
-      </c>
-      <c r="C36" s="94" t="s">
-        <v>2116</v>
-      </c>
-      <c r="D36" s="94" t="s">
-        <v>2116</v>
-      </c>
-      <c r="E36" s="94" t="s">
-        <v>2116</v>
+      <c r="B36" s="110" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C36" s="111" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D36" s="111" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E36" s="111" t="s">
+        <v>2206</v>
       </c>
       <c r="F36" s="84" t="s">
-        <v>2117</v>
+        <v>2207</v>
       </c>
       <c r="G36" s="84" t="s">
-        <v>2118</v>
+        <v>2208</v>
       </c>
       <c r="H36" s="84" t="s">
-        <v>2119</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="92"/>
+      <c r="A37" s="109"/>
       <c r="B37" s="31" t="s">
-        <v>2120</v>
-      </c>
-      <c r="C37" s="95" t="s">
-        <v>1989</v>
+        <v>2210</v>
+      </c>
+      <c r="C37" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>2121</v>
+        <v>2211</v>
       </c>
       <c r="E37" s="43" t="s">
-        <v>2122</v>
+        <v>2212</v>
       </c>
       <c r="F37" s="72" t="s">
-        <v>2123</v>
+        <v>2213</v>
       </c>
       <c r="G37" s="72" t="s">
-        <v>2124</v>
+        <v>2214</v>
       </c>
       <c r="H37" s="72" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="92"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="31" t="s">
-        <v>2125</v>
-      </c>
-      <c r="C38" s="95" t="s">
-        <v>1989</v>
+        <v>2215</v>
+      </c>
+      <c r="C38" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>2095</v>
+        <v>2185</v>
       </c>
       <c r="F38" s="72" t="s">
-        <v>2103</v>
+        <v>2193</v>
       </c>
       <c r="G38" s="72" t="s">
-        <v>2126</v>
+        <v>2216</v>
       </c>
       <c r="H38" s="72" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="96" t="s">
+      <c r="A39" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="B39" s="97" t="s">
-        <v>2127</v>
-      </c>
-      <c r="C39" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="D39" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="E39" s="94" t="s">
+      <c r="B39" s="114" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C39" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="D39" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="E39" s="111" t="s">
         <v>216</v>
       </c>
       <c r="F39" s="88" t="s">
-        <v>2128</v>
+        <v>2218</v>
       </c>
       <c r="G39" s="88" t="s">
-        <v>2129</v>
+        <v>2219</v>
       </c>
       <c r="H39" s="88" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="96"/>
+      <c r="A40" s="113"/>
       <c r="B40" s="33" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C40" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F40" s="76" t="s">
+        <v>2221</v>
+      </c>
+      <c r="G40" s="76" t="s">
+        <v>2222</v>
+      </c>
+      <c r="H40" s="76" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="113"/>
+      <c r="B41" s="33" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C41" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>2225</v>
+      </c>
+      <c r="F41" s="76" t="s">
+        <v>2176</v>
+      </c>
+      <c r="G41" s="76" t="s">
+        <v>2226</v>
+      </c>
+      <c r="H41" s="76" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="113"/>
+      <c r="B42" s="33" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>2231</v>
+      </c>
+      <c r="F42" s="76" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G42" s="76" t="s">
+        <v>2233</v>
+      </c>
+      <c r="H42" s="76" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="113"/>
+      <c r="B43" s="33" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C43" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D43" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" s="76" t="s">
+        <v>2236</v>
+      </c>
+      <c r="G43" s="76" t="s">
+        <v>2237</v>
+      </c>
+      <c r="H43" s="76" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="113"/>
+      <c r="B44" s="33" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C44" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F44" s="76" t="s">
         <v>2130</v>
       </c>
-      <c r="C40" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D40" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F40" s="76" t="s">
-        <v>2131</v>
-      </c>
-      <c r="G40" s="76" t="s">
-        <v>2132</v>
-      </c>
-      <c r="H40" s="76" t="s">
-        <v>2133</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="96"/>
-      <c r="B41" s="33" t="s">
+      <c r="G44" s="76" t="s">
+        <v>2137</v>
+      </c>
+      <c r="H44" s="76" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="113"/>
+      <c r="B45" s="33" t="s">
+        <v>2241</v>
+      </c>
+      <c r="C45" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D45" s="43" t="s">
         <v>2134</v>
       </c>
-      <c r="C41" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D41" s="36" t="s">
-        <v>2135</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>2135</v>
-      </c>
-      <c r="F41" s="76" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G41" s="76" t="s">
-        <v>2136</v>
-      </c>
-      <c r="H41" s="76" t="s">
+      <c r="E45" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F45" s="76" t="s">
+        <v>2176</v>
+      </c>
+      <c r="G45" s="76" t="s">
         <v>2137</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="96"/>
-      <c r="B42" s="33" t="s">
-        <v>2138</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>2139</v>
-      </c>
-      <c r="D42" s="5" t="s">
+      <c r="H45" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="109" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" s="110" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C46" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="D46" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="E46" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="F46" s="84" t="s">
+        <v>2243</v>
+      </c>
+      <c r="G46" s="84" t="s">
+        <v>2244</v>
+      </c>
+      <c r="H46" s="84" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="109"/>
+      <c r="B47" s="31" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C47" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F47" s="72" t="s">
+        <v>2247</v>
+      </c>
+      <c r="G47" s="72" t="s">
+        <v>2248</v>
+      </c>
+      <c r="H47" s="72" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="109"/>
+      <c r="B48" s="31" t="s">
+        <v>2249</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D48" s="36" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F48" s="72" t="s">
+        <v>2253</v>
+      </c>
+      <c r="G48" s="72" t="s">
+        <v>2254</v>
+      </c>
+      <c r="H48" s="72" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="109"/>
+      <c r="B49" s="31" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C49" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D49" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F49" s="72" t="s">
+        <v>2257</v>
+      </c>
+      <c r="G49" s="72" t="s">
+        <v>2258</v>
+      </c>
+      <c r="H49" s="72" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="109"/>
+      <c r="B50" s="31" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C50" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D50" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F50" s="72" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G50" s="72" t="s">
+        <v>2261</v>
+      </c>
+      <c r="H50" s="72" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="109"/>
+      <c r="B51" s="31" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C51" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D51" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F51" s="72" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G51" s="72" t="s">
+        <v>2264</v>
+      </c>
+      <c r="H51" s="72" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="109"/>
+      <c r="B52" s="31" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D52" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F52" s="72" t="s">
+        <v>2087</v>
+      </c>
+      <c r="G52" s="72" t="s">
+        <v>2137</v>
+      </c>
+      <c r="H52" s="72" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="113" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" s="114" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C53" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="E53" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="F53" s="88" t="s">
+        <v>2267</v>
+      </c>
+      <c r="G53" s="88" t="s">
+        <v>2268</v>
+      </c>
+      <c r="H53" s="88" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="113"/>
+      <c r="B54" s="33" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F54" s="76" t="s">
         <v>2140</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>2141</v>
-      </c>
-      <c r="F42" s="76" t="s">
-        <v>2142</v>
-      </c>
-      <c r="G42" s="76" t="s">
-        <v>2143</v>
-      </c>
-      <c r="H42" s="76" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="96"/>
-      <c r="B43" s="33" t="s">
-        <v>2145</v>
-      </c>
-      <c r="C43" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D43" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F43" s="76" t="s">
-        <v>2146</v>
-      </c>
-      <c r="G43" s="76" t="s">
-        <v>2147</v>
-      </c>
-      <c r="H43" s="76" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="96"/>
-      <c r="B44" s="33" t="s">
-        <v>2149</v>
-      </c>
-      <c r="C44" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D44" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E44" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="F44" s="76" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G44" s="76" t="s">
-        <v>2047</v>
-      </c>
-      <c r="H44" s="76" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="96"/>
-      <c r="B45" s="33" t="s">
-        <v>2151</v>
-      </c>
-      <c r="C45" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D45" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E45" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="F45" s="76" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G45" s="76" t="s">
-        <v>2047</v>
-      </c>
-      <c r="H45" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="92" t="s">
-        <v>182</v>
-      </c>
-      <c r="B46" s="93" t="s">
-        <v>2152</v>
-      </c>
-      <c r="C46" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="D46" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="E46" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="F46" s="84" t="s">
-        <v>2153</v>
-      </c>
-      <c r="G46" s="84" t="s">
-        <v>2154</v>
-      </c>
-      <c r="H46" s="84" t="s">
-        <v>2155</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="92"/>
-      <c r="B47" s="31" t="s">
-        <v>2156</v>
-      </c>
-      <c r="C47" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D47" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F47" s="72" t="s">
-        <v>2157</v>
-      </c>
-      <c r="G47" s="72" t="s">
-        <v>2158</v>
-      </c>
-      <c r="H47" s="72" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="92"/>
-      <c r="B48" s="31" t="s">
-        <v>2159</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>2160</v>
-      </c>
-      <c r="D48" s="36" t="s">
-        <v>2161</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>2162</v>
-      </c>
-      <c r="F48" s="72" t="s">
-        <v>2163</v>
-      </c>
-      <c r="G48" s="72" t="s">
-        <v>2164</v>
-      </c>
-      <c r="H48" s="72" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="92"/>
-      <c r="B49" s="31" t="s">
-        <v>2166</v>
-      </c>
-      <c r="C49" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D49" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F49" s="72" t="s">
-        <v>2167</v>
-      </c>
-      <c r="G49" s="72" t="s">
-        <v>2168</v>
-      </c>
-      <c r="H49" s="72" t="s">
-        <v>2169</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="92"/>
-      <c r="B50" s="31" t="s">
-        <v>2170</v>
-      </c>
-      <c r="C50" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D50" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F50" s="72" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G50" s="72" t="s">
-        <v>2171</v>
-      </c>
-      <c r="H50" s="72" t="s">
-        <v>2172</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="92"/>
-      <c r="B51" s="31" t="s">
-        <v>2173</v>
-      </c>
-      <c r="C51" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D51" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F51" s="72" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G51" s="72" t="s">
-        <v>2174</v>
-      </c>
-      <c r="H51" s="72" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="92"/>
-      <c r="B52" s="31" t="s">
-        <v>2175</v>
-      </c>
-      <c r="C52" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D52" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E52" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="F52" s="72" t="s">
-        <v>1997</v>
-      </c>
-      <c r="G52" s="72" t="s">
-        <v>2047</v>
-      </c>
-      <c r="H52" s="72" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="96" t="s">
-        <v>183</v>
-      </c>
-      <c r="B53" s="97" t="s">
+      <c r="G54" s="76" t="s">
+        <v>2271</v>
+      </c>
+      <c r="H54" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="113"/>
+      <c r="B55" s="33" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>2275</v>
+      </c>
+      <c r="F55" s="76" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G55" s="76" t="s">
+        <v>2277</v>
+      </c>
+      <c r="H55" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="113"/>
+      <c r="B56" s="33" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C56" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E56" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F56" s="76" t="s">
+        <v>2279</v>
+      </c>
+      <c r="G56" s="76" t="s">
+        <v>2280</v>
+      </c>
+      <c r="H56" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="113"/>
+      <c r="B57" s="33" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E57" s="36" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F57" s="76" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G57" s="76" t="s">
+        <v>2283</v>
+      </c>
+      <c r="H57" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="113"/>
+      <c r="B58" s="33" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C58" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D58" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E58" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F58" s="76" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G58" s="76" t="s">
+        <v>2285</v>
+      </c>
+      <c r="H58" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="113"/>
+      <c r="B59" s="33" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>2287</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>2288</v>
+      </c>
+      <c r="F59" s="76" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G59" s="76" t="s">
+        <v>2289</v>
+      </c>
+      <c r="H59" s="76" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="109" t="s">
+        <v>184</v>
+      </c>
+      <c r="B60" s="110" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C60" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="D60" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="E60" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="F60" s="84" t="s">
+        <v>2292</v>
+      </c>
+      <c r="G60" s="84" t="s">
+        <v>2293</v>
+      </c>
+      <c r="H60" s="84" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="109"/>
+      <c r="B61" s="31" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F61" s="72" t="s">
+        <v>2297</v>
+      </c>
+      <c r="G61" s="72" t="s">
+        <v>2298</v>
+      </c>
+      <c r="H61" s="72" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="109"/>
+      <c r="B62" s="31" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F62" s="72" t="s">
+        <v>2300</v>
+      </c>
+      <c r="G62" s="72" t="s">
+        <v>2301</v>
+      </c>
+      <c r="H62" s="72" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="109"/>
+      <c r="B63" s="31" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C63" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D63" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E63" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F63" s="72" t="s">
+        <v>2303</v>
+      </c>
+      <c r="G63" s="72" t="s">
+        <v>2304</v>
+      </c>
+      <c r="H63" s="72" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="109"/>
+      <c r="B64" s="31" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C64" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D64" s="43" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E64" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F64" s="72" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G64" s="72" t="s">
+        <v>2306</v>
+      </c>
+      <c r="H64" s="72" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="109"/>
+      <c r="B65" s="31" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>2308</v>
+      </c>
+      <c r="E65" s="36" t="s">
+        <v>2309</v>
+      </c>
+      <c r="F65" s="72" t="s">
+        <v>2310</v>
+      </c>
+      <c r="G65" s="72" t="s">
+        <v>2311</v>
+      </c>
+      <c r="H65" s="72" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="113" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="114" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C66" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="D66" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="E66" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="F66" s="88" t="s">
+        <v>2087</v>
+      </c>
+      <c r="G66" s="88" t="s">
+        <v>2314</v>
+      </c>
+      <c r="H66" s="88" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="113"/>
+      <c r="B67" s="33" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C67" s="36" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D67" s="36" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E67" s="36" t="s">
+        <v>2318</v>
+      </c>
+      <c r="F67" s="76" t="s">
+        <v>2319</v>
+      </c>
+      <c r="G67" s="76" t="s">
+        <v>2320</v>
+      </c>
+      <c r="H67" s="76" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="113"/>
+      <c r="B68" s="33" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C68" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D68" s="36" t="s">
+        <v>2323</v>
+      </c>
+      <c r="E68" s="36" t="s">
+        <v>2324</v>
+      </c>
+      <c r="F68" s="76" t="s">
         <v>2176</v>
       </c>
-      <c r="C53" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="D53" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="E53" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="F53" s="88" t="s">
-        <v>2177</v>
-      </c>
-      <c r="G53" s="88" t="s">
-        <v>2178</v>
-      </c>
-      <c r="H53" s="88" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="96"/>
-      <c r="B54" s="33" t="s">
-        <v>2180</v>
-      </c>
-      <c r="C54" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="D54" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F54" s="76" t="s">
-        <v>2050</v>
-      </c>
-      <c r="G54" s="76" t="s">
+      <c r="G68" s="76" t="s">
+        <v>2325</v>
+      </c>
+      <c r="H68" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="113"/>
+      <c r="B69" s="33" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C69" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D69" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E69" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F69" s="76" t="s">
+        <v>2327</v>
+      </c>
+      <c r="G69" s="76" t="s">
+        <v>2328</v>
+      </c>
+      <c r="H69" s="76" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="113"/>
+      <c r="B70" s="33" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C70" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D70" s="36" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E70" s="36" t="s">
+        <v>2331</v>
+      </c>
+      <c r="F70" s="76" t="s">
+        <v>2130</v>
+      </c>
+      <c r="G70" s="76" t="s">
         <v>2181</v>
       </c>
-      <c r="H54" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="96"/>
-      <c r="B55" s="33" t="s">
-        <v>2182</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>2183</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>2184</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>2185</v>
-      </c>
-      <c r="F55" s="76" t="s">
-        <v>2186</v>
-      </c>
-      <c r="G55" s="76" t="s">
-        <v>2187</v>
-      </c>
-      <c r="H55" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="96"/>
-      <c r="B56" s="33" t="s">
-        <v>2188</v>
-      </c>
-      <c r="C56" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D56" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="E56" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F56" s="76" t="s">
-        <v>2189</v>
-      </c>
-      <c r="G56" s="76" t="s">
-        <v>2190</v>
-      </c>
-      <c r="H56" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="96"/>
-      <c r="B57" s="33" t="s">
-        <v>2191</v>
-      </c>
-      <c r="C57" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D57" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E57" s="36" t="s">
-        <v>2192</v>
-      </c>
-      <c r="F57" s="76" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G57" s="76" t="s">
-        <v>2193</v>
-      </c>
-      <c r="H57" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="96"/>
-      <c r="B58" s="33" t="s">
-        <v>2194</v>
-      </c>
-      <c r="C58" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D58" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F58" s="76" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G58" s="76" t="s">
-        <v>2195</v>
-      </c>
-      <c r="H58" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="96"/>
-      <c r="B59" s="33" t="s">
-        <v>2196</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>2197</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>2197</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>2198</v>
-      </c>
-      <c r="F59" s="76" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G59" s="76" t="s">
-        <v>2199</v>
-      </c>
-      <c r="H59" s="76" t="s">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="B60" s="93" t="s">
-        <v>2201</v>
-      </c>
-      <c r="C60" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="D60" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="E60" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="F60" s="84" t="s">
-        <v>2202</v>
-      </c>
-      <c r="G60" s="84" t="s">
-        <v>2203</v>
-      </c>
-      <c r="H60" s="84" t="s">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="92"/>
-      <c r="B61" s="31" t="s">
-        <v>2205</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>2206</v>
-      </c>
-      <c r="D61" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="E61" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F61" s="72" t="s">
-        <v>2207</v>
-      </c>
-      <c r="G61" s="72" t="s">
-        <v>2208</v>
-      </c>
-      <c r="H61" s="72" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="92"/>
-      <c r="B62" s="31" t="s">
-        <v>2209</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>2206</v>
-      </c>
-      <c r="D62" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="E62" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F62" s="72" t="s">
-        <v>2210</v>
-      </c>
-      <c r="G62" s="72" t="s">
-        <v>2211</v>
-      </c>
-      <c r="H62" s="72" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="92"/>
-      <c r="B63" s="31" t="s">
-        <v>2212</v>
-      </c>
-      <c r="C63" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D63" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E63" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F63" s="72" t="s">
-        <v>2213</v>
-      </c>
-      <c r="G63" s="72" t="s">
-        <v>2214</v>
-      </c>
-      <c r="H63" s="72" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="92"/>
-      <c r="B64" s="31" t="s">
-        <v>2215</v>
-      </c>
-      <c r="C64" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D64" s="43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="E64" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F64" s="72" t="s">
-        <v>2186</v>
-      </c>
-      <c r="G64" s="72" t="s">
-        <v>2216</v>
-      </c>
-      <c r="H64" s="72" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="92"/>
-      <c r="B65" s="31" t="s">
-        <v>2217</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>2218</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>2218</v>
-      </c>
-      <c r="E65" s="36" t="s">
-        <v>2219</v>
-      </c>
-      <c r="F65" s="72" t="s">
-        <v>2220</v>
-      </c>
-      <c r="G65" s="72" t="s">
-        <v>2221</v>
-      </c>
-      <c r="H65" s="72" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="96" t="s">
-        <v>134</v>
-      </c>
-      <c r="B66" s="97" t="s">
-        <v>2223</v>
-      </c>
-      <c r="C66" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="D66" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="E66" s="94" t="s">
-        <v>216</v>
-      </c>
-      <c r="F66" s="88" t="s">
-        <v>1997</v>
-      </c>
-      <c r="G66" s="88" t="s">
-        <v>2224</v>
-      </c>
-      <c r="H66" s="88" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="96"/>
-      <c r="B67" s="33" t="s">
-        <v>2225</v>
-      </c>
-      <c r="C67" s="36" t="s">
-        <v>2226</v>
-      </c>
-      <c r="D67" s="36" t="s">
-        <v>2227</v>
-      </c>
-      <c r="E67" s="36" t="s">
-        <v>2228</v>
-      </c>
-      <c r="F67" s="76" t="s">
-        <v>2229</v>
-      </c>
-      <c r="G67" s="76" t="s">
-        <v>2230</v>
-      </c>
-      <c r="H67" s="76" t="s">
-        <v>2231</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="96"/>
-      <c r="B68" s="33" t="s">
-        <v>2232</v>
-      </c>
-      <c r="C68" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D68" s="36" t="s">
-        <v>2233</v>
-      </c>
-      <c r="E68" s="36" t="s">
-        <v>2234</v>
-      </c>
-      <c r="F68" s="76" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G68" s="76" t="s">
-        <v>2235</v>
-      </c>
-      <c r="H68" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="96"/>
-      <c r="B69" s="33" t="s">
-        <v>2236</v>
-      </c>
-      <c r="C69" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D69" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="E69" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F69" s="76" t="s">
-        <v>2237</v>
-      </c>
-      <c r="G69" s="76" t="s">
-        <v>2238</v>
-      </c>
-      <c r="H69" s="76" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="96"/>
-      <c r="B70" s="33" t="s">
-        <v>2239</v>
-      </c>
-      <c r="C70" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D70" s="36" t="s">
-        <v>2240</v>
-      </c>
-      <c r="E70" s="36" t="s">
-        <v>2241</v>
-      </c>
-      <c r="F70" s="76" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G70" s="76" t="s">
-        <v>2091</v>
-      </c>
       <c r="H70" s="76" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="96"/>
+      <c r="A71" s="113"/>
       <c r="B71" s="33" t="s">
-        <v>2242</v>
-      </c>
-      <c r="C71" s="95" t="s">
-        <v>1989</v>
+        <v>2332</v>
+      </c>
+      <c r="C71" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="D71" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="E71" s="36" t="s">
         <v>216</v>
       </c>
       <c r="F71" s="76" t="s">
-        <v>1997</v>
+        <v>2087</v>
       </c>
       <c r="G71" s="76" t="s">
-        <v>2243</v>
+        <v>2333</v>
       </c>
       <c r="H71" s="76" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="96"/>
+      <c r="A72" s="113"/>
       <c r="B72" s="33" t="s">
-        <v>2244</v>
+        <v>2334</v>
       </c>
       <c r="C72" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="D72" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="E72" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>2050</v>
+        <v>2140</v>
       </c>
       <c r="G72" s="76" t="s">
-        <v>2245</v>
+        <v>2335</v>
       </c>
       <c r="H72" s="76" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="96"/>
+      <c r="A73" s="113"/>
       <c r="B73" s="33" t="s">
-        <v>2246</v>
+        <v>2336</v>
       </c>
       <c r="C73" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="D73" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="E73" s="43" t="s">
-        <v>2044</v>
+        <v>2134</v>
       </c>
       <c r="F73" s="76" t="s">
-        <v>2247</v>
+        <v>2337</v>
       </c>
       <c r="G73" s="76" t="s">
-        <v>2248</v>
+        <v>2338</v>
       </c>
       <c r="H73" s="76" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="96"/>
+      <c r="A74" s="113"/>
       <c r="B74" s="33" t="s">
-        <v>2249</v>
-      </c>
-      <c r="C74" s="95" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D74" s="95" t="s">
-        <v>1989</v>
+        <v>2339</v>
+      </c>
+      <c r="C74" s="112" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D74" s="112" t="s">
+        <v>1991</v>
       </c>
       <c r="E74" s="36" t="s">
         <v>216</v>
       </c>
       <c r="F74" s="76" t="s">
-        <v>2086</v>
+        <v>2176</v>
       </c>
       <c r="G74" s="76" t="s">
-        <v>2250</v>
+        <v>2340</v>
       </c>
       <c r="H74" s="76" t="s">
-        <v>2251</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="92" t="s">
-        <v>2252</v>
-      </c>
-      <c r="B75" s="93" t="s">
-        <v>2253</v>
-      </c>
-      <c r="C75" s="99" t="s">
-        <v>2254</v>
-      </c>
-      <c r="D75" s="99" t="s">
-        <v>2255</v>
-      </c>
-      <c r="E75" s="99" t="s">
-        <v>2256</v>
+      <c r="A75" s="109" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B75" s="110" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C75" s="116" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D75" s="116" t="s">
+        <v>2345</v>
+      </c>
+      <c r="E75" s="116" t="s">
+        <v>2346</v>
       </c>
       <c r="F75" s="84" t="s">
-        <v>1997</v>
+        <v>2087</v>
       </c>
       <c r="G75" s="84" t="s">
-        <v>2257</v>
+        <v>2347</v>
       </c>
       <c r="H75" s="84" t="s">
-        <v>2258</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="100" t="s">
-        <v>2259</v>
+      <c r="A77" s="104" t="s">
+        <v>2349</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>2260</v>
+        <v>2013</v>
       </c>
       <c r="C77" s="43" t="s">
-        <v>2261</v>
-      </c>
-      <c r="D77" s="95" t="s">
-        <v>2262</v>
+        <v>2350</v>
+      </c>
+      <c r="D77" s="112" t="s">
+        <v>2351</v>
       </c>
       <c r="F77" s="79" t="s">
-        <v>2263</v>
+        <v>2352</v>
       </c>
       <c r="G77" s="79"/>
       <c r="H77" s="79"/>
@@ -34692,7 +35950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -34709,12 +35967,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>2264</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>2265</v>
+        <v>2354</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -34730,654 +35988,654 @@
         <v>1844</v>
       </c>
       <c r="C4" s="89" t="s">
-        <v>2266</v>
-      </c>
-      <c r="D4" s="101" t="s">
-        <v>2267</v>
-      </c>
-      <c r="E4" s="102" t="s">
-        <v>2268</v>
+        <v>2355</v>
+      </c>
+      <c r="D4" s="117" t="s">
+        <v>2356</v>
+      </c>
+      <c r="E4" s="97" t="s">
+        <v>2357</v>
       </c>
       <c r="F4" s="90" t="s">
-        <v>2269</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="81" t="s">
-        <v>1972</v>
-      </c>
-      <c r="B5" s="103" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B5" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="104" t="s">
-        <v>2270</v>
-      </c>
-      <c r="D5" s="105" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E5" s="106" t="s">
-        <v>2271</v>
-      </c>
-      <c r="F5" s="107" t="s">
-        <v>2272</v>
+      <c r="C5" s="119" t="s">
+        <v>2359</v>
+      </c>
+      <c r="D5" s="120" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E5" s="121" t="s">
+        <v>2360</v>
+      </c>
+      <c r="F5" s="122" t="s">
+        <v>2361</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="81"/>
-      <c r="B6" s="108" t="s">
+      <c r="B6" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="109" t="s">
-        <v>2273</v>
-      </c>
-      <c r="D6" s="110" t="s">
-        <v>2274</v>
-      </c>
-      <c r="E6" s="111" t="s">
-        <v>2275</v>
+      <c r="C6" s="124" t="s">
+        <v>2362</v>
+      </c>
+      <c r="D6" s="125" t="s">
+        <v>2363</v>
+      </c>
+      <c r="E6" s="126" t="s">
+        <v>2364</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>2276</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="81"/>
-      <c r="B7" s="112" t="s">
+      <c r="B7" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="109" t="s">
-        <v>2277</v>
-      </c>
-      <c r="D7" s="110" t="s">
-        <v>2278</v>
-      </c>
-      <c r="E7" s="111" t="s">
-        <v>1974</v>
+      <c r="C7" s="124" t="s">
+        <v>2366</v>
+      </c>
+      <c r="D7" s="125" t="s">
+        <v>2367</v>
+      </c>
+      <c r="E7" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>2279</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="87" t="s">
         <v>178</v>
       </c>
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="104" t="s">
-        <v>2280</v>
-      </c>
-      <c r="D8" s="105" t="s">
-        <v>2281</v>
-      </c>
-      <c r="E8" s="106" t="s">
-        <v>2282</v>
-      </c>
-      <c r="F8" s="107" t="s">
-        <v>1974</v>
+      <c r="C8" s="119" t="s">
+        <v>2369</v>
+      </c>
+      <c r="D8" s="120" t="s">
+        <v>2370</v>
+      </c>
+      <c r="E8" s="121" t="s">
+        <v>2371</v>
+      </c>
+      <c r="F8" s="122" t="s">
+        <v>2065</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="87"/>
-      <c r="B9" s="108" t="s">
+      <c r="B9" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="109" t="s">
-        <v>2283</v>
-      </c>
-      <c r="D9" s="110" t="s">
-        <v>2284</v>
-      </c>
-      <c r="E9" s="111" t="s">
-        <v>2285</v>
+      <c r="C9" s="124" t="s">
+        <v>2372</v>
+      </c>
+      <c r="D9" s="125" t="s">
+        <v>2373</v>
+      </c>
+      <c r="E9" s="126" t="s">
+        <v>2374</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="87"/>
-      <c r="B10" s="112" t="s">
+      <c r="B10" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="109" t="s">
-        <v>2286</v>
-      </c>
-      <c r="D10" s="110" t="s">
-        <v>2287</v>
-      </c>
-      <c r="E10" s="111" t="s">
-        <v>1974</v>
+      <c r="C10" s="124" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D10" s="125" t="s">
+        <v>2376</v>
+      </c>
+      <c r="E10" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="81" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="104" t="s">
-        <v>2288</v>
-      </c>
-      <c r="D11" s="105" t="s">
-        <v>2289</v>
-      </c>
-      <c r="E11" s="106" t="s">
-        <v>2290</v>
-      </c>
-      <c r="F11" s="107" t="s">
-        <v>2291</v>
+      <c r="C11" s="119" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D11" s="120" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E11" s="121" t="s">
+        <v>2379</v>
+      </c>
+      <c r="F11" s="122" t="s">
+        <v>2380</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="81"/>
-      <c r="B12" s="108" t="s">
+      <c r="B12" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="109" t="s">
-        <v>2292</v>
-      </c>
-      <c r="D12" s="110" t="s">
-        <v>2293</v>
-      </c>
-      <c r="E12" s="111" t="s">
-        <v>1974</v>
+      <c r="C12" s="124" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D12" s="125" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E12" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="81"/>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="109" t="s">
-        <v>2294</v>
-      </c>
-      <c r="D13" s="110" t="s">
-        <v>2295</v>
-      </c>
-      <c r="E13" s="111" t="s">
-        <v>1974</v>
+      <c r="C13" s="124" t="s">
+        <v>2383</v>
+      </c>
+      <c r="D13" s="125" t="s">
+        <v>2384</v>
+      </c>
+      <c r="E13" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="103" t="s">
+      <c r="B14" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="104" t="s">
-        <v>2296</v>
-      </c>
-      <c r="D14" s="105" t="s">
-        <v>2297</v>
-      </c>
-      <c r="E14" s="106" t="s">
-        <v>2298</v>
-      </c>
-      <c r="F14" s="107" t="s">
-        <v>1974</v>
+      <c r="C14" s="119" t="s">
+        <v>2385</v>
+      </c>
+      <c r="D14" s="120" t="s">
+        <v>2386</v>
+      </c>
+      <c r="E14" s="121" t="s">
+        <v>2387</v>
+      </c>
+      <c r="F14" s="122" t="s">
+        <v>2065</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="87"/>
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="109" t="s">
-        <v>2299</v>
-      </c>
-      <c r="D15" s="110" t="s">
-        <v>2300</v>
-      </c>
-      <c r="E15" s="111" t="s">
-        <v>1974</v>
+      <c r="C15" s="124" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D15" s="125" t="s">
+        <v>2389</v>
+      </c>
+      <c r="E15" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="87"/>
-      <c r="B16" s="112" t="s">
+      <c r="B16" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="109" t="s">
-        <v>2301</v>
-      </c>
-      <c r="D16" s="110" t="s">
-        <v>2302</v>
-      </c>
-      <c r="E16" s="111" t="s">
-        <v>1974</v>
+      <c r="C16" s="124" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D16" s="125" t="s">
+        <v>2391</v>
+      </c>
+      <c r="E16" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="81" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="104" t="s">
-        <v>2303</v>
-      </c>
-      <c r="D17" s="105" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E17" s="106" t="s">
-        <v>2304</v>
-      </c>
-      <c r="F17" s="107" t="s">
-        <v>1974</v>
+      <c r="C17" s="119" t="s">
+        <v>2392</v>
+      </c>
+      <c r="D17" s="120" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E17" s="121" t="s">
+        <v>2393</v>
+      </c>
+      <c r="F17" s="122" t="s">
+        <v>2065</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="81"/>
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="109" t="s">
-        <v>2303</v>
-      </c>
-      <c r="D18" s="110" t="s">
-        <v>2305</v>
-      </c>
-      <c r="E18" s="111" t="s">
-        <v>1974</v>
+      <c r="C18" s="124" t="s">
+        <v>2392</v>
+      </c>
+      <c r="D18" s="125" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E18" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="81"/>
-      <c r="B19" s="112" t="s">
+      <c r="B19" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="109" t="s">
-        <v>2306</v>
-      </c>
-      <c r="D19" s="110" t="s">
-        <v>2307</v>
-      </c>
-      <c r="E19" s="111" t="s">
-        <v>1974</v>
+      <c r="C19" s="124" t="s">
+        <v>2395</v>
+      </c>
+      <c r="D19" s="125" t="s">
+        <v>2396</v>
+      </c>
+      <c r="E19" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="87" t="s">
         <v>181</v>
       </c>
-      <c r="B20" s="103" t="s">
+      <c r="B20" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="104" t="s">
-        <v>2308</v>
-      </c>
-      <c r="D20" s="105" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E20" s="106" t="s">
-        <v>2309</v>
-      </c>
-      <c r="F20" s="107" t="s">
-        <v>2310</v>
+      <c r="C20" s="119" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D20" s="120" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>2398</v>
+      </c>
+      <c r="F20" s="122" t="s">
+        <v>2399</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="87"/>
-      <c r="B21" s="108" t="s">
+      <c r="B21" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="109" t="s">
-        <v>2311</v>
-      </c>
-      <c r="D21" s="110" t="s">
-        <v>2312</v>
-      </c>
-      <c r="E21" s="111" t="s">
-        <v>2313</v>
+      <c r="C21" s="124" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D21" s="125" t="s">
+        <v>2401</v>
+      </c>
+      <c r="E21" s="126" t="s">
+        <v>2402</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>2314</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="87"/>
-      <c r="B22" s="112" t="s">
+      <c r="B22" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="109" t="s">
-        <v>2315</v>
-      </c>
-      <c r="D22" s="110" t="s">
-        <v>2312</v>
-      </c>
-      <c r="E22" s="111" t="s">
-        <v>1974</v>
+      <c r="C22" s="124" t="s">
+        <v>2404</v>
+      </c>
+      <c r="D22" s="125" t="s">
+        <v>2401</v>
+      </c>
+      <c r="E22" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>2316</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="81" t="s">
         <v>182</v>
       </c>
-      <c r="B23" s="103" t="s">
+      <c r="B23" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="104" t="s">
-        <v>2317</v>
-      </c>
-      <c r="D23" s="105" t="s">
-        <v>2318</v>
-      </c>
-      <c r="E23" s="106" t="s">
-        <v>2319</v>
-      </c>
-      <c r="F23" s="107" t="s">
-        <v>2320</v>
+      <c r="C23" s="119" t="s">
+        <v>2406</v>
+      </c>
+      <c r="D23" s="120" t="s">
+        <v>2407</v>
+      </c>
+      <c r="E23" s="121" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F23" s="122" t="s">
+        <v>2409</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="81"/>
-      <c r="B24" s="108" t="s">
+      <c r="B24" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="109" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D24" s="110" t="s">
-        <v>2322</v>
-      </c>
-      <c r="E24" s="111" t="s">
-        <v>2323</v>
+      <c r="C24" s="124" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D24" s="125" t="s">
+        <v>2411</v>
+      </c>
+      <c r="E24" s="126" t="s">
+        <v>2412</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="81"/>
-      <c r="B25" s="112" t="s">
+      <c r="B25" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="109" t="s">
-        <v>2324</v>
-      </c>
-      <c r="D25" s="110" t="s">
-        <v>2318</v>
-      </c>
-      <c r="E25" s="111" t="s">
-        <v>1974</v>
+      <c r="C25" s="124" t="s">
+        <v>2413</v>
+      </c>
+      <c r="D25" s="125" t="s">
+        <v>2407</v>
+      </c>
+      <c r="E25" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="87" t="s">
         <v>183</v>
       </c>
-      <c r="B26" s="103" t="s">
+      <c r="B26" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="104" t="s">
-        <v>2325</v>
-      </c>
-      <c r="D26" s="105" t="s">
-        <v>2326</v>
-      </c>
-      <c r="E26" s="106" t="s">
-        <v>2327</v>
-      </c>
-      <c r="F26" s="107" t="s">
-        <v>2328</v>
+      <c r="C26" s="119" t="s">
+        <v>2414</v>
+      </c>
+      <c r="D26" s="120" t="s">
+        <v>2415</v>
+      </c>
+      <c r="E26" s="121" t="s">
+        <v>2416</v>
+      </c>
+      <c r="F26" s="122" t="s">
+        <v>2417</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="87"/>
-      <c r="B27" s="108" t="s">
+      <c r="B27" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="109" t="s">
-        <v>2329</v>
-      </c>
-      <c r="D27" s="110" t="s">
-        <v>2330</v>
-      </c>
-      <c r="E27" s="111" t="s">
-        <v>1974</v>
+      <c r="C27" s="124" t="s">
+        <v>2418</v>
+      </c>
+      <c r="D27" s="125" t="s">
+        <v>2419</v>
+      </c>
+      <c r="E27" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>2331</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="87"/>
-      <c r="B28" s="112" t="s">
+      <c r="B28" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="109" t="s">
-        <v>2332</v>
-      </c>
-      <c r="D28" s="110" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E28" s="111" t="s">
-        <v>1974</v>
+      <c r="C28" s="124" t="s">
+        <v>2421</v>
+      </c>
+      <c r="D28" s="125" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E28" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>2333</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="81" t="s">
         <v>184</v>
       </c>
-      <c r="B29" s="103" t="s">
+      <c r="B29" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="104" t="s">
-        <v>2334</v>
-      </c>
-      <c r="D29" s="105" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E29" s="106" t="s">
-        <v>2335</v>
-      </c>
-      <c r="F29" s="107" t="s">
-        <v>2336</v>
+      <c r="C29" s="119" t="s">
+        <v>2423</v>
+      </c>
+      <c r="D29" s="120" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E29" s="121" t="s">
+        <v>2424</v>
+      </c>
+      <c r="F29" s="122" t="s">
+        <v>2425</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="81"/>
-      <c r="B30" s="108" t="s">
+      <c r="B30" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="109" t="s">
-        <v>2337</v>
-      </c>
-      <c r="D30" s="110" t="s">
-        <v>2335</v>
-      </c>
-      <c r="E30" s="111" t="s">
-        <v>1974</v>
+      <c r="C30" s="124" t="s">
+        <v>2426</v>
+      </c>
+      <c r="D30" s="125" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E30" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>2338</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="81"/>
-      <c r="B31" s="112" t="s">
+      <c r="B31" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="109" t="s">
-        <v>2339</v>
-      </c>
-      <c r="D31" s="110" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E31" s="111" t="s">
-        <v>1974</v>
+      <c r="C31" s="124" t="s">
+        <v>2428</v>
+      </c>
+      <c r="D31" s="125" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E31" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="103" t="s">
+      <c r="B32" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="104" t="s">
-        <v>2340</v>
-      </c>
-      <c r="D32" s="105" t="s">
-        <v>2341</v>
-      </c>
-      <c r="E32" s="106" t="s">
-        <v>2342</v>
-      </c>
-      <c r="F32" s="107" t="s">
-        <v>1974</v>
+      <c r="C32" s="119" t="s">
+        <v>2429</v>
+      </c>
+      <c r="D32" s="120" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E32" s="121" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F32" s="122" t="s">
+        <v>2065</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="87"/>
-      <c r="B33" s="108" t="s">
+      <c r="B33" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="109" t="s">
-        <v>2343</v>
-      </c>
-      <c r="D33" s="110" t="s">
-        <v>2344</v>
-      </c>
-      <c r="E33" s="111" t="s">
-        <v>2345</v>
+      <c r="C33" s="124" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D33" s="125" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E33" s="126" t="s">
+        <v>2434</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="111" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="87"/>
-      <c r="B34" s="112" t="s">
+      <c r="B34" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="109" t="s">
-        <v>2346</v>
-      </c>
-      <c r="D34" s="110" t="s">
-        <v>2341</v>
-      </c>
-      <c r="E34" s="111" t="s">
-        <v>1974</v>
+      <c r="C34" s="124" t="s">
+        <v>2435</v>
+      </c>
+      <c r="D34" s="125" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E34" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>1974</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="81" t="s">
-        <v>2252</v>
-      </c>
-      <c r="B35" s="103" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B35" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="104" t="s">
-        <v>1974</v>
-      </c>
-      <c r="D35" s="105" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E35" s="106" t="s">
-        <v>1974</v>
-      </c>
-      <c r="F35" s="107" t="s">
-        <v>2347</v>
+      <c r="C35" s="119" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D35" s="120" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E35" s="121" t="s">
+        <v>2065</v>
+      </c>
+      <c r="F35" s="122" t="s">
+        <v>2436</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="81"/>
-      <c r="B36" s="108" t="s">
+      <c r="B36" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="109" t="s">
-        <v>1974</v>
-      </c>
-      <c r="D36" s="110" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E36" s="111" t="s">
-        <v>1974</v>
+      <c r="C36" s="124" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D36" s="125" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E36" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>2348</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="81"/>
-      <c r="B37" s="112" t="s">
+      <c r="B37" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="109" t="s">
-        <v>1974</v>
-      </c>
-      <c r="D37" s="110" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E37" s="111" t="s">
-        <v>1974</v>
+      <c r="C37" s="124" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D37" s="125" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E37" s="126" t="s">
+        <v>2065</v>
       </c>
       <c r="F37" s="26" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="104" t="s">
         <v>2349</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="100" t="s">
-        <v>2259</v>
-      </c>
-      <c r="B39" s="109" t="s">
-        <v>2260</v>
-      </c>
-      <c r="C39" s="110" t="s">
-        <v>2350</v>
-      </c>
-      <c r="D39" s="111" t="s">
-        <v>1989</v>
+      <c r="B39" s="124" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C39" s="125" t="s">
+        <v>2439</v>
+      </c>
+      <c r="D39" s="126" t="s">
+        <v>1991</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>2351</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="79" t="s">
-        <v>2352</v>
+        <v>2441</v>
       </c>
       <c r="B41" s="79"/>
       <c r="C41" s="79"/>
@@ -35413,7 +36671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -35432,12 +36690,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="70" t="s">
-        <v>2353</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="79" t="s">
-        <v>2354</v>
+        <v>2443</v>
       </c>
       <c r="B2" s="79"/>
       <c r="C2" s="79"/>
@@ -35449,7 +36707,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>2355</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35457,489 +36715,489 @@
         <v>1740</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2356</v>
+        <v>2445</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2357</v>
+        <v>2446</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2358</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="113" t="s">
-        <v>2359</v>
+      <c r="A6" s="128" t="s">
+        <v>2448</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>2360</v>
+        <v>2449</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>2361</v>
+        <v>2450</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>2362</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="113" t="s">
-        <v>2363</v>
+      <c r="A7" s="128" t="s">
+        <v>2452</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2364</v>
+        <v>2453</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>2365</v>
+        <v>2454</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2366</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="113" t="s">
-        <v>2367</v>
+      <c r="A8" s="128" t="s">
+        <v>2456</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>2368</v>
+        <v>2457</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>2369</v>
+        <v>2458</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>2370</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="113" t="s">
-        <v>2371</v>
+      <c r="A9" s="128" t="s">
+        <v>2460</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>2372</v>
+        <v>2461</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>2373</v>
+        <v>2462</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>2374</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="113" t="s">
-        <v>2375</v>
+      <c r="A10" s="128" t="s">
+        <v>2464</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>2376</v>
+        <v>2465</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>2377</v>
+        <v>2466</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>2378</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="114" t="s">
-        <v>2379</v>
-      </c>
-      <c r="B11" s="114"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
+      <c r="A11" s="129" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>2380</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="71" t="s">
-        <v>2381</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>2382</v>
+        <v>2471</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2383</v>
+        <v>2472</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2384</v>
+        <v>2473</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2385</v>
+        <v>2474</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>2386</v>
+        <v>2475</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>2387</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="113" t="s">
-        <v>2388</v>
+      <c r="B16" s="128" t="s">
+        <v>2477</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>2389</v>
+        <v>2478</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>2390</v>
+        <v>2479</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>2391</v>
+        <v>2480</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>2392</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="113" t="s">
-        <v>2393</v>
+      <c r="B17" s="128" t="s">
+        <v>2482</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>2394</v>
+        <v>2483</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>2395</v>
+        <v>2484</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>2396</v>
+        <v>2485</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>2397</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="113" t="s">
-        <v>2398</v>
+      <c r="B18" s="128" t="s">
+        <v>2487</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>2399</v>
+        <v>2488</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>2400</v>
+        <v>2489</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>2401</v>
+        <v>2490</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>2402</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="113" t="s">
-        <v>2403</v>
+      <c r="B19" s="128" t="s">
+        <v>2492</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>2404</v>
+        <v>2493</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>2405</v>
+        <v>2494</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>2406</v>
+        <v>2495</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>2407</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="113" t="s">
-        <v>2408</v>
+      <c r="B20" s="128" t="s">
+        <v>2497</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>2409</v>
+        <v>2498</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>2410</v>
+        <v>2499</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>2411</v>
+        <v>2500</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>2412</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>2413</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>2382</v>
+        <v>2471</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2414</v>
+        <v>2503</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>2415</v>
+        <v>2504</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2416</v>
+        <v>2505</v>
       </c>
       <c r="E23" s="89" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="F23" s="90" t="s">
-        <v>1967</v>
+        <v>1975</v>
       </c>
       <c r="G23" s="91" t="s">
-        <v>1968</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="113" t="s">
-        <v>2417</v>
+      <c r="B24" s="128" t="s">
+        <v>2506</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>2418</v>
+        <v>2507</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>2419</v>
+        <v>2508</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>2420</v>
+        <v>2509</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>2421</v>
+        <v>2510</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>2422</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="113" t="s">
-        <v>2423</v>
+      <c r="B25" s="128" t="s">
+        <v>2512</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>2424</v>
+        <v>2513</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>2425</v>
+        <v>2514</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>2426</v>
+        <v>2515</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>2427</v>
+        <v>2516</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>2428</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="113" t="s">
-        <v>2429</v>
+      <c r="B26" s="128" t="s">
+        <v>2518</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>2430</v>
+        <v>2519</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>2431</v>
+        <v>2520</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>2432</v>
+        <v>2521</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>2433</v>
+        <v>2522</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>2434</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B27" s="113" t="s">
-        <v>2435</v>
+      <c r="B27" s="128" t="s">
+        <v>2524</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>2436</v>
+        <v>2525</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>2437</v>
+        <v>2526</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>2438</v>
+        <v>2527</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>2439</v>
+        <v>2528</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>2440</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="113" t="s">
-        <v>2441</v>
+      <c r="B28" s="128" t="s">
+        <v>2530</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>2442</v>
+        <v>2531</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>2443</v>
+        <v>2532</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>2444</v>
+        <v>2533</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>2445</v>
+        <v>2534</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>2446</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B29" s="113" t="s">
-        <v>2447</v>
+      <c r="B29" s="128" t="s">
+        <v>2536</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>2448</v>
+        <v>2537</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>2449</v>
+        <v>2538</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>2450</v>
+        <v>2539</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>2451</v>
+        <v>2540</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>2452</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B30" s="113" t="s">
-        <v>2453</v>
+      <c r="B30" s="128" t="s">
+        <v>2542</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>2454</v>
+        <v>2543</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>2455</v>
+        <v>2544</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>2456</v>
+        <v>2545</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>2457</v>
+        <v>2546</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>2458</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B31" s="113" t="s">
-        <v>2459</v>
+      <c r="B31" s="128" t="s">
+        <v>2548</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>2460</v>
+        <v>2549</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>2461</v>
+        <v>2550</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>2462</v>
+        <v>2551</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>2463</v>
+        <v>2552</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>2464</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B32" s="113" t="s">
-        <v>2003</v>
+      <c r="B32" s="128" t="s">
+        <v>2093</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>2465</v>
+        <v>2554</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>2466</v>
+        <v>2555</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>2004</v>
+        <v>2094</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>2467</v>
+        <v>2556</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>2006</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B33" s="113" t="s">
-        <v>2014</v>
+      <c r="B33" s="128" t="s">
+        <v>2104</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>2468</v>
+        <v>2557</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>2469</v>
+        <v>2558</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>2470</v>
+        <v>2559</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>2471</v>
+        <v>2560</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>2472</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>2473</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="79" t="s">
-        <v>2474</v>
+        <v>2563</v>
       </c>
       <c r="B36" s="79"/>
       <c r="C36" s="79"/>
@@ -35950,467 +37208,467 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>2475</v>
+        <v>2564</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>2476</v>
+        <v>2565</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>2477</v>
+        <v>2566</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2385</v>
+        <v>2474</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>2014</v>
+        <v>2104</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>2478</v>
+        <v>1969</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>2479</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="34" t="s">
-        <v>2480</v>
+        <v>2568</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>2481</v>
+        <v>2569</v>
       </c>
       <c r="C38" s="72" t="s">
-        <v>2482</v>
+        <v>2570</v>
       </c>
       <c r="D38" s="72" t="s">
-        <v>2483</v>
+        <v>2571</v>
       </c>
       <c r="E38" s="72" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F38" s="115" t="s">
-        <v>2485</v>
+        <v>2572</v>
+      </c>
+      <c r="F38" s="99" t="s">
+        <v>2573</v>
       </c>
       <c r="G38" s="72" t="s">
-        <v>2486</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="75" t="s">
-        <v>2487</v>
+        <v>2575</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>2488</v>
+        <v>2576</v>
       </c>
       <c r="C39" s="76" t="s">
-        <v>2489</v>
+        <v>2577</v>
       </c>
       <c r="D39" s="76" t="s">
-        <v>2490</v>
+        <v>2578</v>
       </c>
       <c r="E39" s="76" t="s">
-        <v>2491</v>
-      </c>
-      <c r="F39" s="115" t="s">
-        <v>2492</v>
+        <v>2579</v>
+      </c>
+      <c r="F39" s="99" t="s">
+        <v>2580</v>
       </c>
       <c r="G39" s="76" t="s">
-        <v>2493</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="34" t="s">
-        <v>2494</v>
+        <v>2582</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>2495</v>
+        <v>2583</v>
       </c>
       <c r="C40" s="72" t="s">
-        <v>2496</v>
+        <v>2584</v>
       </c>
       <c r="D40" s="72" t="s">
-        <v>2497</v>
+        <v>2585</v>
       </c>
       <c r="E40" s="72" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F40" s="115" t="s">
-        <v>2499</v>
+        <v>2586</v>
+      </c>
+      <c r="F40" s="99" t="s">
+        <v>2587</v>
       </c>
       <c r="G40" s="72" t="s">
-        <v>2500</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="75" t="s">
-        <v>2501</v>
+        <v>2589</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>2502</v>
+        <v>2590</v>
       </c>
       <c r="C41" s="76" t="s">
-        <v>2503</v>
+        <v>2591</v>
       </c>
       <c r="D41" s="76" t="s">
-        <v>2504</v>
+        <v>2592</v>
       </c>
       <c r="E41" s="76" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F41" s="115" t="s">
-        <v>2506</v>
+        <v>2593</v>
+      </c>
+      <c r="F41" s="99" t="s">
+        <v>2594</v>
       </c>
       <c r="G41" s="76" t="s">
-        <v>2507</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="34" t="s">
-        <v>2508</v>
+        <v>2596</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>2509</v>
+        <v>2597</v>
       </c>
       <c r="C42" s="72" t="s">
-        <v>2510</v>
+        <v>2598</v>
       </c>
       <c r="D42" s="72" t="s">
-        <v>2511</v>
+        <v>2599</v>
       </c>
       <c r="E42" s="72" t="s">
-        <v>2512</v>
-      </c>
-      <c r="F42" s="115" t="s">
-        <v>2513</v>
+        <v>2600</v>
+      </c>
+      <c r="F42" s="99" t="s">
+        <v>2601</v>
       </c>
       <c r="G42" s="72" t="s">
-        <v>2514</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="75" t="s">
-        <v>2515</v>
+        <v>2603</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>2516</v>
+        <v>2604</v>
       </c>
       <c r="C43" s="76" t="s">
-        <v>2517</v>
+        <v>2605</v>
       </c>
       <c r="D43" s="76" t="s">
-        <v>2518</v>
+        <v>2606</v>
       </c>
       <c r="E43" s="76" t="s">
-        <v>2519</v>
-      </c>
-      <c r="F43" s="115" t="s">
-        <v>2520</v>
+        <v>2607</v>
+      </c>
+      <c r="F43" s="99" t="s">
+        <v>2608</v>
       </c>
       <c r="G43" s="76" t="s">
-        <v>2521</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="34" t="s">
-        <v>2522</v>
+        <v>2610</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>2523</v>
+        <v>2611</v>
       </c>
       <c r="C44" s="72" t="s">
-        <v>2524</v>
+        <v>2612</v>
       </c>
       <c r="D44" s="72" t="s">
-        <v>2525</v>
+        <v>2613</v>
       </c>
       <c r="E44" s="72" t="s">
-        <v>2526</v>
-      </c>
-      <c r="F44" s="115" t="s">
-        <v>2527</v>
+        <v>2614</v>
+      </c>
+      <c r="F44" s="99" t="s">
+        <v>2615</v>
       </c>
       <c r="G44" s="72" t="s">
-        <v>2528</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="75" t="s">
-        <v>2529</v>
+        <v>2617</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>2530</v>
+        <v>2618</v>
       </c>
       <c r="C45" s="76" t="s">
-        <v>2531</v>
+        <v>2619</v>
       </c>
       <c r="D45" s="76" t="s">
-        <v>2532</v>
+        <v>2620</v>
       </c>
       <c r="E45" s="76" t="s">
-        <v>2533</v>
-      </c>
-      <c r="F45" s="115" t="s">
-        <v>2534</v>
+        <v>2621</v>
+      </c>
+      <c r="F45" s="99" t="s">
+        <v>2622</v>
       </c>
       <c r="G45" s="76" t="s">
-        <v>2535</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="34" t="s">
-        <v>2536</v>
+        <v>2624</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>2537</v>
+        <v>2625</v>
       </c>
       <c r="C46" s="72" t="s">
-        <v>2538</v>
+        <v>2626</v>
       </c>
       <c r="D46" s="72" t="s">
-        <v>2539</v>
+        <v>2627</v>
       </c>
       <c r="E46" s="72" t="s">
-        <v>2540</v>
-      </c>
-      <c r="F46" s="115" t="s">
-        <v>2541</v>
+        <v>2628</v>
+      </c>
+      <c r="F46" s="99" t="s">
+        <v>2629</v>
       </c>
       <c r="G46" s="72" t="s">
-        <v>2542</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="75" t="s">
-        <v>2543</v>
+        <v>2631</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>2544</v>
+        <v>2632</v>
       </c>
       <c r="C47" s="76" t="s">
-        <v>2545</v>
+        <v>2633</v>
       </c>
       <c r="D47" s="76" t="s">
-        <v>2546</v>
+        <v>2634</v>
       </c>
       <c r="E47" s="76" t="s">
-        <v>2547</v>
-      </c>
-      <c r="F47" s="116" t="s">
-        <v>2548</v>
+        <v>2635</v>
+      </c>
+      <c r="F47" s="101" t="s">
+        <v>2636</v>
       </c>
       <c r="G47" s="76" t="s">
-        <v>2549</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="34" t="s">
-        <v>2550</v>
+        <v>2638</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>2551</v>
+        <v>2639</v>
       </c>
       <c r="C48" s="72" t="s">
-        <v>2552</v>
+        <v>2640</v>
       </c>
       <c r="D48" s="72" t="s">
-        <v>2553</v>
+        <v>2641</v>
       </c>
       <c r="E48" s="72" t="s">
-        <v>2554</v>
-      </c>
-      <c r="F48" s="117" t="s">
-        <v>2555</v>
+        <v>2642</v>
+      </c>
+      <c r="F48" s="100" t="s">
+        <v>2643</v>
       </c>
       <c r="G48" s="72" t="s">
-        <v>2556</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="75" t="s">
-        <v>2557</v>
+        <v>2645</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>2558</v>
+        <v>2646</v>
       </c>
       <c r="C49" s="76" t="s">
-        <v>2559</v>
+        <v>2647</v>
       </c>
       <c r="D49" s="76" t="s">
-        <v>2560</v>
+        <v>2648</v>
       </c>
       <c r="E49" s="76" t="s">
-        <v>2561</v>
-      </c>
-      <c r="F49" s="116" t="s">
-        <v>2562</v>
+        <v>2649</v>
+      </c>
+      <c r="F49" s="101" t="s">
+        <v>2650</v>
       </c>
       <c r="G49" s="76" t="s">
-        <v>2563</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="34" t="s">
-        <v>2564</v>
+        <v>2652</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>2565</v>
+        <v>2653</v>
       </c>
       <c r="C50" s="72" t="s">
-        <v>2566</v>
+        <v>2654</v>
       </c>
       <c r="D50" s="72" t="s">
-        <v>2567</v>
+        <v>2655</v>
       </c>
       <c r="E50" s="72" t="s">
-        <v>2568</v>
-      </c>
-      <c r="F50" s="116" t="s">
-        <v>2569</v>
+        <v>2656</v>
+      </c>
+      <c r="F50" s="101" t="s">
+        <v>2657</v>
       </c>
       <c r="G50" s="72" t="s">
-        <v>2570</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="75" t="s">
-        <v>2571</v>
+        <v>2659</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>2572</v>
+        <v>2660</v>
       </c>
       <c r="C51" s="76" t="s">
-        <v>2573</v>
+        <v>2661</v>
       </c>
       <c r="D51" s="76" t="s">
-        <v>2574</v>
+        <v>2662</v>
       </c>
       <c r="E51" s="76" t="s">
-        <v>2575</v>
-      </c>
-      <c r="F51" s="115" t="s">
-        <v>2576</v>
+        <v>2663</v>
+      </c>
+      <c r="F51" s="99" t="s">
+        <v>2664</v>
       </c>
       <c r="G51" s="76" t="s">
-        <v>2577</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="34" t="s">
-        <v>2578</v>
+        <v>2666</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>2579</v>
+        <v>2667</v>
       </c>
       <c r="C52" s="72" t="s">
-        <v>2580</v>
+        <v>2668</v>
       </c>
       <c r="D52" s="72" t="s">
-        <v>2581</v>
+        <v>2669</v>
       </c>
       <c r="E52" s="72" t="s">
-        <v>2582</v>
-      </c>
-      <c r="F52" s="117" t="s">
-        <v>2583</v>
+        <v>2670</v>
+      </c>
+      <c r="F52" s="100" t="s">
+        <v>2671</v>
       </c>
       <c r="G52" s="72" t="s">
-        <v>2584</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="75" t="s">
-        <v>2585</v>
+        <v>2673</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>2586</v>
+        <v>2674</v>
       </c>
       <c r="C53" s="76" t="s">
-        <v>2587</v>
+        <v>2675</v>
       </c>
       <c r="D53" s="76" t="s">
-        <v>2588</v>
+        <v>2676</v>
       </c>
       <c r="E53" s="76" t="s">
-        <v>2589</v>
-      </c>
-      <c r="F53" s="117" t="s">
-        <v>2590</v>
+        <v>2677</v>
+      </c>
+      <c r="F53" s="100" t="s">
+        <v>2678</v>
       </c>
       <c r="G53" s="76" t="s">
-        <v>2591</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="34" t="s">
-        <v>2592</v>
+        <v>2680</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>2593</v>
+        <v>2681</v>
       </c>
       <c r="C54" s="72" t="s">
-        <v>2594</v>
+        <v>2682</v>
       </c>
       <c r="D54" s="72" t="s">
-        <v>2595</v>
+        <v>2683</v>
       </c>
       <c r="E54" s="72" t="s">
-        <v>2596</v>
-      </c>
-      <c r="F54" s="117" t="s">
-        <v>2597</v>
+        <v>2684</v>
+      </c>
+      <c r="F54" s="100" t="s">
+        <v>2685</v>
       </c>
       <c r="G54" s="72" t="s">
-        <v>2598</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="75" t="s">
-        <v>2599</v>
+        <v>2687</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>2600</v>
+        <v>2688</v>
       </c>
       <c r="C55" s="76" t="s">
-        <v>2601</v>
+        <v>2689</v>
       </c>
       <c r="D55" s="76" t="s">
-        <v>2602</v>
+        <v>2690</v>
       </c>
       <c r="E55" s="76" t="s">
-        <v>2596</v>
-      </c>
-      <c r="F55" s="116" t="s">
-        <v>2603</v>
+        <v>2684</v>
+      </c>
+      <c r="F55" s="101" t="s">
+        <v>2691</v>
       </c>
       <c r="G55" s="76" t="s">
-        <v>2604</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="34" t="s">
-        <v>2605</v>
+        <v>2693</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>2606</v>
+        <v>2694</v>
       </c>
       <c r="C56" s="72" t="s">
-        <v>2607</v>
+        <v>2695</v>
       </c>
       <c r="D56" s="72" t="s">
-        <v>2608</v>
+        <v>2696</v>
       </c>
       <c r="E56" s="72" t="s">
-        <v>2568</v>
-      </c>
-      <c r="F56" s="117" t="s">
-        <v>2597</v>
+        <v>2656</v>
+      </c>
+      <c r="F56" s="100" t="s">
+        <v>2685</v>
       </c>
       <c r="G56" s="72" t="s">
-        <v>2609</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="79" t="s">
-        <v>2610</v>
+        <v>2698</v>
       </c>
       <c r="B57" s="79"/>
       <c r="C57" s="79"/>
@@ -36421,162 +37679,162 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>2611</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="118" t="s">
-        <v>2612</v>
-      </c>
-      <c r="B60" s="118"/>
-      <c r="C60" s="118"/>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
+      <c r="A60" s="130" t="s">
+        <v>2700</v>
+      </c>
+      <c r="B60" s="130"/>
+      <c r="C60" s="130"/>
+      <c r="D60" s="130"/>
+      <c r="E60" s="130"/>
+      <c r="F60" s="130"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>2475</v>
+        <v>2564</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>2613</v>
+        <v>2701</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>2614</v>
+        <v>2702</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>2478</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="113" t="s">
-        <v>2615</v>
+      <c r="A62" s="128" t="s">
+        <v>2703</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>2616</v>
+        <v>2704</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>2617</v>
+        <v>2705</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>2618</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="113" t="s">
-        <v>2619</v>
+      <c r="A63" s="128" t="s">
+        <v>2707</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>2620</v>
+        <v>2708</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>2621</v>
+        <v>2709</v>
       </c>
       <c r="D63" s="36" t="s">
-        <v>2618</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="113" t="s">
+      <c r="A64" s="128" t="s">
         <v>727</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>2622</v>
+        <v>2710</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>2623</v>
+        <v>2711</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>2624</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="113" t="s">
-        <v>2625</v>
+      <c r="A65" s="128" t="s">
+        <v>2713</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>2626</v>
+        <v>2714</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>2627</v>
+        <v>2715</v>
       </c>
       <c r="D65" s="36" t="s">
-        <v>2628</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="113" t="s">
-        <v>2629</v>
+      <c r="A66" s="128" t="s">
+        <v>2717</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>2622</v>
+        <v>2710</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>2630</v>
+        <v>2718</v>
       </c>
       <c r="D66" s="43" t="s">
-        <v>2597</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="113" t="s">
-        <v>2631</v>
+      <c r="A67" s="128" t="s">
+        <v>2719</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>2622</v>
+        <v>2710</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>2632</v>
+        <v>2720</v>
       </c>
       <c r="D67" s="43" t="s">
-        <v>2597</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="113" t="s">
-        <v>2633</v>
+      <c r="A68" s="128" t="s">
+        <v>2721</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>2634</v>
+        <v>2722</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>2635</v>
+        <v>2723</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>2636</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="113" t="s">
-        <v>2637</v>
+      <c r="A69" s="128" t="s">
+        <v>2725</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>2638</v>
+        <v>2726</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>2639</v>
+        <v>2727</v>
       </c>
       <c r="D69" s="36" t="s">
-        <v>2640</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="113" t="s">
-        <v>2641</v>
+      <c r="A70" s="128" t="s">
+        <v>2729</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>2642</v>
+        <v>2730</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>2643</v>
-      </c>
-      <c r="D70" s="119" t="s">
-        <v>2644</v>
+        <v>2731</v>
+      </c>
+      <c r="D70" s="131" t="s">
+        <v>2732</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>2645</v>
+        <v>2733</v>
       </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -36586,7 +37844,7 @@
     </row>
     <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>2646</v>
+        <v>2734</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -36596,7 +37854,7 @@
     </row>
     <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>2647</v>
+        <v>2735</v>
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -36606,7 +37864,7 @@
     </row>
     <row r="75" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>2648</v>
+        <v>2736</v>
       </c>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -36616,7 +37874,7 @@
     </row>
     <row r="76" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>2649</v>
+        <v>2737</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -36626,7 +37884,7 @@
     </row>
     <row r="77" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>2650</v>
+        <v>2738</v>
       </c>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -36636,105 +37894,105 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>2651</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>2652</v>
+        <v>2740</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>2653</v>
+        <v>2741</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>2654</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="113" t="s">
-        <v>2655</v>
+      <c r="A81" s="128" t="s">
+        <v>2743</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>2656</v>
+        <v>2744</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>2657</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="113" t="s">
-        <v>2658</v>
+      <c r="A82" s="128" t="s">
+        <v>2746</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>2659</v>
+        <v>2747</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>2660</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="113" t="s">
-        <v>2661</v>
+      <c r="A83" s="128" t="s">
+        <v>2749</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>2662</v>
+        <v>2750</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>2663</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="113" t="s">
-        <v>2664</v>
+      <c r="A84" s="128" t="s">
+        <v>2752</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>2665</v>
+        <v>2753</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>2666</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="113" t="s">
-        <v>2667</v>
+      <c r="A85" s="128" t="s">
+        <v>2755</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>2668</v>
+        <v>2756</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>2669</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="113" t="s">
-        <v>2670</v>
+      <c r="A86" s="128" t="s">
+        <v>2758</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>2671</v>
+        <v>2759</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>2672</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="113" t="s">
-        <v>2673</v>
+      <c r="A87" s="128" t="s">
+        <v>2761</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>2674</v>
+        <v>2762</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>2675</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>2676</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>2677</v>
+        <v>2765</v>
       </c>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -36744,7 +38002,7 @@
     </row>
     <row r="91" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>2678</v>
+        <v>2766</v>
       </c>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -36754,7 +38012,7 @@
     </row>
     <row r="92" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="14" t="s">
-        <v>2679</v>
+        <v>2767</v>
       </c>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -36764,7 +38022,7 @@
     </row>
     <row r="93" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>2680</v>
+        <v>2768</v>
       </c>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -36774,7 +38032,7 @@
     </row>
     <row r="94" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>2681</v>
+        <v>2769</v>
       </c>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -36784,7 +38042,7 @@
     </row>
     <row r="95" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="14" t="s">
-        <v>2682</v>
+        <v>2770</v>
       </c>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -36820,246 +38078,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="70" t="s">
-        <v>2683</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2684</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2685</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2687</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>2688</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>2689</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Laura Lopez")</f>
-        <v>215</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>2690</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>1584</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>1585</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>1586</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>2691</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Ken Witzgall")</f>
-        <v>2</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>2692</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>1618</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>1619</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>1620</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>2693</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Scott Wood")</f>
-        <v>2</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>2694</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>1634</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>1620</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>2695</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <f aca="false">COUNTIF('Consolidated Data'!$B$2:$B$231,"Jennifer Saxman")</f>
-        <v>11</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>2696</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>2697</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>2698</v>
-      </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-    </row>
-    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>2699</v>
-      </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>2700</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-    </row>
-    <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>2701</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>2702</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>2703</v>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>2704</v>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-    </row>
-    <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>2705</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-    </row>
-    <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>2706</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>